--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -1265,13 +1265,13 @@
         <v>152.89</v>
       </c>
       <c r="H5" s="2">
-        <v>165.35</v>
+        <v>165.05</v>
       </c>
       <c r="I5" s="2">
-        <v>179.68</v>
+        <v>179.07</v>
       </c>
       <c r="J5" s="2">
-        <v>196.25</v>
+        <v>195.31</v>
       </c>
     </row>
     <row r="6">
@@ -1333,13 +1333,13 @@
         <v>75.84</v>
       </c>
       <c r="H7" s="4">
-        <v>82.72999999999999</v>
+        <v>83.02999999999997</v>
       </c>
       <c r="I7" s="4">
-        <v>90.67000000000002</v>
+        <v>91.28000000000003</v>
       </c>
       <c r="J7" s="4">
-        <v>99.84000000000003</v>
+        <v>100.78000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -1367,13 +1367,13 @@
         <v>33.156997333100165</v>
       </c>
       <c r="H8" s="2">
-        <v>33.34811351177039</v>
+        <v>33.46904224443727</v>
       </c>
       <c r="I8" s="2">
-        <v>33.538006288145</v>
+        <v>33.76363972628075</v>
       </c>
       <c r="J8" s="2">
-        <v>33.719477185990755</v>
+        <v>34.036948225201805</v>
       </c>
     </row>
     <row r="9">
@@ -1392,19 +1392,19 @@
         <v>36.5</v>
       </c>
       <c r="E9" s="2">
-        <v>37.58</v>
+        <v>37.71</v>
       </c>
       <c r="F9" s="2">
-        <v>38.69</v>
+        <v>38.96</v>
       </c>
       <c r="G9" s="2">
-        <v>55.43000000000001</v>
+        <v>55.85</v>
       </c>
       <c r="H9" s="2">
-        <v>58.19</v>
+        <v>58.489999999999995</v>
       </c>
       <c r="I9" s="2">
-        <v>61.22</v>
+        <v>61.37</v>
       </c>
       <c r="J9" s="2">
         <v>64.53999999999999</v>
@@ -1698,22 +1698,22 @@
         <v>11.5</v>
       </c>
       <c r="E18" s="4">
-        <v>12.600000000000009</v>
+        <v>12.470000000000006</v>
       </c>
       <c r="F18" s="4">
-        <v>13.770000000000007</v>
+        <v>13.500000000000007</v>
       </c>
       <c r="G18" s="4">
-        <v>20.41</v>
+        <v>19.990000000000002</v>
       </c>
       <c r="H18" s="4">
-        <v>24.539999999999992</v>
+        <v>24.539999999999974</v>
       </c>
       <c r="I18" s="4">
-        <v>29.45000000000001</v>
+        <v>29.910000000000025</v>
       </c>
       <c r="J18" s="4">
-        <v>35.30000000000004</v>
+        <v>36.24000000000004</v>
       </c>
     </row>
     <row r="19">
@@ -1732,22 +1732,22 @@
         <v>7.666666666666666</v>
       </c>
       <c r="E19" s="2">
-        <v>8.076923076923084</v>
+        <v>7.993589743589748</v>
       </c>
       <c r="F19" s="2">
-        <v>8.487426035502962</v>
+        <v>8.321005917159766</v>
       </c>
       <c r="G19" s="2">
-        <v>8.923184540724872</v>
+        <v>8.739561928911819</v>
       </c>
       <c r="H19" s="2">
-        <v>9.891970332150917</v>
+        <v>9.89197033215091</v>
       </c>
       <c r="I19" s="2">
-        <v>10.893286480488259</v>
+        <v>11.063436286295552</v>
       </c>
       <c r="J19" s="2">
-        <v>11.922050727819258</v>
+        <v>12.239521767030306</v>
       </c>
     </row>
     <row r="20">
@@ -1766,22 +1766,22 @@
         <v>11.5</v>
       </c>
       <c r="E20" s="4">
-        <v>12.600000000000009</v>
+        <v>12.470000000000006</v>
       </c>
       <c r="F20" s="4">
-        <v>13.770000000000007</v>
+        <v>13.500000000000007</v>
       </c>
       <c r="G20" s="4">
-        <v>20.41</v>
+        <v>19.990000000000002</v>
       </c>
       <c r="H20" s="4">
-        <v>24.539999999999992</v>
+        <v>24.539999999999974</v>
       </c>
       <c r="I20" s="4">
-        <v>29.45000000000001</v>
+        <v>29.910000000000025</v>
       </c>
       <c r="J20" s="4">
-        <v>35.30000000000004</v>
+        <v>36.24000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.65 % / 補助 65 % / 他 67.34 %</t>
+          <t xml:space="preserve">全社 66.53 % / 補助 65 % / 他 67.16 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.46 % / 補助 65 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 66.24 % / 補助 65 % / 他 66.83 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.28 % / 補助 65 % / 他 67 %</t>
+          <t xml:space="preserve">全社 65.96 % / 補助 65 % / 他 66.5 %</t>
         </is>
       </c>
     </row>
@@ -3111,17 +3111,17 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.35 % / 補助 35 % / 他 32.66 %</t>
+          <t xml:space="preserve">全社 33.47 % / 補助 35 % / 他 32.84 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.54 % / 補助 35 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 33.76 % / 補助 35 % / 他 33.17 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.72 % / 補助 35 % / 他 33 %</t>
+          <t xml:space="preserve">全社 34.04 % / 補助 35 % / 他 33.5 %</t>
         </is>
       </c>
     </row>
@@ -3158,27 +3158,27 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.09 % / 補助 — / 他 24.09 %</t>
+          <t xml:space="preserve">全社 24.17 % / 補助 — / 他 24.17 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.85 % / 補助 — / 他 23.85 %</t>
+          <t xml:space="preserve">全社 24.01 % / 補助 — / 他 24.01 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.23 % / 補助 26 % / 他 23.61 %</t>
+          <t xml:space="preserve">全社 24.42 % / 補助 26 % / 他 23.85 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.46 % / 補助 23.66 % / 他 23.37 %</t>
+          <t xml:space="preserve">全社 23.58 % / 補助 23.66 % / 他 23.54 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.64 % / 補助 21.61 % / 他 23.15 %</t>
+          <t xml:space="preserve">全社 22.7 % / 補助 21.61 % / 他 23.23 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.08 % / 補助 — / 他 8.08 %</t>
+          <t xml:space="preserve">全社 7.99 % / 補助 — / 他 7.99 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.49 % / 補助 — / 他 8.49 %</t>
+          <t xml:space="preserve">全社 8.32 % / 補助 — / 他 8.32 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.92 % / 補助 9 % / 他 8.9 %</t>
+          <t xml:space="preserve">全社 8.74 % / 補助 9 % / 他 8.65 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.89 % / 補助 13.4 % / 他 9.69 %</t>
+          <t xml:space="preserve">全社 11.06 % / 補助 13.4 % / 他 9.94 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.92 % / 補助 15.2 % / 他 10.08 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 15.2 % / 他 10.58 %</t>
         </is>
       </c>
     </row>
@@ -3282,17 +3282,17 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.32 % / 補助 — / 他 10.32 %</t>
+          <t xml:space="preserve">全社 10.24 % / 補助 — / 他 10.24 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.64 % / 補助 — / 他 10.64 %</t>
+          <t xml:space="preserve">全社 10.48 % / 補助 — / 他 10.48 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.42 % / 補助 16.5 % / 他 10.97 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 16.5 % / 他 10.72 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.85 % / 補助 18.52 % / 他 11.61 %</t>
+          <t xml:space="preserve">全社 14.02 % / 補助 18.52 % / 他 11.86 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.62 % / 補助 19.44 % / 他 11.93 %</t>
+          <t xml:space="preserve">全社 14.94 % / 補助 19.44 % / 他 12.42 %</t>
         </is>
       </c>
     </row>
@@ -3344,27 +3344,27 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.75 % / 補助 — / 他 11.75 %</t>
+          <t xml:space="preserve">全社 11.83 % / 補助 — / 他 11.83 %</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.5 % / 補助 — / 他 11.5 %</t>
+          <t xml:space="preserve">全社 11.67 % / 補助 — / 他 11.67 %</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.92 % / 補助 10 % / 他 11.25 %</t>
+          <t xml:space="preserve">全社 11.1 % / 補助 10 % / 他 11.5 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.61 % / 補助 9.67 % / 他 11 %</t>
+          <t xml:space="preserve">全社 10.73 % / 補助 9.67 % / 他 11.17 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.29 % / 補助 9.33 % / 他 10.75 %</t>
+          <t xml:space="preserve">全社 10.35 % / 補助 9.33 % / 他 10.83 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
@@ -3840,17 +3840,17 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.45 % / 補助 — / 他 49.45 %</t>
+          <t xml:space="preserve">全社 49.65 % / 補助 — / 他 49.65 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.91 % / 補助 — / 他 48.91 %</t>
+          <t xml:space="preserve">全社 49.3 % / 補助 — / 他 49.3 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 44.14 % / 補助 34 % / 他 48.38 %</t>
+          <t xml:space="preserve">全社 44.51 % / 補助 34 % / 他 48.96 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.41 % / 補助 27.85 % / 他 47.44 %</t>
+          <t xml:space="preserve">全社 40.12 % / 補助 27.85 % / 他 46.91 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.44 % / 補助 25.23 % / 他 46.99 %</t>
+          <t xml:space="preserve">全社 37.93 % / 補助 25.23 % / 他 45.98 %</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.059 億円/人 / 補助 — / 他 0.059 億円/人</t>
+          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / 他 0.058 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.072 億円/人 / 補助 0.112 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.112 億円/人 / 他 0.062 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.1 億円/人 / 補助 0.227 億円/人 / 他 0.073 億円/人</t>
+          <t xml:space="preserve">全社 0.102 億円/人 / 補助 0.227 億円/人 / 他 0.075 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.118 億円/人 / 補助 0.299 億円/人 / 他 0.078 億円/人</t>
+          <t xml:space="preserve">全社 0.122 億円/人 / 補助 0.299 億円/人 / 他 0.082 億円/人</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.141 億円/人 / 補助 — / 他 0.141 億円/人</t>
+          <t xml:space="preserve">全社 0.14 億円/人 / 補助 — / 他 0.14 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.174 億円/人 / 補助 0.3 億円/人 / 他 0.148 億円/人</t>
+          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.3 億円/人 / 他 0.146 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.209 億円/人 / 補助 0.418 億円/人 / 他 0.163 億円/人</t>
+          <t xml:space="preserve">全社 0.211 億円/人 / 補助 0.418 億円/人 / 他 0.165 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.231 億円/人 / 補助 0.493 億円/人 / 他 0.171 億円/人</t>
+          <t xml:space="preserve">全社 0.234 億円/人 / 補助 0.493 億円/人 / 他 0.175 億円/人</t>
         </is>
       </c>
     </row>
@@ -4460,17 +4460,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.93 倍</t>
+          <t xml:space="preserve">全社 0.94 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.87 倍</t>
+          <t xml:space="preserve">全社 0.88 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 倍</t>
+          <t xml:space="preserve">全社 0.54 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -4522,17 +4522,17 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.6 倍 / 補助 — / 他 4.6 倍</t>
+          <t xml:space="preserve">全社 4.56 倍 / 補助 — / 他 4.56 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.93 倍 / 補助 — / 他 4.93 倍</t>
+          <t xml:space="preserve">全社 4.86 倍 / 補助 — / 他 4.86 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.55 倍 / 補助 2.2 倍 / 他 5.29 倍</t>
+          <t xml:space="preserve">全社 3.5 倍 / 補助 2.2 倍 / 他 5.17 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.68 倍 / 補助 3.62 倍 / 他 6.05 倍</t>
+          <t xml:space="preserve">全社 4.74 倍 / 補助 3.62 倍 / 他 6.18 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.41 倍 / 補助 4.59 倍 / 他 6.47 倍</t>
+          <t xml:space="preserve">全社 5.53 倍 / 補助 4.59 倍 / 他 6.74 倍</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.34 pt</t>
+          <t xml:space="preserve">差 -2.16 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.17 pt</t>
+          <t xml:space="preserve">差 -1.84 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2 pt</t>
+          <t xml:space="preserve">差 -1.5 pt</t>
         </is>
       </c>
     </row>
@@ -4894,17 +4894,17 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.08 pt</t>
+          <t xml:space="preserve">差 -7.99 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.49 pt</t>
+          <t xml:space="preserve">差 -8.32 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.1 pt</t>
+          <t xml:space="preserve">差 0.35 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.71 pt</t>
+          <t xml:space="preserve">差 3.46 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.12 pt</t>
+          <t xml:space="preserve">差 4.62 pt</t>
         </is>
       </c>
     </row>
@@ -5090,22 +5090,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 81.33 %</t>
+          <t xml:space="preserve">寄与率 83.2 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 68.52 %</t>
+          <t xml:space="preserve">寄与率 62.2 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 72.1 %</t>
+          <t xml:space="preserve">寄与率 65.92 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 75.04 %</t>
+          <t xml:space="preserve">寄与率 69.35 %</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5283,110 +5283,110 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">その他事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D10" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率</t>
+          <t xml:space="preserve">その他事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C11" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="D11" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント</t>
+          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="D13" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">その他事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>7.000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="2">
-        <v>4.5</v>
+        <v>-15</v>
       </c>
       <c r="D14" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D15" s="2">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">その他事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="D16" s="2">
         <v>20</v>
@@ -5395,30 +5395,30 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">その他事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="D18" s="2">
         <v>25</v>
@@ -5427,104 +5427,184 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>10.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D19" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
       <c r="D20" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>10</v>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C21" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>45</v>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>-5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">申請補助金額</t>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>10</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B27" s="2">
+        <v>45</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申請補助金額</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルベンチマーク</t>
         </is>
       </c>
-      <c r="B24" s="2">
+      <c r="B29" s="2">
         <v>23</v>
       </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
         <v>100</v>
       </c>
     </row>
@@ -5550,7 +5630,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNCwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDksIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoyOC4xLCJtYXgiOjUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6My45LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MC4xLCJtYXgiOjAuMiwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyNjpwcm9qZWN0OjctMSI6MCwiMjAyNjpwcm9qZWN0OjctNCI6MCwiMjAyNjpwcm9qZWN0OjctNiI6MCwiMjAyNjpwcm9qZWN0OjctOCI6MCwiMjAyNjpwcm9qZWN0OjctOSI6MCwiMjAyNjpwcm9qZWN0OjctMTAiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OjctMTAiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo1LjQsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC4yMywiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjQ5LjkyLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMS43NywiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUxLjkyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi4xNiwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjUzLjk5LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciJ9</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA0LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxLCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwNSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6Wy0wLjE1LDAuMjVdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjI4LjEsIm1heCI6NTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjozLjksIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLjEsIm1heCI6MC4yLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>8.985035501746985</v>
+        <v>9.659350315034555</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -217,7 +217,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>67.36000000000004</v>
+        <v>72.89000000000001</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -269,7 +269,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>35.89786889121551</v>
+        <v>35.239705589815</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -1195,13 +1195,13 @@
         <v>228.73</v>
       </c>
       <c r="H3" s="4">
-        <v>248.07999999999998</v>
+        <v>249.76999999999998</v>
       </c>
       <c r="I3" s="4">
-        <v>270.35</v>
+        <v>273.87</v>
       </c>
       <c r="J3" s="4">
-        <v>296.09000000000003</v>
+        <v>301.62</v>
       </c>
     </row>
     <row r="4">
@@ -1231,13 +1231,13 @@
         <v>40.98249506903351</v>
       </c>
       <c r="H4" s="2">
-        <v>8.459756044244294</v>
+        <v>9.198618458444452</v>
       </c>
       <c r="I4" s="2">
-        <v>8.976942921638198</v>
+        <v>9.648876966809471</v>
       </c>
       <c r="J4" s="2">
-        <v>9.520991307564275</v>
+        <v>10.132544637966912</v>
       </c>
     </row>
     <row r="5">
@@ -1265,13 +1265,13 @@
         <v>152.89</v>
       </c>
       <c r="H5" s="2">
-        <v>165.05</v>
+        <v>166.19</v>
       </c>
       <c r="I5" s="2">
-        <v>179.07</v>
+        <v>181.43</v>
       </c>
       <c r="J5" s="2">
-        <v>195.31</v>
+        <v>198.98</v>
       </c>
     </row>
     <row r="6">
@@ -1333,13 +1333,13 @@
         <v>75.84</v>
       </c>
       <c r="H7" s="4">
-        <v>83.02999999999997</v>
+        <v>83.57999999999998</v>
       </c>
       <c r="I7" s="4">
-        <v>91.28000000000003</v>
+        <v>92.44</v>
       </c>
       <c r="J7" s="4">
-        <v>100.78000000000003</v>
+        <v>102.64000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1367,13 +1367,13 @@
         <v>33.156997333100165</v>
       </c>
       <c r="H8" s="2">
-        <v>33.46904224443727</v>
+        <v>33.462785762901866</v>
       </c>
       <c r="I8" s="2">
-        <v>33.76363972628075</v>
+        <v>33.753240588600434</v>
       </c>
       <c r="J8" s="2">
-        <v>34.036948225201805</v>
+        <v>34.02957363570056</v>
       </c>
     </row>
     <row r="9">
@@ -1401,13 +1401,13 @@
         <v>55.85</v>
       </c>
       <c r="H9" s="2">
-        <v>58.489999999999995</v>
+        <v>58.559999999999995</v>
       </c>
       <c r="I9" s="2">
-        <v>61.37</v>
+        <v>61.49000000000001</v>
       </c>
       <c r="J9" s="2">
-        <v>64.53999999999999</v>
+        <v>64.71000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1435,13 +1435,13 @@
         <v>1.4200000000000002</v>
       </c>
       <c r="H10" s="2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I10" s="2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="J10" s="2">
-        <v>1.63</v>
+        <v>1.6400000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1469,13 +1469,13 @@
         <v>1.4200000000000002</v>
       </c>
       <c r="H11" s="2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="J11" s="2">
-        <v>1.63</v>
+        <v>1.6400000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1537,13 +1537,13 @@
         <v>21.03</v>
       </c>
       <c r="H13" s="2">
-        <v>22.38</v>
+        <v>22.55</v>
       </c>
       <c r="I13" s="2">
-        <v>23.84</v>
+        <v>24.19</v>
       </c>
       <c r="J13" s="2">
-        <v>25.41</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="14">
@@ -1571,13 +1571,13 @@
         <v>21.03</v>
       </c>
       <c r="H14" s="2">
-        <v>22.38</v>
+        <v>22.55</v>
       </c>
       <c r="I14" s="2">
-        <v>23.84</v>
+        <v>24.19</v>
       </c>
       <c r="J14" s="2">
-        <v>25.41</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="15">
@@ -1707,13 +1707,13 @@
         <v>19.990000000000002</v>
       </c>
       <c r="H18" s="4">
-        <v>24.539999999999974</v>
+        <v>25.01999999999999</v>
       </c>
       <c r="I18" s="4">
-        <v>29.910000000000025</v>
+        <v>30.950000000000006</v>
       </c>
       <c r="J18" s="4">
-        <v>36.24000000000004</v>
+        <v>37.930000000000014</v>
       </c>
     </row>
     <row r="19">
@@ -1741,13 +1741,13 @@
         <v>8.739561928911819</v>
       </c>
       <c r="H19" s="2">
-        <v>9.89197033215091</v>
+        <v>10.017215838571483</v>
       </c>
       <c r="I19" s="2">
-        <v>11.063436286295552</v>
+        <v>11.300982217840582</v>
       </c>
       <c r="J19" s="2">
-        <v>12.239521767030306</v>
+        <v>12.575426032756454</v>
       </c>
     </row>
     <row r="20">
@@ -1775,13 +1775,13 @@
         <v>19.990000000000002</v>
       </c>
       <c r="H20" s="4">
-        <v>24.539999999999974</v>
+        <v>25.01999999999999</v>
       </c>
       <c r="I20" s="4">
-        <v>29.910000000000025</v>
+        <v>30.950000000000006</v>
       </c>
       <c r="J20" s="4">
-        <v>36.24000000000004</v>
+        <v>37.930000000000014</v>
       </c>
     </row>
   </sheetData>
@@ -2023,13 +2023,13 @@
         <v>26.231801687579242</v>
       </c>
       <c r="H5" s="2">
-        <v>29.264753305385362</v>
+        <v>29.066741402089924</v>
       </c>
       <c r="I5" s="2">
-        <v>32.49491400036988</v>
+        <v>32.07726293496914</v>
       </c>
       <c r="J5" s="2">
-        <v>35.89786889121551</v>
+        <v>35.239705589815</v>
       </c>
     </row>
     <row r="6">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.46 % / 補助 21 % / 他 4 %</t>
+          <t xml:space="preserve">全社 9.2 % / 補助 21 % / 他 5 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.98 % / 補助 21.01 % / 他 4 %</t>
+          <t xml:space="preserve">全社 9.65 % / 補助 21.01 % / 他 5 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.52 % / 補助 20.99 % / 他 4 %</t>
+          <t xml:space="preserve">全社 10.13 % / 補助 20.99 % / 他 5 %</t>
         </is>
       </c>
     </row>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.53 % / 補助 65 % / 他 67.16 %</t>
+          <t xml:space="preserve">全社 66.54 % / 補助 65 % / 他 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.24 % / 補助 65 % / 他 66.83 %</t>
+          <t xml:space="preserve">全社 66.25 % / 補助 65 % / 他 66.84 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.96 % / 補助 65 % / 他 66.5 %</t>
+          <t xml:space="preserve">全社 65.97 % / 補助 65 % / 他 66.5 %</t>
         </is>
       </c>
     </row>
@@ -3111,17 +3111,17 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.47 % / 補助 35 % / 他 32.84 %</t>
+          <t xml:space="preserve">全社 33.46 % / 補助 35 % / 他 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.76 % / 補助 35 % / 他 33.17 %</t>
+          <t xml:space="preserve">全社 33.75 % / 補助 35 % / 他 33.16 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.04 % / 補助 35 % / 他 33.5 %</t>
+          <t xml:space="preserve">全社 34.03 % / 補助 35 % / 他 33.5 %</t>
         </is>
       </c>
     </row>
@@ -3173,17 +3173,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.58 % / 補助 23.66 % / 他 23.54 %</t>
+          <t xml:space="preserve">全社 23.45 % / 補助 23.66 % / 他 23.36 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.7 % / 補助 21.61 % / 他 23.23 %</t>
+          <t xml:space="preserve">全社 22.45 % / 補助 21.61 % / 他 22.85 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.8 % / 補助 19.79 % / 他 22.92 %</t>
+          <t xml:space="preserve">全社 21.45 % / 補助 19.79 % / 他 22.36 %</t>
         </is>
       </c>
     </row>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.89 % / 補助 11.34 % / 他 9.29 %</t>
+          <t xml:space="preserve">全社 10.02 % / 補助 11.34 % / 他 9.48 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.06 % / 補助 13.4 % / 他 9.94 %</t>
+          <t xml:space="preserve">全社 11.3 % / 補助 13.4 % / 他 10.31 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 15.2 % / 他 10.58 %</t>
+          <t xml:space="preserve">全社 12.58 % / 補助 15.2 % / 他 11.15 %</t>
         </is>
       </c>
     </row>
@@ -3297,17 +3297,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.12 % / 補助 17.53 % / 他 11.29 %</t>
+          <t xml:space="preserve">全社 13.22 % / 補助 17.53 % / 他 11.45 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.02 % / 補助 18.52 % / 他 11.86 %</t>
+          <t xml:space="preserve">全社 14.22 % / 補助 18.52 % / 他 12.19 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.94 % / 補助 19.44 % / 他 12.42 %</t>
+          <t xml:space="preserve">全社 15.23 % / 補助 19.44 % / 他 12.94 %</t>
         </is>
       </c>
     </row>
@@ -3359,17 +3359,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.73 % / 補助 9.67 % / 他 11.17 %</t>
+          <t xml:space="preserve">全社 10.61 % / 補助 9.67 % / 他 11 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.35 % / 補助 9.33 % / 他 10.83 %</t>
+          <t xml:space="preserve">全社 10.13 % / 補助 9.33 % / 他 10.5 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.96 % / 補助 9 % / 他 10.5 %</t>
+          <t xml:space="preserve">全社 9.65 % / 補助 9 % / 他 10 %</t>
         </is>
       </c>
     </row>
@@ -3483,17 +3483,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.02 % / 補助 7.36 % / 他 9.71 %</t>
+          <t xml:space="preserve">全社 9.03 % / 補助 7.36 % / 他 9.71 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.82 % / 補助 6.76 % / 他 9.81 %</t>
+          <t xml:space="preserve">全社 8.83 % / 補助 6.76 % / 他 9.81 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.58 % / 補助 6.22 % / 他 9.91 %</t>
+          <t xml:space="preserve">全社 8.61 % / 補助 6.22 % / 他 9.91 %</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.58 % / 補助 0.39 % / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.57 % / 補助 0.39 % / 他 0.66 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.55 % / 補助 0.34 % / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.54 % / 補助 0.34 % / 他 0.66 %</t>
         </is>
       </c>
     </row>
@@ -3607,17 +3607,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.62 % / 補助 7.8 % / 他 10.38 %</t>
+          <t xml:space="preserve">全社 9.63 % / 補助 7.8 % / 他 10.38 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.4 % / 補助 7.15 % / 他 10.48 %</t>
+          <t xml:space="preserve">全社 9.41 % / 補助 7.15 % / 他 10.47 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.13 % / 補助 6.56 % / 他 10.57 %</t>
+          <t xml:space="preserve">全社 9.15 % / 補助 6.56 % / 他 10.57 %</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3669,17 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.077 億円/人 / 補助 0.107 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">全社 0.078 億円/人 / 補助 0.107 億円/人 / 他 0.072 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.081 億円/人 / 補助 0.114 億円/人 / 他 0.074 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.114 億円/人 / 他 0.075 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.085 億円/人 / 補助 0.122 億円/人 / 他 0.077 億円/人</t>
+          <t xml:space="preserve">全社 0.086 億円/人 / 補助 0.122 億円/人 / 他 0.078 億円/人</t>
         </is>
       </c>
     </row>
@@ -3731,17 +3731,17 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.213 億円/人 / 補助 0.16 億円/人 / 他 0.234 億円/人</t>
+          <t xml:space="preserve">全社 0.214 億円/人 / 補助 0.16 億円/人 / 他 0.236 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.223 億円/人 / 補助 0.17 億円/人 / 他 0.244 億円/人</t>
+          <t xml:space="preserve">全社 0.224 億円/人 / 補助 0.17 億円/人 / 他 0.246 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.233 億円/人 / 補助 0.18 億円/人 / 他 0.254 億円/人</t>
+          <t xml:space="preserve">全社 0.234 億円/人 / 補助 0.18 億円/人 / 他 0.256 億円/人</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.84 % / 補助 6.97 % / 他 3.95 %</t>
+          <t xml:space="preserve">全社 5.21 % / 補助 6.97 % / 他 4.47 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.93 % / 補助 6.95 % / 他 4.01 %</t>
+          <t xml:space="preserve">全社 5.24 % / 補助 6.95 % / 他 4.47 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.98 % / 補助 7.01 % / 他 3.99 %</t>
+          <t xml:space="preserve">全社 5.32 % / 補助 7.01 % / 他 4.52 %</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3855,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.32 % / 補助 30.78 % / 他 47.9 %</t>
+          <t xml:space="preserve">全社 42.14 % / 補助 30.78 % / 他 47.54 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.12 % / 補助 27.85 % / 他 46.91 %</t>
+          <t xml:space="preserve">全社 39.81 % / 補助 27.85 % / 他 46.2 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.93 % / 補助 25.23 % / 他 45.98 %</t>
+          <t xml:space="preserve">全社 37.54 % / 補助 25.23 % / 他 44.96 %</t>
         </is>
       </c>
     </row>
@@ -3979,17 +3979,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.858 億円/人 / 補助 1.454 億円/人 / 他 0.733 億円/人</t>
+          <t xml:space="preserve">全社 0.86 億円/人 / 補助 1.454 億円/人 / 他 0.737 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.921 億円/人 / 補助 1.692 億円/人 / 他 0.755 億円/人</t>
+          <t xml:space="preserve">全社 0.925 億円/人 / 補助 1.692 億円/人 / 他 0.762 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.993 億円/人 / 補助 1.969 億円/人 / 他 0.777 億円/人</t>
+          <t xml:space="preserve">全社 0.999 億円/人 / 補助 1.969 億円/人 / 他 0.788 億円/人</t>
         </is>
       </c>
     </row>
@@ -4041,17 +4041,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.085 億円/人 / 補助 0.165 億円/人 / 他 0.068 億円/人</t>
+          <t xml:space="preserve">全社 0.086 億円/人 / 補助 0.165 億円/人 / 他 0.07 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.102 億円/人 / 補助 0.227 億円/人 / 他 0.075 億円/人</t>
+          <t xml:space="preserve">全社 0.105 億円/人 / 補助 0.227 億円/人 / 他 0.079 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.122 億円/人 / 補助 0.299 億円/人 / 他 0.082 億円/人</t>
+          <t xml:space="preserve">全社 0.126 億円/人 / 補助 0.299 億円/人 / 他 0.088 億円/人</t>
         </is>
       </c>
     </row>
@@ -4103,17 +4103,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.19 億円/人 / 補助 0.354 億円/人 / 他 0.156 億円/人</t>
+          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.354 億円/人 / 他 0.158 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.211 億円/人 / 補助 0.418 億円/人 / 他 0.165 億円/人</t>
+          <t xml:space="preserve">全社 0.214 億円/人 / 補助 0.418 億円/人 / 他 0.169 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.234 億円/人 / 補助 0.493 億円/人 / 他 0.175 億円/人</t>
+          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.493 億円/人 / 他 0.182 億円/人</t>
         </is>
       </c>
     </row>
@@ -4165,17 +4165,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.51 % / 補助 4 % / 他 1 %</t>
+          <t xml:space="preserve">全社 1.92 % / 補助 4 % / 他 1.5 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.52 % / 補助 4.01 % / 他 1 %</t>
+          <t xml:space="preserve">全社 1.93 % / 補助 4.01 % / 他 1.5 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.53 % / 補助 3.99 % / 他 1 %</t>
+          <t xml:space="preserve">全社 1.94 % / 補助 3.99 % / 他 1.5 %</t>
         </is>
       </c>
     </row>
@@ -4227,17 +4227,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.95 pt / 補助 17 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 7.28 pt / 補助 17 pt / 他 3.5 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.46 pt / 補助 17 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 7.72 pt / 補助 17 pt / 他 3.49 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.99 pt / 補助 17 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 8.2 pt / 補助 17 pt / 他 3.51 pt</t>
         </is>
       </c>
     </row>
@@ -4351,17 +4351,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.22 % / 補助 6.2 % / 他 1.99 %</t>
+          <t xml:space="preserve">全社 3.2 % / 補助 6.2 % / 他 1.98 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.96 % / 補助 5.12 % / 他 1.92 %</t>
+          <t xml:space="preserve">全社 2.92 % / 補助 5.12 % / 他 1.88 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.7 % / 補助 4.23 % / 他 1.84 %</t>
+          <t xml:space="preserve">全社 2.65 % / 補助 4.23 % / 他 1.79 %</t>
         </is>
       </c>
     </row>
@@ -4537,17 +4537,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.07 倍 / 補助 2.83 倍 / 他 5.66 倍</t>
+          <t xml:space="preserve">全社 4.13 倍 / 補助 2.83 倍 / 他 5.8 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.74 倍 / 補助 3.62 倍 / 他 6.18 倍</t>
+          <t xml:space="preserve">全社 4.87 倍 / 補助 3.62 倍 / 他 6.48 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.53 倍 / 補助 4.59 倍 / 他 6.74 倍</t>
+          <t xml:space="preserve">全社 5.74 倍 / 補助 4.59 倍 / 他 7.22 倍</t>
         </is>
       </c>
     </row>
@@ -4723,17 +4723,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 29.26 %</t>
+          <t xml:space="preserve">構成比 29.07 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 32.49 %</t>
+          <t xml:space="preserve">構成比 32.08 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 35.9 %</t>
+          <t xml:space="preserve">構成比 35.24 %</t>
         </is>
       </c>
     </row>
@@ -4785,17 +4785,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 4 %</t>
+          <t xml:space="preserve">補助 21 % / 他 5 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21.01 % / 他 4 %</t>
+          <t xml:space="preserve">補助 21.01 % / 他 5 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 20.99 % / 他 4 %</t>
+          <t xml:space="preserve">補助 20.99 % / 他 5 %</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.16 pt</t>
+          <t xml:space="preserve">差 -2.17 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
@@ -4909,17 +4909,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.04 pt</t>
+          <t xml:space="preserve">差 1.86 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.46 pt</t>
+          <t xml:space="preserve">差 3.09 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.62 pt</t>
+          <t xml:space="preserve">差 4.06 pt</t>
         </is>
       </c>
     </row>
@@ -4971,17 +4971,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.454 億円/人 / 他 0.733 億円/人</t>
+          <t xml:space="preserve">補助 1.454 億円/人 / 他 0.737 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.692 億円/人 / 他 0.755 億円/人</t>
+          <t xml:space="preserve">補助 1.692 億円/人 / 他 0.762 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.969 億円/人 / 他 0.777 億円/人</t>
+          <t xml:space="preserve">補助 1.969 億円/人 / 他 0.788 億円/人</t>
         </is>
       </c>
     </row>
@@ -5033,17 +5033,17 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.072 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.114 億円/人 / 他 0.074 億円/人</t>
+          <t xml:space="preserve">補助 0.114 億円/人 / 他 0.075 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.122 億円/人 / 他 0.077 億円/人</t>
+          <t xml:space="preserve">補助 0.122 億円/人 / 他 0.078 億円/人</t>
         </is>
       </c>
     </row>
@@ -5095,17 +5095,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 62.2 %</t>
+          <t xml:space="preserve">寄与率 56.26 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 65.92 %</t>
+          <t xml:space="preserve">寄与率 59.7 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 69.35 %</t>
+          <t xml:space="preserve">寄与率 62.89 %</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>-10</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C22" s="2">
         <v>-5</v>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -5630,7 +5630,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA0LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxLCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwNSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6Wy0wLjE1LDAuMjVdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjI4LjEsIm1heCI6NTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjozLjksIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLjEsIm1heCI6MC4yLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6Wy0wLjE1LDAuMjVdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjI4LjEsIm1heCI6NTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjozLjksIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLjEsIm1heCI6MC4yLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -11,7 +11,8 @@
     <sheet name="補助事業収支" sheetId="4" r:id="rId4"/>
     <sheet name="妥当性診断" sheetId="5" r:id="rId5"/>
     <sheet name="前提・目標" sheetId="6" r:id="rId6"/>
-    <sheet name="モデルデータ" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="入力データ監査" sheetId="7" r:id="rId7"/>
+    <sheet name="モデルデータ" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -198,11 +199,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D7" s="2">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2">
-        <v>35</v>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -224,11 +229,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D8" s="2">
-        <v>82.4</v>
-      </c>
-      <c r="E8" s="2">
-        <v>150</v>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -250,11 +259,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D9" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="2">
-        <v>7</v>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -276,11 +289,15 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
-      <c r="D10" s="2">
-        <v>70</v>
-      </c>
-      <c r="E10" s="2">
-        <v>95</v>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -302,11 +319,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2">
-        <v>35</v>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -328,11 +349,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D12" s="2">
-        <v>74.8</v>
-      </c>
-      <c r="E12" s="2">
-        <v>150</v>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -354,11 +379,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2">
-        <v>35</v>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -380,11 +409,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <v>28.1</v>
-      </c>
-      <c r="E14" s="2">
-        <v>50</v>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -406,11 +439,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D15" s="2">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2">
-        <v>10</v>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -432,11 +469,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D16" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="E16" s="2">
-        <v>7</v>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -458,11 +499,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>6</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -484,11 +529,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.2</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -510,11 +559,15 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
-      <c r="D19" s="2">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2">
-        <v>70</v>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -536,11 +589,15 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
-      <c r="D20" s="2">
-        <v>213</v>
-      </c>
-      <c r="E20" s="2">
-        <v>350</v>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -562,15 +619,19 @@
           <t xml:space="preserve">点</t>
         </is>
       </c>
-      <c r="D21" s="2">
-        <v>23</v>
-      </c>
-      <c r="E21" s="2">
-        <v>40</v>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">参考</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5176,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5177,11 +5238,15 @@
       <c r="B3" s="2">
         <v>5</v>
       </c>
-      <c r="C3" s="2">
-        <v>-5</v>
-      </c>
-      <c r="D3" s="2">
-        <v>30</v>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5210,10 +5275,10 @@
         <v>7.000000000000001</v>
       </c>
       <c r="C5" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5258,10 +5323,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5306,10 +5371,10 @@
         <v>0.5</v>
       </c>
       <c r="C11" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5354,10 +5419,10 @@
         <v>0.5</v>
       </c>
       <c r="C14" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5402,10 +5467,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5418,10 +5483,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -5590,22 +5655,6 @@
       </c>
       <c r="D28" s="2">
         <v>50</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ローカルベンチマーク</t>
-        </is>
-      </c>
-      <c r="B29" s="2">
-        <v>23</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5613,6 +5662,3219 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C213"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="72" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力データ監査（Null／0区別）</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保存値</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力キー</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保存値</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-1</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>138</v>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-11</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>12.88</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>3.22</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>93.84</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>33.58</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-8</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>144</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-11</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>13.44</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>3.36</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>97.92</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>35.04</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-8</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>150</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-11</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>14</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>102</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-8</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>0</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
+        </is>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>0</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
+        </is>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <v>0</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
+        </is>
+      </c>
+      <c r="B40" s="2">
+        <v>0</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
+        </is>
+      </c>
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>0</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>0</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
+        </is>
+      </c>
+      <c r="B45" s="2">
+        <v>132</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+        </is>
+      </c>
+      <c r="B46" s="2">
+        <v>19</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
+        </is>
+      </c>
+      <c r="B47" s="2">
+        <v>5</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
+        </is>
+      </c>
+      <c r="B48" s="2">
+        <v>10</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
+        </is>
+      </c>
+      <c r="B49" s="2">
+        <v>24</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+        </is>
+      </c>
+      <c r="B50" s="2">
+        <v>67</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+        </is>
+      </c>
+      <c r="B51" s="2">
+        <v>39</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+        </is>
+      </c>
+      <c r="B52" s="2">
+        <v>65</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+        </is>
+      </c>
+      <c r="B53" s="2">
+        <v>36</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+        </is>
+      </c>
+      <c r="B54" s="2">
+        <v>7</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
+        </is>
+      </c>
+      <c r="B55" s="2">
+        <v>10</v>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+        </is>
+      </c>
+      <c r="B56" s="2">
+        <v>75</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+        </is>
+      </c>
+      <c r="B57" s="2">
+        <v>29</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+        </is>
+      </c>
+      <c r="B58" s="2">
+        <v>24</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+        </is>
+      </c>
+      <c r="B59" s="2">
+        <v>57</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+        </is>
+      </c>
+      <c r="B60" s="2">
+        <v>54</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+        </is>
+      </c>
+      <c r="B61" s="2">
+        <v>12</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
+        </is>
+      </c>
+      <c r="B62" s="2">
+        <v>5</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+        </is>
+      </c>
+      <c r="B63" s="2">
+        <v>53</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
+        </is>
+      </c>
+      <c r="B64" s="2">
+        <v>143</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+        </is>
+      </c>
+      <c r="B65" s="2">
+        <v>20</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
+        </is>
+      </c>
+      <c r="B66" s="2">
+        <v>8</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
+        </is>
+      </c>
+      <c r="B67" s="2">
+        <v>10</v>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
+        </is>
+      </c>
+      <c r="B68" s="2">
+        <v>25</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+        </is>
+      </c>
+      <c r="B69" s="2">
+        <v>72</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+        </is>
+      </c>
+      <c r="B70" s="2">
+        <v>41</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+        </is>
+      </c>
+      <c r="B71" s="2">
+        <v>71</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+        </is>
+      </c>
+      <c r="B72" s="2">
+        <v>38</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+        </is>
+      </c>
+      <c r="B73" s="2">
+        <v>8</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
+        </is>
+      </c>
+      <c r="B74" s="2">
+        <v>10</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+        </is>
+      </c>
+      <c r="B75" s="2">
+        <v>79</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+        </is>
+      </c>
+      <c r="B76" s="2">
+        <v>31</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+        </is>
+      </c>
+      <c r="B77" s="2">
+        <v>28</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+        </is>
+      </c>
+      <c r="B78" s="2">
+        <v>64</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+        </is>
+      </c>
+      <c r="B79" s="2">
+        <v>61</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+        </is>
+      </c>
+      <c r="B80" s="2">
+        <v>12</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
+        </is>
+      </c>
+      <c r="B81" s="2">
+        <v>6</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+        </is>
+      </c>
+      <c r="B82" s="2">
+        <v>58</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
+        </is>
+      </c>
+      <c r="B83" s="2">
+        <v>156</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+        </is>
+      </c>
+      <c r="B84" s="2">
+        <v>22</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
+        </is>
+      </c>
+      <c r="B85" s="2">
+        <v>10</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
+        </is>
+      </c>
+      <c r="B86" s="2">
+        <v>10</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
+        </is>
+      </c>
+      <c r="B87" s="2">
+        <v>27</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+        </is>
+      </c>
+      <c r="B88" s="2">
+        <v>78</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+        </is>
+      </c>
+      <c r="B89" s="2">
+        <v>43</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+        </is>
+      </c>
+      <c r="B90" s="2">
+        <v>78</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+        </is>
+      </c>
+      <c r="B91" s="2">
+        <v>40</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+        </is>
+      </c>
+      <c r="B92" s="2">
+        <v>9</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
+        </is>
+      </c>
+      <c r="B93" s="2">
+        <v>10</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+        </is>
+      </c>
+      <c r="B94" s="2">
+        <v>83</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+        </is>
+      </c>
+      <c r="B95" s="2">
+        <v>32</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+        </is>
+      </c>
+      <c r="B96" s="2">
+        <v>32</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+        </is>
+      </c>
+      <c r="B97" s="2">
+        <v>73</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+        </is>
+      </c>
+      <c r="B98" s="2">
+        <v>70</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+        </is>
+      </c>
+      <c r="B99" s="2">
+        <v>11</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
+        </is>
+      </c>
+      <c r="B100" s="2">
+        <v>7</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+        </is>
+      </c>
+      <c r="B101" s="2">
+        <v>64</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:investment:0</t>
+        </is>
+      </c>
+      <c r="B102" s="2">
+        <v>15</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:investment:1</t>
+        </is>
+      </c>
+      <c r="B103" s="2">
+        <v>200</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+        </is>
+      </c>
+      <c r="B104" s="2">
+        <v>0</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+        </is>
+      </c>
+      <c r="B105" s="2">
+        <v>100</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+        </is>
+      </c>
+      <c r="B106" s="2">
+        <v>0</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+        </is>
+      </c>
+      <c r="B107" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B108" s="2">
+        <v>0</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B109" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+        </is>
+      </c>
+      <c r="B110" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+        </is>
+      </c>
+      <c r="B111" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B112" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B113" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+        </is>
+      </c>
+      <c r="B114" s="2">
+        <v>0</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+        </is>
+      </c>
+      <c r="B115" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B116" s="2">
+        <v>0</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B117" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+        </is>
+      </c>
+      <c r="B118" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+        </is>
+      </c>
+      <c r="B119" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B120" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B121" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B122" s="2">
+        <v>0</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B123" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+        </is>
+      </c>
+      <c r="B124" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+        </is>
+      </c>
+      <c r="B125" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+        </is>
+      </c>
+      <c r="B126" s="2">
+        <v>0</v>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+        </is>
+      </c>
+      <c r="B127" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B128" s="2">
+        <v>0</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B129" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+        </is>
+      </c>
+      <c r="B130" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+        </is>
+      </c>
+      <c r="B131" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B132" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B133" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+        </is>
+      </c>
+      <c r="B134" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+        </is>
+      </c>
+      <c r="B135" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+        </is>
+      </c>
+      <c r="B136" s="2">
+        <v>0</v>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+        </is>
+      </c>
+      <c r="B137" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B138" s="2">
+        <v>0</v>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B139" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+        </is>
+      </c>
+      <c r="B140" s="2">
+        <v>0.045</v>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+        </is>
+      </c>
+      <c r="B141" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B142" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B143" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+        </is>
+      </c>
+      <c r="B144" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+        </is>
+      </c>
+      <c r="B145" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B146" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B147" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B148" s="2">
+        <v>0</v>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B149" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+        </is>
+      </c>
+      <c r="B150" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+        </is>
+      </c>
+      <c r="B151" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
+        </is>
+      </c>
+      <c r="B152" s="2">
+        <v>1</v>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
+        </is>
+      </c>
+      <c r="B153" s="2">
+        <v>50</v>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
+        </is>
+      </c>
+      <c r="B154" s="2">
+        <v>5</v>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
+        </is>
+      </c>
+      <c r="B155" s="2">
+        <v>20</v>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:investment</t>
+        </is>
+      </c>
+      <c r="B156" s="2">
+        <v>45</v>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:localBenchmark</t>
+        </is>
+      </c>
+      <c r="B157" s="2">
+        <v>23</v>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
+        </is>
+      </c>
+      <c r="B158" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B159" s="2">
+        <v>0.005</v>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+        </is>
+      </c>
+      <c r="B160" s="2">
+        <v>0.015</v>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B161" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
+        </is>
+      </c>
+      <c r="B162" s="2">
+        <v>0.045</v>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B163" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
+        </is>
+      </c>
+      <c r="B164" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B165" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B166" s="2">
+        <v>0.005</v>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+        </is>
+      </c>
+      <c r="B167" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+        </is>
+      </c>
+      <c r="B168" s="2">
+        <v>0</v>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B169" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+        </is>
+      </c>
+      <c r="B170" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B171" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
+        </is>
+      </c>
+      <c r="B172" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+        </is>
+      </c>
+      <c r="B173" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B174" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
+        </is>
+      </c>
+      <c r="B175" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B176" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
+        </is>
+      </c>
+      <c r="B177" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B178" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B179" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+        </is>
+      </c>
+      <c r="B180" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:subsidy</t>
+        </is>
+      </c>
+      <c r="B181" s="2">
+        <v>15</v>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:usefulLife</t>
+        </is>
+      </c>
+      <c r="B182" s="2">
+        <v>10</v>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2">
+        <v>15</v>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2027</t>
+        </is>
+      </c>
+      <c r="B184" s="2">
+        <v>15</v>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2028</t>
+        </is>
+      </c>
+      <c r="B185" s="2">
+        <v>15</v>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2029</t>
+        </is>
+      </c>
+      <c r="B186" s="2">
+        <v>0</v>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2030</t>
+        </is>
+      </c>
+      <c r="B187" s="2">
+        <v>0</v>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2031</t>
+        </is>
+      </c>
+      <c r="B188" s="2">
+        <v>0</v>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
+        </is>
+      </c>
+      <c r="B189" s="2">
+        <v>7</v>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
+        </is>
+      </c>
+      <c r="B190" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B191" s="2">
+        <v>35</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B192" s="2">
+        <v>21</v>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B193" s="2">
+        <v>0</v>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
+        </is>
+      </c>
+      <c r="B194" s="2">
+        <v>10</v>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
+        </is>
+      </c>
+      <c r="B195" s="2">
+        <v>7</v>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B196" s="2">
+        <v>0</v>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+        </is>
+      </c>
+      <c r="B197" s="2">
+        <v>70</v>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B198" s="2">
+        <v>30</v>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B199" s="2">
+        <v>35</v>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B200" s="2">
+        <v>21</v>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B201" s="2">
+        <v>40</v>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B202" s="2">
+        <v>23</v>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B203" s="2">
+        <v>10</v>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B204" s="2">
+        <v>6</v>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B205" s="2">
+        <v>0</v>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B206" s="2">
+        <v>35</v>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B207" s="2">
+        <v>22</v>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B208" s="2">
+        <v>0</v>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B209" s="2">
+        <v>95</v>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B210" s="2">
+        <v>70</v>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B211" s="2">
+        <v>0</v>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B212" s="2">
+        <v>350</v>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
+        </is>
+      </c>
+      <c r="B213" s="2">
+        <v>213</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -5630,7 +8892,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6Wy0wLjE1LDAuMjVdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6Wy0wLjE1LDAuMjVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjE1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjI4LjEsIm1heCI6NTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjozLjksIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLjEsIm1heCI6MC4yLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -8892,7 +8892,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIiwib2ZmaWNlclBheSI6InJhdGUifX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -161,7 +161,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画値</t>
+          <t xml:space="preserve">計画値（基準年→事業化報告3年目・3年間）</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標下限</t>
+          <t xml:space="preserve">目標下限（3年間）</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画上限</t>
+          <t xml:space="preserve">計画上限（3年間）</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -488,15 +488,15 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">年平均役員目標賃上げ率</t>
+          <t xml:space="preserve">投資額／全社売上高</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>6.265856918261115</v>
+        <v>30</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -511,22 +511,22 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">参考</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員給与支給総額の増加額</t>
+          <t xml:space="preserve">付加価値増加額／補助金額</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.06</v>
+        <v>84.20000000000002</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -548,15 +548,15 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">投資額／全社売上高</t>
+          <t xml:space="preserve">ローカルベンチマーク財務分析結果</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">点</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -578,15 +578,15 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">付加価値増加額／補助金額</t>
+          <t xml:space="preserve">年平均役員目標賃上げ率</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>84.20000000000002</v>
+        <v>6.265856918261115</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -601,22 +601,22 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">参考</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ローカルベンチマーク財務分析結果</t>
+          <t xml:space="preserve">役員給与支給総額の増加額</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>23</v>
+        <v>0.06</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">点</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -8892,7 +8892,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIiwib2ZmaWNlclBheSI6InJhdGUifX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -156,12 +156,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">15指標・目標</t>
+          <t xml:space="preserve">15指標・目標（指標名に第6次定義を併記）</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画値（基準年→事業化報告3年目・3年間）</t>
+          <t xml:space="preserve">計画値</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標下限（3年間）</t>
+          <t xml:space="preserve">目標下限</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画上限（3年間）</t>
+          <t xml:space="preserve">計画上限</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -188,7 +188,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社年平均売上高成長率</t>
+          <t xml:space="preserve">全社年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -218,7 +218,7 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社売上高増加額</t>
+          <t xml:space="preserve">全社売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B8" s="2">
@@ -248,7 +248,7 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）</t>
+          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B9" s="2">
@@ -278,7 +278,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高／全社売上高</t>
+          <t xml:space="preserve">補助事業売上高／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -308,7 +308,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均売上高成長率</t>
+          <t xml:space="preserve">補助事業年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -338,7 +338,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高増加額</t>
+          <t xml:space="preserve">補助事業売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -368,7 +368,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均労働生産性の伸び</t>
+          <t xml:space="preserve">補助事業年平均労働生産性の伸び（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -398,7 +398,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業付加価値増加額</t>
+          <t xml:space="preserve">補助事業付加価値増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -428,7 +428,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B15" s="2">
@@ -458,7 +458,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業従業員給与支給総額の増加額</t>
+          <t xml:space="preserve">補助事業従業員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B16" s="2">
@@ -488,7 +488,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">投資額／全社売上高</t>
+          <t xml:space="preserve">投資額／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B17" s="2">
@@ -518,7 +518,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">付加価値増加額／補助金額</t>
+          <t xml:space="preserve">付加価値増加額／補助金額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -548,7 +548,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ローカルベンチマーク財務分析結果</t>
+          <t xml:space="preserve">ローカルベンチマーク財務分析結果（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -578,7 +578,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">年平均役員目標賃上げ率</t>
+          <t xml:space="preserve">年平均役員目標賃上げ率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -608,7 +608,7 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員給与支給総額の増加額</t>
+          <t xml:space="preserve">役員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B21" s="2">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -192,7 +192,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>9.659350315034555</v>
+        <v>10.337444343281588</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>72.89000000000001</v>
+        <v>78.52000000000001</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -282,7 +282,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>35.239705589815</v>
+        <v>34.593978844589095</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -1256,13 +1256,13 @@
         <v>228.73</v>
       </c>
       <c r="H3" s="4">
-        <v>249.76999999999998</v>
+        <v>251.45</v>
       </c>
       <c r="I3" s="4">
-        <v>273.87</v>
+        <v>277.43</v>
       </c>
       <c r="J3" s="4">
-        <v>301.62</v>
+        <v>307.25</v>
       </c>
     </row>
     <row r="4">
@@ -1292,13 +1292,13 @@
         <v>40.98249506903351</v>
       </c>
       <c r="H4" s="2">
-        <v>9.198618458444452</v>
+        <v>9.933108905696674</v>
       </c>
       <c r="I4" s="2">
-        <v>9.648876966809471</v>
+        <v>10.33207397096838</v>
       </c>
       <c r="J4" s="2">
-        <v>10.132544637966912</v>
+        <v>10.748657318963328</v>
       </c>
     </row>
     <row r="5">
@@ -1326,13 +1326,13 @@
         <v>152.89</v>
       </c>
       <c r="H5" s="2">
-        <v>166.19</v>
+        <v>167.32</v>
       </c>
       <c r="I5" s="2">
-        <v>181.43</v>
+        <v>183.81</v>
       </c>
       <c r="J5" s="2">
-        <v>198.98</v>
+        <v>202.73</v>
       </c>
     </row>
     <row r="6">
@@ -1394,13 +1394,13 @@
         <v>75.84</v>
       </c>
       <c r="H7" s="4">
-        <v>83.57999999999998</v>
+        <v>84.13</v>
       </c>
       <c r="I7" s="4">
-        <v>92.44</v>
+        <v>93.62</v>
       </c>
       <c r="J7" s="4">
-        <v>102.64000000000001</v>
+        <v>104.52000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1428,13 +1428,13 @@
         <v>33.156997333100165</v>
       </c>
       <c r="H8" s="2">
-        <v>33.462785762901866</v>
+        <v>33.45794392523365</v>
       </c>
       <c r="I8" s="2">
-        <v>33.753240588600434</v>
+        <v>33.745449302526765</v>
       </c>
       <c r="J8" s="2">
-        <v>34.02957363570056</v>
+        <v>34.017900732302685</v>
       </c>
     </row>
     <row r="9">
@@ -1462,13 +1462,13 @@
         <v>55.85</v>
       </c>
       <c r="H9" s="2">
-        <v>58.559999999999995</v>
+        <v>58.739999999999995</v>
       </c>
       <c r="I9" s="2">
-        <v>61.49000000000001</v>
+        <v>61.870000000000005</v>
       </c>
       <c r="J9" s="2">
-        <v>64.71000000000001</v>
+        <v>65.28</v>
       </c>
     </row>
     <row r="10">
@@ -1768,13 +1768,13 @@
         <v>19.990000000000002</v>
       </c>
       <c r="H18" s="4">
-        <v>25.01999999999999</v>
+        <v>25.389999999999997</v>
       </c>
       <c r="I18" s="4">
-        <v>30.950000000000006</v>
+        <v>31.750000000000014</v>
       </c>
       <c r="J18" s="4">
-        <v>37.930000000000014</v>
+        <v>39.24000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1802,13 +1802,13 @@
         <v>8.739561928911819</v>
       </c>
       <c r="H19" s="2">
-        <v>10.017215838571483</v>
+        <v>10.097434877709285</v>
       </c>
       <c r="I19" s="2">
-        <v>11.300982217840582</v>
+        <v>11.444328299030392</v>
       </c>
       <c r="J19" s="2">
-        <v>12.575426032756454</v>
+        <v>12.771358828315707</v>
       </c>
     </row>
     <row r="20">
@@ -1836,13 +1836,13 @@
         <v>19.990000000000002</v>
       </c>
       <c r="H20" s="4">
-        <v>25.01999999999999</v>
+        <v>25.389999999999997</v>
       </c>
       <c r="I20" s="4">
-        <v>30.950000000000006</v>
+        <v>31.750000000000014</v>
       </c>
       <c r="J20" s="4">
-        <v>37.930000000000014</v>
+        <v>39.24000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2084,13 +2084,13 @@
         <v>26.231801687579242</v>
       </c>
       <c r="H5" s="2">
-        <v>29.066741402089924</v>
+        <v>28.872539272221115</v>
       </c>
       <c r="I5" s="2">
-        <v>32.07726293496914</v>
+        <v>31.665645388025805</v>
       </c>
       <c r="J5" s="2">
-        <v>35.239705589815</v>
+        <v>34.593978844589095</v>
       </c>
     </row>
     <row r="6">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.2 % / 補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">全社 9.93 % / 補助 21 % / 他 6 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.65 % / 補助 21.01 % / 他 5 %</t>
+          <t xml:space="preserve">全社 10.33 % / 補助 21.01 % / 他 6 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.13 % / 補助 20.99 % / 他 5 %</t>
+          <t xml:space="preserve">全社 10.75 % / 補助 20.99 % / 他 6 %</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.97 % / 補助 65 % / 他 66.5 %</t>
+          <t xml:space="preserve">全社 65.98 % / 補助 65 % / 他 66.5 %</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.03 % / 補助 35 % / 他 33.5 %</t>
+          <t xml:space="preserve">全社 34.02 % / 補助 35 % / 他 33.5 %</t>
         </is>
       </c>
     </row>
@@ -3234,17 +3234,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.45 % / 補助 23.66 % / 他 23.36 %</t>
+          <t xml:space="preserve">全社 23.36 % / 補助 23.66 % / 他 23.24 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.45 % / 補助 21.61 % / 他 22.85 %</t>
+          <t xml:space="preserve">全社 22.3 % / 補助 21.61 % / 他 22.62 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.45 % / 補助 19.79 % / 他 22.36 %</t>
+          <t xml:space="preserve">全社 21.25 % / 補助 19.79 % / 他 22.01 %</t>
         </is>
       </c>
     </row>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.02 % / 補助 11.34 % / 他 9.48 %</t>
+          <t xml:space="preserve">全社 10.1 % / 補助 11.34 % / 他 9.59 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.3 % / 補助 13.4 % / 他 10.31 %</t>
+          <t xml:space="preserve">全社 11.44 % / 補助 13.4 % / 他 10.54 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.58 % / 補助 15.2 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 12.77 % / 補助 15.2 % / 他 11.48 %</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.22 % / 補助 17.53 % / 他 11.45 %</t>
+          <t xml:space="preserve">全社 13.28 % / 補助 17.53 % / 他 11.55 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.22 % / 補助 18.52 % / 他 12.19 %</t>
+          <t xml:space="preserve">全社 14.33 % / 補助 18.52 % / 他 12.39 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.23 % / 補助 19.44 % / 他 12.94 %</t>
+          <t xml:space="preserve">全社 15.38 % / 補助 19.44 % / 他 13.23 %</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.65 % / 補助 9 % / 他 10 %</t>
+          <t xml:space="preserve">全社 9.66 % / 補助 9 % / 他 10 %</t>
         </is>
       </c>
     </row>
@@ -3544,17 +3544,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.03 % / 補助 7.36 % / 他 9.71 %</t>
+          <t xml:space="preserve">全社 8.97 % / 補助 7.36 % / 他 9.62 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.83 % / 補助 6.76 % / 他 9.81 %</t>
+          <t xml:space="preserve">全社 8.72 % / 補助 6.76 % / 他 9.63 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 % / 補助 6.22 % / 他 9.91 %</t>
+          <t xml:space="preserve">全社 8.45 % / 補助 6.22 % / 他 9.63 %</t>
         </is>
       </c>
     </row>
@@ -3606,17 +3606,17 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.6 % / 補助 0.44 % / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.6 % / 補助 0.44 % / 他 0.66 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.57 % / 補助 0.39 % / 他 0.66 %</t>
+          <t xml:space="preserve">全社 0.57 % / 補助 0.39 % / 他 0.65 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.54 % / 補助 0.34 % / 他 0.66 %</t>
+          <t xml:space="preserve">全社 0.53 % / 補助 0.34 % / 他 0.64 %</t>
         </is>
       </c>
     </row>
@@ -3668,17 +3668,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.63 % / 補助 7.8 % / 他 10.38 %</t>
+          <t xml:space="preserve">全社 9.56 % / 補助 7.8 % / 他 10.28 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.41 % / 補助 7.15 % / 他 10.47 %</t>
+          <t xml:space="preserve">全社 9.29 % / 補助 7.15 % / 他 10.28 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.15 % / 補助 6.56 % / 他 10.57 %</t>
+          <t xml:space="preserve">全社 8.99 % / 補助 6.56 % / 他 10.27 %</t>
         </is>
       </c>
     </row>
@@ -3916,17 +3916,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.14 % / 補助 30.78 % / 他 47.54 %</t>
+          <t xml:space="preserve">全社 41.87 % / 補助 30.78 % / 他 47.09 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.81 % / 補助 27.85 % / 他 46.2 %</t>
+          <t xml:space="preserve">全社 39.32 % / 補助 27.85 % / 他 45.34 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.54 % / 補助 25.23 % / 他 44.96 %</t>
+          <t xml:space="preserve">全社 36.89 % / 補助 25.23 % / 他 43.71 %</t>
         </is>
       </c>
     </row>
@@ -4040,17 +4040,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.86 億円/人 / 補助 1.454 億円/人 / 他 0.737 億円/人</t>
+          <t xml:space="preserve">全社 0.866 億円/人 / 補助 1.454 億円/人 / 他 0.744 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.925 億円/人 / 補助 1.692 億円/人 / 他 0.762 億円/人</t>
+          <t xml:space="preserve">全社 0.937 億円/人 / 補助 1.692 億円/人 / 他 0.777 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.999 億円/人 / 補助 1.969 億円/人 / 他 0.788 億円/人</t>
+          <t xml:space="preserve">全社 1.018 億円/人 / 補助 1.969 億円/人 / 他 0.811 億円/人</t>
         </is>
       </c>
     </row>
@@ -4102,17 +4102,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.086 億円/人 / 補助 0.165 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.165 億円/人 / 他 0.071 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.105 億円/人 / 補助 0.227 億円/人 / 他 0.079 億円/人</t>
+          <t xml:space="preserve">全社 0.107 億円/人 / 補助 0.227 億円/人 / 他 0.082 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.126 億円/人 / 補助 0.299 億円/人 / 他 0.088 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.299 億円/人 / 他 0.093 億円/人</t>
         </is>
       </c>
     </row>
@@ -4164,17 +4164,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.354 億円/人 / 他 0.158 億円/人</t>
+          <t xml:space="preserve">全社 0.193 億円/人 / 補助 0.354 億円/人 / 他 0.159 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.214 億円/人 / 補助 0.418 億円/人 / 他 0.169 億円/人</t>
+          <t xml:space="preserve">全社 0.216 億円/人 / 補助 0.418 億円/人 / 他 0.172 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.493 億円/人 / 他 0.182 億円/人</t>
+          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.493 億円/人 / 他 0.187 億円/人</t>
         </is>
       </c>
     </row>
@@ -4288,17 +4288,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.28 pt / 補助 17 pt / 他 3.5 pt</t>
+          <t xml:space="preserve">全社 8.01 pt / 補助 17 pt / 他 4.5 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.72 pt / 補助 17 pt / 他 3.49 pt</t>
+          <t xml:space="preserve">全社 8.4 pt / 補助 17 pt / 他 4.5 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.2 pt / 補助 17 pt / 他 3.51 pt</t>
+          <t xml:space="preserve">全社 8.81 pt / 補助 17 pt / 他 4.5 pt</t>
         </is>
       </c>
     </row>
@@ -4412,17 +4412,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.2 % / 補助 6.2 % / 他 1.98 %</t>
+          <t xml:space="preserve">全社 3.18 % / 補助 6.2 % / 他 1.96 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.92 % / 補助 5.12 % / 他 1.88 %</t>
+          <t xml:space="preserve">全社 2.88 % / 補助 5.12 % / 他 1.85 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.65 % / 補助 4.23 % / 他 1.79 %</t>
+          <t xml:space="preserve">全社 2.6 % / 補助 4.23 % / 他 1.74 %</t>
         </is>
       </c>
     </row>
@@ -4598,17 +4598,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.13 倍 / 補助 2.83 倍 / 他 5.8 倍</t>
+          <t xml:space="preserve">全社 4.17 倍 / 補助 2.83 倍 / 他 5.9 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 倍 / 補助 3.62 倍 / 他 6.48 倍</t>
+          <t xml:space="preserve">全社 4.97 倍 / 補助 3.62 倍 / 他 6.71 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.74 倍 / 補助 4.59 倍 / 他 7.22 倍</t>
+          <t xml:space="preserve">全社 5.91 倍 / 補助 4.59 倍 / 他 7.59 倍</t>
         </is>
       </c>
     </row>
@@ -4784,17 +4784,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 29.07 %</t>
+          <t xml:space="preserve">構成比 28.87 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 32.08 %</t>
+          <t xml:space="preserve">構成比 31.67 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 35.24 %</t>
+          <t xml:space="preserve">構成比 34.59 %</t>
         </is>
       </c>
     </row>
@@ -4846,17 +4846,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">補助 21 % / 他 6 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21.01 % / 他 5 %</t>
+          <t xml:space="preserve">補助 21.01 % / 他 6 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 20.99 % / 他 5 %</t>
+          <t xml:space="preserve">補助 20.99 % / 他 6 %</t>
         </is>
       </c>
     </row>
@@ -4970,17 +4970,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.86 pt</t>
+          <t xml:space="preserve">差 1.74 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.09 pt</t>
+          <t xml:space="preserve">差 2.86 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.06 pt</t>
+          <t xml:space="preserve">差 3.72 pt</t>
         </is>
       </c>
     </row>
@@ -5032,17 +5032,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.454 億円/人 / 他 0.737 億円/人</t>
+          <t xml:space="preserve">補助 1.454 億円/人 / 他 0.744 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.692 億円/人 / 他 0.762 億円/人</t>
+          <t xml:space="preserve">補助 1.692 億円/人 / 他 0.777 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.969 億円/人 / 他 0.788 億円/人</t>
+          <t xml:space="preserve">補助 1.969 億円/人 / 他 0.811 億円/人</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 56.26 %</t>
+          <t xml:space="preserve">寄与率 52.41 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 59.7 %</t>
+          <t xml:space="preserve">寄与率 55.66 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 62.89 %</t>
+          <t xml:space="preserve">寄与率 58.61 %</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2">
         <v>-10</v>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -94,15 +94,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -153,85 +153,67 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申請区分</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一般企業（100億宣言企業以外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">15指標・目標（指標名に第6次定義を併記）</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">計画値</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">単位</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目標下限</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">計画上限</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社年平均売上高成長率（第6次定義：undefined）</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <v>10.337444343281588</v>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">%/年</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">努力</t>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">制度上の必須条件</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標値</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">判定</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社売上高増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">全社年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>78.52000000000001</v>
+        <v>10.337444343281588</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -241,27 +223,27 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）（第6次定義：undefined）</t>
+          <t xml:space="preserve">全社売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>6.630139377100797</v>
+        <v>78.52000000000001</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -271,27 +253,27 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高／全社売上高（第6次定義：undefined）</t>
+          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>34.593978844589095</v>
+        <v>6.626397837416431</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -301,27 +283,27 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均売上高成長率（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業売上高／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>20.99861119003372</v>
+        <v>34.593978844589095</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -331,27 +313,27 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>46.290000000000006</v>
+        <v>20.99861119003372</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -361,27 +343,27 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均労働生産性の伸び（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>18.045577428925764</v>
+        <v>46.290000000000006</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -391,27 +373,27 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業付加価値増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業年平均労働生産性の伸び（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>12.630000000000003</v>
+        <v>18.038550488172866</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -421,27 +403,27 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業付加価値増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>6.978386656855995</v>
+        <v>12.630000000000003</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -451,27 +433,27 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業従業員給与支給総額の増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>1.8100000000000005</v>
+        <v>6.971782645069546</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -481,27 +463,27 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">投資額／全社売上高（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業従業員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>1.8100000000000005</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -511,18 +493,18 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">付加価値増加額／補助金額（第6次定義：undefined）</t>
+          <t xml:space="preserve">投資額／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>84.20000000000002</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -531,7 +513,7 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -541,27 +523,27 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ローカルベンチマーク財務分析結果（第6次定義：undefined）</t>
+          <t xml:space="preserve">付加価値増加額／補助金額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>23</v>
+        <v>84.20000000000002</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">点</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -571,27 +553,27 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">年平均役員目標賃上げ率（第6次定義：undefined）</t>
+          <t xml:space="preserve">ローカルベンチマーク財務分析結果（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>6.265856918261115</v>
+        <v>23</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">点</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
@@ -601,37 +583,67 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">年平均役員目標賃上げ率（第6次定義：undefined）</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>6.265856918261115</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%/年</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標未設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">役員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>0.06</v>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参考</t>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
@@ -1088,13 +1100,13 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.2318840579710149</v>
+        <v>1.1821974965229487</v>
       </c>
       <c r="C27" s="2">
-        <v>1.2500000000000002</v>
+        <v>1.2203389830508478</v>
       </c>
       <c r="D27" s="2">
-        <v>1.0666666666666667</v>
+        <v>1.0596026490066224</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1342,31 +1354,31 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="C6" s="2">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -1444,37 +1456,37 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>33.58</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2">
-        <v>35.04</v>
+        <v>34.69</v>
       </c>
       <c r="D9" s="2">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>37.71</v>
+        <v>37.64</v>
       </c>
       <c r="F9" s="2">
-        <v>38.96</v>
+        <v>38.92</v>
       </c>
       <c r="G9" s="2">
-        <v>55.85</v>
+        <v>55.84</v>
       </c>
       <c r="H9" s="2">
-        <v>58.739999999999995</v>
+        <v>58.769999999999996</v>
       </c>
       <c r="I9" s="2">
-        <v>61.870000000000005</v>
+        <v>61.95</v>
       </c>
       <c r="J9" s="2">
-        <v>65.28</v>
+        <v>65.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-8 うち役員の人件費（億円）</t>
+          <t xml:space="preserve">2-8 うち役員の人件費（自動計算）（億円）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -1512,31 +1524,31 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="C11" s="2">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E11" s="2">
-        <v>1.04</v>
+        <v>0.94</v>
       </c>
       <c r="F11" s="2">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="G11" s="2">
-        <v>1.4200000000000002</v>
+        <v>1.31</v>
       </c>
       <c r="H11" s="2">
-        <v>1.5</v>
+        <v>1.3800000000000001</v>
       </c>
       <c r="I11" s="2">
-        <v>1.57</v>
+        <v>1.4500000000000002</v>
       </c>
       <c r="J11" s="2">
-        <v>1.6400000000000001</v>
+        <v>1.5099999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -1546,44 +1558,44 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G12" s="2">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-11 うち従業員の人件費（億円）</t>
+          <t xml:space="preserve">2-11 うち従業員の人件費（自動計算）（億円）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>12.88</v>
+        <v>12.4</v>
       </c>
       <c r="C13" s="2">
-        <v>13.44</v>
+        <v>13.19</v>
       </c>
       <c r="D13" s="2">
         <v>14</v>
@@ -1614,31 +1626,31 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>12.88</v>
+        <v>11.78</v>
       </c>
       <c r="C14" s="2">
-        <v>13.44</v>
+        <v>12.53</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="E14" s="2">
-        <v>14.71</v>
+        <v>13.97</v>
       </c>
       <c r="F14" s="2">
-        <v>15.45</v>
+        <v>14.68</v>
       </c>
       <c r="G14" s="2">
-        <v>21.03</v>
+        <v>20.22</v>
       </c>
       <c r="H14" s="2">
-        <v>22.55</v>
+        <v>21.69</v>
       </c>
       <c r="I14" s="2">
-        <v>24.19</v>
+        <v>23.28</v>
       </c>
       <c r="J14" s="2">
-        <v>25.97</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -1648,31 +1660,31 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="D15" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="G15" s="2">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="16">
@@ -1682,31 +1694,31 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="C16" s="2">
-        <v>3.36</v>
+        <v>2.59</v>
       </c>
       <c r="D16" s="2">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="F16" s="2">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="G16" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H16" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J16" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="17">
@@ -1716,31 +1728,31 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="C17" s="2">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="H17" s="2">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J17" s="2">
-        <v>0</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="18">
@@ -1750,31 +1762,31 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <v>10.579999999999995</v>
+        <v>11.159999999999997</v>
       </c>
       <c r="C18" s="4">
-        <v>11.04</v>
+        <v>11.389999999999997</v>
       </c>
       <c r="D18" s="4">
-        <v>11.5</v>
+        <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>12.470000000000006</v>
+        <v>12.540000000000006</v>
       </c>
       <c r="F18" s="4">
-        <v>13.500000000000007</v>
+        <v>13.540000000000006</v>
       </c>
       <c r="G18" s="4">
-        <v>19.990000000000002</v>
+        <v>20</v>
       </c>
       <c r="H18" s="4">
-        <v>25.389999999999997</v>
+        <v>25.359999999999996</v>
       </c>
       <c r="I18" s="4">
-        <v>31.750000000000014</v>
+        <v>31.67000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>39.24000000000001</v>
+        <v>39.10000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1784,31 +1796,31 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.666666666666663</v>
+        <v>8.086956521739127</v>
       </c>
       <c r="C19" s="2">
-        <v>7.666666666666666</v>
+        <v>7.9097222222222205</v>
       </c>
       <c r="D19" s="2">
-        <v>7.666666666666666</v>
+        <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.993589743589748</v>
+        <v>8.038461538461544</v>
       </c>
       <c r="F19" s="2">
-        <v>8.321005917159766</v>
+        <v>8.345660749506907</v>
       </c>
       <c r="G19" s="2">
-        <v>8.739561928911819</v>
+        <v>8.743933895859747</v>
       </c>
       <c r="H19" s="2">
-        <v>10.097434877709285</v>
+        <v>10.085504076357127</v>
       </c>
       <c r="I19" s="2">
-        <v>11.444328299030392</v>
+        <v>11.415492196229682</v>
       </c>
       <c r="J19" s="2">
-        <v>12.771358828315707</v>
+        <v>12.725793327908871</v>
       </c>
     </row>
     <row r="20">
@@ -1818,31 +1830,687 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <v>10.579999999999995</v>
+        <v>11.159999999999997</v>
       </c>
       <c r="C20" s="4">
-        <v>11.04</v>
+        <v>11.389999999999997</v>
       </c>
       <c r="D20" s="4">
-        <v>11.5</v>
+        <v>11.600000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>12.470000000000006</v>
+        <v>12.540000000000006</v>
       </c>
       <c r="F20" s="4">
-        <v>13.500000000000007</v>
+        <v>13.540000000000006</v>
       </c>
       <c r="G20" s="4">
-        <v>19.990000000000002</v>
+        <v>20</v>
       </c>
       <c r="H20" s="4">
-        <v>25.389999999999997</v>
+        <v>25.359999999999996</v>
       </c>
       <c r="I20" s="4">
-        <v>31.750000000000014</v>
+        <v>31.67000000000001</v>
       </c>
       <c r="J20" s="4">
-        <v>39.24000000000001</v>
+        <v>39.10000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-19 税引前当期純利益（モデル未対応）（億円）</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-20 当期純利益（モデル未対応）（億円）</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-21 給与支給総額（常時使用する従業員）（億円）</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="C23" s="2">
+        <v>13.19</v>
+      </c>
+      <c r="D23" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" s="2">
+        <v>14.71</v>
+      </c>
+      <c r="F23" s="2">
+        <v>15.45</v>
+      </c>
+      <c r="G23" s="2">
+        <v>21.03</v>
+      </c>
+      <c r="H23" s="2">
+        <v>22.55</v>
+      </c>
+      <c r="I23" s="2">
+        <v>24.19</v>
+      </c>
+      <c r="J23" s="2">
+        <v>25.97</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-22 給与支給総額（役員）（億円）</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.04</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.4200000000000002</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1.57</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1.6400000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-23 減価償却費（合計）（億円）</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>3.22</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3.36</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="G25" s="2">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-24 付加価値額（億円）</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <v>27.699999999999996</v>
+      </c>
+      <c r="C26" s="4">
+        <v>28.9</v>
+      </c>
+      <c r="D26" s="4">
+        <v>30.1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>31.790000000000006</v>
+      </c>
+      <c r="F26" s="4">
+        <v>33.57000000000001</v>
+      </c>
+      <c r="G26" s="4">
+        <v>50.45</v>
+      </c>
+      <c r="H26" s="4">
+        <v>57.41</v>
+      </c>
+      <c r="I26" s="4">
+        <v>65.43</v>
+      </c>
+      <c r="J26" s="4">
+        <v>74.71000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-25 付加価値増加率（%）</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C27" s="2">
+        <v>4.332129963898934</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4.152249134948116</v>
+      </c>
+      <c r="E27" s="2">
+        <v>5.614617940199351</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5.599245045611823</v>
+      </c>
+      <c r="G27" s="2">
+        <v>50.28299076556446</v>
+      </c>
+      <c r="H27" s="2">
+        <v>13.79583746283448</v>
+      </c>
+      <c r="I27" s="2">
+        <v>13.96969169134299</v>
+      </c>
+      <c r="J27" s="2">
+        <v>14.183096438942378</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-26 売上高付加価値率（%）</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>20.072463768115938</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20.069444444444443</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20.06666666666667</v>
+      </c>
+      <c r="E28" s="2">
+        <v>20.37820512820513</v>
+      </c>
+      <c r="F28" s="2">
+        <v>20.69156804733728</v>
+      </c>
+      <c r="G28" s="2">
+        <v>22.056573252306215</v>
+      </c>
+      <c r="H28" s="2">
+        <v>22.831576854245377</v>
+      </c>
+      <c r="I28" s="2">
+        <v>23.584327578127816</v>
+      </c>
+      <c r="J28" s="2">
+        <v>24.315703824247358</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-27 常時使用する従業員数（就業時間換算）（人）</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>212</v>
+      </c>
+      <c r="C29" s="2">
+        <v>221</v>
+      </c>
+      <c r="D29" s="2">
+        <v>230</v>
+      </c>
+      <c r="E29" s="2">
+        <v>232</v>
+      </c>
+      <c r="F29" s="2">
+        <v>235</v>
+      </c>
+      <c r="G29" s="2">
+        <v>285</v>
+      </c>
+      <c r="H29" s="2">
+        <v>291</v>
+      </c>
+      <c r="I29" s="2">
+        <v>296</v>
+      </c>
+      <c r="J29" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-28 役員数（人）</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>7</v>
+      </c>
+      <c r="H30" s="2">
+        <v>7</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7</v>
+      </c>
+      <c r="J30" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-29 従業員1人当たり給与支給総額（億円/人）</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>0.05849056603773585</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.059683257918552036</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.06086956521739131</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.0634051724137931</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.06574468085106383</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.07378947368421053</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.0774914089347079</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.08172297297297297</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.08599337748344371</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-30 従業員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C32" s="2">
+        <v>2.0391183768792898</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1.9876718198899024</v>
+      </c>
+      <c r="E32" s="2">
+        <v>4.1656403940886655</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3.689775373533699</v>
+      </c>
+      <c r="G32" s="2">
+        <v>12.23641628342702</v>
+      </c>
+      <c r="H32" s="2">
+        <v>5.016887999960784</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5.460687960687949</v>
+      </c>
+      <c r="J32" s="2">
+        <v>5.225463973126665</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-31 役員1人当たり給与支給総額（億円/人）</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>0.184</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.192</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.21600000000000003</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.20285714285714287</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.22428571428571428</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.2342857142857143</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-32 役員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>4.347826086956519</v>
+      </c>
+      <c r="D34" s="2">
+        <v>4.166666666666674</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3.8461538461538547</v>
+      </c>
+      <c r="G34" s="2">
+        <v>-6.084656084656093</v>
+      </c>
+      <c r="H34" s="2">
+        <v>5.633802816901401</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4.666666666666663</v>
+      </c>
+      <c r="J34" s="2">
+        <v>4.458598726114649</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-33 労働生産性（億円/人）</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>0.12764976958525343</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.12787610619469025</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.12808510638297874</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.13413502109704645</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.13987500000000003</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.17277397260273974</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0.1926510067114094</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.21594059405940597</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0.24177993527508093</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-34 EBITDA（億円）</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <v>14.379999999999997</v>
+      </c>
+      <c r="C36" s="4">
+        <v>14.749999999999996</v>
+      </c>
+      <c r="D36" s="4">
+        <v>15.100000000000001</v>
+      </c>
+      <c r="E36" s="4">
+        <v>16.040000000000006</v>
+      </c>
+      <c r="F36" s="4">
+        <v>17.040000000000006</v>
+      </c>
+      <c r="G36" s="4">
+        <v>28</v>
+      </c>
+      <c r="H36" s="4">
+        <v>33.36</v>
+      </c>
+      <c r="I36" s="4">
+        <v>39.67000000000001</v>
+      </c>
+      <c r="J36" s="4">
+        <v>47.10000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-35 EBITDAマージン（%）</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>10.420289855072461</v>
+      </c>
+      <c r="C37" s="2">
+        <v>10.243055555555552</v>
+      </c>
+      <c r="D37" s="2">
+        <v>10.066666666666668</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10.282051282051285</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.50295857988166</v>
+      </c>
+      <c r="G37" s="2">
+        <v>12.241507454203647</v>
+      </c>
+      <c r="H37" s="2">
+        <v>13.267051103599126</v>
+      </c>
+      <c r="I37" s="2">
+        <v>14.299102476300332</v>
+      </c>
+      <c r="J37" s="2">
+        <v>15.329536208299432</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-36 EBITDA増加率（%）</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C38" s="2">
+        <v>2.5730180806675884</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2.3728813559322326</v>
+      </c>
+      <c r="E38" s="2">
+        <v>6.225165562913948</v>
+      </c>
+      <c r="F38" s="2">
+        <v>6.234413965087282</v>
+      </c>
+      <c r="G38" s="2">
+        <v>64.31924882629102</v>
+      </c>
+      <c r="H38" s="2">
+        <v>19.14285714285715</v>
+      </c>
+      <c r="I38" s="2">
+        <v>18.914868105515616</v>
+      </c>
+      <c r="J38" s="2">
+        <v>18.729518527854804</v>
       </c>
     </row>
   </sheetData>
@@ -2456,13 +3124,13 @@
         <v>48</v>
       </c>
       <c r="H15" s="2">
-        <v>49.92</v>
+        <v>50</v>
       </c>
       <c r="I15" s="2">
-        <v>51.92</v>
+        <v>52</v>
       </c>
       <c r="J15" s="2">
-        <v>53.99</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -2534,13 +3202,13 @@
         <v>0.09999999999999999</v>
       </c>
       <c r="H17" s="2">
-        <v>0.10697115384615384</v>
+        <v>0.10679999999999999</v>
       </c>
       <c r="I17" s="2">
-        <v>0.11440677966101695</v>
+        <v>0.11423076923076923</v>
       </c>
       <c r="J17" s="2">
-        <v>0.12243007964437859</v>
+        <v>0.12240740740740741</v>
       </c>
     </row>
     <row r="18">
@@ -2580,13 +3248,13 @@
         </is>
       </c>
       <c r="H18" s="2">
-        <v>6.971153846153855</v>
+        <v>6.800000000000006</v>
       </c>
       <c r="I18" s="2">
-        <v>6.95105694153495</v>
+        <v>6.957649092480556</v>
       </c>
       <c r="J18" s="2">
-        <v>7.012958503975364</v>
+        <v>7.157999750592348</v>
       </c>
     </row>
     <row r="19">
@@ -2714,13 +3382,13 @@
         <v>0.3</v>
       </c>
       <c r="H21" s="2">
-        <v>0.3541987673343605</v>
+        <v>0.3536538461538461</v>
       </c>
       <c r="I21" s="2">
-        <v>0.4182121661721067</v>
+        <v>0.41759259259259246</v>
       </c>
       <c r="J21" s="2">
-        <v>0.4934809787462047</v>
+        <v>0.4933928571428572</v>
       </c>
     </row>
     <row r="22">
@@ -3204,47 +3872,47 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.33 % / 補助 — / 他 24.33 %</t>
+          <t xml:space="preserve">全社 23.91 % / 補助 — / 他 23.91 %</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.33 % / 補助 — / 他 24.33 %</t>
+          <t xml:space="preserve">全社 24.09 % / 補助 — / 他 24.09 %</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.33 % / 補助 — / 他 24.33 %</t>
+          <t xml:space="preserve">全社 24.27 % / 補助 — / 他 24.27 %</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.17 % / 補助 — / 他 24.17 %</t>
+          <t xml:space="preserve">全社 24.13 % / 補助 — / 他 24.13 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.01 % / 補助 — / 他 24.01 %</t>
+          <t xml:space="preserve">全社 23.99 % / 補助 — / 他 23.99 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.42 % / 補助 26 % / 他 23.85 %</t>
+          <t xml:space="preserve">全社 24.41 % / 補助 26 % / 他 23.85 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.36 % / 補助 23.66 % / 他 23.24 %</t>
+          <t xml:space="preserve">全社 23.37 % / 補助 23.66 % / 他 23.25 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.3 % / 補助 21.61 % / 他 22.62 %</t>
+          <t xml:space="preserve">全社 22.33 % / 補助 21.61 % / 他 22.67 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.25 % / 補助 19.79 % / 他 22.01 %</t>
+          <t xml:space="preserve">全社 21.29 % / 補助 19.79 % / 他 22.08 %</t>
         </is>
       </c>
     </row>
@@ -3266,27 +3934,27 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.67 % / 補助 — / 他 7.67 %</t>
+          <t xml:space="preserve">全社 8.09 % / 補助 — / 他 8.09 %</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.67 % / 補助 — / 他 7.67 %</t>
+          <t xml:space="preserve">全社 7.91 % / 補助 — / 他 7.91 %</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.67 % / 補助 — / 他 7.67 %</t>
+          <t xml:space="preserve">全社 7.73 % / 補助 — / 他 7.73 %</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.99 % / 補助 — / 他 7.99 %</t>
+          <t xml:space="preserve">全社 8.04 % / 補助 — / 他 8.04 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.32 % / 補助 — / 他 8.32 %</t>
+          <t xml:space="preserve">全社 8.35 % / 補助 — / 他 8.35 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
@@ -3296,17 +3964,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.1 % / 補助 11.34 % / 他 9.59 %</t>
+          <t xml:space="preserve">全社 10.09 % / 補助 11.34 % / 他 9.58 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.44 % / 補助 13.4 % / 他 10.54 %</t>
+          <t xml:space="preserve">全社 11.42 % / 補助 13.4 % / 他 10.5 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.77 % / 補助 15.2 % / 他 11.48 %</t>
+          <t xml:space="preserve">全社 12.73 % / 補助 15.2 % / 他 11.42 %</t>
         </is>
       </c>
     </row>
@@ -3328,47 +3996,47 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 — / 他 10 %</t>
+          <t xml:space="preserve">全社 10.42 % / 補助 — / 他 10.42 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 — / 他 10 %</t>
+          <t xml:space="preserve">全社 10.24 % / 補助 — / 他 10.24 %</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 — / 他 10 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 — / 他 10.07 %</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.24 % / 補助 — / 他 10.24 %</t>
+          <t xml:space="preserve">全社 10.28 % / 補助 — / 他 10.28 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.48 % / 補助 — / 他 10.48 %</t>
+          <t xml:space="preserve">全社 10.5 % / 補助 — / 他 10.5 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 16.5 % / 他 10.72 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 16.5 % / 他 10.73 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.28 % / 補助 17.53 % / 他 11.55 %</t>
+          <t xml:space="preserve">全社 13.27 % / 補助 17.53 % / 他 11.53 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.33 % / 補助 18.52 % / 他 12.39 %</t>
+          <t xml:space="preserve">全社 14.3 % / 補助 18.52 % / 他 12.34 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.38 % / 補助 19.44 % / 他 13.23 %</t>
+          <t xml:space="preserve">全社 15.33 % / 補助 19.44 % / 他 13.16 %</t>
         </is>
       </c>
     </row>
@@ -3514,12 +4182,12 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.33 % / 補助 — / 他 9.33 %</t>
+          <t xml:space="preserve">全社 8.99 % / 補助 — / 他 8.99 %</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.33 % / 補助 — / 他 9.33 %</t>
+          <t xml:space="preserve">全社 9.16 % / 補助 — / 他 9.16 %</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -3638,12 +4306,12 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 — / 他 10 %</t>
+          <t xml:space="preserve">全社 9.65 % / 補助 — / 他 9.65 %</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 — / 他 10 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 — / 他 9.83 %</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -3700,19 +4368,19 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / 他 0.058 億円/人</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全社 0.06 億円/人 / 補助 — / 他 0.06 億円/人</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 0.061 億円/人 / 補助 — / 他 0.061 億円/人</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 — / 他 0.061 億円/人</t>
-        </is>
-      </c>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 — / 他 0.061 億円/人</t>
-        </is>
-      </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">全社 0.063 億円/人 / 補助 — / 他 0.063 億円/人</t>
@@ -3730,7 +4398,7 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.078 億円/人 / 補助 0.107 億円/人 / 他 0.072 億円/人</t>
+          <t xml:space="preserve">全社 0.077 億円/人 / 補助 0.107 億円/人 / 他 0.071 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
@@ -3829,42 +4497,42 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -0 % / 補助 — / 他 -0 %</t>
+          <t xml:space="preserve">全社 2.04 % / 補助 — / 他 2.04 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0 % / 補助 — / 他 0 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 — / 他 1.99 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.03 % / 補助 — / 他 4.03 %</t>
+          <t xml:space="preserve">全社 4.17 % / 補助 — / 他 4.17 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.99 % / 補助 — / 他 3.99 %</t>
+          <t xml:space="preserve">全社 3.69 % / 補助 — / 他 3.69 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.07 % / 補助 — / 他 4.01 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 — / 他 4.16 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.21 % / 補助 6.97 % / 他 4.47 %</t>
+          <t xml:space="preserve">全社 5.02 % / 補助 6.8 % / 他 4.28 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.24 % / 補助 6.95 % / 他 4.47 %</t>
+          <t xml:space="preserve">全社 5.46 % / 補助 6.96 % / 他 4.74 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.32 % / 補助 7.01 % / 他 4.52 %</t>
+          <t xml:space="preserve">全社 5.23 % / 補助 7.16 % / 他 4.37 %</t>
         </is>
       </c>
     </row>
@@ -3886,47 +4554,47 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50 % / 補助 — / 他 50 %</t>
+          <t xml:space="preserve">全社 48.09 % / 補助 — / 他 48.09 %</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50 % / 補助 — / 他 50 %</t>
+          <t xml:space="preserve">全社 48.96 % / 補助 — / 他 48.96 %</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50 % / 補助 — / 他 50 %</t>
+          <t xml:space="preserve">全社 49.83 % / 補助 — / 他 49.83 %</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.65 % / 補助 — / 他 49.65 %</t>
+          <t xml:space="preserve">全社 49.54 % / 補助 — / 他 49.54 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.3 % / 補助 — / 他 49.3 %</t>
+          <t xml:space="preserve">全社 49.24 % / 補助 — / 他 49.24 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 44.51 % / 補助 34 % / 他 48.96 %</t>
+          <t xml:space="preserve">全社 44.5 % / 補助 34 % / 他 48.94 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.87 % / 補助 30.78 % / 他 47.09 %</t>
+          <t xml:space="preserve">全社 41.89 % / 補助 30.78 % / 他 47.13 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.32 % / 補助 27.85 % / 他 45.34 %</t>
+          <t xml:space="preserve">全社 39.37 % / 補助 27.85 % / 他 45.43 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 36.89 % / 補助 25.23 % / 他 43.71 %</t>
+          <t xml:space="preserve">全社 36.96 % / 補助 25.23 % / 他 43.84 %</t>
         </is>
       </c>
     </row>
@@ -4010,19 +4678,19 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 0.651 億円/人 / 補助 — / 他 0.651 億円/人</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / 他 0.652 億円/人</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / 他 0.652 億円/人</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / 他 0.652 億円/人</t>
-        </is>
-      </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">全社 0.672 億円/人 / 補助 — / 他 0.672 億円/人</t>
@@ -4030,7 +4698,7 @@
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.692 億円/人 / 補助 — / 他 0.692 億円/人</t>
+          <t xml:space="preserve">全社 0.69 億円/人 / 補助 — / 他 0.69 億円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
@@ -4040,17 +4708,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.866 億円/人 / 補助 1.454 億円/人 / 他 0.744 億円/人</t>
+          <t xml:space="preserve">全社 0.864 億円/人 / 補助 1.452 億円/人 / 他 0.742 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.937 億円/人 / 補助 1.692 億円/人 / 他 0.777 億円/人</t>
+          <t xml:space="preserve">全社 0.937 億円/人 / 補助 1.689 億円/人 / 他 0.777 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.018 億円/人 / 補助 1.969 億円/人 / 他 0.811 億円/人</t>
+          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.968 億円/人 / 他 0.81 億円/人</t>
         </is>
       </c>
     </row>
@@ -4072,19 +4740,19 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 0.053 億円/人 / 補助 — / 他 0.053 億円/人</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全社 0.052 億円/人 / 補助 — / 他 0.052 億円/人</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 0.05 億円/人 / 補助 — / 他 0.05 億円/人</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 — / 他 0.05 億円/人</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 — / 他 0.05 億円/人</t>
-        </is>
-      </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">全社 0.054 億円/人 / 補助 — / 他 0.054 億円/人</t>
@@ -4107,12 +4775,12 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.107 億円/人 / 補助 0.227 億円/人 / 他 0.082 億円/人</t>
+          <t xml:space="preserve">全社 0.107 億円/人 / 補助 0.226 億円/人 / 他 0.082 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.299 億円/人 / 他 0.093 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.299 億円/人 / 他 0.093 億円/人</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4802,7 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 — / 他 0.127 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / 他 0.128 億円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -4174,7 +4842,7 @@
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.493 億円/人 / 他 0.187 億円/人</t>
+          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.493 億円/人 / 他 0.186 億円/人</t>
         </is>
       </c>
     </row>
@@ -4201,42 +4869,42 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.35 % / 補助 — / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.25 % / 補助 — / 他 4.25 %</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 % / 補助 — / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.07 % / 補助 — / 他 4.07 %</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1 % / 補助 — / 他 1 %</t>
+          <t xml:space="preserve">全社 0.87 % / 補助 — / 他 0.87 %</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1 % / 補助 — / 他 1 %</t>
+          <t xml:space="preserve">全社 1.29 % / 補助 — / 他 1.29 %</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.46 % / 補助 — / 他 1 %</t>
+          <t xml:space="preserve">全社 21.28 % / 補助 — / 他 0.85 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.92 % / 補助 4 % / 他 1.5 %</t>
+          <t xml:space="preserve">全社 2.11 % / 補助 4.17 % / 他 1.69 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.93 % / 補助 4.01 % / 他 1.5 %</t>
+          <t xml:space="preserve">全社 1.72 % / 補助 4 % / 他 1.24 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.94 % / 補助 3.99 % / 他 1.5 %</t>
+          <t xml:space="preserve">全社 2.03 % / 補助 3.85 % / 他 1.64 %</t>
         </is>
       </c>
     </row>
@@ -4263,42 +4931,42 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0 pt / 補助 — / 他 0 pt</t>
+          <t xml:space="preserve">全社 0.1 pt / 補助 — / 他 0.1 pt</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0 pt / 補助 — / 他 0 pt</t>
+          <t xml:space="preserve">全社 0.09 pt / 補助 — / 他 0.09 pt</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3 pt / 補助 — / 他 3 pt</t>
+          <t xml:space="preserve">全社 3.13 pt / 補助 — / 他 3.13 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3 pt / 補助 — / 他 3 pt</t>
+          <t xml:space="preserve">全社 2.71 pt / 補助 — / 他 2.71 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.52 pt / 補助 — / 他 3 pt</t>
+          <t xml:space="preserve">全社 19.71 pt / 補助 — / 他 3.15 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.01 pt / 補助 17 pt / 他 4.5 pt</t>
+          <t xml:space="preserve">全社 7.83 pt / 補助 16.83 pt / 他 4.31 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.4 pt / 補助 17 pt / 他 4.5 pt</t>
+          <t xml:space="preserve">全社 8.61 pt / 補助 17.01 pt / 他 4.75 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.81 pt / 補助 17 pt / 他 4.5 pt</t>
+          <t xml:space="preserve">全社 8.72 pt / 補助 17.14 pt / 他 4.36 pt</t>
         </is>
       </c>
     </row>
@@ -4506,17 +5174,17 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.36 倍</t>
+          <t xml:space="preserve">全社 0.35 倍</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.56 倍</t>
+          <t xml:space="preserve">全社 0.54 倍</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 倍</t>
+          <t xml:space="preserve">全社 0.66 倍</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
@@ -4568,27 +5236,27 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.29 倍 / 補助 — / 他 4.29 倍</t>
+          <t xml:space="preserve">全社 4.47 倍 / 補助 — / 他 4.47 倍</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.29 倍 / 補助 — / 他 4.29 倍</t>
+          <t xml:space="preserve">全社 4.39 倍 / 補助 — / 他 4.39 倍</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.29 倍 / 補助 — / 他 4.29 倍</t>
+          <t xml:space="preserve">全社 4.31 倍 / 補助 — / 他 4.31 倍</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.56 倍 / 補助 — / 他 4.56 倍</t>
+          <t xml:space="preserve">全社 4.58 倍 / 補助 — / 他 4.58 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.86 倍 / 補助 — / 他 4.86 倍</t>
+          <t xml:space="preserve">全社 4.87 倍 / 補助 — / 他 4.87 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
@@ -4598,17 +5266,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 倍 / 補助 2.83 倍 / 他 5.9 倍</t>
+          <t xml:space="preserve">全社 4.17 倍 / 補助 2.83 倍 / 他 5.89 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.97 倍 / 補助 3.62 倍 / 他 6.71 倍</t>
+          <t xml:space="preserve">全社 4.96 倍 / 補助 3.62 倍 / 他 6.69 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.91 倍 / 補助 4.59 倍 / 他 7.59 倍</t>
+          <t xml:space="preserve">全社 5.89 倍 / 補助 4.59 倍 / 他 7.55 倍</t>
         </is>
       </c>
     </row>
@@ -4940,27 +5608,27 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -7.67 pt</t>
+          <t xml:space="preserve">差 -8.09 pt</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -7.67 pt</t>
+          <t xml:space="preserve">差 -7.91 pt</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -7.67 pt</t>
+          <t xml:space="preserve">差 -7.73 pt</t>
         </is>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -7.99 pt</t>
+          <t xml:space="preserve">差 -8.04 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.32 pt</t>
+          <t xml:space="preserve">差 -8.35 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
@@ -4970,17 +5638,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.74 pt</t>
+          <t xml:space="preserve">差 1.76 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.86 pt</t>
+          <t xml:space="preserve">差 2.9 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.72 pt</t>
+          <t xml:space="preserve">差 3.79 pt</t>
         </is>
       </c>
     </row>
@@ -5002,19 +5670,19 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助 — / 他 0.651 億円/人</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">補助 — / 他 0.652 億円/人</t>
         </is>
       </c>
-      <c r="E36" s="0" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">補助 — / 他 0.652 億円/人</t>
         </is>
       </c>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 — / 他 0.652 億円/人</t>
-        </is>
-      </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">補助 — / 他 0.672 億円/人</t>
@@ -5022,7 +5690,7 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.692 億円/人</t>
+          <t xml:space="preserve">補助 — / 他 0.69 億円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
@@ -5032,17 +5700,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.454 億円/人 / 他 0.744 億円/人</t>
+          <t xml:space="preserve">補助 1.452 億円/人 / 他 0.742 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.692 億円/人 / 他 0.777 億円/人</t>
+          <t xml:space="preserve">補助 1.689 億円/人 / 他 0.777 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.969 億円/人 / 他 0.811 億円/人</t>
+          <t xml:space="preserve">補助 1.968 億円/人 / 他 0.81 億円/人</t>
         </is>
       </c>
     </row>
@@ -5064,19 +5732,19 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助 — / 他 0.058 億円/人</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助 — / 他 0.06 億円/人</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">補助 — / 他 0.061 億円/人</t>
         </is>
       </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 — / 他 0.061 億円/人</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 — / 他 0.061 億円/人</t>
-        </is>
-      </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">補助 — / 他 0.063 億円/人</t>
@@ -5094,7 +5762,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.072 億円/人</t>
+          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.071 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
@@ -5151,22 +5819,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 83.2 %</t>
+          <t xml:space="preserve">寄与率 83.59 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 52.41 %</t>
+          <t xml:space="preserve">寄与率 52.8 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 55.66 %</t>
+          <t xml:space="preserve">寄与率 56.1 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 58.61 %</t>
+          <t xml:space="preserve">寄与率 59.08 %</t>
         </is>
       </c>
     </row>
@@ -5176,13 +5844,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5198,10 +5867,15 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">制度上の必須条件</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">許容下限</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">許容上限</t>
         </is>
@@ -5220,10 +5894,15 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">制度上の必須条件</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">許容下限</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">許容上限</t>
         </is>
@@ -5240,10 +5919,15 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5258,10 +5942,15 @@
       <c r="B4" s="2">
         <v>21</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
         <v>-5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>40</v>
       </c>
     </row>
@@ -5274,10 +5963,15 @@
       <c r="B5" s="2">
         <v>7.000000000000001</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5290,10 +5984,15 @@
       <c r="B6" s="2">
         <v>7.000000000000001</v>
       </c>
-      <c r="C6" s="2">
-        <v>-5</v>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+        </is>
       </c>
       <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5306,10 +6005,15 @@
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
         <v>-3</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5322,10 +6026,15 @@
       <c r="B8" s="2">
         <v>1</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5338,10 +6047,15 @@
       <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5354,10 +6068,15 @@
       <c r="B10" s="2">
         <v>4</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
         <v>-10</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5370,10 +6089,15 @@
       <c r="B11" s="2">
         <v>0.5</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5386,10 +6110,15 @@
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
         <v>8</v>
       </c>
     </row>
@@ -5402,10 +6131,15 @@
       <c r="B13" s="2">
         <v>1</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
         <v>-5</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5418,10 +6152,15 @@
       <c r="B14" s="2">
         <v>0.5</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5434,10 +6173,15 @@
       <c r="B15" s="2">
         <v>21</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
         <v>-5</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>40</v>
       </c>
     </row>
@@ -5450,10 +6194,15 @@
       <c r="B16" s="2">
         <v>6</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
         <v>-10</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5466,10 +6215,15 @@
       <c r="B17" s="2">
         <v>0</v>
       </c>
-      <c r="C17" s="2">
-        <v>0</v>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5482,10 +6236,15 @@
       <c r="B18" s="2">
         <v>1</v>
       </c>
-      <c r="C18" s="2">
-        <v>0</v>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5498,10 +6257,15 @@
       <c r="B19" s="2">
         <v>7.000000000000001</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D19" s="2">
         <v>4.5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5514,10 +6278,15 @@
       <c r="B20" s="2">
         <v>4.5</v>
       </c>
-      <c r="C20" s="2">
-        <v>0</v>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
         <v>8</v>
       </c>
     </row>
@@ -5530,10 +6299,15 @@
       <c r="B21" s="2">
         <v>4</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D21" s="2">
         <v>-3</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5546,10 +6320,15 @@
       <c r="B22" s="2">
         <v>1.5</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D22" s="2">
         <v>-5</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5562,10 +6341,15 @@
       <c r="B23" s="2">
         <v>9</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D23" s="2">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="2">
         <v>25</v>
       </c>
     </row>
@@ -5578,10 +6362,15 @@
       <c r="B24" s="2">
         <v>10</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D24" s="2">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="2">
         <v>25</v>
       </c>
     </row>
@@ -5594,10 +6383,15 @@
       <c r="B25" s="2">
         <v>6</v>
       </c>
-      <c r="C25" s="2">
-        <v>0</v>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5612,10 +6406,15 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5632,10 +6431,15 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5650,11 +6454,20 @@
       <c r="B28" s="2">
         <v>15</v>
       </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>50</v>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5663,7 +6476,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -5723,11 +6536,11 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-11</t>
+          <t xml:space="preserve">actual:company:2023:2-10</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>12.88</v>
+        <v>0.09</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5738,11 +6551,11 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-12</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>3.22</v>
+        <v>11.78</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5753,11 +6566,11 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-13</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>93.84</v>
+        <v>0.62</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -5768,11 +6581,11 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-7</t>
+          <t xml:space="preserve">actual:company:2023:2-14</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>33.58</v>
+        <v>2.48</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -5783,11 +6596,11 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-8</t>
+          <t xml:space="preserve">actual:company:2023:2-15</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -5798,11 +6611,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-1</t>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>144</v>
+        <v>93.84</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -5813,11 +6626,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-11</t>
+          <t xml:space="preserve">actual:company:2023:2-4</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>13.44</v>
+        <v>0.74</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5828,11 +6641,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>3.36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -5843,11 +6656,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-9</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>97.92</v>
+        <v>0.83</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -5858,11 +6671,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>35.04</v>
+        <v>144</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -5873,11 +6686,11 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-8</t>
+          <t xml:space="preserve">actual:company:2024:2-10</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.96</v>
+        <v>0.1</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -5888,11 +6701,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-1</t>
+          <t xml:space="preserve">actual:company:2024:2-12</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>150</v>
+        <v>12.53</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -5903,11 +6716,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-11</t>
+          <t xml:space="preserve">actual:company:2024:2-13</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>0.66</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -5918,11 +6731,11 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-14</t>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -5933,11 +6746,11 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-15</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>102</v>
+        <v>0.67</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -5948,11 +6761,11 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>36.5</v>
+        <v>97.92</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -5963,11 +6776,11 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-8</t>
+          <t xml:space="preserve">actual:company:2024:2-4</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -5978,187 +6791,187 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-1</t>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0</v>
+        <v>34.69</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:company:2024:2-9</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-10</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-12</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-13</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:company:2025:2-15</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-4</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-9</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
         </is>
       </c>
       <c r="B33" s="2">
@@ -6173,7 +6986,7 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -6188,7 +7001,7 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B35" s="2">
@@ -6203,7 +7016,7 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-9</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -6218,7 +7031,7 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B37" s="2">
@@ -6233,7 +7046,7 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B38" s="2">
@@ -6248,7 +7061,7 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B39" s="2">
@@ -6263,7 +7076,7 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B40" s="2">
@@ -6278,7 +7091,7 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B41" s="2">
@@ -6293,7 +7106,7 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
         </is>
       </c>
       <c r="B42" s="2">
@@ -6308,7 +7121,7 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -6323,7 +7136,7 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
         </is>
       </c>
       <c r="B44" s="2">
@@ -6338,191 +7151,191 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -6533,11 +7346,11 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B58" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
@@ -6548,11 +7361,11 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
@@ -6563,11 +7376,11 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
@@ -6578,11 +7391,11 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
@@ -6593,11 +7406,11 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
@@ -6608,11 +7421,11 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
@@ -6623,11 +7436,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -6638,11 +7451,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -6653,11 +7466,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -6668,7 +7481,7 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -6683,11 +7496,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -6698,11 +7511,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -6713,11 +7526,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -6728,11 +7541,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -6743,11 +7556,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -6758,11 +7571,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -6773,11 +7586,11 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
@@ -6788,11 +7601,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -6803,11 +7616,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -6818,11 +7631,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -6833,11 +7646,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -6848,11 +7661,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -6863,11 +7676,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -6878,11 +7691,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -6893,11 +7706,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -6908,11 +7721,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -6923,11 +7736,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -6938,11 +7751,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -6953,7 +7766,7 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B86" s="2">
@@ -6968,11 +7781,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -6983,11 +7796,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -6998,11 +7811,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -7013,11 +7826,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -7028,11 +7841,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -7043,11 +7856,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -7058,11 +7871,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -7073,11 +7886,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -7088,11 +7901,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -7103,11 +7916,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -7118,11 +7931,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -7133,11 +7946,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -7148,11 +7961,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -7163,11 +7976,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -7178,11 +7991,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -7193,11 +8006,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -7208,11 +8021,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -7223,26 +8036,26 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -7253,26 +8066,26 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>0.03</v>
+        <v>32</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -7283,26 +8096,26 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>0.02</v>
+        <v>73</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -7313,11 +8126,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>-0.05</v>
+        <v>70</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -7328,11 +8141,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>0.1</v>
+        <v>11</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -7343,11 +8156,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>-0.05</v>
+        <v>7</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -7358,11 +8171,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>0.1</v>
+        <v>64</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -7373,26 +8186,26 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>0.08</v>
+        <v>200</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -7403,7 +8216,7 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B116" s="2">
@@ -7418,11 +8231,11 @@
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>0.08</v>
+        <v>100</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -7433,26 +8246,26 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -7463,26 +8276,26 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -7493,26 +8306,26 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -7523,11 +8336,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -7538,11 +8351,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -7553,7 +8366,7 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B126" s="2">
@@ -7568,11 +8381,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -7583,7 +8396,7 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B128" s="2">
@@ -7598,11 +8411,11 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -7613,11 +8426,11 @@
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -7628,7 +8441,7 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B131" s="2">
@@ -7643,11 +8456,11 @@
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -7658,7 +8471,7 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B133" s="2">
@@ -7673,26 +8486,26 @@
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
@@ -7703,26 +8516,26 @@
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -7733,7 +8546,7 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B138" s="2">
@@ -7748,11 +8561,11 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
@@ -7763,26 +8576,26 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -7793,11 +8606,11 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -7808,11 +8621,11 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -7823,11 +8636,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -7838,11 +8651,11 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -7853,7 +8666,7 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B146" s="2">
@@ -7868,11 +8681,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -7883,7 +8696,7 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B148" s="2">
@@ -7898,11 +8711,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -7913,26 +8726,26 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -7943,11 +8756,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>1</v>
+        <v>0.045</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -7958,11 +8771,11 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>50</v>
+        <v>0.1</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
@@ -7973,26 +8786,26 @@
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>20</v>
+        <v>0.1</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
@@ -8003,11 +8816,11 @@
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>45</v>
+        <v>-0.05</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8018,11 +8831,11 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>23</v>
+        <v>0.4</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
@@ -8033,11 +8846,11 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8048,11 +8861,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.005</v>
+        <v>0.4</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8063,26 +8876,26 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
@@ -8093,11 +8906,11 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8108,11 +8921,11 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
@@ -8123,11 +8936,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8138,11 +8951,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.04</v>
+        <v>50</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -8153,11 +8966,11 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.005</v>
+        <v>5</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8168,11 +8981,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -8183,26 +8996,26 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.07</v>
+        <v>23</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -8213,11 +9026,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8228,11 +9041,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -8243,11 +9056,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.05</v>
+        <v>0.015</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -8258,11 +9071,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -8273,11 +9086,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -8288,11 +9101,11 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -8303,11 +9116,11 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -8318,11 +9131,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -8333,11 +9146,11 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.21</v>
+        <v>0.005</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -8348,11 +9161,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -8363,26 +9176,26 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>15</v>
+        <v>0.07</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -8393,11 +9206,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>10</v>
+        <v>0.04</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -8408,11 +9221,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -8423,11 +9236,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>15</v>
+        <v>0.05</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -8438,11 +9251,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>15</v>
+        <v>0.06</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -8453,56 +9266,56 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>7</v>
+        <v>0.21</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -8513,11 +9326,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>3.5</v>
+        <v>0.21</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -8528,11 +9341,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>35</v>
+        <v>0.01</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -8543,11 +9356,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>21</v>
+        <v>0.09</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -8558,22 +9371,22 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B194" s="2">
@@ -8588,11 +9401,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -8603,26 +9416,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -8633,56 +9446,56 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -8693,11 +9506,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -8708,11 +9521,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -8723,11 +9536,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -8738,7 +9551,7 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B205" s="2">
@@ -8753,11 +9566,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -8768,11 +9581,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -8783,7 +9596,7 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B208" s="2">
@@ -8798,11 +9611,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -8813,11 +9626,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -8828,26 +9641,26 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -8858,13 +9671,193 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B213" s="2">
+        <v>40</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B214" s="2">
+        <v>23</v>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B215" s="2">
+        <v>10</v>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B216" s="2">
+        <v>6</v>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B217" s="2">
+        <v>0</v>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B218" s="2">
+        <v>35</v>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B219" s="2">
+        <v>22</v>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B220" s="2">
+        <v>0</v>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B221" s="2">
+        <v>95</v>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B222" s="2">
+        <v>70</v>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B223" s="2">
+        <v>0</v>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B224" s="2">
+        <v>350</v>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B213" s="2">
+      <c r="B225" s="2">
         <v>213</v>
       </c>
-      <c r="C213" s="0" t="inlineStr">
+      <c r="C225" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -8892,7 +9885,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjg4LCJvZmZpY2VyUGF5IjowLjkyLCJkZXByZWNpYXRpb24iOjMuMjIsIm90aGVyU2dhIjoxNi41NiwiaGVhZGNvdW50IjoyMTEuNiwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjQ0LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjAuOCwib2ZmaWNlckNvdW50Ijo1fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjV9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjE1fSx7InllYXIiOjIwMjcsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NDkuOTIsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTEuOTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTMuOTksIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMuNTgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi04IjowLjkyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTEiOjEyLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjMuMjIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzUuMDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi04IjowLjk2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTEiOjEzLjQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjMuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjUsImFjdHVhbDpjb21wYW55OjIwMjU6Mi04IjoxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTEiOjE0LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjMuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjE5LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyLjUzLCJlbXBsb3llZUJvbnVzIjowLjY2LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjg2LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC43Nywic2dhRGVwcmVjaWF0aW9uIjoyLjU5LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY3fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMy4zLCJlbXBsb3llZUJvbnVzIjowLjcsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuOSwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuOCwic2dhRGVwcmVjaWF0aW9uIjoyLjcsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuN319XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIsImN1cnJlbnRBc3NldHMiOjY3LCJjYXNoIjoyNCwiZml4ZWRBc3NldHMiOjY1LCJ0YW5naWJsZUFzc2V0cyI6NTMsImJ1aWxkaW5ncyI6MTksIm1hY2hpbmVyeSI6MjQsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo3LCJzb2Z0d2FyZSI6NSwibGlhYmlsaXRpZXMiOjc1LCJjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzYsImxvbmdUZXJtRGVidCI6MjksIm5ldEFzc2V0cyI6NTcsInNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiY2FwaXRhbCI6MTAsImNhcGV4Ijo1fSx7InllYXIiOjIwMjQsImFzc2V0cyI6MTQzLCJjdXJyZW50QXNzZXRzIjo3MiwiY2FzaCI6MjUsImZpeGVkQXNzZXRzIjo3MSwidGFuZ2libGVBc3NldHMiOjU4LCJidWlsZGluZ3MiOjIwLCJtYWNoaW5lcnkiOjI4LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OCwic29mdHdhcmUiOjYsImxpYWJpbGl0aWVzIjo3OSwiY3VycmVudExpYWJpbGl0aWVzIjo0MSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM4LCJsb25nVGVybURlYnQiOjMxLCJuZXRBc3NldHMiOjY0LCJzaGFyZWhvbGRlckVxdWl0eSI6NjEsImNhcGl0YWwiOjEwLCJjYXBleCI6OH0seyJ5ZWFyIjoyMDI1LCJhc3NldHMiOjE1NiwiY3VycmVudEFzc2V0cyI6NzgsImNhc2giOjI3LCJmaXhlZEFzc2V0cyI6NzgsInRhbmdpYmxlQXNzZXRzIjo2NCwiYnVpbGRpbmdzIjoyMiwibWFjaGluZXJ5IjozMiwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjksInNvZnR3YXJlIjo3LCJsaWFiaWxpdGllcyI6ODMsImN1cnJlbnRMaWFiaWxpdGllcyI6NDMsInNob3J0VGVybURlYnQiOjExLCJmaXhlZExpYWJpbGl0aWVzIjo0MCwibG9uZ1Rlcm1EZWJ0IjozMiwibmV0QXNzZXRzIjo3Mywic2hhcmVob2xkZXJFcXVpdHkiOjcwLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjEwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyNywidmFsdWUiOjE1fSx7InllYXIiOjIwMjgsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDksIm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjQ1LCJzdWJzaWR5IjoxNSwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyNjpwcm9qZWN0OjctMSI6MCwiMjAyNjpwcm9qZWN0OjctNCI6MCwiMjAyNjpwcm9qZWN0OjctNiI6MCwiMjAyNjpwcm9qZWN0OjctOCI6MCwiMjAyNjpwcm9qZWN0OjctOSI6MCwiMjAyNjpwcm9qZWN0OjctMTAiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OjctMTAiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo1LjQsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC4yMywiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjUwLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMS43NywiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi4xNiwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -1829,38 +1829,44 @@
           <t xml:space="preserve">2-18 経常利益（億円）</t>
         </is>
       </c>
-      <c r="B20" s="4">
-        <v>11.159999999999997</v>
-      </c>
-      <c r="C20" s="4">
-        <v>11.389999999999997</v>
-      </c>
-      <c r="D20" s="4">
-        <v>11.600000000000001</v>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="E20" s="4">
-        <v>12.540000000000006</v>
+        <v>12.54</v>
       </c>
       <c r="F20" s="4">
-        <v>13.540000000000006</v>
+        <v>13.54</v>
       </c>
       <c r="G20" s="4">
         <v>20</v>
       </c>
       <c r="H20" s="4">
-        <v>25.359999999999996</v>
+        <v>25.36</v>
       </c>
       <c r="I20" s="4">
-        <v>31.67000000000001</v>
+        <v>31.67</v>
       </c>
       <c r="J20" s="4">
-        <v>39.10000000000001</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-19 税引前当期純利益（モデル未対応）（億円）</t>
+          <t xml:space="preserve">2-19 税引前当期純利益（億円）</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -1878,41 +1884,29 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="E21" s="2">
+        <v>12.54</v>
+      </c>
+      <c r="F21" s="2">
+        <v>13.54</v>
+      </c>
+      <c r="G21" s="2">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2">
+        <v>25.36</v>
+      </c>
+      <c r="I21" s="2">
+        <v>31.67</v>
+      </c>
+      <c r="J21" s="2">
+        <v>39.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-20 当期純利益（モデル未対応）（億円）</t>
+          <t xml:space="preserve">2-20 当期純利益（億円）</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -1930,35 +1924,23 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="E22" s="2">
+        <v>8.78</v>
+      </c>
+      <c r="F22" s="2">
+        <v>9.48</v>
+      </c>
+      <c r="G22" s="2">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2">
+        <v>17.75</v>
+      </c>
+      <c r="I22" s="2">
+        <v>22.17</v>
+      </c>
+      <c r="J22" s="2">
+        <v>27.37</v>
       </c>
     </row>
     <row r="23">
@@ -6476,7 +6458,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -6611,11 +6593,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-18</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>93.84</v>
+        <v>10.88</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6626,11 +6608,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-4</t>
+          <t xml:space="preserve">actual:company:2023:2-19</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.74</v>
+        <v>10.88</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6641,11 +6623,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-7</t>
+          <t xml:space="preserve">actual:company:2023:2-20</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>33</v>
+        <v>7.62</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6656,11 +6638,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-9</t>
+          <t xml:space="preserve">actual:company:2023:2-27</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.83</v>
+        <v>212</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6671,11 +6653,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-1</t>
+          <t xml:space="preserve">actual:company:2023:2-28</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6686,11 +6668,11 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-10</t>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.1</v>
+        <v>93.84</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -6701,11 +6683,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-12</t>
+          <t xml:space="preserve">actual:company:2023:2-4</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>12.53</v>
+        <v>0.74</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6716,11 +6698,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-13</t>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0.66</v>
+        <v>33</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6731,11 +6713,11 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-9</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.59</v>
+        <v>0.83</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6746,11 +6728,11 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-15</t>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.67</v>
+        <v>144</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6761,11 +6743,11 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-10</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>97.92</v>
+        <v>0.1</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6776,11 +6758,11 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-4</t>
+          <t xml:space="preserve">actual:company:2024:2-12</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>0.77</v>
+        <v>12.53</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6791,11 +6773,11 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-13</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>34.69</v>
+        <v>0.66</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6806,11 +6788,11 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-9</t>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.86</v>
+        <v>2.59</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6821,11 +6803,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-1</t>
+          <t xml:space="preserve">actual:company:2024:2-15</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>150</v>
+        <v>0.67</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6836,11 +6818,11 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-10</t>
+          <t xml:space="preserve">actual:company:2024:2-18</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0.1</v>
+        <v>11.1</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6851,11 +6833,11 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-12</t>
+          <t xml:space="preserve">actual:company:2024:2-19</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6866,11 +6848,11 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-13</t>
+          <t xml:space="preserve">actual:company:2024:2-20</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0.7</v>
+        <v>7.77</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6881,11 +6863,11 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-14</t>
+          <t xml:space="preserve">actual:company:2024:2-27</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>2.7</v>
+        <v>221</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6896,11 +6878,11 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-15</t>
+          <t xml:space="preserve">actual:company:2024:2-28</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
@@ -6911,11 +6893,11 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>102</v>
+        <v>97.92</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6926,11 +6908,11 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-4</t>
+          <t xml:space="preserve">actual:company:2024:2-4</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6941,11 +6923,11 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>36.4</v>
+        <v>34.69</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6956,11 +6938,11 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-9</t>
+          <t xml:space="preserve">actual:company:2024:2-9</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6971,232 +6953,232 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-10</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-12</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-13</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-15</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-18</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:company:2025:2-19</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-20</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-27</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-28</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-4</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-9</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-9</t>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
         </is>
       </c>
       <c r="B48" s="2">
@@ -7211,7 +7193,7 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
         </is>
       </c>
       <c r="B49" s="2">
@@ -7226,7 +7208,7 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B50" s="2">
@@ -7241,7 +7223,7 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B51" s="2">
@@ -7256,7 +7238,7 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -7271,7 +7253,7 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B53" s="2">
@@ -7286,7 +7268,7 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B54" s="2">
@@ -7301,7 +7283,7 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B55" s="2">
@@ -7316,7 +7298,7 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -7331,236 +7313,236 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
         </is>
       </c>
       <c r="B58" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7571,11 +7553,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7586,7 +7568,7 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B74" s="2">
@@ -7601,11 +7583,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7616,11 +7598,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -7631,11 +7613,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -7646,11 +7628,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -7661,11 +7643,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -7676,11 +7658,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -7691,11 +7673,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -7706,11 +7688,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -7721,11 +7703,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -7736,11 +7718,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -7751,11 +7733,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -7766,11 +7748,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -7781,11 +7763,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -7796,11 +7778,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -7811,11 +7793,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -7826,11 +7808,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -7841,11 +7823,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -7856,11 +7838,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -7871,11 +7853,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -7886,11 +7868,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -7901,11 +7883,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -7916,11 +7898,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -7931,11 +7913,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -7946,11 +7928,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -7961,11 +7943,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -7976,11 +7958,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -7991,11 +7973,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8006,11 +7988,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8021,11 +8003,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8036,11 +8018,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8051,11 +8033,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8066,11 +8048,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8081,11 +8063,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8096,11 +8078,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8111,11 +8093,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8126,11 +8108,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8141,11 +8123,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8156,11 +8138,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8171,11 +8153,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8186,11 +8168,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8201,11 +8183,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8216,26 +8198,26 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8246,26 +8228,26 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0.03</v>
+        <v>9</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8276,26 +8258,26 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0.02</v>
+        <v>83</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8306,11 +8288,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>-0.05</v>
+        <v>32</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8321,11 +8303,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>0.1</v>
+        <v>32</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8336,11 +8318,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>-0.05</v>
+        <v>73</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8351,11 +8333,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0.1</v>
+        <v>70</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8366,26 +8348,26 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0.08</v>
+        <v>7</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8396,26 +8378,26 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0.08</v>
+        <v>15</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -8426,11 +8408,11 @@
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>-0.1</v>
+        <v>200</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8441,26 +8423,26 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>-0.1</v>
+        <v>100</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8471,56 +8453,56 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8531,11 +8513,11 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.25</v>
+        <v>-0.05</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8546,26 +8528,26 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
@@ -8576,41 +8558,41 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8621,26 +8603,26 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8651,11 +8633,11 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -8666,11 +8648,11 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8681,11 +8663,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -8696,56 +8678,56 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8756,11 +8738,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.045</v>
+        <v>0.25</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8771,56 +8753,56 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8831,11 +8813,11 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0.4</v>
+        <v>-0.03</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
@@ -8846,11 +8828,11 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8861,11 +8843,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.4</v>
+        <v>-0.03</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8876,26 +8858,26 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
@@ -8906,11 +8888,11 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8921,26 +8903,26 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8951,26 +8933,26 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8981,11 +8963,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>20</v>
+        <v>0.045</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -8996,11 +8978,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>45</v>
+        <v>0.1</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -9011,26 +8993,26 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -9041,11 +9023,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.005</v>
+        <v>-0.05</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9056,11 +9038,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.015</v>
+        <v>0.4</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -9071,11 +9053,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -9086,11 +9068,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.045</v>
+        <v>0.4</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9101,26 +9083,26 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9131,7 +9113,7 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B177" s="2">
@@ -9146,11 +9128,11 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.005</v>
+        <v>0.25</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9161,11 +9143,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9176,26 +9158,26 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.07</v>
+        <v>5</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9206,11 +9188,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.04</v>
+        <v>20</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9221,11 +9203,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.04</v>
+        <v>45</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9236,11 +9218,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.05</v>
+        <v>23</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9251,11 +9233,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9266,11 +9248,11 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.06</v>
+        <v>0.005</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9281,11 +9263,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.07</v>
+        <v>0.015</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9296,11 +9278,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.07</v>
+        <v>0.01</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9311,11 +9293,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.21</v>
+        <v>0.045</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9326,11 +9308,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9341,11 +9323,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9356,11 +9338,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9371,11 +9353,11 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>15</v>
+        <v>0.005</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9386,11 +9368,11 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9401,26 +9383,26 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>15</v>
+        <v>0.07</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9431,11 +9413,11 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9446,56 +9428,56 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>7</v>
+        <v>0.06</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9506,11 +9488,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>3.5</v>
+        <v>0.07</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9521,11 +9503,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>35</v>
+        <v>0.07</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9536,11 +9518,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>21</v>
+        <v>0.21</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9551,26 +9533,26 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>10</v>
+        <v>0.01</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9581,11 +9563,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>7</v>
+        <v>0.09</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9596,26 +9578,26 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9626,11 +9608,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9641,11 +9623,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9656,11 +9638,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9671,56 +9653,56 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9731,22 +9713,22 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B218" s="2">
@@ -9761,11 +9743,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9776,7 +9758,7 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B220" s="2">
@@ -9791,11 +9773,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -9806,11 +9788,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9821,7 +9803,7 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B223" s="2">
@@ -9836,11 +9818,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9851,13 +9833,238 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B225" s="2">
+        <v>30</v>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B226" s="2">
+        <v>35</v>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B227" s="2">
+        <v>21</v>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B228" s="2">
+        <v>40</v>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B229" s="2">
+        <v>23</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B230" s="2">
+        <v>10</v>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B231" s="2">
+        <v>6</v>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B232" s="2">
+        <v>0</v>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B233" s="2">
+        <v>35</v>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B234" s="2">
+        <v>22</v>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B235" s="2">
+        <v>0</v>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B236" s="2">
+        <v>95</v>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B237" s="2">
+        <v>70</v>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B238" s="2">
+        <v>0</v>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B239" s="2">
+        <v>350</v>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B225" s="2">
+      <c r="B240" s="2">
         <v>213</v>
       </c>
-      <c r="C225" s="0" t="inlineStr">
+      <c r="C240" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -9885,7 +10092,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTQ0LCJjb2dzIjo5Ny45MiwiZW1wbG95ZWVQYXkiOjEzLjE5LCJvZmZpY2VyUGF5IjowLjk2LCJkZXByZWNpYXRpb24iOjMuMzYsIm90aGVyU2dhIjoxNy4yOCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyLjUzLCJlbXBsb3llZUJvbnVzIjowLjY2LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjg2LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC43Nywic2dhRGVwcmVjaWF0aW9uIjoyLjU5LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY3fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMy4zLCJlbXBsb3llZUJvbnVzIjowLjcsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuOSwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuOCwic2dhRGVwcmVjaWF0aW9uIjoyLjcsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuN319XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIsImN1cnJlbnRBc3NldHMiOjY3LCJjYXNoIjoyNCwiZml4ZWRBc3NldHMiOjY1LCJ0YW5naWJsZUFzc2V0cyI6NTMsImJ1aWxkaW5ncyI6MTksIm1hY2hpbmVyeSI6MjQsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo3LCJzb2Z0d2FyZSI6NSwibGlhYmlsaXRpZXMiOjc1LCJjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzYsImxvbmdUZXJtRGVidCI6MjksIm5ldEFzc2V0cyI6NTcsInNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiY2FwaXRhbCI6MTAsImNhcGV4Ijo1fSx7InllYXIiOjIwMjQsImFzc2V0cyI6MTQzLCJjdXJyZW50QXNzZXRzIjo3MiwiY2FzaCI6MjUsImZpeGVkQXNzZXRzIjo3MSwidGFuZ2libGVBc3NldHMiOjU4LCJidWlsZGluZ3MiOjIwLCJtYWNoaW5lcnkiOjI4LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OCwic29mdHdhcmUiOjYsImxpYWJpbGl0aWVzIjo3OSwiY3VycmVudExpYWJpbGl0aWVzIjo0MSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM4LCJsb25nVGVybURlYnQiOjMxLCJuZXRBc3NldHMiOjY0LCJzaGFyZWhvbGRlckVxdWl0eSI6NjEsImNhcGl0YWwiOjEwLCJjYXBleCI6OH0seyJ5ZWFyIjoyMDI1LCJhc3NldHMiOjE1NiwiY3VycmVudEFzc2V0cyI6NzgsImNhc2giOjI3LCJmaXhlZEFzc2V0cyI6NzgsInRhbmdpYmxlQXNzZXRzIjo2NCwiYnVpbGRpbmdzIjoyMiwibWFjaGluZXJ5IjozMiwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjksInNvZnR3YXJlIjo3LCJsaWFiaWxpdGllcyI6ODMsImN1cnJlbnRMaWFiaWxpdGllcyI6NDMsInNob3J0VGVybURlYnQiOjExLCJmaXhlZExpYWJpbGl0aWVzIjo0MCwibG9uZ1Rlcm1EZWJ0IjozMiwibmV0QXNzZXRzIjo3Mywic2hhcmVob2xkZXJFcXVpdHkiOjcwLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjEwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyNywidmFsdWUiOjE1fSx7InllYXIiOjIwMjgsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDksIm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjQ1LCJzdWJzaWR5IjoxNSwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyNjpwcm9qZWN0OjctMSI6MCwiMjAyNjpwcm9qZWN0OjctNCI6MCwiMjAyNjpwcm9qZWN0OjctNiI6MCwiMjAyNjpwcm9qZWN0OjctOCI6MCwiMjAyNjpwcm9qZWN0OjctOSI6MCwiMjAyNjpwcm9qZWN0OjctMTAiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OjctMTAiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo1LjQsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC4yMywiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjUwLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMS43NywiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi4xNiwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuODgsInByZVRheEluY29tZSI6MTAuODgsIm5ldEluY29tZSI6Ny42Mn19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjEsInByZVRheEluY29tZSI6MTEuMSwibmV0SW5jb21lIjo3Ljc3fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMy4zLCJlbXBsb3llZUJvbnVzIjowLjcsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuOSwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuOCwic2dhRGVwcmVjaWF0aW9uIjoyLjcsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNywib3JkaW5hcnlJbmNvbWUiOjExLjMsInByZVRheEluY29tZSI6MTEuMywibmV0SW5jb21lIjo3LjkxfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjc4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjY5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNTMsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuNCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -1829,20 +1829,14 @@
           <t xml:space="preserve">2-18 経常利益（億円）</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="B20" s="4">
+        <v>10.67</v>
+      </c>
+      <c r="C20" s="4">
+        <v>11.14</v>
+      </c>
+      <c r="D20" s="4">
+        <v>11.600000000000003</v>
       </c>
       <c r="E20" s="4">
         <v>12.54</v>
@@ -1854,13 +1848,13 @@
         <v>20</v>
       </c>
       <c r="H20" s="4">
-        <v>25.36</v>
+        <v>25.359999999999996</v>
       </c>
       <c r="I20" s="4">
-        <v>31.67</v>
+        <v>31.66999999999999</v>
       </c>
       <c r="J20" s="4">
-        <v>39.1</v>
+        <v>39.10000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1869,20 +1863,14 @@
           <t xml:space="preserve">2-19 税引前当期純利益（億円）</t>
         </is>
       </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="B21" s="2">
+        <v>10.67</v>
+      </c>
+      <c r="C21" s="2">
+        <v>11.14</v>
+      </c>
+      <c r="D21" s="2">
+        <v>11.600000000000003</v>
       </c>
       <c r="E21" s="2">
         <v>12.54</v>
@@ -1894,13 +1882,13 @@
         <v>20</v>
       </c>
       <c r="H21" s="2">
-        <v>25.36</v>
+        <v>25.359999999999996</v>
       </c>
       <c r="I21" s="2">
-        <v>31.67</v>
+        <v>31.66999999999999</v>
       </c>
       <c r="J21" s="2">
-        <v>39.1</v>
+        <v>39.10000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1909,20 +1897,14 @@
           <t xml:space="preserve">2-20 当期純利益（億円）</t>
         </is>
       </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="B22" s="2">
+        <v>7.47</v>
+      </c>
+      <c r="C22" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="D22" s="2">
+        <v>8.120000000000001</v>
       </c>
       <c r="E22" s="2">
         <v>8.78</v>
@@ -1934,13 +1916,13 @@
         <v>14</v>
       </c>
       <c r="H22" s="2">
-        <v>17.75</v>
+        <v>17.750999999999998</v>
       </c>
       <c r="I22" s="2">
-        <v>22.17</v>
+        <v>22.168999999999993</v>
       </c>
       <c r="J22" s="2">
-        <v>27.37</v>
+        <v>27.372</v>
       </c>
     </row>
     <row r="23">
@@ -6597,7 +6579,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6612,7 +6594,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6627,7 +6609,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>7.62</v>
+        <v>7.47</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6822,7 +6804,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>11.1</v>
+        <v>11.14</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6837,7 +6819,7 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>11.1</v>
+        <v>11.14</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6852,7 +6834,7 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <v>7.77</v>
+        <v>7.8</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -7047,7 +7029,7 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -7062,7 +7044,7 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -7077,7 +7059,7 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <v>7.91</v>
+        <v>8.12</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -10092,7 +10074,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuODgsInByZVRheEluY29tZSI6MTAuODgsIm5ldEluY29tZSI6Ny42Mn19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjEsInByZVRheEluY29tZSI6MTEuMSwibmV0SW5jb21lIjo3Ljc3fX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE1MCwiY29ncyI6MTAyLCJlbXBsb3llZVBheSI6MTQsIm9mZmljZXJQYXkiOjEsImRlcHJlY2lhdGlvbiI6My41LCJvdGhlclNnYSI6MTgsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMy4zLCJlbXBsb3llZUJvbnVzIjowLjcsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuOSwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuOCwic2dhRGVwcmVjaWF0aW9uIjoyLjcsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNywib3JkaW5hcnlJbmNvbWUiOjExLjMsInByZVRheEluY29tZSI6MTEuMywibmV0SW5jb21lIjo3LjkxfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjc4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjg4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjY5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNTMsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuNCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6Ny40N319LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjcuOH19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjAsImNvZ3MiOjAsImVtcGxveWVlUGF5IjowLCJvZmZpY2VyUGF5IjowLCJkZXByZWNpYXRpb24iOjAsIm90aGVyU2dhIjowLCJoZWFkY291bnQiOjAsIm9mZmljZXJDb3VudCI6MH0sIm90aGVyIjp7InNhbGVzIjoxNTAsImNvZ3MiOjEwMiwiZW1wbG95ZWVQYXkiOjE0LCJvZmZpY2VyUGF5IjoxLCJkZXByZWNpYXRpb24iOjMuNSwib3RoZXJTZ2EiOjE4LCJoZWFkY291bnQiOjIzMCwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTMuMywiZW1wbG95ZWVCb251cyI6MC43LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjksIm9mZmljZXJCb251cyI6MC4xLCJjb2dzRGVwcmVjaWF0aW9uIjowLjgsInNnYURlcHJlY2lhdGlvbiI6Mi43LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjcsIm9yZGluYXJ5SW5jb21lIjoxMS42MDAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJuZXRJbmNvbWUiOjguMTIwMDAwMDAwMDAwMDAxfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjc4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNDcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjY5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNTMsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny44LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo4LjEyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjAsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJmdXR1cmUtY2FwZXg6MjAyNiI6MTUsImZ1dHVyZS1jYXBleDoyMDI3IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjgiOjE1LCJmdXR1cmUtY2FwZXg6MjAyOSI6MCwiZnV0dXJlLWNhcGV4OjIwMzAiOjAsImZ1dHVyZS1jYXBleDoyMDMxIjowLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjQsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5IjoxNSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -3650,47 +3650,47 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.35 % / 補助 — / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.35 % / 補助 — / ベース 4.35 %</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 % / 補助 — / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.17 % / 補助 — / ベース 4.17 %</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4 % / 補助 — / 他 4 %</t>
+          <t xml:space="preserve">全社 4 % / 補助 — / ベース 4 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4 % / 補助 — / 他 4 %</t>
+          <t xml:space="preserve">全社 4 % / 補助 — / ベース 4 %</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.98 % / 補助 — / 他 4 %</t>
+          <t xml:space="preserve">全社 40.98 % / 補助 — / ベース 4 %</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.93 % / 補助 21 % / 他 6 %</t>
+          <t xml:space="preserve">全社 9.93 % / 補助 21 % / ベース 6 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.33 % / 補助 21.01 % / 他 6 %</t>
+          <t xml:space="preserve">全社 10.33 % / 補助 21.01 % / ベース 6 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.75 % / 補助 20.99 % / 他 6 %</t>
+          <t xml:space="preserve">全社 10.75 % / 補助 20.99 % / ベース 6 %</t>
         </is>
       </c>
     </row>
@@ -3712,47 +3712,47 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 — / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 — / ベース 68 %</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 — / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 — / ベース 68 %</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 — / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 — / ベース 68 %</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.83 % / 補助 — / 他 67.83 %</t>
+          <t xml:space="preserve">全社 67.83 % / 補助 — / ベース 67.83 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.67 % / 補助 — / 他 67.67 %</t>
+          <t xml:space="preserve">全社 67.67 % / 補助 — / ベース 67.67 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.84 % / 補助 65 % / 他 67.5 %</t>
+          <t xml:space="preserve">全社 66.84 % / 補助 65 % / ベース 67.5 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.54 % / 補助 65 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 66.54 % / 補助 65 % / ベース 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.25 % / 補助 65 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 66.25 % / 補助 65 % / ベース 66.84 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.98 % / 補助 65 % / 他 66.5 %</t>
+          <t xml:space="preserve">全社 65.98 % / 補助 65 % / ベース 66.5 %</t>
         </is>
       </c>
     </row>
@@ -3774,47 +3774,47 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 — / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 — / ベース 32 %</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 — / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 — / ベース 32 %</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 — / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 — / ベース 32 %</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.17 % / 補助 — / 他 32.17 %</t>
+          <t xml:space="preserve">全社 32.17 % / 補助 — / ベース 32.17 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.33 % / 補助 — / 他 32.33 %</t>
+          <t xml:space="preserve">全社 32.33 % / 補助 — / ベース 32.33 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.16 % / 補助 35 % / 他 32.5 %</t>
+          <t xml:space="preserve">全社 33.16 % / 補助 35 % / ベース 32.5 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.46 % / 補助 35 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 33.46 % / 補助 35 % / ベース 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.75 % / 補助 35 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 33.75 % / 補助 35 % / ベース 33.16 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.02 % / 補助 35 % / 他 33.5 %</t>
+          <t xml:space="preserve">全社 34.02 % / 補助 35 % / ベース 33.5 %</t>
         </is>
       </c>
     </row>
@@ -3836,47 +3836,47 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.91 % / 補助 — / 他 23.91 %</t>
+          <t xml:space="preserve">全社 23.91 % / 補助 — / ベース 23.91 %</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.09 % / 補助 — / 他 24.09 %</t>
+          <t xml:space="preserve">全社 24.09 % / 補助 — / ベース 24.09 %</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.27 % / 補助 — / 他 24.27 %</t>
+          <t xml:space="preserve">全社 24.27 % / 補助 — / ベース 24.27 %</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.13 % / 補助 — / 他 24.13 %</t>
+          <t xml:space="preserve">全社 24.13 % / 補助 — / ベース 24.13 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.99 % / 補助 — / 他 23.99 %</t>
+          <t xml:space="preserve">全社 23.99 % / 補助 — / ベース 23.99 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.41 % / 補助 26 % / 他 23.85 %</t>
+          <t xml:space="preserve">全社 24.41 % / 補助 26 % / ベース 23.85 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.37 % / 補助 23.66 % / 他 23.25 %</t>
+          <t xml:space="preserve">全社 23.37 % / 補助 23.66 % / ベース 23.25 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.33 % / 補助 21.61 % / 他 22.67 %</t>
+          <t xml:space="preserve">全社 22.33 % / 補助 21.61 % / ベース 22.67 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.29 % / 補助 19.79 % / 他 22.08 %</t>
+          <t xml:space="preserve">全社 21.29 % / 補助 19.79 % / ベース 22.08 %</t>
         </is>
       </c>
     </row>
@@ -3898,47 +3898,47 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.09 % / 補助 — / 他 8.09 %</t>
+          <t xml:space="preserve">全社 8.09 % / 補助 — / ベース 8.09 %</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.91 % / 補助 — / 他 7.91 %</t>
+          <t xml:space="preserve">全社 7.91 % / 補助 — / ベース 7.91 %</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.73 % / 補助 — / 他 7.73 %</t>
+          <t xml:space="preserve">全社 7.73 % / 補助 — / ベース 7.73 %</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.04 % / 補助 — / 他 8.04 %</t>
+          <t xml:space="preserve">全社 8.04 % / 補助 — / ベース 8.04 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.35 % / 補助 — / 他 8.35 %</t>
+          <t xml:space="preserve">全社 8.35 % / 補助 — / ベース 8.35 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.74 % / 補助 9 % / 他 8.65 %</t>
+          <t xml:space="preserve">全社 8.74 % / 補助 9 % / ベース 8.65 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.09 % / 補助 11.34 % / 他 9.58 %</t>
+          <t xml:space="preserve">全社 10.09 % / 補助 11.34 % / ベース 9.58 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.42 % / 補助 13.4 % / 他 10.5 %</t>
+          <t xml:space="preserve">全社 11.42 % / 補助 13.4 % / ベース 10.5 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.73 % / 補助 15.2 % / 他 11.42 %</t>
+          <t xml:space="preserve">全社 12.73 % / 補助 15.2 % / ベース 11.42 %</t>
         </is>
       </c>
     </row>
@@ -3960,47 +3960,47 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.42 % / 補助 — / 他 10.42 %</t>
+          <t xml:space="preserve">全社 10.42 % / 補助 — / ベース 10.42 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.24 % / 補助 — / 他 10.24 %</t>
+          <t xml:space="preserve">全社 10.24 % / 補助 — / ベース 10.24 %</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 — / 他 10.07 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 — / ベース 10.07 %</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.28 % / 補助 — / 他 10.28 %</t>
+          <t xml:space="preserve">全社 10.28 % / 補助 — / ベース 10.28 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.5 % / 補助 — / 他 10.5 %</t>
+          <t xml:space="preserve">全社 10.5 % / 補助 — / ベース 10.5 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 16.5 % / 他 10.73 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 16.5 % / ベース 10.73 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.27 % / 補助 17.53 % / 他 11.53 %</t>
+          <t xml:space="preserve">全社 13.27 % / 補助 17.53 % / ベース 11.53 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.3 % / 補助 18.52 % / 他 12.34 %</t>
+          <t xml:space="preserve">全社 14.3 % / 補助 18.52 % / ベース 12.34 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.33 % / 補助 19.44 % / 他 13.16 %</t>
+          <t xml:space="preserve">全社 15.33 % / 補助 19.44 % / ベース 13.16 %</t>
         </is>
       </c>
     </row>
@@ -4022,47 +4022,47 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 — / 他 12 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 — / ベース 12 %</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 — / 他 12 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 — / ベース 12 %</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 — / 他 12 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 — / ベース 12 %</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.83 % / 補助 — / 他 11.83 %</t>
+          <t xml:space="preserve">全社 11.83 % / 補助 — / ベース 11.83 %</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.67 % / 補助 — / 他 11.67 %</t>
+          <t xml:space="preserve">全社 11.67 % / 補助 — / ベース 11.67 %</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.1 % / 補助 10 % / 他 11.5 %</t>
+          <t xml:space="preserve">全社 11.1 % / 補助 10 % / ベース 11.5 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.61 % / 補助 9.67 % / 他 11 %</t>
+          <t xml:space="preserve">全社 10.61 % / 補助 9.67 % / ベース 11 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.13 % / 補助 9.33 % / 他 10.5 %</t>
+          <t xml:space="preserve">全社 10.13 % / 補助 9.33 % / ベース 10.5 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.66 % / 補助 9 % / 他 10 %</t>
+          <t xml:space="preserve">全社 9.66 % / 補助 9 % / ベース 10 %</t>
         </is>
       </c>
     </row>
@@ -4146,47 +4146,47 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.99 % / 補助 — / 他 8.99 %</t>
+          <t xml:space="preserve">全社 8.99 % / 補助 — / ベース 8.99 %</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.16 % / 補助 — / 他 9.16 %</t>
+          <t xml:space="preserve">全社 9.16 % / 補助 — / ベース 9.16 %</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.33 % / 補助 — / 他 9.33 %</t>
+          <t xml:space="preserve">全社 9.33 % / 補助 — / ベース 9.33 %</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.43 % / 補助 — / 他 9.43 %</t>
+          <t xml:space="preserve">全社 9.43 % / 補助 — / ベース 9.43 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.52 % / 補助 — / 他 9.52 %</t>
+          <t xml:space="preserve">全社 9.52 % / 補助 — / ベース 9.52 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.19 % / 補助 8 % / 他 9.62 %</t>
+          <t xml:space="preserve">全社 9.19 % / 補助 8 % / ベース 9.62 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.97 % / 補助 7.36 % / 他 9.62 %</t>
+          <t xml:space="preserve">全社 8.97 % / 補助 7.36 % / ベース 9.62 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.72 % / 補助 6.76 % / 他 9.63 %</t>
+          <t xml:space="preserve">全社 8.72 % / 補助 6.76 % / ベース 9.63 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.45 % / 補助 6.22 % / 他 9.63 %</t>
+          <t xml:space="preserve">全社 8.45 % / 補助 6.22 % / ベース 9.63 %</t>
         </is>
       </c>
     </row>
@@ -4208,47 +4208,47 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 — / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 — / ベース 0.67 %</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 — / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 — / ベース 0.67 %</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 — / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 — / ベース 0.67 %</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 — / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 — / ベース 0.67 %</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 — / 他 0.67 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 — / ベース 0.67 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.62 % / 補助 0.5 % / 他 0.66 %</t>
+          <t xml:space="preserve">全社 0.62 % / 補助 0.5 % / ベース 0.66 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.6 % / 補助 0.44 % / 他 0.66 %</t>
+          <t xml:space="preserve">全社 0.6 % / 補助 0.44 % / ベース 0.66 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.57 % / 補助 0.39 % / 他 0.65 %</t>
+          <t xml:space="preserve">全社 0.57 % / 補助 0.39 % / ベース 0.65 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 % / 補助 0.34 % / 他 0.64 %</t>
+          <t xml:space="preserve">全社 0.53 % / 補助 0.34 % / ベース 0.64 %</t>
         </is>
       </c>
     </row>
@@ -4270,47 +4270,47 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.65 % / 補助 — / 他 9.65 %</t>
+          <t xml:space="preserve">全社 9.65 % / 補助 — / ベース 9.65 %</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.83 % / 補助 — / 他 9.83 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 — / ベース 9.83 %</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 — / 他 10 %</t>
+          <t xml:space="preserve">全社 10 % / 補助 — / ベース 10 %</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.1 % / 補助 — / 他 10.1 %</t>
+          <t xml:space="preserve">全社 10.1 % / 補助 — / ベース 10.1 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.19 % / 補助 — / 他 10.19 %</t>
+          <t xml:space="preserve">全社 10.19 % / 補助 — / ベース 10.19 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.82 % / 補助 8.5 % / 他 10.28 %</t>
+          <t xml:space="preserve">全社 9.82 % / 補助 8.5 % / ベース 10.28 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.56 % / 補助 7.8 % / 他 10.28 %</t>
+          <t xml:space="preserve">全社 9.56 % / 補助 7.8 % / ベース 10.28 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.29 % / 補助 7.15 % / 他 10.28 %</t>
+          <t xml:space="preserve">全社 9.29 % / 補助 7.15 % / ベース 10.28 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.99 % / 補助 6.56 % / 他 10.27 %</t>
+          <t xml:space="preserve">全社 8.99 % / 補助 6.56 % / ベース 10.27 %</t>
         </is>
       </c>
     </row>
@@ -4332,47 +4332,47 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / 他 0.058 億円/人</t>
+          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / ベース 0.058 億円/人</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.06 億円/人 / 補助 — / 他 0.06 億円/人</t>
+          <t xml:space="preserve">全社 0.06 億円/人 / 補助 — / ベース 0.06 億円/人</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 — / 他 0.061 億円/人</t>
+          <t xml:space="preserve">全社 0.061 億円/人 / 補助 — / ベース 0.061 億円/人</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 — / 他 0.063 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 — / ベース 0.063 億円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 — / 他 0.066 億円/人</t>
+          <t xml:space="preserve">全社 0.066 億円/人 / 補助 — / ベース 0.066 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.1 億円/人 / 他 0.068 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.1 億円/人 / ベース 0.068 億円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.077 億円/人 / 補助 0.107 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">全社 0.077 億円/人 / 補助 0.107 億円/人 / ベース 0.071 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.114 億円/人 / 他 0.075 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.114 億円/人 / ベース 0.075 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.086 億円/人 / 補助 0.122 億円/人 / 他 0.078 億円/人</t>
+          <t xml:space="preserve">全社 0.086 億円/人 / 補助 0.122 億円/人 / ベース 0.078 億円/人</t>
         </is>
       </c>
     </row>
@@ -4394,47 +4394,47 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.184 億円/人 / 補助 — / 他 0.184 億円/人</t>
+          <t xml:space="preserve">全社 0.184 億円/人 / 補助 — / ベース 0.184 億円/人</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.192 億円/人 / 補助 — / 他 0.192 億円/人</t>
+          <t xml:space="preserve">全社 0.192 億円/人 / 補助 — / ベース 0.192 億円/人</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 — / 他 0.2 億円/人</t>
+          <t xml:space="preserve">全社 0.2 億円/人 / 補助 — / ベース 0.2 億円/人</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.208 億円/人 / 補助 — / 他 0.208 億円/人</t>
+          <t xml:space="preserve">全社 0.208 億円/人 / 補助 — / ベース 0.208 億円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.216 億円/人 / 補助 — / 他 0.216 億円/人</t>
+          <t xml:space="preserve">全社 0.216 億円/人 / 補助 — / ベース 0.216 億円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.203 億円/人 / 補助 0.15 億円/人 / 他 0.224 億円/人</t>
+          <t xml:space="preserve">全社 0.203 億円/人 / 補助 0.15 億円/人 / ベース 0.224 億円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.214 億円/人 / 補助 0.16 億円/人 / 他 0.236 億円/人</t>
+          <t xml:space="preserve">全社 0.214 億円/人 / 補助 0.16 億円/人 / ベース 0.236 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.224 億円/人 / 補助 0.17 億円/人 / 他 0.246 億円/人</t>
+          <t xml:space="preserve">全社 0.224 億円/人 / 補助 0.17 億円/人 / ベース 0.246 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.234 億円/人 / 補助 0.18 億円/人 / 他 0.256 億円/人</t>
+          <t xml:space="preserve">全社 0.234 億円/人 / 補助 0.18 億円/人 / ベース 0.256 億円/人</t>
         </is>
       </c>
     </row>
@@ -4456,47 +4456,47 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.04 % / 補助 — / 他 2.04 %</t>
+          <t xml:space="preserve">全社 2.04 % / 補助 — / ベース 2.04 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.99 % / 補助 — / 他 1.99 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 — / ベース 1.99 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 % / 補助 — / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.17 % / 補助 — / ベース 4.17 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 % / 補助 — / 他 3.69 %</t>
+          <t xml:space="preserve">全社 3.69 % / 補助 — / ベース 3.69 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 — / 他 4.16 %</t>
+          <t xml:space="preserve">全社 12.24 % / 補助 — / ベース 4.16 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.02 % / 補助 6.8 % / 他 4.28 %</t>
+          <t xml:space="preserve">全社 5.02 % / 補助 6.8 % / ベース 4.28 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.46 % / 補助 6.96 % / 他 4.74 %</t>
+          <t xml:space="preserve">全社 5.46 % / 補助 6.96 % / ベース 4.74 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.23 % / 補助 7.16 % / 他 4.37 %</t>
+          <t xml:space="preserve">全社 5.23 % / 補助 7.16 % / ベース 4.37 %</t>
         </is>
       </c>
     </row>
@@ -4518,47 +4518,47 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.09 % / 補助 — / 他 48.09 %</t>
+          <t xml:space="preserve">全社 48.09 % / 補助 — / ベース 48.09 %</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.96 % / 補助 — / 他 48.96 %</t>
+          <t xml:space="preserve">全社 48.96 % / 補助 — / ベース 48.96 %</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.83 % / 補助 — / 他 49.83 %</t>
+          <t xml:space="preserve">全社 49.83 % / 補助 — / ベース 49.83 %</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.54 % / 補助 — / 他 49.54 %</t>
+          <t xml:space="preserve">全社 49.54 % / 補助 — / ベース 49.54 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.24 % / 補助 — / 他 49.24 %</t>
+          <t xml:space="preserve">全社 49.24 % / 補助 — / ベース 49.24 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 44.5 % / 補助 34 % / 他 48.94 %</t>
+          <t xml:space="preserve">全社 44.5 % / 補助 34 % / ベース 48.94 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.89 % / 補助 30.78 % / 他 47.13 %</t>
+          <t xml:space="preserve">全社 41.89 % / 補助 30.78 % / ベース 47.13 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.37 % / 補助 27.85 % / 他 45.43 %</t>
+          <t xml:space="preserve">全社 39.37 % / 補助 27.85 % / ベース 45.43 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 36.96 % / 補助 25.23 % / 他 43.84 %</t>
+          <t xml:space="preserve">全社 36.96 % / 補助 25.23 % / ベース 43.84 %</t>
         </is>
       </c>
     </row>
@@ -4642,47 +4642,47 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.651 億円/人 / 補助 — / 他 0.651 億円/人</t>
+          <t xml:space="preserve">全社 0.651 億円/人 / 補助 — / ベース 0.651 億円/人</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / 他 0.652 億円/人</t>
+          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / ベース 0.652 億円/人</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / 他 0.652 億円/人</t>
+          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / ベース 0.652 億円/人</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.672 億円/人 / 補助 — / 他 0.672 億円/人</t>
+          <t xml:space="preserve">全社 0.672 億円/人 / 補助 — / ベース 0.672 億円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.69 億円/人 / 補助 — / 他 0.69 億円/人</t>
+          <t xml:space="preserve">全社 0.69 億円/人 / 補助 — / ベース 0.69 億円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.803 億円/人 / 補助 1.25 億円/人 / 他 0.712 億円/人</t>
+          <t xml:space="preserve">全社 0.803 億円/人 / 補助 1.25 億円/人 / ベース 0.712 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.864 億円/人 / 補助 1.452 億円/人 / 他 0.742 億円/人</t>
+          <t xml:space="preserve">全社 0.864 億円/人 / 補助 1.452 億円/人 / ベース 0.742 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.937 億円/人 / 補助 1.689 億円/人 / 他 0.777 億円/人</t>
+          <t xml:space="preserve">全社 0.937 億円/人 / 補助 1.689 億円/人 / ベース 0.777 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.968 億円/人 / 他 0.81 億円/人</t>
+          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.968 億円/人 / ベース 0.81 億円/人</t>
         </is>
       </c>
     </row>
@@ -4704,47 +4704,47 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.053 億円/人 / 補助 — / 他 0.053 億円/人</t>
+          <t xml:space="preserve">全社 0.053 億円/人 / 補助 — / ベース 0.053 億円/人</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.052 億円/人 / 補助 — / 他 0.052 億円/人</t>
+          <t xml:space="preserve">全社 0.052 億円/人 / 補助 — / ベース 0.052 億円/人</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 — / 他 0.05 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 — / ベース 0.05 億円/人</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.054 億円/人 / 補助 — / 他 0.054 億円/人</t>
+          <t xml:space="preserve">全社 0.054 億円/人 / 補助 — / ベース 0.054 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / 他 0.058 億円/人</t>
+          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / ベース 0.058 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.112 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.112 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.165 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.165 億円/人 / ベース 0.071 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.107 億円/人 / 補助 0.226 億円/人 / 他 0.082 億円/人</t>
+          <t xml:space="preserve">全社 0.107 億円/人 / 補助 0.226 億円/人 / ベース 0.082 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.299 億円/人 / 他 0.093 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.299 億円/人 / ベース 0.093 億円/人</t>
         </is>
       </c>
     </row>
@@ -4766,47 +4766,47 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / 他 0.128 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / ベース 0.128 億円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / 他 0.128 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / ベース 0.128 億円/人</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / 他 0.128 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / ベース 0.128 億円/人</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.134 億円/人 / 補助 — / 他 0.134 億円/人</t>
+          <t xml:space="preserve">全社 0.134 億円/人 / 補助 — / ベース 0.134 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.14 億円/人 / 補助 — / 他 0.14 億円/人</t>
+          <t xml:space="preserve">全社 0.14 億円/人 / 補助 — / ベース 0.14 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.3 億円/人 / 他 0.146 億円/人</t>
+          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.3 億円/人 / ベース 0.146 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.193 億円/人 / 補助 0.354 億円/人 / 他 0.159 億円/人</t>
+          <t xml:space="preserve">全社 0.193 億円/人 / 補助 0.354 億円/人 / ベース 0.159 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.216 億円/人 / 補助 0.418 億円/人 / 他 0.172 億円/人</t>
+          <t xml:space="preserve">全社 0.216 億円/人 / 補助 0.418 億円/人 / ベース 0.172 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.493 億円/人 / 他 0.186 億円/人</t>
+          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.493 億円/人 / ベース 0.186 億円/人</t>
         </is>
       </c>
     </row>
@@ -4828,47 +4828,47 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.25 % / 補助 — / 他 4.25 %</t>
+          <t xml:space="preserve">全社 4.25 % / 補助 — / ベース 4.25 %</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.07 % / 補助 — / 他 4.07 %</t>
+          <t xml:space="preserve">全社 4.07 % / 補助 — / ベース 4.07 %</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.87 % / 補助 — / 他 0.87 %</t>
+          <t xml:space="preserve">全社 0.87 % / 補助 — / ベース 0.87 %</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.29 % / 補助 — / 他 1.29 %</t>
+          <t xml:space="preserve">全社 1.29 % / 補助 — / ベース 1.29 %</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.28 % / 補助 — / 他 0.85 %</t>
+          <t xml:space="preserve">全社 21.28 % / 補助 — / ベース 0.85 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.11 % / 補助 4.17 % / 他 1.69 %</t>
+          <t xml:space="preserve">全社 2.11 % / 補助 4.17 % / ベース 1.69 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.72 % / 補助 4 % / 他 1.24 %</t>
+          <t xml:space="preserve">全社 1.72 % / 補助 4 % / ベース 1.24 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.03 % / 補助 3.85 % / 他 1.64 %</t>
+          <t xml:space="preserve">全社 2.03 % / 補助 3.85 % / ベース 1.64 %</t>
         </is>
       </c>
     </row>
@@ -4890,47 +4890,47 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.1 pt / 補助 — / 他 0.1 pt</t>
+          <t xml:space="preserve">全社 0.1 pt / 補助 — / ベース 0.1 pt</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.09 pt / 補助 — / 他 0.09 pt</t>
+          <t xml:space="preserve">全社 0.09 pt / 補助 — / ベース 0.09 pt</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.13 pt / 補助 — / 他 3.13 pt</t>
+          <t xml:space="preserve">全社 3.13 pt / 補助 — / ベース 3.13 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 pt / 補助 — / 他 2.71 pt</t>
+          <t xml:space="preserve">全社 2.71 pt / 補助 — / ベース 2.71 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.71 pt / 補助 — / 他 3.15 pt</t>
+          <t xml:space="preserve">全社 19.71 pt / 補助 — / ベース 3.15 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.83 pt / 補助 16.83 pt / 他 4.31 pt</t>
+          <t xml:space="preserve">全社 7.83 pt / 補助 16.83 pt / ベース 4.31 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 pt / 補助 17.01 pt / 他 4.75 pt</t>
+          <t xml:space="preserve">全社 8.61 pt / 補助 17.01 pt / ベース 4.75 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.72 pt / 補助 17.14 pt / 他 4.36 pt</t>
+          <t xml:space="preserve">全社 8.72 pt / 補助 17.14 pt / ベース 4.36 pt</t>
         </is>
       </c>
     </row>
@@ -5014,47 +5014,47 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 — / 他 2.33 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 — / ベース 2.33 %</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 — / 他 2.33 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 — / ベース 2.33 %</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 — / 他 2.33 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 — / ベース 2.33 %</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.24 % / 補助 — / 他 2.24 %</t>
+          <t xml:space="preserve">全社 2.24 % / 補助 — / ベース 2.24 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.16 % / 補助 — / 他 2.16 %</t>
+          <t xml:space="preserve">全社 2.16 % / 補助 — / ベース 2.16 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.5 % / 補助 7.5 % / 他 2.07 %</t>
+          <t xml:space="preserve">全社 3.5 % / 補助 7.5 % / ベース 2.07 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.18 % / 補助 6.2 % / 他 1.96 %</t>
+          <t xml:space="preserve">全社 3.18 % / 補助 6.2 % / ベース 1.96 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.88 % / 補助 5.12 % / 他 1.85 %</t>
+          <t xml:space="preserve">全社 2.88 % / 補助 5.12 % / ベース 1.85 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.6 % / 補助 4.23 % / 他 1.74 %</t>
+          <t xml:space="preserve">全社 2.6 % / 補助 4.23 % / ベース 1.74 %</t>
         </is>
       </c>
     </row>
@@ -5200,47 +5200,47 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.47 倍 / 補助 — / 他 4.47 倍</t>
+          <t xml:space="preserve">全社 4.47 倍 / 補助 — / ベース 4.47 倍</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.39 倍 / 補助 — / 他 4.39 倍</t>
+          <t xml:space="preserve">全社 4.39 倍 / 補助 — / ベース 4.39 倍</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.31 倍 / 補助 — / 他 4.31 倍</t>
+          <t xml:space="preserve">全社 4.31 倍 / 補助 — / ベース 4.31 倍</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.58 倍 / 補助 — / 他 4.58 倍</t>
+          <t xml:space="preserve">全社 4.58 倍 / 補助 — / ベース 4.58 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 倍 / 補助 — / 他 4.87 倍</t>
+          <t xml:space="preserve">全社 4.87 倍 / 補助 — / ベース 4.87 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.5 倍 / 補助 2.2 倍 / 他 5.17 倍</t>
+          <t xml:space="preserve">全社 3.5 倍 / 補助 2.2 倍 / ベース 5.17 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 倍 / 補助 2.83 倍 / 他 5.89 倍</t>
+          <t xml:space="preserve">全社 4.17 倍 / 補助 2.83 倍 / ベース 5.89 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.96 倍 / 補助 3.62 倍 / 他 6.69 倍</t>
+          <t xml:space="preserve">全社 4.96 倍 / 補助 3.62 倍 / ベース 6.69 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.89 倍 / 補助 4.59 倍 / 他 7.55 倍</t>
+          <t xml:space="preserve">全社 5.89 倍 / 補助 4.59 倍 / ベース 7.55 倍</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. 補助事業とその他事業の比較</t>
+          <t xml:space="preserve">5. 補助事業とベース事業の比較</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
@@ -5448,47 +5448,47 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 —</t>
+          <t xml:space="preserve">補助 — / ベース —</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 4.35 %</t>
+          <t xml:space="preserve">補助 — / ベース 4.35 %</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 4.17 %</t>
+          <t xml:space="preserve">補助 — / ベース 4.17 %</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 4 %</t>
+          <t xml:space="preserve">補助 — / ベース 4 %</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 4 %</t>
+          <t xml:space="preserve">補助 — / ベース 4 %</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 4 %</t>
+          <t xml:space="preserve">補助 — / ベース 4 %</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 6 %</t>
+          <t xml:space="preserve">補助 21 % / ベース 6 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21.01 % / 他 6 %</t>
+          <t xml:space="preserve">補助 21.01 % / ベース 6 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 20.99 % / 他 6 %</t>
+          <t xml:space="preserve">補助 20.99 % / ベース 6 %</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業原価率－その他事業原価率</t>
+          <t xml:space="preserve">補助事業原価率－ベース事業原価率</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業営業利益率－その他事業営業利益率</t>
+          <t xml:space="preserve">補助事業営業利益率－ベース事業営業利益率</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -5634,47 +5634,47 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.651 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.651 億円/人</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.652 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.652 億円/人</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.652 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.652 億円/人</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.672 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.672 億円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.69 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.69 億円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.25 億円/人 / 他 0.712 億円/人</t>
+          <t xml:space="preserve">補助 1.25 億円/人 / ベース 0.712 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.452 億円/人 / 他 0.742 億円/人</t>
+          <t xml:space="preserve">補助 1.452 億円/人 / ベース 0.742 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.689 億円/人 / 他 0.777 億円/人</t>
+          <t xml:space="preserve">補助 1.689 億円/人 / ベース 0.777 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.968 億円/人 / 他 0.81 億円/人</t>
+          <t xml:space="preserve">補助 1.968 億円/人 / ベース 0.81 億円/人</t>
         </is>
       </c>
     </row>
@@ -5696,47 +5696,47 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.058 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.058 億円/人</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.06 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.06 億円/人</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.061 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.061 億円/人</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.063 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.063 億円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 0.066 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 0.066 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.1 億円/人 / 他 0.068 億円/人</t>
+          <t xml:space="preserve">補助 0.1 億円/人 / ベース 0.068 億円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.071 億円/人</t>
+          <t xml:space="preserve">補助 0.107 億円/人 / ベース 0.071 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.114 億円/人 / 他 0.075 億円/人</t>
+          <t xml:space="preserve">補助 0.114 億円/人 / ベース 0.075 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.122 億円/人 / 他 0.078 億円/人</t>
+          <t xml:space="preserve">補助 0.122 億円/人 / ベース 0.078 億円/人</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -6047,7 +6047,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -6068,7 +6068,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -6089,7 +6089,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -6110,7 +6110,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6152,7 +6152,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B16" s="2">
@@ -6194,7 +6194,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -6236,7 +6236,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -6278,7 +6278,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6320,7 +6320,7 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B24" s="2">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -5808,7 +5808,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5900,11 +5900,11 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率（売上実績が0の場合の開始水準）</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5912,20 +5912,20 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>40</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率（売上実績が0の場合の開始水準）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>7.000000000000001</v>
+        <v>68</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5936,38 +5936,38 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">実効税率</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>7.000000000000001</v>
+        <v>30</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -5975,20 +5975,20 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E7" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -6005,15 +6005,15 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>6</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D9" s="2">
@@ -6026,7 +6026,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D10" s="2">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="E10" s="2">
         <v>20</v>
@@ -6047,11 +6047,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6068,11 +6068,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6083,17 +6083,17 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="D13" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E13" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6131,11 +6131,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6143,20 +6143,20 @@
         </is>
       </c>
       <c r="D15" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6164,20 +6164,20 @@
         </is>
       </c>
       <c r="D16" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6185,20 +6185,20 @@
         </is>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6209,17 +6209,17 @@
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.000000000000001</v>
+        <v>21</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6227,20 +6227,20 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <v>4.5</v>
+        <v>-5</v>
       </c>
       <c r="E19" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6248,20 +6248,20 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E20" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6269,20 +6269,20 @@
         </is>
       </c>
       <c r="D21" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6290,20 +6290,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>9</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6311,20 +6311,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E23" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6332,20 +6332,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6356,79 +6356,184 @@
         <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D26" s="2">
+        <v>-3</v>
+      </c>
+      <c r="E26" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>45</v>
+        <v>1.5</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D27" s="2">
+        <v>-5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>9</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D28" s="2">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>10</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D29" s="2">
+        <v>4</v>
+      </c>
+      <c r="E29" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>6</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <v>45</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B28" s="2">
+      <c r="B33" s="2">
         <v>15</v>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6440,7 +6545,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C240"/>
+  <dimension ref="A1:C255"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8375,26 +8480,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>200</v>
+        <v>0.6</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8405,26 +8510,26 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8435,7 +8540,7 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B133" s="2">
@@ -8450,11 +8555,11 @@
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>0.03</v>
+        <v>100</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8465,7 +8570,7 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -8480,11 +8585,11 @@
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8495,26 +8600,26 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
@@ -8525,26 +8630,26 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8555,26 +8660,26 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8585,26 +8690,26 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8615,26 +8720,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8645,26 +8750,26 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8675,7 +8780,7 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B149" s="2">
@@ -8690,11 +8795,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -8705,26 +8810,26 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8735,26 +8840,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8765,26 +8870,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8795,26 +8900,26 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8825,11 +8930,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8840,11 +8945,11 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
@@ -8855,26 +8960,26 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8885,7 +8990,7 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -8900,11 +9005,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8915,7 +9020,7 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B165" s="2">
@@ -8930,11 +9035,11 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8945,11 +9050,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.045</v>
+        <v>-0.03</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -8960,11 +9065,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8975,26 +9080,26 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -9005,7 +9110,7 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B171" s="2">
@@ -9020,11 +9125,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -9035,26 +9140,26 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9065,7 +9170,7 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
@@ -9080,11 +9185,11 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9095,11 +9200,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9110,11 +9215,11 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9125,26 +9230,26 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>50</v>
+        <v>0.1</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9155,11 +9260,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>5</v>
+        <v>-0.05</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9170,11 +9275,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>20</v>
+        <v>0.4</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9185,11 +9290,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>45</v>
+        <v>-0.05</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9200,11 +9305,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>23</v>
+        <v>0.4</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9215,26 +9320,26 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9245,11 +9350,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9260,11 +9365,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9275,11 +9380,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.045</v>
+        <v>1</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9290,11 +9395,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.04</v>
+        <v>50</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9305,11 +9410,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.06</v>
+        <v>5</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9320,11 +9425,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.04</v>
+        <v>20</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9335,11 +9440,11 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9350,11 +9455,11 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>0.1</v>
+        <v>45</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9365,26 +9470,26 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.07</v>
+        <v>0.01</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9395,11 +9500,11 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9410,11 +9515,11 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9425,11 +9530,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.05</v>
+        <v>0.015</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9440,11 +9545,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9455,11 +9560,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9470,11 +9575,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9485,11 +9590,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.07</v>
+        <v>0.045</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9500,11 +9605,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9515,11 +9620,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9530,11 +9635,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9545,11 +9650,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.09</v>
+        <v>0.005</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9560,11 +9665,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>15</v>
+        <v>0.1</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9575,26 +9680,26 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>15</v>
+        <v>0.07</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9605,11 +9710,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>15</v>
+        <v>0.68</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9620,11 +9725,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9635,56 +9740,56 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>7</v>
+        <v>0.06</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9695,11 +9800,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>3.5</v>
+        <v>0.07</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9710,11 +9815,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>35</v>
+        <v>0.07</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9725,11 +9830,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>21</v>
+        <v>0.21</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9740,26 +9845,26 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>10</v>
+        <v>0.01</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -9770,11 +9875,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>7</v>
+        <v>0.09</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9785,26 +9890,26 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9815,11 +9920,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9830,11 +9935,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9845,11 +9950,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9860,56 +9965,56 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -9920,22 +10025,22 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B233" s="2">
@@ -9950,11 +10055,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -9965,7 +10070,7 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B235" s="2">
@@ -9980,11 +10085,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -9995,11 +10100,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10010,7 +10115,7 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B238" s="2">
@@ -10025,11 +10130,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10040,13 +10145,238 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B240" s="2">
+        <v>30</v>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B241" s="2">
+        <v>35</v>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B242" s="2">
+        <v>21</v>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B243" s="2">
+        <v>40</v>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B244" s="2">
+        <v>23</v>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B245" s="2">
+        <v>10</v>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B246" s="2">
+        <v>6</v>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B247" s="2">
+        <v>0</v>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B248" s="2">
+        <v>35</v>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B249" s="2">
+        <v>22</v>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B250" s="2">
+        <v>0</v>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B251" s="2">
+        <v>95</v>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B252" s="2">
+        <v>70</v>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B253" s="2">
+        <v>0</v>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B254" s="2">
+        <v>350</v>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B240" s="2">
+      <c r="B255" s="2">
         <v>213</v>
       </c>
-      <c r="C240" s="0" t="inlineStr">
+      <c r="C255" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -10074,7 +10404,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6Ny40N319LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjcuOH19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjAsImNvZ3MiOjAsImVtcGxveWVlUGF5IjowLCJvZmZpY2VyUGF5IjowLCJkZXByZWNpYXRpb24iOjAsIm90aGVyU2dhIjowLCJoZWFkY291bnQiOjAsIm9mZmljZXJDb3VudCI6MH0sIm90aGVyIjp7InNhbGVzIjoxNTAsImNvZ3MiOjEwMiwiZW1wbG95ZWVQYXkiOjE0LCJvZmZpY2VyUGF5IjoxLCJkZXByZWNpYXRpb24iOjMuNSwib3RoZXJTZ2EiOjE4LCJoZWFkY291bnQiOjIzMCwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTMuMywiZW1wbG95ZWVCb251cyI6MC43LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjksIm9mZmljZXJCb251cyI6MC4xLCJjb2dzRGVwcmVjaWF0aW9uIjowLjgsInNnYURlcHJlY2lhdGlvbiI6Mi43LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjcsIm9yZGluYXJ5SW5jb21lIjoxMS42MDAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJuZXRJbmNvbWUiOjguMTIwMDAwMDAwMDAwMDAxfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjUuNCwiMjAyODpwcm9qZWN0OjctOCI6NC44LCIyMDI4OnByb2plY3Q6Ny05IjowLjMsIjIwMjg6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjg6cHJvamVjdDo3LTEzIjo0OCwiMjAyODpwcm9qZWN0OjctMTQiOjIsIjIwMjk6cHJvamVjdDo3LTEiOjcyLjYsIjIwMjk6cHJvamVjdDo3LTQiOjI1LjQxLCIyMDI5OnByb2plY3Q6Ny02Ijo4LjIzLCIyMDI5OnByb2plY3Q6Ny04Ijo1LjM0LCIyMDI5OnByb2plY3Q6Ny05IjowLjMyLCIyMDI5OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Ny44NSwiMjAzMDpwcm9qZWN0OjctNCI6MzAuNzUsIjIwMzA6cHJvamVjdDo3LTYiOjExLjc3LCIyMDMwOnByb2plY3Q6Ny04Ijo1Ljk0LCIyMDMwOnByb2plY3Q6Ny05IjowLjM0LCIyMDMwOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMwOnByb2plY3Q6Ny0xMyI6NTIsIjIwMzA6cHJvamVjdDo3LTE0IjoyLCIyMDMxOnByb2plY3Q6Ny0xIjoxMDYuMjksIjIwMzE6cHJvamVjdDo3LTQiOjM3LjIsIjIwMzE6cHJvamVjdDo3LTYiOjE2LjE2LCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6Ny0xMCI6NC41LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjc4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNDcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjY5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNTMsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny44LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo4LjEyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjAsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJmdXR1cmUtY2FwZXg6MjAyNiI6MTUsImZ1dHVyZS1jYXBleDoyMDI3IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjgiOjE1LCJmdXR1cmUtY2FwZXg6MjAyOSI6MCwiZnV0dXJlLWNhcGV4OjIwMzAiOjAsImZ1dHVyZS1jYXBleDoyMDMxIjowLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjQsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5IjoxNSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6Ny40N319LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjcuOH19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjAsImNvZ3MiOjAsImVtcGxveWVlUGF5IjowLCJvZmZpY2VyUGF5IjowLCJkZXByZWNpYXRpb24iOjAsIm90aGVyU2dhIjowLCJoZWFkY291bnQiOjAsIm9mZmljZXJDb3VudCI6MH0sIm90aGVyIjp7InNhbGVzIjoxNTAsImNvZ3MiOjEwMiwiZW1wbG95ZWVQYXkiOjE0LCJvZmZpY2VyUGF5IjoxLCJkZXByZWNpYXRpb24iOjMuNSwib3RoZXJTZ2EiOjE4LCJoZWFkY291bnQiOjIzMCwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTMuMywiZW1wbG95ZWVCb251cyI6MC43LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjksIm9mZmljZXJCb251cyI6MC4xLCJjb2dzRGVwcmVjaWF0aW9uIjowLjgsInNnYURlcHJlY2lhdGlvbiI6Mi43LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjcsIm9yZGluYXJ5SW5jb21lIjoxMS42MDAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJuZXRJbmNvbWUiOjguMTIwMDAwMDAwMDAwMDAxfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjY6cHJvamVjdDo3LTEiOjAsIjIwMjY6cHJvamVjdDo3LTQiOjAsIjIwMjY6cHJvamVjdDo3LTYiOjAsIjIwMjY6cHJvamVjdDo3LTgiOjAsIjIwMjY6cHJvamVjdDo3LTkiOjAsIjIwMjY6cHJvamVjdDo3LTEwIjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDo3LTEwIjowLCIyMDI3OnByb2plY3Q6Ny0xMyI6MCwiMjAyNzpwcm9qZWN0OjctMTQiOjAsIjIwMjg6cHJvamVjdDo3LTEiOjYwLCIyMDI4OnByb2plY3Q6Ny00IjoyMSwiMjAyODpwcm9qZWN0OjctNiI6NS40LCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OjctMTAiOjQuNSwiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjguMjMsIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTEuNzcsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDo3LTEwIjo0LjUsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTYuMTYsIjIwMzE6cHJvamVjdDo3LTgiOjYuNjEsIjIwMzE6cHJvamVjdDo3LTkiOjAuMzYsIjIwMzE6cHJvamVjdDo3LTEwIjo0LjUsIjIwMzE6cHJvamVjdDo3LTEzIjo1NCwiMjAzMTpwcm9qZWN0OjctMTQiOjJ9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTMuODQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjc0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny40NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjguMTIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjQsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5IjoxNSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>18.038550488172866</v>
+        <v>16.782428588993525</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>12.630000000000003</v>
+        <v>12.400000000000002</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>84.20000000000002</v>
+        <v>82.66666666666667</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G6" s="2">
-        <v>0.8</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="H6" s="2">
-        <v>0.8</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="I6" s="2">
-        <v>0.8</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="J6" s="2">
-        <v>0.8</v>
+        <v>1.8299999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>37.64</v>
+        <v>37.63</v>
       </c>
       <c r="F9" s="2">
-        <v>38.92</v>
+        <v>38.91</v>
       </c>
       <c r="G9" s="2">
-        <v>55.84</v>
+        <v>55</v>
       </c>
       <c r="H9" s="2">
-        <v>58.769999999999996</v>
+        <v>58</v>
       </c>
       <c r="I9" s="2">
-        <v>61.95</v>
+        <v>61.25</v>
       </c>
       <c r="J9" s="2">
-        <v>65.42</v>
+        <v>64.78999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1539,16 +1539,16 @@
         <v>0.97</v>
       </c>
       <c r="G11" s="2">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="H11" s="2">
-        <v>1.3800000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="I11" s="2">
-        <v>1.4500000000000002</v>
+        <v>1.4200000000000002</v>
       </c>
       <c r="J11" s="2">
-        <v>1.5099999999999998</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="12">
@@ -1573,16 +1573,16 @@
         <v>0.11</v>
       </c>
       <c r="G12" s="2">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H12" s="2">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I12" s="2">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="J12" s="2">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="13">
@@ -1641,16 +1641,16 @@
         <v>14.68</v>
       </c>
       <c r="G14" s="2">
-        <v>20.22</v>
+        <v>19.98</v>
       </c>
       <c r="H14" s="2">
-        <v>21.69</v>
+        <v>21.42</v>
       </c>
       <c r="I14" s="2">
-        <v>23.28</v>
+        <v>22.98</v>
       </c>
       <c r="J14" s="2">
-        <v>25</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="15">
@@ -1675,16 +1675,16 @@
         <v>0.77</v>
       </c>
       <c r="G15" s="2">
-        <v>0.81</v>
+        <v>1.05</v>
       </c>
       <c r="H15" s="2">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="I15" s="2">
-        <v>0.91</v>
+        <v>1.21</v>
       </c>
       <c r="J15" s="2">
-        <v>0.97</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
@@ -1703,22 +1703,22 @@
         <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F16" s="2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G16" s="2">
-        <v>7.2</v>
+        <v>6.18</v>
       </c>
       <c r="H16" s="2">
-        <v>7.2</v>
+        <v>6.18</v>
       </c>
       <c r="I16" s="2">
-        <v>7.2</v>
+        <v>6.18</v>
       </c>
       <c r="J16" s="2">
-        <v>7.2</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="17">
@@ -1737,22 +1737,22 @@
         <v>0.7</v>
       </c>
       <c r="E17" s="2">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="F17" s="2">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="G17" s="2">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="H17" s="2">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="I17" s="2">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="J17" s="2">
-        <v>0.94</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="18">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>12.540000000000006</v>
+        <v>12.550000000000004</v>
       </c>
       <c r="F18" s="4">
-        <v>13.540000000000006</v>
+        <v>13.550000000000011</v>
       </c>
       <c r="G18" s="4">
-        <v>20</v>
+        <v>20.840000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>25.359999999999996</v>
+        <v>26.13</v>
       </c>
       <c r="I18" s="4">
-        <v>31.67000000000001</v>
+        <v>32.37000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>39.10000000000001</v>
+        <v>39.73000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>8.038461538461544</v>
+        <v>8.044871794871797</v>
       </c>
       <c r="F19" s="2">
-        <v>8.345660749506907</v>
+        <v>8.351824457593695</v>
       </c>
       <c r="G19" s="2">
-        <v>8.743933895859747</v>
+        <v>9.11117911948586</v>
       </c>
       <c r="H19" s="2">
-        <v>10.085504076357127</v>
+        <v>10.39172797772917</v>
       </c>
       <c r="I19" s="2">
-        <v>11.415492196229682</v>
+        <v>11.667808095735865</v>
       </c>
       <c r="J19" s="2">
-        <v>12.725793327908871</v>
+        <v>12.930838079739631</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.600000000000003</v>
       </c>
       <c r="E20" s="4">
-        <v>12.54</v>
+        <v>11.77</v>
       </c>
       <c r="F20" s="4">
-        <v>13.54</v>
+        <v>12.74</v>
       </c>
       <c r="G20" s="4">
         <v>20</v>
       </c>
       <c r="H20" s="4">
-        <v>25.359999999999996</v>
+        <v>25.240000000000002</v>
       </c>
       <c r="I20" s="4">
-        <v>31.66999999999999</v>
+        <v>31.419999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>39.10000000000001</v>
+        <v>38.730000000000004</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.600000000000003</v>
       </c>
       <c r="E21" s="2">
-        <v>12.54</v>
+        <v>11.77</v>
       </c>
       <c r="F21" s="2">
-        <v>13.54</v>
+        <v>12.74</v>
       </c>
       <c r="G21" s="2">
         <v>20</v>
       </c>
       <c r="H21" s="2">
-        <v>25.359999999999996</v>
+        <v>25.240000000000002</v>
       </c>
       <c r="I21" s="2">
-        <v>31.66999999999999</v>
+        <v>31.419999999999998</v>
       </c>
       <c r="J21" s="2">
-        <v>39.10000000000001</v>
+        <v>38.730000000000004</v>
       </c>
     </row>
     <row r="22">
@@ -1898,31 +1898,31 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>8.120000000000001</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>8.78</v>
+        <v>8.24</v>
       </c>
       <c r="F22" s="2">
-        <v>9.48</v>
+        <v>8.92</v>
       </c>
       <c r="G22" s="2">
         <v>14</v>
       </c>
       <c r="H22" s="2">
-        <v>17.750999999999998</v>
+        <v>17.67</v>
       </c>
       <c r="I22" s="2">
-        <v>22.168999999999993</v>
+        <v>21.990000000000002</v>
       </c>
       <c r="J22" s="2">
-        <v>27.372</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="23">
@@ -2043,22 +2043,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.790000000000006</v>
+        <v>31.800000000000004</v>
       </c>
       <c r="F26" s="4">
-        <v>33.57000000000001</v>
+        <v>33.58000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>50.45</v>
+        <v>51.290000000000006</v>
       </c>
       <c r="H26" s="4">
-        <v>57.41</v>
+        <v>58.18</v>
       </c>
       <c r="I26" s="4">
-        <v>65.43</v>
+        <v>66.13000000000002</v>
       </c>
       <c r="J26" s="4">
-        <v>74.71000000000001</v>
+        <v>75.34000000000002</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.152249134948116</v>
       </c>
       <c r="E27" s="2">
-        <v>5.614617940199351</v>
+        <v>5.6478405315614655</v>
       </c>
       <c r="F27" s="2">
-        <v>5.599245045611823</v>
+        <v>5.597484276729592</v>
       </c>
       <c r="G27" s="2">
-        <v>50.28299076556446</v>
+        <v>52.739726027397225</v>
       </c>
       <c r="H27" s="2">
-        <v>13.79583746283448</v>
+        <v>13.433417820237858</v>
       </c>
       <c r="I27" s="2">
-        <v>13.96969169134299</v>
+        <v>13.664489515297396</v>
       </c>
       <c r="J27" s="2">
-        <v>14.183096438942378</v>
+        <v>13.927113261757128</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.37820512820513</v>
+        <v>20.384615384615387</v>
       </c>
       <c r="F28" s="2">
-        <v>20.69156804733728</v>
+        <v>20.69773175542407</v>
       </c>
       <c r="G28" s="2">
-        <v>22.056573252306215</v>
+        <v>22.423818475932325</v>
       </c>
       <c r="H28" s="2">
-        <v>22.831576854245377</v>
+        <v>23.13780075561742</v>
       </c>
       <c r="I28" s="2">
-        <v>23.584327578127816</v>
+        <v>23.836643477634006</v>
       </c>
       <c r="J28" s="2">
-        <v>24.315703824247358</v>
+        <v>24.52074857607812</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.13413502109704645</v>
+        <v>0.13417721518987344</v>
       </c>
       <c r="F35" s="2">
-        <v>0.13987500000000003</v>
+        <v>0.13991666666666672</v>
       </c>
       <c r="G35" s="2">
-        <v>0.17277397260273974</v>
+        <v>0.17565068493150687</v>
       </c>
       <c r="H35" s="2">
-        <v>0.1926510067114094</v>
+        <v>0.19523489932885907</v>
       </c>
       <c r="I35" s="2">
-        <v>0.21594059405940597</v>
+        <v>0.21825082508250834</v>
       </c>
       <c r="J35" s="2">
-        <v>0.24177993527508093</v>
+        <v>0.24381877022653728</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>16.040000000000006</v>
+        <v>16.050000000000004</v>
       </c>
       <c r="F36" s="4">
-        <v>17.040000000000006</v>
+        <v>17.05000000000001</v>
       </c>
       <c r="G36" s="4">
-        <v>28</v>
+        <v>28.840000000000003</v>
       </c>
       <c r="H36" s="4">
-        <v>33.36</v>
+        <v>34.129999999999995</v>
       </c>
       <c r="I36" s="4">
-        <v>39.67000000000001</v>
+        <v>40.37000000000001</v>
       </c>
       <c r="J36" s="4">
-        <v>47.10000000000001</v>
+        <v>47.73000000000002</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.282051282051285</v>
+        <v>10.28846153846154</v>
       </c>
       <c r="F37" s="2">
-        <v>10.50295857988166</v>
+        <v>10.509122287968447</v>
       </c>
       <c r="G37" s="2">
-        <v>12.241507454203647</v>
+        <v>12.608752677829758</v>
       </c>
       <c r="H37" s="2">
-        <v>13.267051103599126</v>
+        <v>13.573275004971167</v>
       </c>
       <c r="I37" s="2">
-        <v>14.299102476300332</v>
+        <v>14.551418375806513</v>
       </c>
       <c r="J37" s="2">
-        <v>15.329536208299432</v>
+        <v>15.534580960130192</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>2.3728813559322326</v>
       </c>
       <c r="E38" s="2">
-        <v>6.225165562913948</v>
+        <v>6.291390728476842</v>
       </c>
       <c r="F38" s="2">
-        <v>6.234413965087282</v>
+        <v>6.230529595015621</v>
       </c>
       <c r="G38" s="2">
-        <v>64.31924882629102</v>
+        <v>69.14956011730196</v>
       </c>
       <c r="H38" s="2">
-        <v>19.14285714285715</v>
+        <v>18.342579750346722</v>
       </c>
       <c r="I38" s="2">
-        <v>18.914868105515616</v>
+        <v>18.283035452680974</v>
       </c>
       <c r="J38" s="2">
-        <v>18.729518527854804</v>
+        <v>18.231359920733237</v>
       </c>
     </row>
   </sheetData>
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>5.399999999999999</v>
+        <v>6.219999999999999</v>
       </c>
       <c r="H8" s="4">
-        <v>8.229999999999997</v>
+        <v>8.989999999999998</v>
       </c>
       <c r="I8" s="4">
-        <v>11.769999999999992</v>
+        <v>12.449999999999992</v>
       </c>
       <c r="J8" s="4">
-        <v>16.160000000000004</v>
+        <v>16.750000000000004</v>
       </c>
     </row>
     <row r="9">
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="G9" s="2">
-        <v>8.999999999999998</v>
+        <v>10.366666666666664</v>
       </c>
       <c r="H9" s="2">
-        <v>11.33608815426997</v>
+        <v>12.382920110192837</v>
       </c>
       <c r="I9" s="2">
-        <v>13.397837222538412</v>
+        <v>14.171883892999423</v>
       </c>
       <c r="J9" s="2">
-        <v>15.203688023332395</v>
+        <v>15.758773167748616</v>
       </c>
     </row>
     <row r="10">
@@ -3005,16 +3005,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <v>15</v>
+        <v>15.82</v>
       </c>
       <c r="H13" s="4">
-        <v>18.389999999999997</v>
+        <v>19.15</v>
       </c>
       <c r="I13" s="4">
-        <v>22.549999999999994</v>
+        <v>23.229999999999993</v>
       </c>
       <c r="J13" s="4">
-        <v>27.630000000000003</v>
+        <v>28.220000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -3054,13 +3054,13 @@
         </is>
       </c>
       <c r="H14" s="2">
-        <v>22.599999999999977</v>
+        <v>21.049304677623248</v>
       </c>
       <c r="I14" s="2">
-        <v>22.620989668297973</v>
+        <v>21.305483028720595</v>
       </c>
       <c r="J14" s="2">
-        <v>22.52771618625282</v>
+        <v>21.480843736547616</v>
       </c>
     </row>
     <row r="15">
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="G21" s="2">
-        <v>0.3</v>
+        <v>0.3164</v>
       </c>
       <c r="H21" s="2">
-        <v>0.3536538461538461</v>
+        <v>0.36826923076923074</v>
       </c>
       <c r="I21" s="2">
-        <v>0.41759259259259246</v>
+        <v>0.43018518518518506</v>
       </c>
       <c r="J21" s="2">
-        <v>0.4933928571428572</v>
+        <v>0.5039285714285715</v>
       </c>
     </row>
     <row r="22">
@@ -3851,32 +3851,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.13 % / 補助 — / ベース 24.13 %</t>
+          <t xml:space="preserve">全社 24.12 % / 補助 — / ベース 24.12 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.99 % / 補助 — / ベース 23.99 %</t>
+          <t xml:space="preserve">全社 23.98 % / 補助 — / ベース 23.98 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.41 % / 補助 26 % / ベース 23.85 %</t>
+          <t xml:space="preserve">全社 24.05 % / 補助 24.63 % / ベース 23.84 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.37 % / 補助 23.66 % / ベース 23.25 %</t>
+          <t xml:space="preserve">全社 23.07 % / 補助 22.62 % / ベース 23.25 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.33 % / 補助 21.61 % / ベース 22.67 %</t>
+          <t xml:space="preserve">全社 22.08 % / 補助 20.83 % / ベース 22.66 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.29 % / 補助 19.79 % / ベース 22.08 %</t>
+          <t xml:space="preserve">全社 21.09 % / 補助 19.24 % / ベース 22.06 %</t>
         </is>
       </c>
     </row>
@@ -3923,22 +3923,22 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.74 % / 補助 9 % / ベース 8.65 %</t>
+          <t xml:space="preserve">全社 9.11 % / 補助 10.37 % / ベース 8.66 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.09 % / 補助 11.34 % / ベース 9.58 %</t>
+          <t xml:space="preserve">全社 10.39 % / 補助 12.38 % / ベース 9.58 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.42 % / 補助 13.4 % / ベース 10.5 %</t>
+          <t xml:space="preserve">全社 11.67 % / 補助 14.17 % / ベース 10.51 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.73 % / 補助 15.2 % / ベース 11.42 %</t>
+          <t xml:space="preserve">全社 12.93 % / 補助 15.76 % / ベース 11.44 %</t>
         </is>
       </c>
     </row>
@@ -3975,32 +3975,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.28 % / 補助 — / ベース 10.28 %</t>
+          <t xml:space="preserve">全社 10.29 % / 補助 — / ベース 10.29 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.5 % / 補助 — / ベース 10.5 %</t>
+          <t xml:space="preserve">全社 10.51 % / 補助 — / ベース 10.51 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 16.5 % / ベース 10.73 %</t>
+          <t xml:space="preserve">全社 12.61 % / 補助 17.87 % / ベース 10.74 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.27 % / 補助 17.53 % / ベース 11.53 %</t>
+          <t xml:space="preserve">全社 13.57 % / 補助 18.58 % / ベース 11.54 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.3 % / 補助 18.52 % / ベース 12.34 %</t>
+          <t xml:space="preserve">全社 14.55 % / 補助 19.29 % / ベース 12.35 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.33 % / 補助 19.44 % / ベース 13.16 %</t>
+          <t xml:space="preserve">全社 15.53 % / 補助 19.99 % / ベース 13.18 %</t>
         </is>
       </c>
     </row>
@@ -4533,32 +4533,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.54 % / 補助 — / ベース 49.54 %</t>
+          <t xml:space="preserve">全社 49.53 % / 補助 — / ベース 49.53 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.24 % / 補助 — / ベース 49.24 %</t>
+          <t xml:space="preserve">全社 49.23 % / 補助 — / ベース 49.23 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 44.5 % / 補助 34 % / ベース 48.94 %</t>
+          <t xml:space="preserve">全社 43.77 % / 補助 32.24 % / ベース 48.91 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.89 % / 補助 30.78 % / ベース 47.13 %</t>
+          <t xml:space="preserve">全社 41.34 % / 補助 29.56 % / ベース 47.12 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.37 % / 補助 27.85 % / ベース 45.43 %</t>
+          <t xml:space="preserve">全社 38.95 % / 補助 27.03 % / ベース 45.41 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 36.96 % / 補助 25.23 % / ベース 43.84 %</t>
+          <t xml:space="preserve">全社 36.65 % / 補助 24.7 % / ベース 43.8 %</t>
         </is>
       </c>
     </row>
@@ -4729,22 +4729,22 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.112 億円/人 / ベース 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.073 億円/人 / 補助 0.13 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.165 億円/人 / ベース 0.071 億円/人</t>
+          <t xml:space="preserve">全社 0.09 億円/人 / 補助 0.18 億円/人 / ベース 0.071 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.107 億円/人 / 補助 0.226 億円/人 / ベース 0.082 億円/人</t>
+          <t xml:space="preserve">全社 0.109 億円/人 / 補助 0.239 億円/人 / ベース 0.082 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.299 億円/人 / ベース 0.093 億円/人</t>
+          <t xml:space="preserve">全社 0.132 億円/人 / 補助 0.31 億円/人 / ベース 0.093 億円/人</t>
         </is>
       </c>
     </row>
@@ -4791,22 +4791,22 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.3 億円/人 / ベース 0.146 億円/人</t>
+          <t xml:space="preserve">全社 0.176 億円/人 / 補助 0.316 億円/人 / ベース 0.147 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.193 億円/人 / 補助 0.354 億円/人 / ベース 0.159 億円/人</t>
+          <t xml:space="preserve">全社 0.195 億円/人 / 補助 0.368 億円/人 / ベース 0.159 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.216 億円/人 / 補助 0.418 億円/人 / ベース 0.172 億円/人</t>
+          <t xml:space="preserve">全社 0.218 億円/人 / 補助 0.43 億円/人 / ベース 0.172 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.493 億円/人 / ベース 0.186 億円/人</t>
+          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.504 億円/人 / ベース 0.186 億円/人</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.94 倍</t>
+          <t xml:space="preserve">全社 0.93 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.54 倍</t>
+          <t xml:space="preserve">全社 0.52 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.58 倍 / 補助 — / ベース 4.58 倍</t>
+          <t xml:space="preserve">全社 4.59 倍 / 補助 — / ベース 4.59 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -5225,22 +5225,22 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.5 倍 / 補助 2.2 倍 / ベース 5.17 倍</t>
+          <t xml:space="preserve">全社 3.61 倍 / 補助 2.38 倍 / ベース 5.18 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 倍 / 補助 2.83 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 4.27 倍 / 補助 3 倍 / ベース 5.9 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.96 倍 / 補助 3.62 倍 / ベース 6.69 倍</t>
+          <t xml:space="preserve">全社 5.05 倍 / 補助 3.77 倍 / ベース 6.69 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.89 倍 / 補助 4.59 倍 / ベース 7.55 倍</t>
+          <t xml:space="preserve">全社 5.97 倍 / 補助 4.72 倍 / ベース 7.57 倍</t>
         </is>
       </c>
     </row>
@@ -5597,22 +5597,22 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.35 pt</t>
+          <t xml:space="preserve">差 1.7 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.76 pt</t>
+          <t xml:space="preserve">差 2.8 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.9 pt</t>
+          <t xml:space="preserve">差 3.66 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.79 pt</t>
+          <t xml:space="preserve">差 4.32 pt</t>
         </is>
       </c>
     </row>
@@ -5783,22 +5783,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 83.59 %</t>
+          <t xml:space="preserve">寄与率 85.32 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 52.8 %</t>
+          <t xml:space="preserve">寄与率 52.36 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 56.1 %</t>
+          <t xml:space="preserve">寄与率 55.45 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 59.08 %</t>
+          <t xml:space="preserve">寄与率 58.42 %</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5911,11 +5911,15 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>99</v>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5932,290 +5936,346 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>99</v>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率</t>
+          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>60</v>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D7" s="2">
-        <v>-5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>40</v>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>7.000000000000001</v>
+        <v>90</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2</v>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>7.000000000000001</v>
+        <v>90</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>10</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 減価償却費のうち売上原価に含める割合</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D10" s="2">
-        <v>-3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>20</v>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 減価償却費のうち売上原価に含める割合</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2</v>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>10</v>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <v>-10</v>
-      </c>
-      <c r="E13" s="2">
-        <v>20</v>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2</v>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>-0.5</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>8</v>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>8</v>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>-5</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -6236,11 +6296,11 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>6</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6248,41 +6308,41 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6290,20 +6350,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E22" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>7.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6311,20 +6371,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6335,17 +6395,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6353,20 +6413,20 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E25" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6374,20 +6434,20 @@
         </is>
       </c>
       <c r="D26" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6395,62 +6455,66 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="2">
-        <v>4</v>
-      </c>
-      <c r="E28" s="2">
-        <v>25</v>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D29" s="2">
+        <v>-5</v>
+      </c>
+      <c r="E29" s="2">
         <v>10</v>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D29" s="2">
-        <v>4</v>
-      </c>
-      <c r="E29" s="2">
-        <v>25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6461,79 +6525,335 @@
         <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D31" s="2">
+        <v>-5</v>
+      </c>
+      <c r="E31" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D32" s="2">
+        <v>-10</v>
+      </c>
+      <c r="E32" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <v>1</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+        </is>
+      </c>
+      <c r="B38" s="2">
+        <v>4</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
+        <v>-3</v>
+      </c>
+      <c r="E38" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D39" s="2">
+        <v>-5</v>
+      </c>
+      <c r="E39" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B40" s="2">
+        <v>9</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B41" s="2">
+        <v>10</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>6</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>10</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>45</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B33" s="2">
+      <c r="B45" s="2">
         <v>15</v>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
         </is>
       </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6545,7 +6865,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C255"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -6714,11 +7034,11 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -6939,11 +7259,11 @@
         </is>
       </c>
       <c r="B26" s="2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -7164,11 +7484,11 @@
         </is>
       </c>
       <c r="B41" s="2">
-        <v>8.12</v>
+        <v>0</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8890,7 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -8585,11 +8905,11 @@
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8600,7 +8920,7 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B137" s="2">
@@ -8615,11 +8935,11 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
@@ -8630,7 +8950,7 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
@@ -8645,11 +8965,11 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.99</v>
+        <v>0.02</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8660,26 +8980,26 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8690,26 +9010,26 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8720,26 +9040,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8750,26 +9070,26 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8780,26 +9100,26 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -8810,26 +9130,26 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8840,26 +9160,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8870,26 +9190,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8900,7 +9220,7 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -8915,11 +9235,11 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8930,26 +9250,26 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
@@ -8960,7 +9280,7 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B161" s="2">
@@ -8975,11 +9295,11 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8990,7 +9310,7 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -9005,11 +9325,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -9020,26 +9340,26 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -9050,11 +9370,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -9065,7 +9385,7 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B168" s="2">
@@ -9080,26 +9400,26 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -9110,11 +9430,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9125,11 +9445,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -9140,7 +9460,7 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B173" s="2">
@@ -9155,11 +9475,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9170,7 +9490,7 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
@@ -9185,11 +9505,11 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9200,26 +9520,26 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9230,7 +9550,7 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B179" s="2">
@@ -9245,11 +9565,11 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9260,26 +9580,26 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9290,11 +9610,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>-0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9305,11 +9625,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9320,26 +9640,26 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9350,11 +9670,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9365,11 +9685,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9380,11 +9700,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>1</v>
+        <v>-0.05</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9395,11 +9715,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9410,11 +9730,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9425,11 +9745,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9440,26 +9760,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9470,26 +9790,26 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9500,26 +9820,26 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.68</v>
+        <v>0.1</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9530,11 +9850,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.015</v>
+        <v>0.045</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9545,11 +9865,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9560,26 +9880,26 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9590,26 +9910,26 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9620,11 +9940,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9635,11 +9955,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9650,11 +9970,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.005</v>
+        <v>-0.05</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9665,11 +9985,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9680,7 +10000,7 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B209" s="2">
@@ -9695,11 +10015,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9710,11 +10030,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.68</v>
+        <v>0.04</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9725,11 +10045,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9740,11 +10060,11 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -9755,11 +10075,11 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -9770,11 +10090,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.06</v>
+        <v>5</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -9785,11 +10105,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>0.06</v>
+        <v>20</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9800,11 +10120,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.07</v>
+        <v>0.3</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9815,11 +10135,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>0.07</v>
+        <v>45</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9830,11 +10150,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>0.21</v>
+        <v>23</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9845,11 +10165,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9860,7 +10180,7 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B221" s="2">
@@ -9875,11 +10195,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.09</v>
+        <v>0.005</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9890,11 +10210,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>15</v>
+        <v>0.68</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9905,11 +10225,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>10</v>
+        <v>0.95</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9920,26 +10240,26 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>15</v>
+        <v>0.015</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9950,11 +10270,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>15</v>
+        <v>0.01</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9965,56 +10285,56 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>7</v>
+        <v>0.04</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10025,11 +10345,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>3.5</v>
+        <v>0.045</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10040,11 +10360,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>35</v>
+        <v>0.04</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10055,11 +10375,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>21</v>
+        <v>0.004</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10070,26 +10390,26 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>10</v>
+        <v>0.04</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10100,11 +10420,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>7</v>
+        <v>0.005</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10115,26 +10435,26 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>70</v>
+        <v>0.25</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10145,26 +10465,26 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>35</v>
+        <v>0.07</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10175,11 +10495,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>21</v>
+        <v>0.68</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10190,11 +10510,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>40</v>
+        <v>0.95</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10205,26 +10525,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>10</v>
+        <v>0.04</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10235,11 +10555,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>6</v>
+        <v>0.04</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10250,41 +10570,41 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>22</v>
+        <v>0.9</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
@@ -10295,26 +10615,26 @@
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>95</v>
+        <v>0.06</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
@@ -10325,11 +10645,11 @@
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>70</v>
+        <v>0.07</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10340,26 +10660,26 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>350</v>
+        <v>0.005</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10370,13 +10690,553 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
+        </is>
+      </c>
+      <c r="B255" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B256" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B257" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+        </is>
+      </c>
+      <c r="B258" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:subsidy</t>
+        </is>
+      </c>
+      <c r="B259" s="2">
+        <v>15</v>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:usefulLife</t>
+        </is>
+      </c>
+      <c r="B260" s="2">
+        <v>10</v>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2026</t>
+        </is>
+      </c>
+      <c r="B261" s="2">
+        <v>15</v>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2027</t>
+        </is>
+      </c>
+      <c r="B262" s="2">
+        <v>15</v>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2028</t>
+        </is>
+      </c>
+      <c r="B263" s="2">
+        <v>15</v>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2029</t>
+        </is>
+      </c>
+      <c r="B264" s="2">
+        <v>0</v>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2030</t>
+        </is>
+      </c>
+      <c r="B265" s="2">
+        <v>0</v>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2031</t>
+        </is>
+      </c>
+      <c r="B266" s="2">
+        <v>0</v>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
+        </is>
+      </c>
+      <c r="B267" s="2">
+        <v>7</v>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
+        </is>
+      </c>
+      <c r="B268" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B269" s="2">
+        <v>35</v>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B270" s="2">
+        <v>21</v>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B271" s="2">
+        <v>0</v>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
+        </is>
+      </c>
+      <c r="B272" s="2">
+        <v>10</v>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
+        </is>
+      </c>
+      <c r="B273" s="2">
+        <v>7</v>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B274" s="2">
+        <v>0</v>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+        </is>
+      </c>
+      <c r="B275" s="2">
+        <v>70</v>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B276" s="2">
+        <v>30</v>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B277" s="2">
+        <v>35</v>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B278" s="2">
+        <v>21</v>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B279" s="2">
+        <v>40</v>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B280" s="2">
+        <v>23</v>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B281" s="2">
+        <v>10</v>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B282" s="2">
+        <v>6</v>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B283" s="2">
+        <v>0</v>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B284" s="2">
+        <v>35</v>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B285" s="2">
+        <v>22</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B286" s="2">
+        <v>0</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B287" s="2">
+        <v>95</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B288" s="2">
+        <v>70</v>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>0</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>350</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B255" s="2">
+      <c r="B291" s="2">
         <v>213</v>
       </c>
-      <c r="C255" s="0" t="inlineStr">
+      <c r="C291" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -10404,7 +11264,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6Ny40N319LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjcuOH19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjAsImNvZ3MiOjAsImVtcGxveWVlUGF5IjowLCJvZmZpY2VyUGF5IjowLCJkZXByZWNpYXRpb24iOjAsIm90aGVyU2dhIjowLCJoZWFkY291bnQiOjAsIm9mZmljZXJDb3VudCI6MH0sIm90aGVyIjp7InNhbGVzIjoxNTAsImNvZ3MiOjEwMiwiZW1wbG95ZWVQYXkiOjE0LCJvZmZpY2VyUGF5IjoxLCJkZXByZWNpYXRpb24iOjMuNSwib3RoZXJTZ2EiOjE4LCJoZWFkY291bnQiOjIzMCwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTMuMywiZW1wbG95ZWVCb251cyI6MC43LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjksIm9mZmljZXJCb251cyI6MC4xLCJjb2dzRGVwcmVjaWF0aW9uIjowLjgsInNnYURlcHJlY2lhdGlvbiI6Mi43LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjcsIm9yZGluYXJ5SW5jb21lIjoxMS42MDAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJuZXRJbmNvbWUiOjguMTIwMDAwMDAwMDAwMDAxfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjY6cHJvamVjdDo3LTEiOjAsIjIwMjY6cHJvamVjdDo3LTQiOjAsIjIwMjY6cHJvamVjdDo3LTYiOjAsIjIwMjY6cHJvamVjdDo3LTgiOjAsIjIwMjY6cHJvamVjdDo3LTkiOjAsIjIwMjY6cHJvamVjdDo3LTEwIjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDo3LTEwIjowLCIyMDI3OnByb2plY3Q6Ny0xMyI6MCwiMjAyNzpwcm9qZWN0OjctMTQiOjAsIjIwMjg6cHJvamVjdDo3LTEiOjYwLCIyMDI4OnByb2plY3Q6Ny00IjoyMSwiMjAyODpwcm9qZWN0OjctNiI6NS40LCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OjctMTAiOjQuNSwiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjguMjMsIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDo3LTEwIjo0LjUsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTEuNzcsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDo3LTEwIjo0LjUsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTYuMTYsIjIwMzE6cHJvamVjdDo3LTgiOjYuNjEsIjIwMzE6cHJvamVjdDo3LTkiOjAuMzYsIjIwMzE6cHJvamVjdDo3LTEwIjo0LjUsIjIwMzE6cHJvamVjdDo3LTEzIjo1NCwiMjAzMTpwcm9qZWN0OjctMTQiOjJ9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTMuODQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjc0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny40NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjguMTIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjQsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjI1LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5IjoxNSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjYuMjIsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC45OSwiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjUwLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMi40NSwiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi43NSwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny45MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC42OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjUzLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -5091,17 +5091,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.62 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.25 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.56 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.93 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.88 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5277,17 +5277,17 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.4 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.42 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.43 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -6787,7 +6787,7 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">新規投資の平均耐用年数（減価償却費の自動予測用・モデル内管理・第6次公式様式外）</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -6865,7 +6865,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C291"/>
+  <dimension ref="A1:C285"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -10780,11 +10780,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10795,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10810,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10825,22 +10825,22 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B265" s="2">
@@ -10855,22 +10855,22 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B267" s="2">
@@ -10885,26 +10885,26 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10915,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10930,26 +10930,26 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10960,11 +10960,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10975,26 +10975,26 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -11005,11 +11005,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -11020,26 +11020,26 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -11050,11 +11050,11 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
@@ -11065,26 +11065,26 @@
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11095,11 +11095,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
@@ -11125,11 +11125,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11140,103 +11140,13 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>22</v>
+        <v>213</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
-        </is>
-      </c>
-      <c r="B286" s="2">
-        <v>0</v>
-      </c>
-      <c r="C286" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">明示的な0</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
-        </is>
-      </c>
-      <c r="B287" s="2">
-        <v>95</v>
-      </c>
-      <c r="C287" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
-        </is>
-      </c>
-      <c r="B288" s="2">
-        <v>70</v>
-      </c>
-      <c r="C288" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
-        </is>
-      </c>
-      <c r="B289" s="2">
-        <v>0</v>
-      </c>
-      <c r="C289" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">明示的な0</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
-        </is>
-      </c>
-      <c r="B290" s="2">
-        <v>350</v>
-      </c>
-      <c r="C290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
-        </is>
-      </c>
-      <c r="B291" s="2">
-        <v>213</v>
-      </c>
-      <c r="C291" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11264,7 +11174,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjYuMjIsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC45OSwiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjUwLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMi40NSwiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi43NSwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny45MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC42OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjUzLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjYuMjIsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC45OSwiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjUwLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMi40NSwiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi43NSwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny45MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC42OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjUzLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>16.782428588993525</v>
+        <v>16.77162220995747</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="2">
-        <v>1.8299999999999998</v>
+        <v>1.93</v>
       </c>
       <c r="H6" s="2">
-        <v>1.8299999999999998</v>
+        <v>1.93</v>
       </c>
       <c r="I6" s="2">
-        <v>1.8299999999999998</v>
+        <v>1.93</v>
       </c>
       <c r="J6" s="2">
-        <v>1.8299999999999998</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>37.63</v>
+        <v>37.53</v>
       </c>
       <c r="F9" s="2">
-        <v>38.91</v>
+        <v>38.81</v>
       </c>
       <c r="G9" s="2">
-        <v>55</v>
+        <v>54.89</v>
       </c>
       <c r="H9" s="2">
-        <v>58</v>
+        <v>57.89</v>
       </c>
       <c r="I9" s="2">
-        <v>61.25</v>
+        <v>61.14</v>
       </c>
       <c r="J9" s="2">
-        <v>64.78999999999999</v>
+        <v>64.68</v>
       </c>
     </row>
     <row r="10">
@@ -1703,22 +1703,22 @@
         <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F16" s="2">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G16" s="2">
-        <v>6.18</v>
+        <v>6.07</v>
       </c>
       <c r="H16" s="2">
-        <v>6.18</v>
+        <v>6.07</v>
       </c>
       <c r="I16" s="2">
-        <v>6.18</v>
+        <v>6.07</v>
       </c>
       <c r="J16" s="2">
-        <v>6.18</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="17">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>12.550000000000004</v>
+        <v>12.650000000000006</v>
       </c>
       <c r="F18" s="4">
-        <v>13.550000000000011</v>
+        <v>13.650000000000006</v>
       </c>
       <c r="G18" s="4">
-        <v>20.840000000000003</v>
+        <v>20.950000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>26.13</v>
+        <v>26.24</v>
       </c>
       <c r="I18" s="4">
-        <v>32.37000000000001</v>
+        <v>32.48000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>39.73000000000002</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>8.044871794871797</v>
+        <v>8.108974358974361</v>
       </c>
       <c r="F19" s="2">
-        <v>8.351824457593695</v>
+        <v>8.413461538461542</v>
       </c>
       <c r="G19" s="2">
-        <v>9.11117911948586</v>
+        <v>9.159270755913088</v>
       </c>
       <c r="H19" s="2">
-        <v>10.39172797772917</v>
+        <v>10.435474249353748</v>
       </c>
       <c r="I19" s="2">
-        <v>11.667808095735865</v>
+        <v>11.707457737086836</v>
       </c>
       <c r="J19" s="2">
-        <v>12.930838079739631</v>
+        <v>12.966639544344996</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.600000000000003</v>
       </c>
       <c r="E20" s="4">
-        <v>11.77</v>
+        <v>11.87</v>
       </c>
       <c r="F20" s="4">
-        <v>12.74</v>
+        <v>12.84</v>
       </c>
       <c r="G20" s="4">
-        <v>20</v>
+        <v>20.11</v>
       </c>
       <c r="H20" s="4">
-        <v>25.240000000000002</v>
+        <v>25.35</v>
       </c>
       <c r="I20" s="4">
-        <v>31.419999999999998</v>
+        <v>31.53</v>
       </c>
       <c r="J20" s="4">
-        <v>38.730000000000004</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.600000000000003</v>
       </c>
       <c r="E21" s="2">
-        <v>11.77</v>
+        <v>11.87</v>
       </c>
       <c r="F21" s="2">
-        <v>12.74</v>
+        <v>12.84</v>
       </c>
       <c r="G21" s="2">
-        <v>20</v>
+        <v>20.11</v>
       </c>
       <c r="H21" s="2">
-        <v>25.240000000000002</v>
+        <v>25.35</v>
       </c>
       <c r="I21" s="2">
-        <v>31.419999999999998</v>
+        <v>31.53</v>
       </c>
       <c r="J21" s="2">
-        <v>38.730000000000004</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>8.24</v>
+        <v>8.31</v>
       </c>
       <c r="F22" s="2">
-        <v>8.92</v>
+        <v>8.99</v>
       </c>
       <c r="G22" s="2">
-        <v>14</v>
+        <v>14.080000000000002</v>
       </c>
       <c r="H22" s="2">
-        <v>17.67</v>
+        <v>17.75</v>
       </c>
       <c r="I22" s="2">
-        <v>21.990000000000002</v>
+        <v>22.07</v>
       </c>
       <c r="J22" s="2">
-        <v>27.11</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="23">
@@ -2043,22 +2043,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.800000000000004</v>
+        <v>31.900000000000006</v>
       </c>
       <c r="F26" s="4">
-        <v>33.58000000000001</v>
+        <v>33.68000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>51.290000000000006</v>
+        <v>51.400000000000006</v>
       </c>
       <c r="H26" s="4">
-        <v>58.18</v>
+        <v>58.29</v>
       </c>
       <c r="I26" s="4">
-        <v>66.13000000000002</v>
+        <v>66.24000000000001</v>
       </c>
       <c r="J26" s="4">
-        <v>75.34000000000002</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.152249134948116</v>
       </c>
       <c r="E27" s="2">
-        <v>5.6478405315614655</v>
+        <v>5.980066445182741</v>
       </c>
       <c r="F27" s="2">
-        <v>5.597484276729592</v>
+        <v>5.579937304075244</v>
       </c>
       <c r="G27" s="2">
-        <v>52.739726027397225</v>
+        <v>52.6128266033254</v>
       </c>
       <c r="H27" s="2">
-        <v>13.433417820237858</v>
+        <v>13.404669260700386</v>
       </c>
       <c r="I27" s="2">
-        <v>13.664489515297396</v>
+        <v>13.638703036541443</v>
       </c>
       <c r="J27" s="2">
-        <v>13.927113261757128</v>
+        <v>13.903985507246365</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.384615384615387</v>
+        <v>20.448717948717952</v>
       </c>
       <c r="F28" s="2">
-        <v>20.69773175542407</v>
+        <v>20.759368836291916</v>
       </c>
       <c r="G28" s="2">
-        <v>22.423818475932325</v>
+        <v>22.471910112359552</v>
       </c>
       <c r="H28" s="2">
-        <v>23.13780075561742</v>
+        <v>23.181547027241997</v>
       </c>
       <c r="I28" s="2">
-        <v>23.836643477634006</v>
+        <v>23.87629311898497</v>
       </c>
       <c r="J28" s="2">
-        <v>24.52074857607812</v>
+        <v>24.556550040683483</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.13417721518987344</v>
+        <v>0.1345991561181435</v>
       </c>
       <c r="F35" s="2">
-        <v>0.13991666666666672</v>
+        <v>0.14033333333333337</v>
       </c>
       <c r="G35" s="2">
-        <v>0.17565068493150687</v>
+        <v>0.176027397260274</v>
       </c>
       <c r="H35" s="2">
-        <v>0.19523489932885907</v>
+        <v>0.19560402684563757</v>
       </c>
       <c r="I35" s="2">
-        <v>0.21825082508250834</v>
+        <v>0.21861386138613864</v>
       </c>
       <c r="J35" s="2">
-        <v>0.24381877022653728</v>
+        <v>0.2441747572815534</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>16.050000000000004</v>
+        <v>16.150000000000006</v>
       </c>
       <c r="F36" s="4">
-        <v>17.05000000000001</v>
+        <v>17.150000000000006</v>
       </c>
       <c r="G36" s="4">
-        <v>28.840000000000003</v>
+        <v>28.950000000000003</v>
       </c>
       <c r="H36" s="4">
-        <v>34.129999999999995</v>
+        <v>34.239999999999995</v>
       </c>
       <c r="I36" s="4">
-        <v>40.37000000000001</v>
+        <v>40.48000000000001</v>
       </c>
       <c r="J36" s="4">
-        <v>47.73000000000002</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.28846153846154</v>
+        <v>10.352564102564106</v>
       </c>
       <c r="F37" s="2">
-        <v>10.509122287968447</v>
+        <v>10.570759368836296</v>
       </c>
       <c r="G37" s="2">
-        <v>12.608752677829758</v>
+        <v>12.656844314256984</v>
       </c>
       <c r="H37" s="2">
-        <v>13.573275004971167</v>
+        <v>13.617021276595743</v>
       </c>
       <c r="I37" s="2">
-        <v>14.551418375806513</v>
+        <v>14.591068017157486</v>
       </c>
       <c r="J37" s="2">
-        <v>15.534580960130192</v>
+        <v>15.570382424735557</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>2.3728813559322326</v>
       </c>
       <c r="E38" s="2">
-        <v>6.291390728476842</v>
+        <v>6.953642384105985</v>
       </c>
       <c r="F38" s="2">
-        <v>6.230529595015621</v>
+        <v>6.19195046439629</v>
       </c>
       <c r="G38" s="2">
-        <v>69.14956011730196</v>
+        <v>68.80466472303203</v>
       </c>
       <c r="H38" s="2">
-        <v>18.342579750346722</v>
+        <v>18.27288428324694</v>
       </c>
       <c r="I38" s="2">
-        <v>18.283035452680974</v>
+        <v>18.224299065420603</v>
       </c>
       <c r="J38" s="2">
-        <v>18.231359920733237</v>
+        <v>18.181818181818166</v>
       </c>
     </row>
   </sheetData>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>6.219999999999999</v>
+        <v>6.229999999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>8.989999999999998</v>
+        <v>8.999999999999996</v>
       </c>
       <c r="I8" s="4">
-        <v>12.449999999999992</v>
+        <v>12.45999999999999</v>
       </c>
       <c r="J8" s="4">
-        <v>16.750000000000004</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="9">
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="G9" s="2">
-        <v>10.366666666666664</v>
+        <v>10.383333333333328</v>
       </c>
       <c r="H9" s="2">
-        <v>12.382920110192837</v>
+        <v>12.39669421487603</v>
       </c>
       <c r="I9" s="2">
-        <v>14.171883892999423</v>
+        <v>14.183266932270906</v>
       </c>
       <c r="J9" s="2">
-        <v>15.758773167748616</v>
+        <v>15.768181390535329</v>
       </c>
     </row>
     <row r="10">
@@ -2952,7 +2952,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（億円）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -2971,260 +2971,238 @@
         <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="H12" s="2">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="I12" s="2">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="J12" s="2">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7-11 付加価値（億円）</t>
-        </is>
-      </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>15.82</v>
-      </c>
-      <c r="H13" s="4">
-        <v>19.15</v>
-      </c>
-      <c r="I13" s="4">
-        <v>23.229999999999993</v>
-      </c>
-      <c r="J13" s="4">
-        <v>28.220000000000002</v>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（億円）</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3.37</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3.37</v>
+      </c>
+      <c r="I13" s="2">
+        <v>3.37</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-12 付加価値増加率（%）</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>4.5</v>
       </c>
       <c r="H14" s="2">
-        <v>21.049304677623248</v>
+        <v>4.5</v>
       </c>
       <c r="I14" s="2">
-        <v>21.305483028720595</v>
+        <v>4.5</v>
       </c>
       <c r="J14" s="2">
-        <v>21.480843736547616</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7-13 常時使用する従業員数（就業時間換算）（人）</t>
-        </is>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>48</v>
-      </c>
-      <c r="H15" s="2">
-        <v>50</v>
-      </c>
-      <c r="I15" s="2">
-        <v>52</v>
-      </c>
-      <c r="J15" s="2">
-        <v>54</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7-11 付加価値（億円）</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>15.829999999999998</v>
+      </c>
+      <c r="H15" s="4">
+        <v>19.159999999999997</v>
+      </c>
+      <c r="I15" s="4">
+        <v>23.23999999999999</v>
+      </c>
+      <c r="J15" s="4">
+        <v>28.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-14 役員数（人）</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>2</v>
+          <t xml:space="preserve">7-12 付加価値増加率（%）</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>21.03600758054327</v>
       </c>
       <c r="I16" s="2">
-        <v>2</v>
+        <v>21.294363256784955</v>
       </c>
       <c r="J16" s="2">
-        <v>2</v>
+        <v>21.471600688468207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-13 常時使用する従業員数（就業時間換算）（人）</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
       </c>
       <c r="G17" s="2">
-        <v>0.09999999999999999</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2">
-        <v>0.10679999999999999</v>
+        <v>50</v>
       </c>
       <c r="I17" s="2">
-        <v>0.11423076923076923</v>
+        <v>52</v>
       </c>
       <c r="J17" s="2">
-        <v>0.12240740740740741</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-16 従業員1人当たり給与支給総額の上昇率（%）</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-14 役員数（人）</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>6.800000000000006</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2">
-        <v>6.957649092480556</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>7.157999750592348</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
@@ -3253,22 +3231,22 @@
         </is>
       </c>
       <c r="G19" s="2">
-        <v>0.15</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="H19" s="2">
-        <v>0.16</v>
+        <v>0.10679999999999999</v>
       </c>
       <c r="I19" s="2">
-        <v>0.17</v>
+        <v>0.11423076923076923</v>
       </c>
       <c r="J19" s="2">
-        <v>0.18</v>
+        <v>0.12240740740740741</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-18 役員1人当たり給与支給総額の上昇率（%）</t>
+          <t xml:space="preserve">7-16 従業員1人当たり給与支給総額の上昇率（%）</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -3302,19 +3280,19 @@
         </is>
       </c>
       <c r="H20" s="2">
-        <v>6.666666666666665</v>
+        <v>6.800000000000006</v>
       </c>
       <c r="I20" s="2">
-        <v>6.25</v>
+        <v>6.957649092480556</v>
       </c>
       <c r="J20" s="2">
-        <v>5.88235294117645</v>
+        <v>7.157999750592348</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -3343,63 +3321,153 @@
         </is>
       </c>
       <c r="G21" s="2">
-        <v>0.3164</v>
+        <v>0.15</v>
       </c>
       <c r="H21" s="2">
-        <v>0.36826923076923074</v>
+        <v>0.16</v>
       </c>
       <c r="I21" s="2">
-        <v>0.43018518518518506</v>
+        <v>0.17</v>
       </c>
       <c r="J21" s="2">
-        <v>0.5039285714285715</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">7-18 役員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="2">
+        <v>6.666666666666665</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5.88235294117645</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" s="2">
+        <v>0.3166</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.3684615384615384</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.43037037037037024</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.5041071428571429</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">7-20 市場伸び率（年あたり）（%）</t>
         </is>
       </c>
-      <c r="B22" s="2">
+      <c r="B24" s="2">
         <v>5</v>
       </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3851,32 +3919,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.12 % / 補助 — / ベース 24.12 %</t>
+          <t xml:space="preserve">全社 24.06 % / 補助 — / ベース 24.06 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.98 % / 補助 — / ベース 23.98 %</t>
+          <t xml:space="preserve">全社 23.92 % / 補助 — / ベース 23.92 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.05 % / 補助 24.63 % / ベース 23.84 %</t>
+          <t xml:space="preserve">全社 24 % / 補助 24.62 % / ベース 23.78 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.07 % / 補助 22.62 % / ベース 23.25 %</t>
+          <t xml:space="preserve">全社 23.02 % / 補助 22.6 % / ベース 23.19 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.08 % / 補助 20.83 % / ベース 22.66 %</t>
+          <t xml:space="preserve">全社 22.04 % / 補助 20.82 % / ベース 22.6 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.09 % / 補助 19.24 % / ベース 22.06 %</t>
+          <t xml:space="preserve">全社 21.05 % / 補助 19.23 % / ベース 22.01 %</t>
         </is>
       </c>
     </row>
@@ -3913,32 +3981,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.04 % / 補助 — / ベース 8.04 %</t>
+          <t xml:space="preserve">全社 8.11 % / 補助 — / ベース 8.11 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.35 % / 補助 — / ベース 8.35 %</t>
+          <t xml:space="preserve">全社 8.41 % / 補助 — / ベース 8.41 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.11 % / 補助 10.37 % / ベース 8.66 %</t>
+          <t xml:space="preserve">全社 9.16 % / 補助 10.38 % / ベース 8.72 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.39 % / 補助 12.38 % / ベース 9.58 %</t>
+          <t xml:space="preserve">全社 10.44 % / 補助 12.4 % / ベース 9.64 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.67 % / 補助 14.17 % / ベース 10.51 %</t>
+          <t xml:space="preserve">全社 11.71 % / 補助 14.18 % / ベース 10.56 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.93 % / 補助 15.76 % / ベース 11.44 %</t>
+          <t xml:space="preserve">全社 12.97 % / 補助 15.77 % / ベース 11.48 %</t>
         </is>
       </c>
     </row>
@@ -3975,32 +4043,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.29 % / 補助 — / ベース 10.29 %</t>
+          <t xml:space="preserve">全社 10.35 % / 補助 — / ベース 10.35 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.51 % / 補助 — / ベース 10.51 %</t>
+          <t xml:space="preserve">全社 10.57 % / 補助 — / ベース 10.57 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.61 % / 補助 17.87 % / ベース 10.74 %</t>
+          <t xml:space="preserve">全社 12.66 % / 補助 17.88 % / ベース 10.8 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.57 % / 補助 18.58 % / ベース 11.54 %</t>
+          <t xml:space="preserve">全社 13.62 % / 補助 18.6 % / ベース 11.6 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.55 % / 補助 19.29 % / ベース 12.35 %</t>
+          <t xml:space="preserve">全社 14.59 % / 補助 19.31 % / ベース 12.41 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.53 % / 補助 19.99 % / ベース 13.18 %</t>
+          <t xml:space="preserve">全社 15.57 % / 補助 20 % / ベース 13.23 %</t>
         </is>
       </c>
     </row>
@@ -4533,32 +4601,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.53 % / 補助 — / ベース 49.53 %</t>
+          <t xml:space="preserve">全社 49.37 % / 補助 — / ベース 49.37 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.23 % / 補助 — / ベース 49.23 %</t>
+          <t xml:space="preserve">全社 49.08 % / 補助 — / ベース 49.08 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.77 % / 補助 32.24 % / ベース 48.91 %</t>
+          <t xml:space="preserve">全社 43.68 % / 補助 32.22 % / ベース 48.78 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.34 % / 補助 29.56 % / ベース 47.12 %</t>
+          <t xml:space="preserve">全社 41.26 % / 補助 29.54 % / ベース 47 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.95 % / 補助 27.03 % / ベース 45.41 %</t>
+          <t xml:space="preserve">全社 38.89 % / 補助 27.02 % / ベース 45.3 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 36.65 % / 補助 24.7 % / ベース 43.8 %</t>
+          <t xml:space="preserve">全社 36.59 % / 補助 24.69 % / ベース 43.71 %</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4787,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.054 億円/人 / 補助 — / ベース 0.054 億円/人</t>
+          <t xml:space="preserve">全社 0.055 億円/人 / 補助 — / ベース 0.055 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -4729,17 +4797,17 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.073 億円/人 / 補助 0.13 億円/人 / ベース 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.13 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.09 億円/人 / 補助 0.18 億円/人 / ベース 0.071 億円/人</t>
+          <t xml:space="preserve">全社 0.09 億円/人 / 補助 0.18 億円/人 / ベース 0.072 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.109 億円/人 / 補助 0.239 億円/人 / ベース 0.082 億円/人</t>
+          <t xml:space="preserve">全社 0.11 億円/人 / 補助 0.24 億円/人 / ベース 0.082 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
@@ -4781,7 +4849,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.134 億円/人 / 補助 — / ベース 0.134 億円/人</t>
+          <t xml:space="preserve">全社 0.135 億円/人 / 補助 — / ベース 0.135 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -4791,22 +4859,22 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.176 億円/人 / 補助 0.316 億円/人 / ベース 0.147 億円/人</t>
+          <t xml:space="preserve">全社 0.176 億円/人 / 補助 0.317 億円/人 / ベース 0.147 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.195 億円/人 / 補助 0.368 億円/人 / ベース 0.159 億円/人</t>
+          <t xml:space="preserve">全社 0.196 億円/人 / 補助 0.368 億円/人 / ベース 0.159 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.218 億円/人 / 補助 0.43 億円/人 / ベース 0.172 億円/人</t>
+          <t xml:space="preserve">全社 0.219 億円/人 / 補助 0.43 億円/人 / ベース 0.173 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.504 億円/人 / ベース 0.186 億円/人</t>
+          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.504 億円/人 / ベース 0.187 億円/人</t>
         </is>
       </c>
     </row>
@@ -5215,32 +5283,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.59 倍 / 補助 — / ベース 4.59 倍</t>
+          <t xml:space="preserve">全社 4.61 倍 / 補助 — / ベース 4.61 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 倍 / 補助 — / ベース 4.87 倍</t>
+          <t xml:space="preserve">全社 4.9 倍 / 補助 — / ベース 4.9 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.61 倍 / 補助 2.38 倍 / ベース 5.18 倍</t>
+          <t xml:space="preserve">全社 3.62 倍 / 補助 2.38 倍 / ベース 5.21 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.27 倍 / 補助 3 倍 / ベース 5.9 倍</t>
+          <t xml:space="preserve">全社 4.28 倍 / 補助 3 倍 / ベース 5.93 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.05 倍 / 補助 3.77 倍 / ベース 6.69 倍</t>
+          <t xml:space="preserve">全社 5.06 倍 / 補助 3.77 倍 / ベース 6.72 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.97 倍 / 補助 4.72 倍 / ベース 7.57 倍</t>
+          <t xml:space="preserve">全社 5.98 倍 / 補助 4.72 倍 / ベース 7.59 倍</t>
         </is>
       </c>
     </row>
@@ -5587,32 +5655,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.04 pt</t>
+          <t xml:space="preserve">差 -8.11 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.35 pt</t>
+          <t xml:space="preserve">差 -8.41 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.7 pt</t>
+          <t xml:space="preserve">差 1.66 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.8 pt</t>
+          <t xml:space="preserve">差 2.76 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.66 pt</t>
+          <t xml:space="preserve">差 3.62 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.32 pt</t>
+          <t xml:space="preserve">差 4.28 pt</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5851,7 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 85.32 %</t>
+          <t xml:space="preserve">寄与率 85.34 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -5808,7 +5876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -6050,11 +6118,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 減価償却費のうち売上原価に含める割合</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6075,11 +6143,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 減価償却費のうち売上原価に含める割合</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6100,11 +6168,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6125,11 +6193,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6150,7 +6218,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6175,11 +6243,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6200,11 +6268,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6225,82 +6293,74 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D17" s="2">
+        <v>-5</v>
+      </c>
+      <c r="E17" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>21</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D19" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>7.000000000000001</v>
+        <v>4</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6308,41 +6368,41 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E20" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>7.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6350,20 +6410,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6371,20 +6431,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6395,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -6413,41 +6473,45 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2</v>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6455,45 +6519,41 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E27" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6504,17 +6564,17 @@
         <v>-5</v>
       </c>
       <c r="E29" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6522,20 +6582,20 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E30" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6543,20 +6603,20 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6564,20 +6624,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6585,20 +6645,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6609,38 +6669,42 @@
         <v>0</v>
       </c>
       <c r="E34" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>7.000000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D35" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="E35" s="2">
-        <v>10</v>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6648,66 +6712,62 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E36" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D37" s="2">
+        <v>-5</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B38" s="2">
+        <v>9</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
         <v>4</v>
       </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D38" s="2">
-        <v>-3</v>
-      </c>
       <c r="E38" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6715,20 +6775,20 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6736,124 +6796,57 @@
         </is>
       </c>
       <c r="D40" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業投資額</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D41" s="2">
-        <v>4</v>
-      </c>
-      <c r="E41" s="2">
-        <v>25</v>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新規投資の平均耐用年数（減価償却費の自動予測用・モデル内管理・第6次公式様式外）</t>
-        </is>
-      </c>
-      <c r="B43" s="2">
-        <v>10</v>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助事業投資額</t>
-        </is>
-      </c>
-      <c r="B44" s="2">
-        <v>45</v>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">申請補助金額</t>
-        </is>
-      </c>
-      <c r="B45" s="2">
-        <v>15</v>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
         </is>
       </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6865,7 +6858,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C288"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -7600,7 +7593,7 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B49" s="2">
@@ -7615,7 +7608,7 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B50" s="2">
@@ -7630,7 +7623,7 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B51" s="2">
@@ -7645,7 +7638,7 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -7660,7 +7653,7 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B53" s="2">
@@ -7675,7 +7668,7 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B54" s="2">
@@ -7690,7 +7683,7 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:project:2023:P2-14</t>
         </is>
       </c>
       <c r="B55" s="2">
@@ -7705,7 +7698,7 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:project:2023:P2-4</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -7720,7 +7713,7 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B57" s="2">
@@ -7825,7 +7818,7 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2024:P2-14</t>
         </is>
       </c>
       <c r="B64" s="2">
@@ -7840,7 +7833,7 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2024:P2-4</t>
         </is>
       </c>
       <c r="B65" s="2">
@@ -7855,7 +7848,7 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B66" s="2">
@@ -7870,7 +7863,7 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -7885,7 +7878,7 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B68" s="2">
@@ -7900,7 +7893,7 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B69" s="2">
@@ -7915,7 +7908,7 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B70" s="2">
@@ -7930,7 +7923,7 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B71" s="2">
@@ -7945,56 +7938,56 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2025:P2-14</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2025:P2-4</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -8005,11 +7998,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -8020,11 +8013,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -8035,11 +8028,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -8050,11 +8043,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -8065,11 +8058,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -8080,11 +8073,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -8095,11 +8088,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -8110,11 +8103,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -8125,11 +8118,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -8140,11 +8133,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -8155,11 +8148,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -8170,11 +8163,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -8185,11 +8178,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -8200,11 +8193,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -8215,11 +8208,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -8230,11 +8223,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -8245,11 +8238,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -8260,11 +8253,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -8275,11 +8268,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -8290,11 +8283,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -8305,11 +8298,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -8320,11 +8313,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -8335,11 +8328,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -8350,11 +8343,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -8365,11 +8358,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -8380,11 +8373,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8395,11 +8388,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8410,11 +8403,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8425,11 +8418,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8440,11 +8433,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8455,11 +8448,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8470,11 +8463,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8485,11 +8478,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8500,11 +8493,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8515,11 +8508,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8530,11 +8523,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8545,11 +8538,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8560,11 +8553,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8575,11 +8568,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8590,11 +8583,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8605,11 +8598,11 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -8620,11 +8613,11 @@
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8635,11 +8628,11 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8650,11 +8643,11 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8665,11 +8658,11 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -8680,11 +8673,11 @@
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8695,11 +8688,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8710,11 +8703,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8725,11 +8718,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8740,11 +8733,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8755,11 +8748,11 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8770,11 +8763,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8785,11 +8778,11 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8800,26 +8793,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8830,11 +8823,11 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8845,41 +8838,41 @@
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8890,161 +8883,161 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -9055,26 +9048,26 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>-0.05</v>
+        <v>1</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -9085,11 +9078,11 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -9100,11 +9093,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>-0.05</v>
+        <v>0.5</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -9115,11 +9108,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -9130,11 +9123,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -9145,11 +9138,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -9160,26 +9153,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -9190,161 +9183,161 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -9355,26 +9348,26 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -9385,11 +9378,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -9400,26 +9393,26 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -9430,11 +9423,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9445,41 +9438,41 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9490,131 +9483,131 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9625,26 +9618,26 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>-0.03</v>
+        <v>1</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9655,11 +9648,11 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9670,11 +9663,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>-0.03</v>
+        <v>0.5</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9685,11 +9678,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9700,11 +9693,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9715,11 +9708,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9730,11 +9723,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9745,11 +9738,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9760,26 +9753,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9790,71 +9783,71 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.045</v>
+        <v>0.1</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9865,41 +9858,41 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.1</v>
+        <v>0.045</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9910,41 +9903,41 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9955,26 +9948,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9985,11 +9978,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -10000,26 +9993,26 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -10030,11 +10023,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -10045,26 +10038,26 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -10075,11 +10068,11 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>50</v>
+        <v>0.04</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -10090,11 +10083,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10105,11 +10098,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -10120,11 +10113,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.3</v>
+        <v>50</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -10135,11 +10128,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10150,11 +10143,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10165,11 +10158,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10180,11 +10173,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0.01</v>
+        <v>45</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10195,11 +10188,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.005</v>
+        <v>23</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10210,11 +10203,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.68</v>
+        <v>0.2</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10225,11 +10218,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.95</v>
+        <v>0.01</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10240,26 +10233,26 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.015</v>
+        <v>0.68</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -10270,11 +10263,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.01</v>
+        <v>0.95</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10285,26 +10278,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.9</v>
+        <v>0.015</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10315,11 +10308,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.045</v>
+        <v>0.01</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10330,11 +10323,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>0.04</v>
+        <v>-0.005</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10345,11 +10338,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.045</v>
+        <v>0.9</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10360,11 +10353,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10375,11 +10368,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10390,11 +10383,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10405,7 +10398,7 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
@@ -10420,11 +10413,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10435,11 +10428,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10450,11 +10443,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10465,26 +10458,26 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10495,11 +10488,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10510,41 +10503,41 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10555,11 +10548,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.04</v>
+        <v>0.95</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10570,41 +10563,41 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
@@ -10615,11 +10608,11 @@
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10630,26 +10623,26 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.07</v>
+        <v>0.9</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10660,11 +10653,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10675,11 +10668,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10690,11 +10683,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.21</v>
+        <v>0.07</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10698,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.21</v>
+        <v>0.07</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10720,11 +10713,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10735,11 +10728,11 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10750,11 +10743,11 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>15</v>
+        <v>0.21</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10765,11 +10758,11 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>10</v>
+        <v>0.01</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
@@ -10780,11 +10773,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7</v>
+        <v>0.09</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10788,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>3.5</v>
+        <v>15</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10803,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10825,11 +10818,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10840,26 +10833,26 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10870,11 +10863,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10885,7 +10878,7 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B268" s="2">
@@ -10900,11 +10893,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10908,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10930,26 +10923,26 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10960,11 +10953,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10975,11 +10968,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10990,11 +10983,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -11005,11 +10998,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -11020,26 +11013,26 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -11050,11 +11043,11 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
@@ -11065,7 +11058,7 @@
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B280" s="2">
@@ -11080,11 +11073,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11095,11 +11088,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11110,7 +11103,7 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
@@ -11125,11 +11118,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11140,13 +11133,58 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B285" s="2">
+        <v>70</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B286" s="2">
+        <v>0</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B287" s="2">
+        <v>350</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B285" s="2">
+      <c r="B288" s="2">
         <v>213</v>
       </c>
-      <c r="C285" s="0" t="inlineStr">
+      <c r="C288" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11174,7 +11212,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6Ny0xMCI6MCwiMjAyNjpwcm9qZWN0OjctMTMiOjAsIjIwMjY6cHJvamVjdDo3LTE0IjowLCIyMDI3OnByb2plY3Q6Ny0xIjowLCIyMDI3OnByb2plY3Q6Ny00IjowLCIyMDI3OnByb2plY3Q6Ny02IjowLCIyMDI3OnByb2plY3Q6Ny04IjowLCIyMDI3OnByb2plY3Q6Ny05IjowLCIyMDI3OnByb2plY3Q6Ny0xMCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MCwiMjAyODpwcm9qZWN0OjctNCI6MjEsIjIwMjg6cHJvamVjdDo3LTYiOjYuMjIsIjIwMjg6cHJvamVjdDo3LTgiOjQuOCwiMjAyODpwcm9qZWN0OjctOSI6MC4zLCIyMDI4OnByb2plY3Q6Ny0xMCI6NC41LCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3Mi42LCIyMDI5OnByb2plY3Q6Ny00IjoyNS40MSwiMjAyOTpwcm9qZWN0OjctNiI6OC45OSwiMjAyOTpwcm9qZWN0OjctOCI6NS4zNCwiMjAyOTpwcm9qZWN0OjctOSI6MC4zMiwiMjAyOTpwcm9qZWN0OjctMTAiOjQuNSwiMjAyOTpwcm9qZWN0OjctMTMiOjUwLCIyMDI5OnByb2plY3Q6Ny0xNCI6MiwiMjAzMDpwcm9qZWN0OjctMSI6ODcuODUsIjIwMzA6cHJvamVjdDo3LTQiOjMwLjc1LCIyMDMwOnByb2plY3Q6Ny02IjoxMi40NSwiMjAzMDpwcm9qZWN0OjctOCI6NS45NCwiMjAzMDpwcm9qZWN0OjctOSI6MC4zNCwiMjAzMDpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2LjI5LCIyMDMxOnByb2plY3Q6Ny00IjozNy4yLCIyMDMxOnByb2plY3Q6Ny02IjoxNi43NSwiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OjctMTAiOjQuNSwiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny45MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC42OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjUzLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjksIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTIuNDYsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTYuNzYsIjIwMzE6cHJvamVjdDo3LTgiOjYuNjEsIjIwMzE6cHJvamVjdDo3LTkiOjAuMzYsIjIwMzE6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMxOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzE6cHJvamVjdDo3LTEzIjo1NCwiMjAzMTpwcm9qZWN0OjctMTQiOjJ9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTMuODQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjc0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjAsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuNCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -6858,7 +6858,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C288"/>
+  <dimension ref="A1:C285"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -10128,11 +10128,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10143,11 +10143,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10158,11 +10158,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.3</v>
+        <v>23</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10173,11 +10173,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>45</v>
+        <v>0.2</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10188,11 +10188,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>23</v>
+        <v>0.01</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10203,11 +10203,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.2</v>
+        <v>0.005</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10218,11 +10218,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.01</v>
+        <v>0.68</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10233,11 +10233,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0.005</v>
+        <v>0.95</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -10248,26 +10248,26 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.95</v>
+        <v>0.015</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10278,26 +10278,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10308,11 +10308,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.01</v>
+        <v>0.9</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10323,11 +10323,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>-0.005</v>
+        <v>0.045</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10338,11 +10338,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
@@ -10368,7 +10368,7 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
@@ -10383,11 +10383,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.045</v>
+        <v>0.004</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10398,11 +10398,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10413,11 +10413,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10428,11 +10428,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.06</v>
+        <v>0.005</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10443,11 +10443,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10458,11 +10458,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.005</v>
+        <v>0.25</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10473,26 +10473,26 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.25</v>
+        <v>0.07</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10503,26 +10503,26 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0.07</v>
+        <v>0.95</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
@@ -10533,26 +10533,26 @@
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.95</v>
+        <v>0.04</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10563,26 +10563,26 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
@@ -10593,26 +10593,26 @@
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10623,26 +10623,26 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.9</v>
+        <v>0.06</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10653,11 +10653,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10668,11 +10668,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10683,11 +10683,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.07</v>
+        <v>0.005</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10698,11 +10698,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.07</v>
+        <v>0.21</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10713,11 +10713,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.005</v>
+        <v>0.21</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10728,11 +10728,11 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10743,11 +10743,11 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10758,11 +10758,11 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>0.01</v>
+        <v>15</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
@@ -10773,11 +10773,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>0.09</v>
+        <v>7</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10788,11 +10788,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>15</v>
+        <v>3.5</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10803,11 +10803,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10818,11 +10818,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10833,26 +10833,26 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10863,11 +10863,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B268" s="2">
@@ -10893,11 +10893,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10908,11 +10908,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10923,26 +10923,26 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10953,11 +10953,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10968,11 +10968,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10983,11 +10983,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10998,11 +10998,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -11013,26 +11013,26 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -11043,11 +11043,11 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B280" s="2">
@@ -11073,11 +11073,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11088,11 +11088,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
@@ -11118,11 +11118,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>95</v>
+        <v>350</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11133,58 +11133,13 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>70</v>
+        <v>213</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
-        </is>
-      </c>
-      <c r="B286" s="2">
-        <v>0</v>
-      </c>
-      <c r="C286" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">明示的な0</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
-        </is>
-      </c>
-      <c r="B287" s="2">
-        <v>350</v>
-      </c>
-      <c r="C287" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
-        </is>
-      </c>
-      <c r="B288" s="2">
-        <v>213</v>
-      </c>
-      <c r="C288" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11212,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjpbMCwxXSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjpbMCwwLjNdLCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOlstMC41LDAuNV0sImVmZmVjdGl2ZVRheFJhdGUiOlswLDAuNl0sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJvdGhlck9mZmljZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjksIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTIuNDYsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTYuNzYsIjIwMzE6cHJvamVjdDo3LTgiOjYuNjEsIjIwMzE6cHJvamVjdDo3LTkiOjAuMzYsIjIwMzE6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMxOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzE6cHJvamVjdDo3LTEzIjo1NCwiMjAzMTpwcm9qZWN0OjctMTQiOjJ9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTMuODQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjc0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjAsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuNCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjksIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTIuNDYsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTYuNzYsIjIwMzE6cHJvamVjdDo3LTgiOjYuNjEsIjIwMzE6cHJvamVjdDo3LTkiOjAuMzYsIjIwMzE6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMxOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzE6cHJvamVjdDo3LTEzIjo1NCwiMjAzMTpwcm9qZWN0OjctMTQiOjJ9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTMuODQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjc0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjAsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuNCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>16.77162220995747</v>
+        <v>17.51148327112062</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>12.400000000000002</v>
+        <v>12.940000000000005</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>82.66666666666667</v>
+        <v>86.26666666666671</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1474,13 +1474,13 @@
         <v>54.89</v>
       </c>
       <c r="H9" s="2">
-        <v>57.89</v>
+        <v>58.370000000000005</v>
       </c>
       <c r="I9" s="2">
-        <v>61.14</v>
+        <v>62.11</v>
       </c>
       <c r="J9" s="2">
-        <v>64.68</v>
+        <v>66.15</v>
       </c>
     </row>
     <row r="10">
@@ -1780,13 +1780,13 @@
         <v>20.950000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>26.24</v>
+        <v>25.759999999999998</v>
       </c>
       <c r="I18" s="4">
-        <v>32.48000000000001</v>
+        <v>31.51000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>39.84</v>
+        <v>38.370000000000005</v>
       </c>
     </row>
     <row r="19">
@@ -1814,13 +1814,13 @@
         <v>9.159270755913088</v>
       </c>
       <c r="H19" s="2">
-        <v>10.435474249353748</v>
+        <v>10.244581427719227</v>
       </c>
       <c r="I19" s="2">
-        <v>11.707457737086836</v>
+        <v>11.357819990628268</v>
       </c>
       <c r="J19" s="2">
-        <v>12.966639544344996</v>
+        <v>12.488201790073232</v>
       </c>
     </row>
     <row r="20">
@@ -1848,13 +1848,13 @@
         <v>20.11</v>
       </c>
       <c r="H20" s="4">
-        <v>25.35</v>
+        <v>24.869999999999997</v>
       </c>
       <c r="I20" s="4">
-        <v>31.53</v>
+        <v>30.56</v>
       </c>
       <c r="J20" s="4">
-        <v>38.84</v>
+        <v>37.370000000000005</v>
       </c>
     </row>
     <row r="21">
@@ -1882,13 +1882,13 @@
         <v>20.11</v>
       </c>
       <c r="H21" s="2">
-        <v>25.35</v>
+        <v>24.869999999999997</v>
       </c>
       <c r="I21" s="2">
-        <v>31.53</v>
+        <v>30.56</v>
       </c>
       <c r="J21" s="2">
-        <v>38.84</v>
+        <v>37.370000000000005</v>
       </c>
     </row>
     <row r="22">
@@ -1916,13 +1916,13 @@
         <v>14.080000000000002</v>
       </c>
       <c r="H22" s="2">
-        <v>17.75</v>
+        <v>17.4</v>
       </c>
       <c r="I22" s="2">
-        <v>22.07</v>
+        <v>21.39</v>
       </c>
       <c r="J22" s="2">
-        <v>27.19</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="23">
@@ -2052,13 +2052,13 @@
         <v>51.400000000000006</v>
       </c>
       <c r="H26" s="4">
-        <v>58.29</v>
+        <v>57.81</v>
       </c>
       <c r="I26" s="4">
-        <v>66.24000000000001</v>
+        <v>65.27000000000001</v>
       </c>
       <c r="J26" s="4">
-        <v>75.45</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="27">
@@ -2088,13 +2088,13 @@
         <v>52.6128266033254</v>
       </c>
       <c r="H27" s="2">
-        <v>13.404669260700386</v>
+        <v>12.470817120622568</v>
       </c>
       <c r="I27" s="2">
-        <v>13.638703036541443</v>
+        <v>12.904341809375563</v>
       </c>
       <c r="J27" s="2">
-        <v>13.903985507246365</v>
+        <v>13.344568714570237</v>
       </c>
     </row>
     <row r="28">
@@ -2122,13 +2122,13 @@
         <v>22.471910112359552</v>
       </c>
       <c r="H28" s="2">
-        <v>23.181547027241997</v>
+        <v>22.990654205607477</v>
       </c>
       <c r="I28" s="2">
-        <v>23.87629311898497</v>
+        <v>23.526655372526406</v>
       </c>
       <c r="J28" s="2">
-        <v>24.556550040683483</v>
+        <v>24.078112286411717</v>
       </c>
     </row>
     <row r="29">
@@ -2364,13 +2364,13 @@
         <v>0.176027397260274</v>
       </c>
       <c r="H35" s="2">
-        <v>0.19560402684563757</v>
+        <v>0.19399328859060402</v>
       </c>
       <c r="I35" s="2">
-        <v>0.21861386138613864</v>
+        <v>0.21541254125412546</v>
       </c>
       <c r="J35" s="2">
-        <v>0.2441747572815534</v>
+        <v>0.23941747572815536</v>
       </c>
     </row>
     <row r="36">
@@ -2398,13 +2398,13 @@
         <v>28.950000000000003</v>
       </c>
       <c r="H36" s="4">
-        <v>34.239999999999995</v>
+        <v>33.76</v>
       </c>
       <c r="I36" s="4">
-        <v>40.48000000000001</v>
+        <v>39.510000000000005</v>
       </c>
       <c r="J36" s="4">
-        <v>47.84</v>
+        <v>46.370000000000005</v>
       </c>
     </row>
     <row r="37">
@@ -2432,13 +2432,13 @@
         <v>12.656844314256984</v>
       </c>
       <c r="H37" s="2">
-        <v>13.617021276595743</v>
+        <v>13.426128454961225</v>
       </c>
       <c r="I37" s="2">
-        <v>14.591068017157486</v>
+        <v>14.241430270698915</v>
       </c>
       <c r="J37" s="2">
-        <v>15.570382424735557</v>
+        <v>15.091944670463795</v>
       </c>
     </row>
     <row r="38">
@@ -2468,13 +2468,13 @@
         <v>68.80466472303203</v>
       </c>
       <c r="H38" s="2">
-        <v>18.27288428324694</v>
+        <v>16.61485319516405</v>
       </c>
       <c r="I38" s="2">
-        <v>18.224299065420603</v>
+        <v>17.031990521327046</v>
       </c>
       <c r="J38" s="2">
-        <v>18.181818181818166</v>
+        <v>17.36269298911668</v>
       </c>
     </row>
   </sheetData>
@@ -2828,13 +2828,13 @@
         <v>6.229999999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>8.999999999999996</v>
+        <v>9.119999999999996</v>
       </c>
       <c r="I8" s="4">
-        <v>12.45999999999999</v>
+        <v>12.74999999999999</v>
       </c>
       <c r="J8" s="4">
-        <v>16.76</v>
+        <v>17.300000000000004</v>
       </c>
     </row>
     <row r="9">
@@ -2872,13 +2872,13 @@
         <v>10.383333333333328</v>
       </c>
       <c r="H9" s="2">
-        <v>12.39669421487603</v>
+        <v>12.561983471074376</v>
       </c>
       <c r="I9" s="2">
-        <v>14.183266932270906</v>
+        <v>14.513375071143983</v>
       </c>
       <c r="J9" s="2">
-        <v>15.768181390535329</v>
+        <v>16.276225421017973</v>
       </c>
     </row>
     <row r="10">
@@ -3076,13 +3076,13 @@
         <v>15.829999999999998</v>
       </c>
       <c r="H15" s="4">
-        <v>19.159999999999997</v>
+        <v>19.279999999999994</v>
       </c>
       <c r="I15" s="4">
-        <v>23.23999999999999</v>
+        <v>23.52999999999999</v>
       </c>
       <c r="J15" s="4">
-        <v>28.23</v>
+        <v>28.770000000000003</v>
       </c>
     </row>
     <row r="16">
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="H16" s="2">
-        <v>21.03600758054327</v>
+        <v>21.794061907770022</v>
       </c>
       <c r="I16" s="2">
-        <v>21.294363256784955</v>
+        <v>22.043568464730278</v>
       </c>
       <c r="J16" s="2">
-        <v>21.471600688468207</v>
+        <v>22.269443263918465</v>
       </c>
     </row>
     <row r="17">
@@ -3414,13 +3414,13 @@
         <v>0.3166</v>
       </c>
       <c r="H23" s="2">
-        <v>0.3684615384615384</v>
+        <v>0.37076923076923063</v>
       </c>
       <c r="I23" s="2">
-        <v>0.43037037037037024</v>
+        <v>0.43574074074074054</v>
       </c>
       <c r="J23" s="2">
-        <v>0.5041071428571429</v>
+        <v>0.51375</v>
       </c>
     </row>
     <row r="24">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.02 % / 補助 22.6 % / ベース 23.19 %</t>
+          <t xml:space="preserve">全社 23.21 % / 補助 22.44 % / ベース 23.53 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.04 % / 補助 20.82 % / ベース 22.6 %</t>
+          <t xml:space="preserve">全社 22.39 % / 補助 20.49 % / ベース 23.27 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.05 % / 補助 19.23 % / ベース 22.01 %</t>
+          <t xml:space="preserve">全社 21.53 % / 補助 18.72 % / ベース 23.01 %</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3996,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.44 % / 補助 12.4 % / ベース 9.64 %</t>
+          <t xml:space="preserve">全社 10.24 % / 補助 12.56 % / ベース 9.3 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.71 % / 補助 14.18 % / ベース 10.56 %</t>
+          <t xml:space="preserve">全社 11.36 % / 補助 14.51 % / ベース 9.9 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.97 % / 補助 15.77 % / ベース 11.48 %</t>
+          <t xml:space="preserve">全社 12.49 % / 補助 16.28 % / ベース 10.48 %</t>
         </is>
       </c>
     </row>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.62 % / 補助 18.6 % / ベース 11.6 %</t>
+          <t xml:space="preserve">全社 13.43 % / 補助 18.76 % / ベース 11.26 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.59 % / 補助 19.31 % / ベース 12.41 %</t>
+          <t xml:space="preserve">全社 14.24 % / 補助 19.64 % / ベース 11.74 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.57 % / 補助 20 % / ベース 13.23 %</t>
+          <t xml:space="preserve">全社 15.09 % / 補助 20.51 % / ベース 12.23 %</t>
         </is>
       </c>
     </row>
@@ -4120,17 +4120,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.61 % / 補助 9.67 % / ベース 11 %</t>
+          <t xml:space="preserve">全社 10.81 % / 補助 9.5 % / ベース 11.33 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.13 % / 補助 9.33 % / ベース 10.5 %</t>
+          <t xml:space="preserve">全社 10.48 % / 補助 9 % / ベース 11.17 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.66 % / 補助 9 % / ベース 10 %</t>
+          <t xml:space="preserve">全社 10.14 % / 補助 8.5 % / ベース 11 %</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.26 % / 補助 29.54 % / ベース 47 %</t>
+          <t xml:space="preserve">全社 41.6 % / 補助 29.36 % / ベース 47.73 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.89 % / 補助 27.02 % / ベース 45.3 %</t>
+          <t xml:space="preserve">全社 39.47 % / 補助 26.69 % / ベース 46.67 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 36.59 % / 補助 24.69 % / ベース 43.71 %</t>
+          <t xml:space="preserve">全社 37.32 % / 補助 24.23 % / ベース 45.65 %</t>
         </is>
       </c>
     </row>
@@ -4802,17 +4802,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.09 億円/人 / 補助 0.18 億円/人 / ベース 0.072 億円/人</t>
+          <t xml:space="preserve">全社 0.089 億円/人 / 補助 0.182 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.11 億円/人 / 補助 0.24 億円/人 / ベース 0.082 億円/人</t>
+          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.245 億円/人 / ベース 0.077 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.132 億円/人 / 補助 0.31 億円/人 / ベース 0.093 億円/人</t>
+          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.32 億円/人 / ベース 0.085 億円/人</t>
         </is>
       </c>
     </row>
@@ -4864,17 +4864,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.196 億円/人 / 補助 0.368 億円/人 / ベース 0.159 億円/人</t>
+          <t xml:space="preserve">全社 0.194 億円/人 / 補助 0.371 億円/人 / ベース 0.157 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.219 億円/人 / 補助 0.43 億円/人 / ベース 0.173 億円/人</t>
+          <t xml:space="preserve">全社 0.215 億円/人 / 補助 0.436 億円/人 / ベース 0.168 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.504 億円/人 / ベース 0.187 億円/人</t>
+          <t xml:space="preserve">全社 0.239 億円/人 / 補助 0.514 億円/人 / ベース 0.179 億円/人</t>
         </is>
       </c>
     </row>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.28 倍 / 補助 3 倍 / ベース 5.93 倍</t>
+          <t xml:space="preserve">全社 4.22 倍 / 補助 3.03 倍 / ベース 5.75 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.06 倍 / 補助 3.77 倍 / ベース 6.72 倍</t>
+          <t xml:space="preserve">全社 4.94 倍 / 補助 3.83 倍 / ベース 6.36 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.98 倍 / 補助 4.72 倍 / ベース 7.59 倍</t>
+          <t xml:space="preserve">全社 5.8 倍 / 補助 4.84 倍 / ベース 7.02 倍</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5670,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.76 pt</t>
+          <t xml:space="preserve">差 3.26 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.62 pt</t>
+          <t xml:space="preserve">差 4.62 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.28 pt</t>
+          <t xml:space="preserve">差 5.79 pt</t>
         </is>
       </c>
     </row>
@@ -5856,17 +5856,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 52.36 %</t>
+          <t xml:space="preserve">寄与率 60.08 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 55.45 %</t>
+          <t xml:space="preserve">寄与率 63.13 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 58.42 %</t>
+          <t xml:space="preserve">寄与率 66.33 %</t>
         </is>
       </c>
     </row>
@@ -6742,11 +6742,11 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6754,20 +6754,20 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -9472,11 +9472,11 @@
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -10072,11 +10072,11 @@
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.1</v>
+        <v>0.005</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.09</v>
+        <v>0.015</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjksIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTIuNDYsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTYuNzYsIjIwMzE6cHJvamVjdDo3LTgiOjYuNjEsIjIwMzE6cHJvamVjdDo3LTkiOjAuMzYsIjIwMzE6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMxOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzE6cHJvamVjdDo3LTEzIjo1NCwiMjAzMTpwcm9qZWN0OjctMTQiOjJ9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTMuODQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjc0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQ0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuOTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNjksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi41MywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTksImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4xNCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjAsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuNCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjkuMTIsIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTIuNzUsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTcuMywiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMzE6cHJvamVjdDpQMi0xNCI6My4zNywiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny45MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC42OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjUzLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>17.51148327112062</v>
+        <v>12.997074798501561</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>12.940000000000005</v>
+        <v>9.750000000000007</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>86.26666666666671</v>
+        <v>65.00000000000004</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1338,13 +1338,13 @@
         <v>152.89</v>
       </c>
       <c r="H5" s="2">
-        <v>167.32</v>
+        <v>170.39</v>
       </c>
       <c r="I5" s="2">
-        <v>183.81</v>
+        <v>187.39000000000001</v>
       </c>
       <c r="J5" s="2">
-        <v>202.73</v>
+        <v>206.92</v>
       </c>
     </row>
     <row r="6">
@@ -1406,13 +1406,13 @@
         <v>75.84</v>
       </c>
       <c r="H7" s="4">
-        <v>84.13</v>
+        <v>81.06</v>
       </c>
       <c r="I7" s="4">
-        <v>93.62</v>
+        <v>90.03999999999999</v>
       </c>
       <c r="J7" s="4">
-        <v>104.52000000000001</v>
+        <v>100.33000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1440,13 +1440,13 @@
         <v>33.156997333100165</v>
       </c>
       <c r="H8" s="2">
-        <v>33.45794392523365</v>
+        <v>32.23702525352953</v>
       </c>
       <c r="I8" s="2">
-        <v>33.745449302526765</v>
+        <v>32.455033702195145</v>
       </c>
       <c r="J8" s="2">
-        <v>34.017900732302685</v>
+        <v>32.654190398698134</v>
       </c>
     </row>
     <row r="9">
@@ -1780,13 +1780,13 @@
         <v>20.950000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>25.759999999999998</v>
+        <v>22.690000000000005</v>
       </c>
       <c r="I18" s="4">
-        <v>31.51000000000001</v>
+        <v>27.929999999999996</v>
       </c>
       <c r="J18" s="4">
-        <v>38.370000000000005</v>
+        <v>34.18000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1814,13 +1814,13 @@
         <v>9.159270755913088</v>
       </c>
       <c r="H19" s="2">
-        <v>10.244581427719227</v>
+        <v>9.023662756015115</v>
       </c>
       <c r="I19" s="2">
-        <v>11.357819990628268</v>
+        <v>10.06740439029665</v>
       </c>
       <c r="J19" s="2">
-        <v>12.488201790073232</v>
+        <v>11.124491456468675</v>
       </c>
     </row>
     <row r="20">
@@ -1848,13 +1848,13 @@
         <v>20.11</v>
       </c>
       <c r="H20" s="4">
-        <v>24.869999999999997</v>
+        <v>21.8</v>
       </c>
       <c r="I20" s="4">
-        <v>30.56</v>
+        <v>26.98</v>
       </c>
       <c r="J20" s="4">
-        <v>37.370000000000005</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="21">
@@ -1882,13 +1882,13 @@
         <v>20.11</v>
       </c>
       <c r="H21" s="2">
-        <v>24.869999999999997</v>
+        <v>21.8</v>
       </c>
       <c r="I21" s="2">
-        <v>30.56</v>
+        <v>26.98</v>
       </c>
       <c r="J21" s="2">
-        <v>37.370000000000005</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="22">
@@ -1916,13 +1916,13 @@
         <v>14.080000000000002</v>
       </c>
       <c r="H22" s="2">
-        <v>17.4</v>
+        <v>15.260000000000002</v>
       </c>
       <c r="I22" s="2">
-        <v>21.39</v>
+        <v>18.89</v>
       </c>
       <c r="J22" s="2">
-        <v>26.16</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="23">
@@ -2052,13 +2052,13 @@
         <v>51.400000000000006</v>
       </c>
       <c r="H26" s="4">
-        <v>57.81</v>
+        <v>54.74000000000001</v>
       </c>
       <c r="I26" s="4">
-        <v>65.27000000000001</v>
+        <v>61.69</v>
       </c>
       <c r="J26" s="4">
-        <v>73.98</v>
+        <v>69.79</v>
       </c>
     </row>
     <row r="27">
@@ -2088,13 +2088,13 @@
         <v>52.6128266033254</v>
       </c>
       <c r="H27" s="2">
-        <v>12.470817120622568</v>
+        <v>6.49805447470817</v>
       </c>
       <c r="I27" s="2">
-        <v>12.904341809375563</v>
+        <v>12.69638290098647</v>
       </c>
       <c r="J27" s="2">
-        <v>13.344568714570237</v>
+        <v>13.130166963851519</v>
       </c>
     </row>
     <row r="28">
@@ -2122,13 +2122,13 @@
         <v>22.471910112359552</v>
       </c>
       <c r="H28" s="2">
-        <v>22.990654205607477</v>
+        <v>21.769735533903365</v>
       </c>
       <c r="I28" s="2">
-        <v>23.526655372526406</v>
+        <v>22.236239772194786</v>
       </c>
       <c r="J28" s="2">
-        <v>24.078112286411717</v>
+        <v>22.71440195280716</v>
       </c>
     </row>
     <row r="29">
@@ -2364,13 +2364,13 @@
         <v>0.176027397260274</v>
       </c>
       <c r="H35" s="2">
-        <v>0.19399328859060402</v>
+        <v>0.18369127516778527</v>
       </c>
       <c r="I35" s="2">
-        <v>0.21541254125412546</v>
+        <v>0.2035973597359736</v>
       </c>
       <c r="J35" s="2">
-        <v>0.23941747572815536</v>
+        <v>0.22585760517799355</v>
       </c>
     </row>
     <row r="36">
@@ -2398,13 +2398,13 @@
         <v>28.950000000000003</v>
       </c>
       <c r="H36" s="4">
-        <v>33.76</v>
+        <v>30.690000000000005</v>
       </c>
       <c r="I36" s="4">
-        <v>39.510000000000005</v>
+        <v>35.92999999999999</v>
       </c>
       <c r="J36" s="4">
-        <v>46.370000000000005</v>
+        <v>42.18000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2432,13 +2432,13 @@
         <v>12.656844314256984</v>
       </c>
       <c r="H37" s="2">
-        <v>13.426128454961225</v>
+        <v>12.20520978325711</v>
       </c>
       <c r="I37" s="2">
-        <v>14.241430270698915</v>
+        <v>12.951014670367297</v>
       </c>
       <c r="J37" s="2">
-        <v>15.091944670463795</v>
+        <v>13.728234336859238</v>
       </c>
     </row>
     <row r="38">
@@ -2468,13 +2468,13 @@
         <v>68.80466472303203</v>
       </c>
       <c r="H38" s="2">
-        <v>16.61485319516405</v>
+        <v>6.010362694300531</v>
       </c>
       <c r="I38" s="2">
-        <v>17.031990521327046</v>
+        <v>17.07396546106219</v>
       </c>
       <c r="J38" s="2">
-        <v>17.36269298911668</v>
+        <v>17.394934595045974</v>
       </c>
     </row>
   </sheetData>
@@ -2750,13 +2750,13 @@
         <v>21</v>
       </c>
       <c r="H6" s="4">
-        <v>25.409999999999997</v>
+        <v>23.229999999999997</v>
       </c>
       <c r="I6" s="4">
-        <v>30.749999999999993</v>
+        <v>28.109999999999992</v>
       </c>
       <c r="J6" s="4">
-        <v>37.2</v>
+        <v>34.010000000000005</v>
       </c>
     </row>
     <row r="7">
@@ -2794,13 +2794,13 @@
         <v>35</v>
       </c>
       <c r="H7" s="2">
-        <v>35</v>
+        <v>31.99724517906336</v>
       </c>
       <c r="I7" s="2">
-        <v>35.002845759817866</v>
+        <v>31.997723392145694</v>
       </c>
       <c r="J7" s="2">
-        <v>34.998588766581996</v>
+        <v>31.997365697619724</v>
       </c>
     </row>
     <row r="8">
@@ -2828,13 +2828,13 @@
         <v>6.229999999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>9.119999999999996</v>
+        <v>6.939999999999996</v>
       </c>
       <c r="I8" s="4">
-        <v>12.74999999999999</v>
+        <v>10.109999999999989</v>
       </c>
       <c r="J8" s="4">
-        <v>17.300000000000004</v>
+        <v>14.110000000000005</v>
       </c>
     </row>
     <row r="9">
@@ -2872,13 +2872,13 @@
         <v>10.383333333333328</v>
       </c>
       <c r="H9" s="2">
-        <v>12.561983471074376</v>
+        <v>9.559228650137737</v>
       </c>
       <c r="I9" s="2">
-        <v>14.513375071143983</v>
+        <v>11.508252703471815</v>
       </c>
       <c r="J9" s="2">
-        <v>16.276225421017973</v>
+        <v>13.2750023520557</v>
       </c>
     </row>
     <row r="10">
@@ -3076,13 +3076,13 @@
         <v>15.829999999999998</v>
       </c>
       <c r="H15" s="4">
-        <v>19.279999999999994</v>
+        <v>17.099999999999994</v>
       </c>
       <c r="I15" s="4">
-        <v>23.52999999999999</v>
+        <v>20.88999999999999</v>
       </c>
       <c r="J15" s="4">
-        <v>28.770000000000003</v>
+        <v>25.580000000000005</v>
       </c>
     </row>
     <row r="16">
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="H16" s="2">
-        <v>21.794061907770022</v>
+        <v>8.022741629816776</v>
       </c>
       <c r="I16" s="2">
-        <v>22.043568464730278</v>
+        <v>22.163742690058452</v>
       </c>
       <c r="J16" s="2">
-        <v>22.269443263918465</v>
+        <v>22.45093346098621</v>
       </c>
     </row>
     <row r="17">
@@ -3414,13 +3414,13 @@
         <v>0.3166</v>
       </c>
       <c r="H23" s="2">
-        <v>0.37076923076923063</v>
+        <v>0.32884615384615373</v>
       </c>
       <c r="I23" s="2">
-        <v>0.43574074074074054</v>
+        <v>0.38685185185185167</v>
       </c>
       <c r="J23" s="2">
-        <v>0.51375</v>
+        <v>0.4567857142857144</v>
       </c>
     </row>
     <row r="24">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.54 % / 補助 65 % / ベース 67.17 %</t>
+          <t xml:space="preserve">全社 67.76 % / 補助 68 % / ベース 67.67 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.25 % / 補助 65 % / ベース 66.84 %</t>
+          <t xml:space="preserve">全社 67.54 % / 補助 68 % / ベース 67.33 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.98 % / 補助 65 % / ベース 66.5 %</t>
+          <t xml:space="preserve">全社 67.35 % / 補助 68 % / ベース 67 %</t>
         </is>
       </c>
     </row>
@@ -3872,17 +3872,17 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.46 % / 補助 35 % / ベース 32.83 %</t>
+          <t xml:space="preserve">全社 32.24 % / 補助 32 % / ベース 32.33 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.75 % / 補助 35 % / ベース 33.16 %</t>
+          <t xml:space="preserve">全社 32.46 % / 補助 32 % / ベース 32.67 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.02 % / 補助 35 % / ベース 33.5 %</t>
+          <t xml:space="preserve">全社 32.65 % / 補助 32 % / ベース 33 %</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3996,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.24 % / 補助 12.56 % / ベース 9.3 %</t>
+          <t xml:space="preserve">全社 9.02 % / 補助 9.56 % / ベース 8.81 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.36 % / 補助 14.51 % / ベース 9.9 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 11.51 % / ベース 9.4 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.49 % / 補助 16.28 % / ベース 10.48 %</t>
+          <t xml:space="preserve">全社 11.12 % / 補助 13.28 % / ベース 9.99 %</t>
         </is>
       </c>
     </row>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.43 % / 補助 18.76 % / ベース 11.26 %</t>
+          <t xml:space="preserve">全社 12.21 % / 補助 15.76 % / ベース 10.76 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.24 % / 補助 19.64 % / ベース 11.74 %</t>
+          <t xml:space="preserve">全社 12.95 % / 補助 16.63 % / ベース 11.25 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.09 % / 補助 20.51 % / ベース 12.23 %</t>
+          <t xml:space="preserve">全社 13.73 % / 補助 17.51 % / ベース 11.73 %</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.6 % / 補助 29.36 % / ベース 47.73 %</t>
+          <t xml:space="preserve">全社 43.93 % / 補助 33.1 % / ベース 48.86 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.47 % / 補助 26.69 % / ベース 46.67 %</t>
+          <t xml:space="preserve">全社 41.76 % / 補助 30.06 % / ベース 47.75 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.32 % / 補助 24.23 % / ベース 45.65 %</t>
+          <t xml:space="preserve">全社 39.56 % / 補助 27.25 % / ベース 46.69 %</t>
         </is>
       </c>
     </row>
@@ -4802,17 +4802,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.089 億円/人 / 補助 0.182 億円/人 / ベース 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.078 億円/人 / 補助 0.139 億円/人 / ベース 0.065 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.245 億円/人 / ベース 0.077 億円/人</t>
+          <t xml:space="preserve">全社 0.094 億円/人 / 補助 0.194 億円/人 / ベース 0.073 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.32 億円/人 / ベース 0.085 億円/人</t>
+          <t xml:space="preserve">全社 0.113 億円/人 / 補助 0.261 億円/人 / ベース 0.081 億円/人</t>
         </is>
       </c>
     </row>
@@ -4864,17 +4864,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.194 億円/人 / 補助 0.371 億円/人 / ベース 0.157 億円/人</t>
+          <t xml:space="preserve">全社 0.184 億円/人 / 補助 0.329 億円/人 / ベース 0.153 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.215 億円/人 / 補助 0.436 億円/人 / ベース 0.168 億円/人</t>
+          <t xml:space="preserve">全社 0.204 億円/人 / 補助 0.387 億円/人 / ベース 0.164 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.239 億円/人 / 補助 0.514 億円/人 / ベース 0.179 億円/人</t>
+          <t xml:space="preserve">全社 0.226 億円/人 / 補助 0.457 億円/人 / ベース 0.175 億円/人</t>
         </is>
       </c>
     </row>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.22 倍 / 補助 3.03 倍 / ベース 5.75 倍</t>
+          <t xml:space="preserve">全社 3.84 倍 / 補助 2.54 倍 / ベース 5.5 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.94 倍 / 補助 3.83 倍 / ベース 6.36 倍</t>
+          <t xml:space="preserve">全社 4.49 倍 / 補助 3.25 倍 / ベース 6.09 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.8 倍 / 補助 4.84 倍 / ベース 7.02 倍</t>
+          <t xml:space="preserve">全社 5.27 倍 / 補助 4.14 倍 / ベース 6.73 倍</t>
         </is>
       </c>
     </row>
@@ -5608,17 +5608,17 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.17 pt</t>
+          <t xml:space="preserve">差 0.34 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.84 pt</t>
+          <t xml:space="preserve">差 0.67 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.5 pt</t>
+          <t xml:space="preserve">差 1 pt</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5670,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.26 pt</t>
+          <t xml:space="preserve">差 0.75 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.62 pt</t>
+          <t xml:space="preserve">差 2.11 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.79 pt</t>
+          <t xml:space="preserve">差 3.29 pt</t>
         </is>
       </c>
     </row>
@@ -5856,17 +5856,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 60.08 %</t>
+          <t xml:space="preserve">寄与率 40.8 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 63.13 %</t>
+          <t xml:space="preserve">寄与率 60.5 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 66.33 %</t>
+          <t xml:space="preserve">寄与率 64 %</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率（売上実績が0の場合の開始水準）</t>
+          <t xml:space="preserve">補助事業 原価率</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5979,21 +5979,17 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率（売上実績が0の場合の開始水準）</t>
+          <t xml:space="preserve">ベース事業 原価率</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -6004,15 +6000,11 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -11167,7 +11159,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjUuNDEsIjIwMjk6cHJvamVjdDo3LTYiOjkuMTIsIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjozMC43NSwiMjAzMDpwcm9qZWN0OjctNiI6MTIuNzUsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzcuMiwiMjAzMTpwcm9qZWN0OjctNiI6MTcuMywiMjAzMTpwcm9qZWN0OjctOCI6Ni42MSwiMjAzMTpwcm9qZWN0OjctOSI6MC4zNiwiMjAzMTpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMzE6cHJvamVjdDpQMi0xNCI6My4zNywiMjAzMTpwcm9qZWN0OjctMTMiOjU0LCIyMDMxOnByb2plY3Q6Ny0xNCI6Mn0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5My44NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS43OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDgsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjowLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi0xNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny45MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC42OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjUzLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjE0LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuNiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MCwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjMuMjMsIjIwMjk6cHJvamVjdDo3LTYiOjYuOTQsIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjoyOC4xMSwiMjAzMDpwcm9qZWN0OjctNiI6MTAuMTEsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzQuMDEsIjIwMzE6cHJvamVjdDo3LTYiOjE0LjExLCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6UDItNCI6MS4xMywiMjAzMTpwcm9qZWN0OlAyLTE0IjozLjM3LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjc4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjY5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNTMsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjQsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5IjoxNSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>10.337444343281588</v>
+        <v>10.337904882306592</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,11 +234,11 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>78.52000000000001</v>
+        <v>7852371</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>6.626397837416431</v>
+        <v>6.618420119006196</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>34.593978844589095</v>
+        <v>34.59479736768336</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>20.99861119003372</v>
+        <v>20.999999999999996</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,11 +354,11 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>46.290000000000006</v>
+        <v>4629366</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>12.997074798501561</v>
+        <v>12.993452414930307</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,11 +414,11 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>9.750000000000007</v>
+        <v>974754</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6.971782645069546</v>
+        <v>6.995674685973974</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,11 +474,11 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1.8100000000000005</v>
+        <v>181443</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>65.00000000000004</v>
+        <v>64.9836</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>6.265856918261115</v>
+        <v>5.999525333106437</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -624,11 +624,11 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.06</v>
+        <v>5730</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">千円</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -712,167 +712,167 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-1 資産総額（億円）</t>
+          <t xml:space="preserve">1-1 資産総額（千円）</t>
         </is>
       </c>
       <c r="B3" s="4">
-        <v>132</v>
+        <v>13200000</v>
       </c>
       <c r="C3" s="4">
-        <v>143</v>
+        <v>14300000</v>
       </c>
       <c r="D3" s="4">
-        <v>156</v>
+        <v>15600000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-2 うち流動資産（億円）</t>
+          <t xml:space="preserve">1-2 うち流動資産（千円）</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>67</v>
+        <v>6700000</v>
       </c>
       <c r="C4" s="2">
-        <v>72</v>
+        <v>7200000</v>
       </c>
       <c r="D4" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-3 うち現金及び預金（億円）</t>
+          <t xml:space="preserve">1-3 うち現金及び預金（千円）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C5" s="2">
-        <v>25</v>
+        <v>2500000</v>
       </c>
       <c r="D5" s="2">
-        <v>27</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-4 うち固定資産（億円）</t>
+          <t xml:space="preserve">1-4 うち固定資産（千円）</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>65</v>
+        <v>6500000</v>
       </c>
       <c r="C6" s="2">
-        <v>71</v>
+        <v>7100000</v>
       </c>
       <c r="D6" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-5 うち有形固定資産（億円）</t>
+          <t xml:space="preserve">1-5 うち有形固定資産（千円）</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>53</v>
+        <v>5300000</v>
       </c>
       <c r="C7" s="2">
-        <v>58</v>
+        <v>5800000</v>
       </c>
       <c r="D7" s="2">
-        <v>64</v>
+        <v>6400000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-6 うち建物及び構築物（億円）</t>
+          <t xml:space="preserve">1-6 うち建物及び構築物（千円）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>19</v>
+        <v>1900000</v>
       </c>
       <c r="C8" s="2">
-        <v>20</v>
+        <v>2000000</v>
       </c>
       <c r="D8" s="2">
-        <v>22</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-7 うち機械装置等（億円）</t>
+          <t xml:space="preserve">1-7 うち機械装置等（千円）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C9" s="2">
-        <v>28</v>
+        <v>2800000</v>
       </c>
       <c r="D9" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-8 うち土地（億円）</t>
+          <t xml:space="preserve">1-8 うち土地（千円）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C10" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="D10" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-9 うち無形固定資産（億円）</t>
+          <t xml:space="preserve">1-9 うち無形固定資産（千円）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
       <c r="C11" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="D11" s="2">
-        <v>9</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-10 うちソフトウェア（億円）</t>
+          <t xml:space="preserve">1-10 うちソフトウェア（千円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C12" s="2">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="D12" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-11 その他資産（自動計算）（億円）</t>
+          <t xml:space="preserve">1-11 その他資産（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -888,103 +888,103 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-12 負債及び純資産合計（自動計算）（億円）</t>
+          <t xml:space="preserve">1-12 負債及び純資産合計（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B14" s="4">
-        <v>132</v>
+        <v>13200000</v>
       </c>
       <c r="C14" s="4">
-        <v>143</v>
+        <v>14300000</v>
       </c>
       <c r="D14" s="4">
-        <v>156</v>
+        <v>15600000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-13 負債総額（億円）</t>
+          <t xml:space="preserve">1-13 負債総額（千円）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>75</v>
+        <v>7500000</v>
       </c>
       <c r="C15" s="2">
-        <v>79</v>
+        <v>7900000</v>
       </c>
       <c r="D15" s="2">
-        <v>83</v>
+        <v>8300000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-14 うち流動負債（億円）</t>
+          <t xml:space="preserve">1-14 うち流動負債（千円）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>39</v>
+        <v>3900000</v>
       </c>
       <c r="C16" s="2">
-        <v>41</v>
+        <v>4100000</v>
       </c>
       <c r="D16" s="2">
-        <v>43</v>
+        <v>4300000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-15 うち短期借入金（億円）</t>
+          <t xml:space="preserve">1-15 うち短期借入金（千円）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="D17" s="2">
-        <v>11</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-16 うち固定負債（億円）</t>
+          <t xml:space="preserve">1-16 うち固定負債（千円）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>36</v>
+        <v>3600000</v>
       </c>
       <c r="C18" s="2">
-        <v>38</v>
+        <v>3800000</v>
       </c>
       <c r="D18" s="2">
-        <v>40</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-17 うち長期借入金（億円）</t>
+          <t xml:space="preserve">1-17 うち長期借入金（千円）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>29</v>
+        <v>2900000</v>
       </c>
       <c r="C19" s="2">
-        <v>31</v>
+        <v>3100000</v>
       </c>
       <c r="D19" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-18 その他負債（自動計算）（億円）</t>
+          <t xml:space="preserve">1-18 その他負債（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -1000,65 +1000,65 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-19 純資産総額（億円）</t>
+          <t xml:space="preserve">1-19 純資産総額（千円）</t>
         </is>
       </c>
       <c r="B21" s="4">
-        <v>57</v>
+        <v>5700000</v>
       </c>
       <c r="C21" s="4">
-        <v>64</v>
+        <v>6400000</v>
       </c>
       <c r="D21" s="4">
-        <v>73</v>
+        <v>7300000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-20 うち株主資本（億円）</t>
+          <t xml:space="preserve">1-20 うち株主資本（千円）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>54</v>
+        <v>5400000</v>
       </c>
       <c r="C22" s="2">
-        <v>61</v>
+        <v>6100000</v>
       </c>
       <c r="D22" s="2">
-        <v>70</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-21 うち資本金（億円）</t>
+          <t xml:space="preserve">1-21 うち資本金（千円）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C23" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="D23" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-22 その他純資産（自動計算）（億円）</t>
+          <t xml:space="preserve">1-22 その他純資産（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>3</v>
+        <v>300000</v>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>300000</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="25">
@@ -1080,17 +1080,17 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-24 新規設備投資による支出（億円）</t>
+          <t xml:space="preserve">1-24 新規設備投資による支出（千円）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C26" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="D26" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="27">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.1821974965229487</v>
+        <v>1.1831239203994226</v>
       </c>
       <c r="C27" s="2">
-        <v>1.2203389830508478</v>
+        <v>1.2205384066142333</v>
       </c>
       <c r="D27" s="2">
-        <v>1.0596026490066224</v>
+        <v>1.0596026490066226</v>
       </c>
     </row>
   </sheetData>
@@ -1246,35 +1246,35 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-1 売上高（億円）</t>
+          <t xml:space="preserve">2-1 売上高（千円）</t>
         </is>
       </c>
       <c r="B3" s="4">
-        <v>138</v>
+        <v>13800000</v>
       </c>
       <c r="C3" s="4">
-        <v>144</v>
+        <v>14400000</v>
       </c>
       <c r="D3" s="4">
-        <v>150</v>
+        <v>15000000</v>
       </c>
       <c r="E3" s="4">
-        <v>156</v>
+        <v>15600000</v>
       </c>
       <c r="F3" s="4">
-        <v>162.24</v>
+        <v>16224000</v>
       </c>
       <c r="G3" s="4">
-        <v>228.73</v>
+        <v>22872960</v>
       </c>
       <c r="H3" s="4">
-        <v>251.45</v>
+        <v>25145338</v>
       </c>
       <c r="I3" s="4">
-        <v>277.43</v>
+        <v>27743058</v>
       </c>
       <c r="J3" s="4">
-        <v>307.25</v>
+        <v>30725331</v>
       </c>
     </row>
     <row r="4">
@@ -1301,118 +1301,118 @@
         <v>4.0000000000000036</v>
       </c>
       <c r="G4" s="2">
-        <v>40.98249506903351</v>
+        <v>40.982248520710066</v>
       </c>
       <c r="H4" s="2">
-        <v>9.933108905696674</v>
+        <v>9.934778883012951</v>
       </c>
       <c r="I4" s="2">
-        <v>10.33207397096838</v>
+        <v>10.33082156223153</v>
       </c>
       <c r="J4" s="2">
-        <v>10.748657318963328</v>
+        <v>10.749618877630574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-3 売上原価（億円）</t>
+          <t xml:space="preserve">2-3 売上原価（千円）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>93.84</v>
+        <v>9384000</v>
       </c>
       <c r="C5" s="2">
-        <v>97.92</v>
+        <v>9792000</v>
       </c>
       <c r="D5" s="2">
-        <v>102</v>
+        <v>10200000</v>
       </c>
       <c r="E5" s="2">
-        <v>105.82</v>
+        <v>10582000</v>
       </c>
       <c r="F5" s="2">
-        <v>109.78</v>
+        <v>10978240</v>
       </c>
       <c r="G5" s="2">
-        <v>152.89</v>
+        <v>15289248</v>
       </c>
       <c r="H5" s="2">
-        <v>170.39</v>
+        <v>17039212</v>
       </c>
       <c r="I5" s="2">
-        <v>187.39000000000001</v>
+        <v>18738890</v>
       </c>
       <c r="J5" s="2">
-        <v>206.92</v>
+        <v>20692266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-4 うち減価償却費（億円）</t>
+          <t xml:space="preserve">2-4 うち減価償却費（千円）</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0.74</v>
+        <v>73600</v>
       </c>
       <c r="C6" s="2">
-        <v>0.77</v>
+        <v>76800</v>
       </c>
       <c r="D6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="F6" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="G6" s="2">
-        <v>1.93</v>
+        <v>193000</v>
       </c>
       <c r="H6" s="2">
-        <v>1.93</v>
+        <v>193000</v>
       </c>
       <c r="I6" s="2">
-        <v>1.93</v>
+        <v>193000</v>
       </c>
       <c r="J6" s="2">
-        <v>1.93</v>
+        <v>193000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-5 売上総利益（億円）</t>
+          <t xml:space="preserve">2-5 売上総利益（千円）</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <v>44.16</v>
+        <v>4416000</v>
       </c>
       <c r="C7" s="4">
-        <v>46.08</v>
+        <v>4608000</v>
       </c>
       <c r="D7" s="4">
-        <v>48</v>
+        <v>4800000</v>
       </c>
       <c r="E7" s="4">
-        <v>50.18000000000001</v>
+        <v>5018000</v>
       </c>
       <c r="F7" s="4">
-        <v>52.46000000000001</v>
+        <v>5245760</v>
       </c>
       <c r="G7" s="4">
-        <v>75.84</v>
+        <v>7583712</v>
       </c>
       <c r="H7" s="4">
-        <v>81.06</v>
+        <v>8106126</v>
       </c>
       <c r="I7" s="4">
-        <v>90.03999999999999</v>
+        <v>9004168</v>
       </c>
       <c r="J7" s="4">
-        <v>100.33000000000001</v>
+        <v>10033065</v>
       </c>
     </row>
     <row r="8">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>31.999999999999996</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2">
         <v>32</v>
@@ -1431,362 +1431,362 @@
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>32.16666666666667</v>
+        <v>32.166666666666664</v>
       </c>
       <c r="F8" s="2">
-        <v>32.33481262327417</v>
+        <v>32.33333333333333</v>
       </c>
       <c r="G8" s="2">
-        <v>33.156997333100165</v>
+        <v>33.15579618903718</v>
       </c>
       <c r="H8" s="2">
-        <v>32.23702525352953</v>
+        <v>32.23709301501535</v>
       </c>
       <c r="I8" s="2">
-        <v>32.455033702195145</v>
+        <v>32.45557140816993</v>
       </c>
       <c r="J8" s="2">
-        <v>32.654190398698134</v>
+        <v>32.65405017117635</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-7 販売費及び一般管理費（億円）</t>
+          <t xml:space="preserve">2-7 販売費及び一般管理費（千円）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>33</v>
+        <v>3301126</v>
       </c>
       <c r="C9" s="2">
-        <v>34.69</v>
+        <v>3469241</v>
       </c>
       <c r="D9" s="2">
-        <v>36.4</v>
+        <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>37.53</v>
+        <v>3752960</v>
       </c>
       <c r="F9" s="2">
-        <v>38.81</v>
+        <v>3880532</v>
       </c>
       <c r="G9" s="2">
-        <v>54.89</v>
+        <v>5489896</v>
       </c>
       <c r="H9" s="2">
-        <v>58.370000000000005</v>
+        <v>5836013</v>
       </c>
       <c r="I9" s="2">
-        <v>62.11</v>
+        <v>6210735</v>
       </c>
       <c r="J9" s="2">
-        <v>66.15</v>
+        <v>6616273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-8 うち役員の人件費（自動計算）（億円）</t>
+          <t xml:space="preserve">2-8 うち役員の人件費（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.92</v>
+        <v>92000</v>
       </c>
       <c r="C10" s="2">
-        <v>0.96</v>
+        <v>96000</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E10" s="2">
-        <v>1.04</v>
+        <v>104000</v>
       </c>
       <c r="F10" s="2">
-        <v>1.08</v>
+        <v>108160</v>
       </c>
       <c r="G10" s="2">
-        <v>1.4200000000000002</v>
+        <v>142486</v>
       </c>
       <c r="H10" s="2">
-        <v>1.5</v>
+        <v>149348</v>
       </c>
       <c r="I10" s="2">
-        <v>1.57</v>
+        <v>156546</v>
       </c>
       <c r="J10" s="2">
-        <v>1.6400000000000001</v>
+        <v>164096</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-9 うち役員報酬（億円）</t>
+          <t xml:space="preserve">2-9 うち役員報酬（千円）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.83</v>
+        <v>82800</v>
       </c>
       <c r="C11" s="2">
-        <v>0.86</v>
+        <v>86400</v>
       </c>
       <c r="D11" s="2">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="E11" s="2">
-        <v>0.94</v>
+        <v>93600</v>
       </c>
       <c r="F11" s="2">
-        <v>0.97</v>
+        <v>97344</v>
       </c>
       <c r="G11" s="2">
-        <v>1.28</v>
+        <v>128237</v>
       </c>
       <c r="H11" s="2">
-        <v>1.35</v>
+        <v>134413</v>
       </c>
       <c r="I11" s="2">
-        <v>1.4200000000000002</v>
+        <v>140891</v>
       </c>
       <c r="J11" s="2">
-        <v>1.47</v>
+        <v>147686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-10 うち役員賞与（億円）</t>
+          <t xml:space="preserve">2-10 うち役員賞与（千円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.09</v>
+        <v>9200</v>
       </c>
       <c r="C12" s="2">
-        <v>0.1</v>
+        <v>9600</v>
       </c>
       <c r="D12" s="2">
-        <v>0.1</v>
+        <v>10000</v>
       </c>
       <c r="E12" s="2">
-        <v>0.1</v>
+        <v>10400</v>
       </c>
       <c r="F12" s="2">
-        <v>0.11</v>
+        <v>10816</v>
       </c>
       <c r="G12" s="2">
-        <v>0.14</v>
+        <v>14249</v>
       </c>
       <c r="H12" s="2">
-        <v>0.15</v>
+        <v>14935</v>
       </c>
       <c r="I12" s="2">
-        <v>0.15</v>
+        <v>15655</v>
       </c>
       <c r="J12" s="2">
-        <v>0.17</v>
+        <v>16410</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-11 うち従業員の人件費（自動計算）（億円）</t>
+          <t xml:space="preserve">2-11 うち従業員の人件費（自動計算）（千円）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>12.4</v>
+        <v>1240326</v>
       </c>
       <c r="C13" s="2">
-        <v>13.19</v>
+        <v>1318841</v>
       </c>
       <c r="D13" s="2">
-        <v>14</v>
+        <v>1400000</v>
       </c>
       <c r="E13" s="2">
-        <v>14.71</v>
+        <v>1470560</v>
       </c>
       <c r="F13" s="2">
-        <v>15.45</v>
+        <v>1544676</v>
       </c>
       <c r="G13" s="2">
-        <v>21.03</v>
+        <v>2102528</v>
       </c>
       <c r="H13" s="2">
-        <v>22.55</v>
+        <v>2255119</v>
       </c>
       <c r="I13" s="2">
-        <v>24.19</v>
+        <v>2419790</v>
       </c>
       <c r="J13" s="2">
-        <v>25.97</v>
+        <v>2597594</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-12 うち従業員の給与（億円）</t>
+          <t xml:space="preserve">2-12 うち従業員の給与（千円）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>11.78</v>
+        <v>1178310</v>
       </c>
       <c r="C14" s="2">
-        <v>12.53</v>
+        <v>1252899</v>
       </c>
       <c r="D14" s="2">
-        <v>13.3</v>
+        <v>1330000</v>
       </c>
       <c r="E14" s="2">
-        <v>13.97</v>
+        <v>1397032</v>
       </c>
       <c r="F14" s="2">
-        <v>14.68</v>
+        <v>1467442</v>
       </c>
       <c r="G14" s="2">
-        <v>19.98</v>
+        <v>1997402</v>
       </c>
       <c r="H14" s="2">
-        <v>21.42</v>
+        <v>2142363</v>
       </c>
       <c r="I14" s="2">
-        <v>22.98</v>
+        <v>2298800</v>
       </c>
       <c r="J14" s="2">
-        <v>24.67</v>
+        <v>2467714</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-13 うち従業員の賞与（億円）</t>
+          <t xml:space="preserve">2-13 うち従業員の賞与（千円）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0.62</v>
+        <v>62016</v>
       </c>
       <c r="C15" s="2">
-        <v>0.66</v>
+        <v>65942</v>
       </c>
       <c r="D15" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="E15" s="2">
-        <v>0.74</v>
+        <v>73528</v>
       </c>
       <c r="F15" s="2">
-        <v>0.77</v>
+        <v>77234</v>
       </c>
       <c r="G15" s="2">
-        <v>1.05</v>
+        <v>105126</v>
       </c>
       <c r="H15" s="2">
-        <v>1.13</v>
+        <v>112756</v>
       </c>
       <c r="I15" s="2">
-        <v>1.21</v>
+        <v>120990</v>
       </c>
       <c r="J15" s="2">
-        <v>1.3</v>
+        <v>129880</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-14 うち減価償却費（億円）</t>
+          <t xml:space="preserve">2-14 うち減価償却費（千円）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>2.48</v>
+        <v>248400</v>
       </c>
       <c r="C16" s="2">
-        <v>2.59</v>
+        <v>259200</v>
       </c>
       <c r="D16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="E16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="F16" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="G16" s="2">
-        <v>6.07</v>
+        <v>607000</v>
       </c>
       <c r="H16" s="2">
-        <v>6.07</v>
+        <v>607000</v>
       </c>
       <c r="I16" s="2">
-        <v>6.07</v>
+        <v>607000</v>
       </c>
       <c r="J16" s="2">
-        <v>6.07</v>
+        <v>607000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-15 うち研究開発費（億円）</t>
+          <t xml:space="preserve">2-15 うち研究開発費（千円）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.64</v>
+        <v>64400</v>
       </c>
       <c r="C17" s="2">
-        <v>0.67</v>
+        <v>67200</v>
       </c>
       <c r="D17" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="E17" s="2">
-        <v>0.62</v>
+        <v>62400</v>
       </c>
       <c r="F17" s="2">
-        <v>0.65</v>
+        <v>64896</v>
       </c>
       <c r="G17" s="2">
-        <v>0.97</v>
+        <v>97492</v>
       </c>
       <c r="H17" s="2">
-        <v>1.08</v>
+        <v>107841</v>
       </c>
       <c r="I17" s="2">
-        <v>1.2</v>
+        <v>119757</v>
       </c>
       <c r="J17" s="2">
-        <v>1.33</v>
+        <v>133531</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-16 営業利益（億円）</t>
+          <t xml:space="preserve">2-16 営業利益（千円）</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <v>11.159999999999997</v>
+        <v>1114874</v>
       </c>
       <c r="C18" s="4">
-        <v>11.389999999999997</v>
+        <v>1138759</v>
       </c>
       <c r="D18" s="4">
-        <v>11.600000000000001</v>
+        <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>12.650000000000006</v>
+        <v>1265040</v>
       </c>
       <c r="F18" s="4">
-        <v>13.650000000000006</v>
+        <v>1365228</v>
       </c>
       <c r="G18" s="4">
-        <v>20.950000000000003</v>
+        <v>2093816</v>
       </c>
       <c r="H18" s="4">
-        <v>22.690000000000005</v>
+        <v>2270113</v>
       </c>
       <c r="I18" s="4">
-        <v>27.929999999999996</v>
+        <v>2793433</v>
       </c>
       <c r="J18" s="4">
-        <v>34.18000000000001</v>
+        <v>3416792</v>
       </c>
     </row>
     <row r="19">
@@ -1796,105 +1796,105 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>8.086956521739127</v>
+        <v>8.078797101449275</v>
       </c>
       <c r="C19" s="2">
-        <v>7.9097222222222205</v>
+        <v>7.908048611111111</v>
       </c>
       <c r="D19" s="2">
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>8.108974358974361</v>
+        <v>8.109230769230768</v>
       </c>
       <c r="F19" s="2">
-        <v>8.413461538461542</v>
+        <v>8.414866863905326</v>
       </c>
       <c r="G19" s="2">
-        <v>9.159270755913088</v>
+        <v>9.154110355633902</v>
       </c>
       <c r="H19" s="2">
-        <v>9.023662756015115</v>
+        <v>9.027967729047825</v>
       </c>
       <c r="I19" s="2">
-        <v>10.06740439029665</v>
+        <v>10.068944094050483</v>
       </c>
       <c r="J19" s="2">
-        <v>11.124491456468675</v>
+        <v>11.12044000437294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-18 経常利益（億円）</t>
+          <t xml:space="preserve">2-18 経常利益（千円）</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <v>10.67</v>
+        <v>1067200</v>
       </c>
       <c r="C20" s="4">
-        <v>11.14</v>
+        <v>1113600</v>
       </c>
       <c r="D20" s="4">
-        <v>11.600000000000003</v>
+        <v>1160000</v>
       </c>
       <c r="E20" s="4">
-        <v>11.87</v>
+        <v>1187040</v>
       </c>
       <c r="F20" s="4">
-        <v>12.84</v>
+        <v>1284108</v>
       </c>
       <c r="G20" s="4">
-        <v>20.11</v>
+        <v>2009451</v>
       </c>
       <c r="H20" s="4">
-        <v>21.8</v>
+        <v>2180686</v>
       </c>
       <c r="I20" s="4">
-        <v>26.98</v>
+        <v>2698641</v>
       </c>
       <c r="J20" s="4">
-        <v>33.18</v>
+        <v>3316312</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-19 税引前当期純利益（億円）</t>
+          <t xml:space="preserve">2-19 税引前当期純利益（千円）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>10.67</v>
+        <v>1067200</v>
       </c>
       <c r="C21" s="2">
-        <v>11.14</v>
+        <v>1113600</v>
       </c>
       <c r="D21" s="2">
-        <v>11.600000000000003</v>
+        <v>1160000</v>
       </c>
       <c r="E21" s="2">
-        <v>11.87</v>
+        <v>1187040</v>
       </c>
       <c r="F21" s="2">
-        <v>12.84</v>
+        <v>1284108</v>
       </c>
       <c r="G21" s="2">
-        <v>20.11</v>
+        <v>2009451</v>
       </c>
       <c r="H21" s="2">
-        <v>21.8</v>
+        <v>2180686</v>
       </c>
       <c r="I21" s="2">
-        <v>26.98</v>
+        <v>2698641</v>
       </c>
       <c r="J21" s="2">
-        <v>33.18</v>
+        <v>3316312</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-20 当期純利益（億円）</t>
+          <t xml:space="preserve">2-20 当期純利益（千円）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -1907,158 +1907,158 @@
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>8.31</v>
+        <v>830928</v>
       </c>
       <c r="F22" s="2">
-        <v>8.99</v>
+        <v>898876</v>
       </c>
       <c r="G22" s="2">
-        <v>14.080000000000002</v>
+        <v>1406616</v>
       </c>
       <c r="H22" s="2">
-        <v>15.260000000000002</v>
+        <v>1526480</v>
       </c>
       <c r="I22" s="2">
-        <v>18.89</v>
+        <v>1889048</v>
       </c>
       <c r="J22" s="2">
-        <v>23.23</v>
+        <v>2321419</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-21 給与支給総額（常時使用する従業員）（億円）</t>
+          <t xml:space="preserve">2-21 給与支給総額（常時使用する従業員）（千円）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>12.4</v>
+        <v>1240326</v>
       </c>
       <c r="C23" s="2">
-        <v>13.19</v>
+        <v>1318841</v>
       </c>
       <c r="D23" s="2">
-        <v>14</v>
+        <v>1400000</v>
       </c>
       <c r="E23" s="2">
-        <v>14.71</v>
+        <v>1470560</v>
       </c>
       <c r="F23" s="2">
-        <v>15.45</v>
+        <v>1544676</v>
       </c>
       <c r="G23" s="2">
-        <v>21.03</v>
+        <v>2102528</v>
       </c>
       <c r="H23" s="2">
-        <v>22.55</v>
+        <v>2255119</v>
       </c>
       <c r="I23" s="2">
-        <v>24.19</v>
+        <v>2419790</v>
       </c>
       <c r="J23" s="2">
-        <v>25.97</v>
+        <v>2597594</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-22 給与支給総額（役員）（億円）</t>
+          <t xml:space="preserve">2-22 給与支給総額（役員）（千円）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0.92</v>
+        <v>92000</v>
       </c>
       <c r="C24" s="2">
-        <v>0.96</v>
+        <v>96000</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="E24" s="2">
-        <v>1.04</v>
+        <v>104000</v>
       </c>
       <c r="F24" s="2">
-        <v>1.08</v>
+        <v>108160</v>
       </c>
       <c r="G24" s="2">
-        <v>1.4200000000000002</v>
+        <v>142486</v>
       </c>
       <c r="H24" s="2">
-        <v>1.5</v>
+        <v>149348</v>
       </c>
       <c r="I24" s="2">
-        <v>1.57</v>
+        <v>156546</v>
       </c>
       <c r="J24" s="2">
-        <v>1.6400000000000001</v>
+        <v>164096</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-23 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">2-23 減価償却費（合計）（千円）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>3.22</v>
+        <v>322000</v>
       </c>
       <c r="C25" s="2">
-        <v>3.36</v>
+        <v>336000</v>
       </c>
       <c r="D25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="E25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="F25" s="2">
-        <v>3.5</v>
+        <v>350000</v>
       </c>
       <c r="G25" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="H25" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="I25" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="J25" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-24 付加価値額（億円）</t>
+          <t xml:space="preserve">2-24 付加価値額（千円）</t>
         </is>
       </c>
       <c r="B26" s="4">
-        <v>27.699999999999996</v>
+        <v>2769200</v>
       </c>
       <c r="C26" s="4">
-        <v>28.9</v>
+        <v>2889600</v>
       </c>
       <c r="D26" s="4">
-        <v>30.1</v>
+        <v>3010000</v>
       </c>
       <c r="E26" s="4">
-        <v>31.900000000000006</v>
+        <v>3189600</v>
       </c>
       <c r="F26" s="4">
-        <v>33.68000000000001</v>
+        <v>3368064</v>
       </c>
       <c r="G26" s="4">
-        <v>51.400000000000006</v>
+        <v>5138830</v>
       </c>
       <c r="H26" s="4">
-        <v>54.74000000000001</v>
+        <v>5474580</v>
       </c>
       <c r="I26" s="4">
-        <v>61.69</v>
+        <v>6169769</v>
       </c>
       <c r="J26" s="4">
-        <v>69.79</v>
+        <v>6978482</v>
       </c>
     </row>
     <row r="27">
@@ -2073,28 +2073,28 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>4.332129963898934</v>
+        <v>4.347826086956519</v>
       </c>
       <c r="D27" s="2">
-        <v>4.152249134948116</v>
+        <v>4.166666666666674</v>
       </c>
       <c r="E27" s="2">
-        <v>5.980066445182741</v>
+        <v>5.966777408637869</v>
       </c>
       <c r="F27" s="2">
-        <v>5.579937304075244</v>
+        <v>5.595184349134685</v>
       </c>
       <c r="G27" s="2">
-        <v>52.6128266033254</v>
+        <v>52.57518859499106</v>
       </c>
       <c r="H27" s="2">
-        <v>6.49805447470817</v>
+        <v>6.533588384904743</v>
       </c>
       <c r="I27" s="2">
-        <v>12.69638290098647</v>
+        <v>12.698490112483519</v>
       </c>
       <c r="J27" s="2">
-        <v>13.130166963851519</v>
+        <v>13.10767064374696</v>
       </c>
     </row>
     <row r="28">
@@ -2104,31 +2104,31 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <v>20.072463768115938</v>
+        <v>20.066666666666666</v>
       </c>
       <c r="C28" s="2">
-        <v>20.069444444444443</v>
+        <v>20.066666666666666</v>
       </c>
       <c r="D28" s="2">
-        <v>20.06666666666667</v>
+        <v>20.066666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>20.448717948717952</v>
+        <v>20.446153846153848</v>
       </c>
       <c r="F28" s="2">
-        <v>20.759368836291916</v>
+        <v>20.759763313609465</v>
       </c>
       <c r="G28" s="2">
-        <v>22.471910112359552</v>
+        <v>22.466834200733093</v>
       </c>
       <c r="H28" s="2">
-        <v>21.769735533903365</v>
+        <v>21.771749498853428</v>
       </c>
       <c r="I28" s="2">
-        <v>22.236239772194786</v>
+        <v>22.23896514940783</v>
       </c>
       <c r="J28" s="2">
-        <v>22.71440195280716</v>
+        <v>22.71247134815244</v>
       </c>
     </row>
     <row r="29">
@@ -2202,35 +2202,35 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-29 従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">2-29 従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>0.05849056603773585</v>
+        <v>5850.594339622641</v>
       </c>
       <c r="C31" s="2">
-        <v>0.059683257918552036</v>
+        <v>5967.606334841629</v>
       </c>
       <c r="D31" s="2">
-        <v>0.06086956521739131</v>
+        <v>6086.95652173913</v>
       </c>
       <c r="E31" s="2">
-        <v>0.0634051724137931</v>
+        <v>6338.620689655172</v>
       </c>
       <c r="F31" s="2">
-        <v>0.06574468085106383</v>
+        <v>6573.0893617021275</v>
       </c>
       <c r="G31" s="2">
-        <v>0.07378947368421053</v>
+        <v>7377.291228070176</v>
       </c>
       <c r="H31" s="2">
-        <v>0.0774914089347079</v>
+        <v>7749.549828178694</v>
       </c>
       <c r="I31" s="2">
-        <v>0.08172297297297297</v>
+        <v>8174.966216216216</v>
       </c>
       <c r="J31" s="2">
-        <v>0.08599337748344371</v>
+        <v>8601.30463576159</v>
       </c>
     </row>
     <row r="32">
@@ -2245,62 +2245,62 @@
         </is>
       </c>
       <c r="C32" s="2">
-        <v>2.0391183768792898</v>
+        <v>2.00000185325675</v>
       </c>
       <c r="D32" s="2">
-        <v>1.9876718198899024</v>
+        <v>1.999967494515853</v>
       </c>
       <c r="E32" s="2">
-        <v>4.1656403940886655</v>
+        <v>4.1344827586206945</v>
       </c>
       <c r="F32" s="2">
-        <v>3.689775373533699</v>
+        <v>3.6990487919495774</v>
       </c>
       <c r="G32" s="2">
-        <v>12.23641628342702</v>
+        <v>12.234762409495016</v>
       </c>
       <c r="H32" s="2">
-        <v>5.016887999960784</v>
+        <v>5.04600657070573</v>
       </c>
       <c r="I32" s="2">
-        <v>5.460687960687949</v>
+        <v>5.48956258711486</v>
       </c>
       <c r="J32" s="2">
-        <v>5.225463973126665</v>
+        <v>5.215170415012493</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-31 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">2-31 役員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>0.184</v>
+        <v>18400</v>
       </c>
       <c r="C33" s="2">
-        <v>0.192</v>
+        <v>19200</v>
       </c>
       <c r="D33" s="2">
-        <v>0.2</v>
+        <v>20000</v>
       </c>
       <c r="E33" s="2">
-        <v>0.20800000000000002</v>
+        <v>20800</v>
       </c>
       <c r="F33" s="2">
-        <v>0.21600000000000003</v>
+        <v>21632</v>
       </c>
       <c r="G33" s="2">
-        <v>0.20285714285714287</v>
+        <v>20355.14285714286</v>
       </c>
       <c r="H33" s="2">
-        <v>0.21428571428571427</v>
+        <v>21335.428571428572</v>
       </c>
       <c r="I33" s="2">
-        <v>0.22428571428571428</v>
+        <v>22363.714285714286</v>
       </c>
       <c r="J33" s="2">
-        <v>0.2342857142857143</v>
+        <v>23442.285714285714</v>
       </c>
     </row>
     <row r="34">
@@ -2324,87 +2324,87 @@
         <v>4.0000000000000036</v>
       </c>
       <c r="F34" s="2">
-        <v>3.8461538461538547</v>
+        <v>4.0000000000000036</v>
       </c>
       <c r="G34" s="2">
-        <v>-6.084656084656093</v>
+        <v>-5.902631022823323</v>
       </c>
       <c r="H34" s="2">
-        <v>5.633802816901401</v>
+        <v>4.815911738697132</v>
       </c>
       <c r="I34" s="2">
-        <v>4.666666666666663</v>
+        <v>4.819615930578247</v>
       </c>
       <c r="J34" s="2">
-        <v>4.458598726114649</v>
+        <v>4.822863567258184</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-33 労働生産性（億円/人）</t>
+          <t xml:space="preserve">2-33 労働生産性（千円/人）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>0.12764976958525343</v>
+        <v>12761.290322580646</v>
       </c>
       <c r="C35" s="2">
-        <v>0.12787610619469025</v>
+        <v>12785.840707964602</v>
       </c>
       <c r="D35" s="2">
-        <v>0.12808510638297874</v>
+        <v>12808.510638297872</v>
       </c>
       <c r="E35" s="2">
-        <v>0.1345991561181435</v>
+        <v>13458.227848101265</v>
       </c>
       <c r="F35" s="2">
-        <v>0.14033333333333337</v>
+        <v>14033.6</v>
       </c>
       <c r="G35" s="2">
-        <v>0.176027397260274</v>
+        <v>17598.73287671233</v>
       </c>
       <c r="H35" s="2">
-        <v>0.18369127516778527</v>
+        <v>18371.073825503358</v>
       </c>
       <c r="I35" s="2">
-        <v>0.2035973597359736</v>
+        <v>20362.27392739274</v>
       </c>
       <c r="J35" s="2">
-        <v>0.22585760517799355</v>
+        <v>22584.084142394822</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-34 EBITDA（億円）</t>
+          <t xml:space="preserve">2-34 EBITDA（千円）</t>
         </is>
       </c>
       <c r="B36" s="4">
-        <v>14.379999999999997</v>
+        <v>1436874</v>
       </c>
       <c r="C36" s="4">
-        <v>14.749999999999996</v>
+        <v>1474759</v>
       </c>
       <c r="D36" s="4">
-        <v>15.100000000000001</v>
+        <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>16.150000000000006</v>
+        <v>1615040</v>
       </c>
       <c r="F36" s="4">
-        <v>17.150000000000006</v>
+        <v>1715228</v>
       </c>
       <c r="G36" s="4">
-        <v>28.950000000000003</v>
+        <v>2893816</v>
       </c>
       <c r="H36" s="4">
-        <v>30.690000000000005</v>
+        <v>3070113</v>
       </c>
       <c r="I36" s="4">
-        <v>35.92999999999999</v>
+        <v>3593433</v>
       </c>
       <c r="J36" s="4">
-        <v>42.18000000000001</v>
+        <v>4216792</v>
       </c>
     </row>
     <row r="37">
@@ -2414,31 +2414,31 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <v>10.420289855072461</v>
+        <v>10.41213043478261</v>
       </c>
       <c r="C37" s="2">
-        <v>10.243055555555552</v>
+        <v>10.241381944444445</v>
       </c>
       <c r="D37" s="2">
-        <v>10.066666666666668</v>
+        <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>10.352564102564106</v>
+        <v>10.352820512820513</v>
       </c>
       <c r="F37" s="2">
-        <v>10.570759368836296</v>
+        <v>10.572164694280078</v>
       </c>
       <c r="G37" s="2">
-        <v>12.656844314256984</v>
+        <v>12.651690030498894</v>
       </c>
       <c r="H37" s="2">
-        <v>12.20520978325711</v>
+        <v>12.209471990394402</v>
       </c>
       <c r="I37" s="2">
-        <v>12.951014670367297</v>
+        <v>12.952548345607756</v>
       </c>
       <c r="J37" s="2">
-        <v>13.728234336859238</v>
+        <v>13.724154834979647</v>
       </c>
     </row>
     <row r="38">
@@ -2453,28 +2453,28 @@
         </is>
       </c>
       <c r="C38" s="2">
-        <v>2.5730180806675884</v>
+        <v>2.6366264543724816</v>
       </c>
       <c r="D38" s="2">
-        <v>2.3728813559322326</v>
+        <v>2.3896107770829067</v>
       </c>
       <c r="E38" s="2">
-        <v>6.953642384105985</v>
+        <v>6.956291390728486</v>
       </c>
       <c r="F38" s="2">
-        <v>6.19195046439629</v>
+        <v>6.20343768575391</v>
       </c>
       <c r="G38" s="2">
-        <v>68.80466472303203</v>
+        <v>68.71319731254385</v>
       </c>
       <c r="H38" s="2">
-        <v>6.010362694300531</v>
+        <v>6.0921979835621975</v>
       </c>
       <c r="I38" s="2">
-        <v>17.07396546106219</v>
+        <v>17.04562665934446</v>
       </c>
       <c r="J38" s="2">
-        <v>17.394934595045974</v>
+        <v>17.347171910537917</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2614,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-1 売上高（億円）</t>
+          <t xml:space="preserve">7-1 売上高（千円）</t>
         </is>
       </c>
       <c r="B3" s="4">
@@ -2633,16 +2633,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <v>60</v>
+        <v>6000000</v>
       </c>
       <c r="H3" s="4">
-        <v>72.6</v>
+        <v>7260000</v>
       </c>
       <c r="I3" s="4">
-        <v>87.85</v>
+        <v>8784600</v>
       </c>
       <c r="J3" s="4">
-        <v>106.29</v>
+        <v>10629366</v>
       </c>
     </row>
     <row r="4">
@@ -2685,10 +2685,10 @@
         <v>20.999999999999996</v>
       </c>
       <c r="I4" s="2">
-        <v>21.00550964187329</v>
+        <v>20.999999999999996</v>
       </c>
       <c r="J4" s="2">
-        <v>20.990324416619256</v>
+        <v>20.999999999999996</v>
       </c>
     </row>
     <row r="5">
@@ -2713,22 +2713,22 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>26.231801687579242</v>
+        <v>26.23184756148745</v>
       </c>
       <c r="H5" s="2">
-        <v>28.872539272221115</v>
+        <v>28.872151171720184</v>
       </c>
       <c r="I5" s="2">
-        <v>31.665645388025805</v>
+        <v>31.66413738528752</v>
       </c>
       <c r="J5" s="2">
-        <v>34.593978844589095</v>
+        <v>34.59479736768336</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-4 売上総利益（億円）</t>
+          <t xml:space="preserve">7-4 売上総利益（千円）</t>
         </is>
       </c>
       <c r="B6" s="4">
@@ -2747,16 +2747,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <v>21</v>
+        <v>2100000</v>
       </c>
       <c r="H6" s="4">
-        <v>23.229999999999997</v>
+        <v>2323200</v>
       </c>
       <c r="I6" s="4">
-        <v>28.109999999999992</v>
+        <v>2811072</v>
       </c>
       <c r="J6" s="4">
-        <v>34.010000000000005</v>
+        <v>3401397</v>
       </c>
     </row>
     <row r="7">
@@ -2794,19 +2794,19 @@
         <v>35</v>
       </c>
       <c r="H7" s="2">
-        <v>31.99724517906336</v>
+        <v>32</v>
       </c>
       <c r="I7" s="2">
-        <v>31.997723392145694</v>
+        <v>32</v>
       </c>
       <c r="J7" s="2">
-        <v>31.997365697619724</v>
+        <v>31.99999887105214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-6 営業利益（億円）</t>
+          <t xml:space="preserve">7-6 営業利益（千円）</t>
         </is>
       </c>
       <c r="B8" s="4">
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>6.229999999999997</v>
+        <v>623000</v>
       </c>
       <c r="H8" s="4">
-        <v>6.939999999999996</v>
+        <v>694256</v>
       </c>
       <c r="I8" s="4">
-        <v>10.109999999999989</v>
+        <v>1011432</v>
       </c>
       <c r="J8" s="4">
-        <v>14.110000000000005</v>
+        <v>1410581</v>
       </c>
     </row>
     <row r="9">
@@ -2869,22 +2869,22 @@
         </is>
       </c>
       <c r="G9" s="2">
-        <v>10.383333333333328</v>
+        <v>10.383333333333333</v>
       </c>
       <c r="H9" s="2">
-        <v>9.559228650137737</v>
+        <v>9.56275482093664</v>
       </c>
       <c r="I9" s="2">
-        <v>11.508252703471815</v>
+        <v>11.51369441978007</v>
       </c>
       <c r="J9" s="2">
-        <v>13.2750023520557</v>
+        <v>13.270603345486457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8 給与支給総額（常時使用する従業員）（億円）</t>
+          <t xml:space="preserve">7-8 給与支給総額（常時使用する従業員）（千円）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -2903,22 +2903,22 @@
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>4.8</v>
+        <v>480000</v>
       </c>
       <c r="H10" s="2">
-        <v>5.34</v>
+        <v>534144</v>
       </c>
       <c r="I10" s="2">
-        <v>5.94</v>
+        <v>594395</v>
       </c>
       <c r="J10" s="2">
-        <v>6.61</v>
+        <v>661443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-9 給与支給総額（役員）（億円）</t>
+          <t xml:space="preserve">7-9 給与支給総額（役員）（千円）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -2937,22 +2937,22 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>0.3</v>
+        <v>30000</v>
       </c>
       <c r="H11" s="2">
-        <v>0.32</v>
+        <v>31800</v>
       </c>
       <c r="I11" s="2">
-        <v>0.34</v>
+        <v>33708</v>
       </c>
       <c r="J11" s="2">
-        <v>0.36</v>
+        <v>35730</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（億円）</t>
+          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（千円）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -2971,22 +2971,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>1.13</v>
+        <v>113000</v>
       </c>
       <c r="H12" s="2">
-        <v>1.13</v>
+        <v>113000</v>
       </c>
       <c r="I12" s="2">
-        <v>1.13</v>
+        <v>113000</v>
       </c>
       <c r="J12" s="2">
-        <v>1.13</v>
+        <v>113000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（億円）</t>
+          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（千円）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -3005,22 +3005,22 @@
         <v>0</v>
       </c>
       <c r="G13" s="2">
-        <v>3.37</v>
+        <v>337000</v>
       </c>
       <c r="H13" s="2">
-        <v>3.37</v>
+        <v>337000</v>
       </c>
       <c r="I13" s="2">
-        <v>3.37</v>
+        <v>337000</v>
       </c>
       <c r="J13" s="2">
-        <v>3.37</v>
+        <v>337000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">7-10 減価償却費（合計）（千円）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -3039,22 +3039,22 @@
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <v>4.5</v>
+        <v>450000</v>
       </c>
       <c r="H14" s="2">
-        <v>4.5</v>
+        <v>450000</v>
       </c>
       <c r="I14" s="2">
-        <v>4.5</v>
+        <v>450000</v>
       </c>
       <c r="J14" s="2">
-        <v>4.5</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-11 付加価値（億円）</t>
+          <t xml:space="preserve">7-11 付加価値（千円）</t>
         </is>
       </c>
       <c r="B15" s="4">
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>15.829999999999998</v>
+        <v>1583000</v>
       </c>
       <c r="H15" s="4">
-        <v>17.099999999999994</v>
+        <v>1710200</v>
       </c>
       <c r="I15" s="4">
-        <v>20.88999999999999</v>
+        <v>2089535</v>
       </c>
       <c r="J15" s="4">
-        <v>25.580000000000005</v>
+        <v>2557754</v>
       </c>
     </row>
     <row r="16">
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="H16" s="2">
-        <v>8.022741629816776</v>
+        <v>8.035375868603921</v>
       </c>
       <c r="I16" s="2">
-        <v>22.163742690058452</v>
+        <v>22.180739094842707</v>
       </c>
       <c r="J16" s="2">
-        <v>22.45093346098621</v>
+        <v>22.407808435848175</v>
       </c>
     </row>
     <row r="17">
@@ -3202,7 +3202,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
@@ -3231,16 +3231,16 @@
         </is>
       </c>
       <c r="G19" s="2">
-        <v>0.09999999999999999</v>
+        <v>10000</v>
       </c>
       <c r="H19" s="2">
-        <v>0.10679999999999999</v>
+        <v>10682.88</v>
       </c>
       <c r="I19" s="2">
-        <v>0.11423076923076923</v>
+        <v>11430.673076923076</v>
       </c>
       <c r="J19" s="2">
-        <v>0.12240740740740741</v>
+        <v>12248.944444444445</v>
       </c>
     </row>
     <row r="20">
@@ -3280,19 +3280,19 @@
         </is>
       </c>
       <c r="H20" s="2">
-        <v>6.800000000000006</v>
+        <v>6.82879999999999</v>
       </c>
       <c r="I20" s="2">
-        <v>6.957649092480556</v>
+        <v>6.999920217423372</v>
       </c>
       <c r="J20" s="2">
-        <v>7.157999750592348</v>
+        <v>7.158558048286268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -3321,16 +3321,16 @@
         </is>
       </c>
       <c r="G21" s="2">
-        <v>0.15</v>
+        <v>15000</v>
       </c>
       <c r="H21" s="2">
-        <v>0.16</v>
+        <v>15900</v>
       </c>
       <c r="I21" s="2">
-        <v>0.17</v>
+        <v>16854</v>
       </c>
       <c r="J21" s="2">
-        <v>0.18</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="22">
@@ -3370,19 +3370,19 @@
         </is>
       </c>
       <c r="H22" s="2">
-        <v>6.666666666666665</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="I22" s="2">
-        <v>6.25</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="J22" s="2">
-        <v>5.88235294117645</v>
+        <v>5.998576005695977</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+          <t xml:space="preserve">7-19 労働生産性（千円/人）</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
@@ -3411,16 +3411,16 @@
         </is>
       </c>
       <c r="G23" s="2">
-        <v>0.3166</v>
+        <v>31660</v>
       </c>
       <c r="H23" s="2">
-        <v>0.32884615384615373</v>
+        <v>32888.46153846154</v>
       </c>
       <c r="I23" s="2">
-        <v>0.38685185185185167</v>
+        <v>38695.09259259259</v>
       </c>
       <c r="J23" s="2">
-        <v>0.4567857142857144</v>
+        <v>45674.17857142857</v>
       </c>
     </row>
     <row r="24">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.33 % / 補助 21.01 % / ベース 6 %</t>
+          <t xml:space="preserve">全社 10.33 % / 補助 21 % / ベース 6 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.75 % / 補助 20.99 % / ベース 6 %</t>
+          <t xml:space="preserve">全社 10.75 % / 補助 21 % / ベース 6 %</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.91 % / 補助 — / ベース 23.91 %</t>
+          <t xml:space="preserve">全社 23.92 % / 補助 — / ベース 23.92 %</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.21 % / 補助 22.44 % / ベース 23.53 %</t>
+          <t xml:space="preserve">全社 23.21 % / 補助 22.44 % / ベース 23.52 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.53 % / 補助 18.72 % / ベース 23.01 %</t>
+          <t xml:space="preserve">全社 21.53 % / 補助 18.73 % / ベース 23.02 %</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.09 % / 補助 — / ベース 8.09 %</t>
+          <t xml:space="preserve">全社 8.08 % / 補助 — / ベース 8.08 %</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.16 % / 補助 10.38 % / ベース 8.72 %</t>
+          <t xml:space="preserve">全社 9.15 % / 補助 10.38 % / ベース 8.72 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.02 % / 補助 9.56 % / ベース 8.81 %</t>
+          <t xml:space="preserve">全社 9.03 % / 補助 9.56 % / ベース 8.81 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.12 % / 補助 13.28 % / ベース 9.99 %</t>
+          <t xml:space="preserve">全社 11.12 % / 補助 13.27 % / ベース 9.98 %</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.42 % / 補助 — / ベース 10.42 %</t>
+          <t xml:space="preserve">全社 10.41 % / 補助 — / ベース 10.41 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -4053,22 +4053,22 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.66 % / 補助 17.88 % / ベース 10.8 %</t>
+          <t xml:space="preserve">全社 12.65 % / 補助 17.88 % / ベース 10.79 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.21 % / 補助 15.76 % / ベース 10.76 %</t>
+          <t xml:space="preserve">全社 12.21 % / 補助 15.76 % / ベース 10.77 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.95 % / 補助 16.63 % / ベース 11.25 %</t>
+          <t xml:space="preserve">全社 12.95 % / 補助 16.64 % / ベース 11.25 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.73 % / 補助 17.51 % / ベース 11.73 %</t>
+          <t xml:space="preserve">全社 13.72 % / 補助 17.5 % / ベース 11.72 %</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.1 % / 補助 10 % / ベース 11.5 %</t>
+          <t xml:space="preserve">全社 11.11 % / 補助 10 % / ベース 11.5 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.81 % / 補助 9.5 % / ベース 11.33 %</t>
+          <t xml:space="preserve">全社 10.8 % / 補助 9.5 % / ベース 11.33 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.72 % / 補助 6.76 % / ベース 9.63 %</t>
+          <t xml:space="preserve">全社 8.72 % / 補助 6.77 % / ベース 9.63 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.62 % / 補助 0.5 % / ベース 0.66 %</t>
+          <t xml:space="preserve">全社 0.62 % / 補助 0.5 % / ベース 0.67 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.6 % / 補助 0.44 % / ベース 0.66 %</t>
+          <t xml:space="preserve">全社 0.59 % / 補助 0.44 % / ベース 0.66 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.57 % / 補助 0.39 % / ベース 0.65 %</t>
+          <t xml:space="preserve">全社 0.56 % / 補助 0.38 % / ベース 0.65 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.1 % / 補助 — / ベース 10.1 %</t>
+          <t xml:space="preserve">全社 10.09 % / 補助 — / ベース 10.09 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -4385,7 +4385,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -4400,54 +4400,54 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / ベース 0.058 億円/人</t>
+          <t xml:space="preserve">全社 5,850.59 千円/人 / 補助 — / ベース 5,850.59 千円/人</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.06 億円/人 / 補助 — / ベース 0.06 億円/人</t>
+          <t xml:space="preserve">全社 5,967.61 千円/人 / 補助 — / ベース 5,967.61 千円/人</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 — / ベース 0.061 億円/人</t>
+          <t xml:space="preserve">全社 6,086.96 千円/人 / 補助 — / ベース 6,086.96 千円/人</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 — / ベース 0.063 億円/人</t>
+          <t xml:space="preserve">全社 6,338.62 千円/人 / 補助 — / ベース 6,338.62 千円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 — / ベース 0.066 億円/人</t>
+          <t xml:space="preserve">全社 6,573.09 千円/人 / 補助 — / ベース 6,573.09 千円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.1 億円/人 / ベース 0.068 億円/人</t>
+          <t xml:space="preserve">全社 7,377.29 千円/人 / 補助 10,000 千円/人 / ベース 6,846.11 千円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.077 億円/人 / 補助 0.107 億円/人 / ベース 0.071 億円/人</t>
+          <t xml:space="preserve">全社 7,749.55 千円/人 / 補助 10,682.88 千円/人 / ベース 7,140.98 千円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.114 億円/人 / ベース 0.075 億円/人</t>
+          <t xml:space="preserve">全社 8,174.97 千円/人 / 補助 11,430.67 千円/人 / ベース 7,481.13 千円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.086 億円/人 / 補助 0.122 億円/人 / ベース 0.078 億円/人</t>
+          <t xml:space="preserve">全社 8,601.3 千円/人 / 補助 12,248.94 千円/人 / ベース 7,807.06 千円/人</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額（参考）（億円/人）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額（参考）（千円/人）</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -4462,47 +4462,47 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.184 億円/人 / 補助 — / ベース 0.184 億円/人</t>
+          <t xml:space="preserve">全社 18,400 千円/人 / 補助 — / ベース 18,400 千円/人</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.192 億円/人 / 補助 — / ベース 0.192 億円/人</t>
+          <t xml:space="preserve">全社 19,200 千円/人 / 補助 — / ベース 19,200 千円/人</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 — / ベース 0.2 億円/人</t>
+          <t xml:space="preserve">全社 20,000 千円/人 / 補助 — / ベース 20,000 千円/人</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.208 億円/人 / 補助 — / ベース 0.208 億円/人</t>
+          <t xml:space="preserve">全社 20,800 千円/人 / 補助 — / ベース 20,800 千円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.216 億円/人 / 補助 — / ベース 0.216 億円/人</t>
+          <t xml:space="preserve">全社 21,632 千円/人 / 補助 — / ベース 21,632 千円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.203 億円/人 / 補助 0.15 億円/人 / ベース 0.224 億円/人</t>
+          <t xml:space="preserve">全社 20,355.14 千円/人 / 補助 15,000 千円/人 / ベース 22,497.2 千円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.214 億円/人 / 補助 0.16 億円/人 / ベース 0.236 億円/人</t>
+          <t xml:space="preserve">全社 21,335.43 千円/人 / 補助 15,900 千円/人 / ベース 23,509.6 千円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.224 億円/人 / 補助 0.17 億円/人 / ベース 0.246 億円/人</t>
+          <t xml:space="preserve">全社 22,363.71 千円/人 / 補助 16,854 千円/人 / ベース 24,567.6 千円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.234 億円/人 / 補助 0.18 億円/人 / ベース 0.256 億円/人</t>
+          <t xml:space="preserve">全社 23,442.29 千円/人 / 補助 17,865 千円/人 / ベース 25,673.2 千円/人</t>
         </is>
       </c>
     </row>
@@ -4529,42 +4529,42 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.04 % / 補助 — / ベース 2.04 %</t>
+          <t xml:space="preserve">全社 2 % / 補助 — / ベース 2 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.99 % / 補助 — / ベース 1.99 %</t>
+          <t xml:space="preserve">全社 2 % / 補助 — / ベース 2 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 % / 補助 — / ベース 4.17 %</t>
+          <t xml:space="preserve">全社 4.13 % / 補助 — / ベース 4.13 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 % / 補助 — / ベース 3.69 %</t>
+          <t xml:space="preserve">全社 3.7 % / 補助 — / ベース 3.7 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 % / 補助 — / ベース 4.16 %</t>
+          <t xml:space="preserve">全社 12.23 % / 補助 — / ベース 4.15 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.02 % / 補助 6.8 % / ベース 4.28 %</t>
+          <t xml:space="preserve">全社 5.05 % / 補助 6.83 % / ベース 4.31 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.46 % / 補助 6.96 % / ベース 4.74 %</t>
+          <t xml:space="preserve">全社 5.49 % / 補助 7 % / ベース 4.76 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.23 % / 補助 7.16 % / ベース 4.37 %</t>
+          <t xml:space="preserve">全社 5.22 % / 補助 7.16 % / ベース 4.36 %</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.09 % / 補助 — / ベース 48.09 %</t>
+          <t xml:space="preserve">全社 48.11 % / 補助 — / ベース 48.11 %</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -4606,17 +4606,17 @@
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.08 % / 補助 — / ベース 49.08 %</t>
+          <t xml:space="preserve">全社 49.07 % / 補助 — / ベース 49.07 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.68 % / 補助 32.22 % / ベース 48.78 %</t>
+          <t xml:space="preserve">全社 43.69 % / 補助 32.22 % / ベース 48.79 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.93 % / 補助 33.1 % / ベース 48.86 %</t>
+          <t xml:space="preserve">全社 43.92 % / 補助 33.09 % / ベース 48.84 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.56 % / 補助 27.25 % / ベース 46.69 %</t>
+          <t xml:space="preserve">全社 39.57 % / 補助 27.26 % / ベース 46.7 %</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">従業員1人当たり売上高（億円/人）</t>
+          <t xml:space="preserve">従業員1人当たり売上高（千円/人）</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -4710,54 +4710,54 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.651 億円/人 / 補助 — / ベース 0.651 億円/人</t>
+          <t xml:space="preserve">全社 65,094.34 千円/人 / 補助 — / ベース 65,094.34 千円/人</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / ベース 0.652 億円/人</t>
+          <t xml:space="preserve">全社 65,158.37 千円/人 / 補助 — / ベース 65,158.37 千円/人</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 — / ベース 0.652 億円/人</t>
+          <t xml:space="preserve">全社 65,217.39 千円/人 / 補助 — / ベース 65,217.39 千円/人</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.672 億円/人 / 補助 — / ベース 0.672 億円/人</t>
+          <t xml:space="preserve">全社 67,241.38 千円/人 / 補助 — / ベース 67,241.38 千円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.69 億円/人 / 補助 — / ベース 0.69 億円/人</t>
+          <t xml:space="preserve">全社 69,038.3 千円/人 / 補助 — / ベース 69,038.3 千円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.803 億円/人 / 補助 1.25 億円/人 / ベース 0.712 億円/人</t>
+          <t xml:space="preserve">全社 80,256 千円/人 / 補助 125,000 千円/人 / ベース 71,193.92 千円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.864 億円/人 / 補助 1.452 億円/人 / ベース 0.742 億円/人</t>
+          <t xml:space="preserve">全社 86,410.1 千円/人 / 補助 145,200 千円/人 / ベース 74,213.02 千円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.937 億円/人 / 補助 1.689 億円/人 / ベース 0.777 億円/人</t>
+          <t xml:space="preserve">全社 93,726.55 千円/人 / 補助 168,934.62 千円/人 / ベース 77,698.6 千円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.968 億円/人 / ベース 0.81 億円/人</t>
+          <t xml:space="preserve">全社 101,739.51 千円/人 / 補助 196,840.11 千円/人 / ベース 81,032.12 千円/人</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1人当たり営業利益（億円/人）</t>
+          <t xml:space="preserve">1人当たり営業利益（千円/人）</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -4772,54 +4772,54 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.053 億円/人 / 補助 — / ベース 0.053 億円/人</t>
+          <t xml:space="preserve">全社 5,258.84 千円/人 / 補助 — / ベース 5,258.84 千円/人</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.052 億円/人 / 補助 — / ベース 0.052 億円/人</t>
+          <t xml:space="preserve">全社 5,152.76 千円/人 / 補助 — / ベース 5,152.76 千円/人</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 — / ベース 0.05 億円/人</t>
+          <t xml:space="preserve">全社 5,043.48 千円/人 / 補助 — / ベース 5,043.48 千円/人</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.055 億円/人 / 補助 — / ベース 0.055 億円/人</t>
+          <t xml:space="preserve">全社 5,452.76 千円/人 / 補助 — / ベース 5,452.76 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.058 億円/人 / 補助 — / ベース 0.058 億円/人</t>
+          <t xml:space="preserve">全社 5,809.48 千円/人 / 補助 — / ベース 5,809.48 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.13 億円/人 / ベース 0.062 億円/人</t>
+          <t xml:space="preserve">全社 7,346.72 千円/人 / 補助 12,979.17 千円/人 / ベース 6,205.97 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.078 億円/人 / 補助 0.139 億円/人 / ベース 0.065 億円/人</t>
+          <t xml:space="preserve">全社 7,801.08 千円/人 / 補助 13,885.12 千円/人 / ベース 6,538.83 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.094 億円/人 / 補助 0.194 億円/人 / ベース 0.073 億円/人</t>
+          <t xml:space="preserve">全社 9,437.27 千円/人 / 補助 19,450.62 千円/人 / ベース 7,303.28 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.113 億円/人 / 補助 0.261 億円/人 / ベース 0.081 億円/人</t>
+          <t xml:space="preserve">全社 11,313.88 千円/人 / 補助 26,121.87 千円/人 / ベース 8,089.56 千円/人</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">労働生産性（億円/人）</t>
+          <t xml:space="preserve">労働生産性（千円/人）</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -4834,47 +4834,47 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / ベース 0.128 億円/人</t>
+          <t xml:space="preserve">全社 12,761.29 千円/人 / 補助 — / ベース 12,761.29 千円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / ベース 0.128 億円/人</t>
+          <t xml:space="preserve">全社 12,785.84 千円/人 / 補助 — / ベース 12,785.84 千円/人</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 — / ベース 0.128 億円/人</t>
+          <t xml:space="preserve">全社 12,808.51 千円/人 / 補助 — / ベース 12,808.51 千円/人</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.135 億円/人 / 補助 — / ベース 0.135 億円/人</t>
+          <t xml:space="preserve">全社 13,458.23 千円/人 / 補助 — / ベース 13,458.23 千円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.14 億円/人 / 補助 — / ベース 0.14 億円/人</t>
+          <t xml:space="preserve">全社 14,033.6 千円/人 / 補助 — / ベース 14,033.6 千円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.176 億円/人 / 補助 0.317 億円/人 / ベース 0.147 億円/人</t>
+          <t xml:space="preserve">全社 17,598.73 千円/人 / 補助 31,660 千円/人 / ベース 14,693.51 千円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.184 億円/人 / 補助 0.329 億円/人 / ベース 0.153 億円/人</t>
+          <t xml:space="preserve">全社 18,371.07 千円/人 / 補助 32,888.46 千円/人 / ベース 15,302.36 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.204 億円/人 / 補助 0.387 億円/人 / ベース 0.164 億円/人</t>
+          <t xml:space="preserve">全社 20,362.27 千円/人 / 補助 38,695.09 千円/人 / ベース 16,386.48 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.226 億円/人 / 補助 0.457 億円/人 / ベース 0.175 億円/人</t>
+          <t xml:space="preserve">全社 22,584.08 千円/人 / 補助 45,674.18 千円/人 / ベース 17,473.23 千円/人</t>
         </is>
       </c>
     </row>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 pt / 補助 17.01 pt / ベース 4.75 pt</t>
+          <t xml:space="preserve">全社 8.61 pt / 補助 17 pt / ベース 4.76 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.72 pt / 補助 17.14 pt / ベース 4.36 pt</t>
+          <t xml:space="preserve">全社 8.72 pt / 補助 17.15 pt / ベース 4.36 pt</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.47 倍 / 補助 — / ベース 4.47 倍</t>
+          <t xml:space="preserve">全社 4.46 倍 / 補助 — / ベース 4.46 倍</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.62 倍 / 補助 2.38 倍 / ベース 5.21 倍</t>
+          <t xml:space="preserve">全社 3.62 倍 / 補助 2.38 倍 / ベース 5.2 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.27 倍 / 補助 4.14 倍 / ベース 6.73 倍</t>
+          <t xml:space="preserve">全社 5.27 倍 / 補助 4.13 倍 / ベース 6.73 倍</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 31.67 %</t>
+          <t xml:space="preserve">構成比 31.66 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21.01 % / ベース 6 %</t>
+          <t xml:space="preserve">補助 21 % / ベース 6 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 20.99 % / ベース 6 %</t>
+          <t xml:space="preserve">補助 21 % / ベース 6 %</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.34 pt</t>
+          <t xml:space="preserve">差 0.33 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.09 pt</t>
+          <t xml:space="preserve">差 -8.08 pt</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.66 pt</t>
+          <t xml:space="preserve">差 1.67 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">事業別1人当たり売上高（億円/人）</t>
+          <t xml:space="preserve">事業別1人当たり売上高（千円/人）</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
@@ -5702,54 +5702,54 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.651 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 65,094.34 千円/人</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.652 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 65,158.37 千円/人</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.652 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 65,217.39 千円/人</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.672 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 67,241.38 千円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.69 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 69,038.3 千円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.25 億円/人 / ベース 0.712 億円/人</t>
+          <t xml:space="preserve">補助 125,000 千円/人 / ベース 71,193.92 千円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.452 億円/人 / ベース 0.742 億円/人</t>
+          <t xml:space="preserve">補助 145,200 千円/人 / ベース 74,213.02 千円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.689 億円/人 / ベース 0.777 億円/人</t>
+          <t xml:space="preserve">補助 168,934.62 千円/人 / ベース 77,698.6 千円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.968 億円/人 / ベース 0.81 億円/人</t>
+          <t xml:space="preserve">補助 196,840.11 千円/人 / ベース 81,032.12 千円/人</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">事業別従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">事業別従業員1人当たり給与支給総額（千円/人）</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
@@ -5764,47 +5764,47 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.058 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 5,850.59 千円/人</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.06 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 5,967.61 千円/人</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.061 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 6,086.96 千円/人</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.063 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 6,338.62 千円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / ベース 0.066 億円/人</t>
+          <t xml:space="preserve">補助 — / ベース 6,573.09 千円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.1 億円/人 / ベース 0.068 億円/人</t>
+          <t xml:space="preserve">補助 10,000 千円/人 / ベース 6,846.11 千円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.107 億円/人 / ベース 0.071 億円/人</t>
+          <t xml:space="preserve">補助 10,682.88 千円/人 / ベース 7,140.98 千円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.114 億円/人 / ベース 0.075 億円/人</t>
+          <t xml:space="preserve">補助 11,430.67 千円/人 / ベース 7,481.13 千円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.122 億円/人 / ベース 0.078 億円/人</t>
+          <t xml:space="preserve">補助 12,248.94 千円/人 / ベース 7,807.06 千円/人</t>
         </is>
       </c>
     </row>
@@ -5851,22 +5851,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 85.34 %</t>
+          <t xml:space="preserve">寄与率 85.51 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 40.8 %</t>
+          <t xml:space="preserve">寄与率 40.42 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 60.5 %</t>
+          <t xml:space="preserve">寄与率 60.61 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 64 %</t>
+          <t xml:space="preserve">寄与率 64.03 %</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -6288,71 +6288,85 @@
           <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
-      <c r="B17" s="2">
-        <v>21</v>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>-5</v>
-      </c>
-      <c r="E17" s="2">
-        <v>40</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（設備導入初年度）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>7.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（基準年度）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.000000000000001</v>
+        <v>6000000</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>10</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>4</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6360,41 +6374,41 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6402,20 +6416,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E22" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6423,20 +6437,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6447,13 +6461,13 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -6465,45 +6479,41 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E25" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6511,41 +6521,45 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2">
-        <v>2</v>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6556,17 +6570,17 @@
         <v>-5</v>
       </c>
       <c r="E29" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6574,20 +6588,20 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6595,20 +6609,20 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E31" s="2">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6616,20 +6630,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E32" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>7.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6637,20 +6651,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6661,42 +6675,38 @@
         <v>0</v>
       </c>
       <c r="E34" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B35" s="2">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
         <v>4.5</v>
       </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="E35" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6704,41 +6714,45 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D37" s="2">
-        <v>-5</v>
-      </c>
-      <c r="E37" s="2">
-        <v>10</v>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6746,20 +6760,20 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E38" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6767,20 +6781,20 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E39" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6791,54 +6805,96 @@
         <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>45</v>
+        <v>0.5</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>6</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B42" s="2">
-        <v>15</v>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="B44" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
         </is>
       </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6850,7 +6906,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C288"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -6899,7 +6955,7 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <v>138</v>
+        <v>13800000</v>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
@@ -6914,7 +6970,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>0.09</v>
+        <v>9200</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -6929,7 +6985,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>11.78</v>
+        <v>1178310</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -6944,7 +7000,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0.62</v>
+        <v>62016</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -6959,7 +7015,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>2.48</v>
+        <v>248400</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -6974,7 +7030,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0.64</v>
+        <v>64400</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -6989,7 +7045,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>10.67</v>
+        <v>1067200</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -7004,7 +7060,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>10.67</v>
+        <v>1067200</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -7064,7 +7120,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>93.84</v>
+        <v>9384000</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -7079,7 +7135,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0.74</v>
+        <v>73600</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -7094,7 +7150,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>33</v>
+        <v>3301126</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -7109,7 +7165,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.83</v>
+        <v>82800</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -7124,7 +7180,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <v>144</v>
+        <v>14400000</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -7139,7 +7195,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>0.1</v>
+        <v>9600</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -7154,7 +7210,7 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>12.53</v>
+        <v>1252899</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -7169,7 +7225,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0.66</v>
+        <v>65942</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -7184,7 +7240,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>2.59</v>
+        <v>259200</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -7199,7 +7255,7 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0.67</v>
+        <v>67200</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -7214,7 +7270,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>11.14</v>
+        <v>1113600</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -7229,7 +7285,7 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>11.14</v>
+        <v>1113600</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -7289,7 +7345,7 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <v>97.92</v>
+        <v>9792000</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -7304,7 +7360,7 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.77</v>
+        <v>76800</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -7319,7 +7375,7 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <v>34.69</v>
+        <v>3469241</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -7334,7 +7390,7 @@
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0.86</v>
+        <v>86400</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -7349,7 +7405,7 @@
         </is>
       </c>
       <c r="B33" s="2">
-        <v>150</v>
+        <v>15000000</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -7364,7 +7420,7 @@
         </is>
       </c>
       <c r="B34" s="2">
-        <v>0.1</v>
+        <v>10000</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -7379,7 +7435,7 @@
         </is>
       </c>
       <c r="B35" s="2">
-        <v>13.3</v>
+        <v>1330000</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -7394,7 +7450,7 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -7409,7 +7465,7 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <v>2.7</v>
+        <v>270000</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
@@ -7424,7 +7480,7 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <v>0.7</v>
+        <v>70000</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -7439,7 +7495,7 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <v>11.6</v>
+        <v>1160000</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -7454,7 +7510,7 @@
         </is>
       </c>
       <c r="B40" s="2">
-        <v>11.6</v>
+        <v>1160000</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -7514,7 +7570,7 @@
         </is>
       </c>
       <c r="B44" s="2">
-        <v>102</v>
+        <v>10200000</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
@@ -7529,7 +7585,7 @@
         </is>
       </c>
       <c r="B45" s="2">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
@@ -7544,7 +7600,7 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <v>36.4</v>
+        <v>3640000</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
@@ -7559,7 +7615,7 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
@@ -7979,7 +8035,7 @@
         </is>
       </c>
       <c r="B75" s="2">
-        <v>132</v>
+        <v>13200000</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7994,7 +8050,7 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <v>19</v>
+        <v>1900000</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -8009,7 +8065,7 @@
         </is>
       </c>
       <c r="B77" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -8024,7 +8080,7 @@
         </is>
       </c>
       <c r="B78" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -8039,7 +8095,7 @@
         </is>
       </c>
       <c r="B79" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -8054,7 +8110,7 @@
         </is>
       </c>
       <c r="B80" s="2">
-        <v>67</v>
+        <v>6700000</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -8069,7 +8125,7 @@
         </is>
       </c>
       <c r="B81" s="2">
-        <v>39</v>
+        <v>3900000</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -8084,7 +8140,7 @@
         </is>
       </c>
       <c r="B82" s="2">
-        <v>65</v>
+        <v>6500000</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -8099,7 +8155,7 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>36</v>
+        <v>3600000</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -8114,7 +8170,7 @@
         </is>
       </c>
       <c r="B84" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -8129,7 +8185,7 @@
         </is>
       </c>
       <c r="B85" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -8144,7 +8200,7 @@
         </is>
       </c>
       <c r="B86" s="2">
-        <v>75</v>
+        <v>7500000</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -8159,7 +8215,7 @@
         </is>
       </c>
       <c r="B87" s="2">
-        <v>29</v>
+        <v>2900000</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -8174,7 +8230,7 @@
         </is>
       </c>
       <c r="B88" s="2">
-        <v>24</v>
+        <v>2400000</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -8189,7 +8245,7 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <v>57</v>
+        <v>5700000</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -8204,7 +8260,7 @@
         </is>
       </c>
       <c r="B90" s="2">
-        <v>54</v>
+        <v>5400000</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -8219,7 +8275,7 @@
         </is>
       </c>
       <c r="B91" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -8234,7 +8290,7 @@
         </is>
       </c>
       <c r="B92" s="2">
-        <v>5</v>
+        <v>500000</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -8249,7 +8305,7 @@
         </is>
       </c>
       <c r="B93" s="2">
-        <v>53</v>
+        <v>5300000</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -8264,7 +8320,7 @@
         </is>
       </c>
       <c r="B94" s="2">
-        <v>143</v>
+        <v>14300000</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -8279,7 +8335,7 @@
         </is>
       </c>
       <c r="B95" s="2">
-        <v>20</v>
+        <v>2000000</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -8294,7 +8350,7 @@
         </is>
       </c>
       <c r="B96" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -8309,7 +8365,7 @@
         </is>
       </c>
       <c r="B97" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -8324,7 +8380,7 @@
         </is>
       </c>
       <c r="B98" s="2">
-        <v>25</v>
+        <v>2500000</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -8339,7 +8395,7 @@
         </is>
       </c>
       <c r="B99" s="2">
-        <v>72</v>
+        <v>7200000</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -8354,7 +8410,7 @@
         </is>
       </c>
       <c r="B100" s="2">
-        <v>41</v>
+        <v>4100000</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -8369,7 +8425,7 @@
         </is>
       </c>
       <c r="B101" s="2">
-        <v>71</v>
+        <v>7100000</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8384,7 +8440,7 @@
         </is>
       </c>
       <c r="B102" s="2">
-        <v>38</v>
+        <v>3800000</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8399,7 +8455,7 @@
         </is>
       </c>
       <c r="B103" s="2">
-        <v>8</v>
+        <v>800000</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8414,7 +8470,7 @@
         </is>
       </c>
       <c r="B104" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8429,7 +8485,7 @@
         </is>
       </c>
       <c r="B105" s="2">
-        <v>79</v>
+        <v>7900000</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8444,7 +8500,7 @@
         </is>
       </c>
       <c r="B106" s="2">
-        <v>31</v>
+        <v>3100000</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8459,7 +8515,7 @@
         </is>
       </c>
       <c r="B107" s="2">
-        <v>28</v>
+        <v>2800000</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8474,7 +8530,7 @@
         </is>
       </c>
       <c r="B108" s="2">
-        <v>64</v>
+        <v>6400000</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8489,7 +8545,7 @@
         </is>
       </c>
       <c r="B109" s="2">
-        <v>61</v>
+        <v>6100000</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8504,7 +8560,7 @@
         </is>
       </c>
       <c r="B110" s="2">
-        <v>12</v>
+        <v>1200000</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8519,7 +8575,7 @@
         </is>
       </c>
       <c r="B111" s="2">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8534,7 +8590,7 @@
         </is>
       </c>
       <c r="B112" s="2">
-        <v>58</v>
+        <v>5800000</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8549,7 +8605,7 @@
         </is>
       </c>
       <c r="B113" s="2">
-        <v>156</v>
+        <v>15600000</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8564,7 +8620,7 @@
         </is>
       </c>
       <c r="B114" s="2">
-        <v>22</v>
+        <v>2200000</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8579,7 +8635,7 @@
         </is>
       </c>
       <c r="B115" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8594,7 +8650,7 @@
         </is>
       </c>
       <c r="B116" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -8609,7 +8665,7 @@
         </is>
       </c>
       <c r="B117" s="2">
-        <v>27</v>
+        <v>2700000</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8624,7 +8680,7 @@
         </is>
       </c>
       <c r="B118" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8639,7 +8695,7 @@
         </is>
       </c>
       <c r="B119" s="2">
-        <v>43</v>
+        <v>4300000</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8654,7 +8710,7 @@
         </is>
       </c>
       <c r="B120" s="2">
-        <v>78</v>
+        <v>7800000</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -8669,7 +8725,7 @@
         </is>
       </c>
       <c r="B121" s="2">
-        <v>40</v>
+        <v>4000000</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8684,7 +8740,7 @@
         </is>
       </c>
       <c r="B122" s="2">
-        <v>9</v>
+        <v>900000</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8699,7 +8755,7 @@
         </is>
       </c>
       <c r="B123" s="2">
-        <v>10</v>
+        <v>1000000</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8714,7 +8770,7 @@
         </is>
       </c>
       <c r="B124" s="2">
-        <v>83</v>
+        <v>8300000</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8729,7 +8785,7 @@
         </is>
       </c>
       <c r="B125" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8744,7 +8800,7 @@
         </is>
       </c>
       <c r="B126" s="2">
-        <v>32</v>
+        <v>3200000</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8759,7 +8815,7 @@
         </is>
       </c>
       <c r="B127" s="2">
-        <v>73</v>
+        <v>7300000</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8774,7 +8830,7 @@
         </is>
       </c>
       <c r="B128" s="2">
-        <v>70</v>
+        <v>7000000</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8789,7 +8845,7 @@
         </is>
       </c>
       <c r="B129" s="2">
-        <v>11</v>
+        <v>1100000</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -8804,7 +8860,7 @@
         </is>
       </c>
       <c r="B130" s="2">
-        <v>7</v>
+        <v>700000</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8819,7 +8875,7 @@
         </is>
       </c>
       <c r="B131" s="2">
-        <v>64</v>
+        <v>6400000</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8864,7 +8920,7 @@
         </is>
       </c>
       <c r="B134" s="2">
-        <v>15</v>
+        <v>1500000</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8879,7 +8935,7 @@
         </is>
       </c>
       <c r="B135" s="2">
-        <v>200</v>
+        <v>20000000</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
@@ -9490,7 +9546,7 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:0</t>
         </is>
       </c>
       <c r="B176" s="2">
@@ -9505,11 +9561,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>1</v>
+        <v>10000000000</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9520,7 +9576,7 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B178" s="2">
@@ -9535,11 +9591,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9550,7 +9606,7 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B180" s="2">
@@ -9565,11 +9621,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9580,7 +9636,7 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B182" s="2">
@@ -9595,11 +9651,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.99</v>
+        <v>0.02</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9610,7 +9666,7 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B184" s="2">
@@ -9625,11 +9681,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9640,26 +9696,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9670,11 +9726,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>-0.03</v>
+        <v>-0.5</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9685,11 +9741,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9700,26 +9756,26 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:0</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.2</v>
+        <v>10000000000</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9730,11 +9786,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9745,11 +9801,11 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9760,11 +9816,11 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>-0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9775,11 +9831,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9790,26 +9846,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9820,26 +9876,26 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9850,7 +9906,7 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B200" s="2">
@@ -9865,11 +9921,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9880,22 +9936,22 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B203" s="2">
@@ -9910,7 +9966,7 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B204" s="2">
@@ -9925,7 +9981,7 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B205" s="2">
@@ -9940,26 +9996,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9970,26 +10026,26 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -10000,26 +10056,26 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -10030,26 +10086,26 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -10060,7 +10116,7 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B214" s="2">
@@ -10075,11 +10131,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10090,26 +10146,26 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>50</v>
+        <v>0.03</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -10120,11 +10176,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>0.3</v>
+        <v>100000</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10135,11 +10191,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>45</v>
+        <v>5000000</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10150,11 +10206,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>23</v>
+        <v>0.3</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10165,11 +10221,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0.2</v>
+        <v>4500000</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10180,11 +10236,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.01</v>
+        <v>23</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10195,11 +10251,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10210,11 +10266,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.68</v>
+        <v>0.01</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10225,11 +10281,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0.95</v>
+        <v>0.005</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -10240,26 +10296,26 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.015</v>
+        <v>0.95</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10270,26 +10326,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10300,11 +10356,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.9</v>
+        <v>0.01</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10315,11 +10371,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>0.045</v>
+        <v>-0.005</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10330,11 +10386,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.04</v>
+        <v>0.9</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10345,7 +10401,7 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
@@ -10360,7 +10416,7 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
@@ -10375,11 +10431,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.004</v>
+        <v>0.045</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10390,11 +10446,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10405,11 +10461,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10420,11 +10476,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10435,11 +10491,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10450,11 +10506,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.25</v>
+        <v>0.005</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10465,26 +10521,26 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:projectBaseYearSales</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.07</v>
+        <v>6000000</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10495,11 +10551,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10510,41 +10566,41 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10555,11 +10611,11 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0.04</v>
+        <v>0.95</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
@@ -10570,22 +10626,22 @@
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectFirstYearSales</t>
         </is>
       </c>
       <c r="B249" s="2">
@@ -10600,11 +10656,11 @@
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10615,11 +10671,11 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
@@ -10630,11 +10686,11 @@
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10645,26 +10701,26 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.07</v>
+        <v>0</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.07</v>
+        <v>0.9</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10675,11 +10731,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10690,11 +10746,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10761,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.21</v>
+        <v>0.07</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10720,11 +10776,11 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.01</v>
+        <v>0.07</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10735,11 +10791,11 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10750,11 +10806,11 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>15</v>
+        <v>0.21</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
@@ -10765,11 +10821,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7</v>
+        <v>0.01</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10780,11 +10836,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>3.5</v>
+        <v>0.015</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10851,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>35</v>
+        <v>1500000</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10866,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10825,26 +10881,26 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10855,11 +10911,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10870,7 +10926,7 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B268" s="2">
@@ -10885,11 +10941,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10900,11 +10956,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10915,26 +10971,26 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10945,11 +11001,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10960,11 +11016,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10975,11 +11031,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10990,11 +11046,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -11005,26 +11061,26 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -11035,11 +11091,11 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
@@ -11050,7 +11106,7 @@
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B280" s="2">
@@ -11065,11 +11121,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11080,11 +11136,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11095,7 +11151,7 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
@@ -11110,11 +11166,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11125,13 +11181,58 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B285" s="2">
+        <v>70</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B286" s="2">
+        <v>0</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B287" s="2">
+        <v>350</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B285" s="2">
+      <c r="B288" s="2">
         <v>213</v>
       </c>
-      <c r="C285" s="0" t="inlineStr">
+      <c r="C288" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11159,7 +11260,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4LCJjb2dzIjo5My44NCwiZW1wbG95ZWVQYXkiOjEyLjQsIm9mZmljZXJQYXkiOjAuOTIsImRlcHJlY2lhdGlvbiI6My4yMiwib3RoZXJTZ2EiOjE2LjU2LCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTEuNzgsImVtcGxveWVlQm9udXMiOjAuNjIsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuODMsIm9mZmljZXJCb251cyI6MC4wOSwiY29nc0RlcHJlY2lhdGlvbiI6MC43NCwic2dhRGVwcmVjaWF0aW9uIjoyLjQ4LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjY0LCJvcmRpbmFyeUluY29tZSI6MTAuNjcsInByZVRheEluY29tZSI6MTAuNjcsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NCwiY29ncyI6OTcuOTIsImVtcGxveWVlUGF5IjoxMy4xOSwib2ZmaWNlclBheSI6MC45NiwiZGVwcmVjaWF0aW9uIjozLjM2LCJvdGhlclNnYSI6MTcuMjgsImhlYWRjb3VudCI6MjIxLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMi41MywiZW1wbG95ZWVCb251cyI6MC42Niwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC44Niwib2ZmaWNlckJvbnVzIjowLjEsImNvZ3NEZXByZWNpYXRpb24iOjAuNzcsInNnYURlcHJlY2lhdGlvbiI6Mi41OSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC42Nywib3JkaW5hcnlJbmNvbWUiOjExLjE0LCJwcmVUYXhJbmNvbWUiOjExLjE0LCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwLCJjb2dzIjoxMDIsImVtcGxveWVlUGF5IjoxNCwib2ZmaWNlclBheSI6MSwiZGVwcmVjaWF0aW9uIjozLjUsIm90aGVyU2dhIjoxOCwiaGVhZGNvdW50IjoyMzAsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEzLjMsImVtcGxveWVlQm9udXMiOjAuNywib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC45LCJvZmZpY2VyQm9udXMiOjAuMSwiY29nc0RlcHJlY2lhdGlvbiI6MC44LCJzZ2FEZXByZWNpYXRpb24iOjIuNywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC43LCJvcmRpbmFyeUluY29tZSI6MTEuNjAwMDAwMDAwMDAwMDAzLCJwcmVUYXhJbmNvbWUiOjExLjYwMDAwMDAwMDAwMDAwMywibmV0SW5jb21lIjowfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjowfSx7InllYXIiOjIwMjcsInZhbHVlIjowfSx7InllYXIiOjIwMjgsInZhbHVlIjowfSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NSwic3Vic2lkeSI6MTUsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC40XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI2OnByb2plY3Q6Ny0xIjowLCIyMDI2OnByb2plY3Q6Ny00IjowLCIyMDI2OnByb2plY3Q6Ny02IjowLCIyMDI2OnByb2plY3Q6Ny04IjowLCIyMDI2OnByb2plY3Q6Ny05IjowLCIyMDI2OnByb2plY3Q6UDItNCI6MCwiMjAyNjpwcm9qZWN0OlAyLTE0IjowLCIyMDI2OnByb2plY3Q6Ny0xMyI6MCwiMjAyNjpwcm9qZWN0OjctMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEiOjAsIjIwMjc6cHJvamVjdDo3LTQiOjAsIjIwMjc6cHJvamVjdDo3LTYiOjAsIjIwMjc6cHJvamVjdDo3LTgiOjAsIjIwMjc6cHJvamVjdDo3LTkiOjAsIjIwMjc6cHJvamVjdDpQMi00IjowLCIyMDI3OnByb2plY3Q6UDItMTQiOjAsIjIwMjc6cHJvamVjdDo3LTEzIjowLCIyMDI3OnByb2plY3Q6Ny0xNCI6MCwiMjAyODpwcm9qZWN0OjctMSI6NjAsIjIwMjg6cHJvamVjdDo3LTQiOjIxLCIyMDI4OnByb2plY3Q6Ny02Ijo2LjIzLCIyMDI4OnByb2plY3Q6Ny04Ijo0LjgsIjIwMjg6cHJvamVjdDo3LTkiOjAuMywiMjAyODpwcm9qZWN0OlAyLTQiOjEuMTMsIjIwMjg6cHJvamVjdDpQMi0xNCI6My4zNywiMjAyODpwcm9qZWN0OjctMTMiOjQ4LCIyMDI4OnByb2plY3Q6Ny0xNCI6MiwiMjAyOTpwcm9qZWN0OjctMSI6NzIuNiwiMjAyOTpwcm9qZWN0OjctNCI6MjMuMjMsIjIwMjk6cHJvamVjdDo3LTYiOjYuOTQsIjIwMjk6cHJvamVjdDo3LTgiOjUuMzQsIjIwMjk6cHJvamVjdDo3LTkiOjAuMzIsIjIwMjk6cHJvamVjdDpQMi00IjoxLjEzLCIyMDI5OnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMjk6cHJvamVjdDo3LTEzIjo1MCwiMjAyOTpwcm9qZWN0OjctMTQiOjIsIjIwMzA6cHJvamVjdDo3LTEiOjg3Ljg1LCIyMDMwOnByb2plY3Q6Ny00IjoyOC4xMSwiMjAzMDpwcm9qZWN0OjctNiI6MTAuMTEsIjIwMzA6cHJvamVjdDo3LTgiOjUuOTQsIjIwMzA6cHJvamVjdDo3LTkiOjAuMzQsIjIwMzA6cHJvamVjdDpQMi00IjoxLjEzLCIyMDMwOnByb2plY3Q6UDItMTQiOjMuMzcsIjIwMzA6cHJvamVjdDo3LTEzIjo1MiwiMjAzMDpwcm9qZWN0OjctMTQiOjIsIjIwMzE6cHJvamVjdDo3LTEiOjEwNi4yOSwiMjAzMTpwcm9qZWN0OjctNCI6MzQuMDEsIjIwMzE6cHJvamVjdDo3LTYiOjE0LjExLCIyMDMxOnByb2plY3Q6Ny04Ijo2LjYxLCIyMDMxOnByb2plY3Q6Ny05IjowLjM2LCIyMDMxOnByb2plY3Q6UDItNCI6MS4xMywiMjAzMTpwcm9qZWN0OlAyLTE0IjozLjM3LCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzOCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkzLjg0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjc4LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40OCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjkyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjY5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNTMsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU5LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMTQsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjowLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS42LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjYsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjQsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5IjoxNSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4MDAwMDAsImNvZ3MiOjkzODQwMDAsImVtcGxveWVlUGF5IjoxMjQwMzI2LCJvZmZpY2VyUGF5Ijo5MjAwMCwiZGVwcmVjaWF0aW9uIjozMjIwMDAsIm90aGVyU2dhIjoxNjU2MDAwLCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTE3ODMxMCwiZW1wbG95ZWVCb251cyI6NjIwMTYsIm9mZmljZXJDb21wZW5zYXRpb24iOjgyODAwLCJvZmZpY2VyQm9udXMiOjkyMDAsImNvZ3NEZXByZWNpYXRpb24iOjczNjAwLCJzZ2FEZXByZWNpYXRpb24iOjI0ODQwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NjQ0MDAsIm9yZGluYXJ5SW5jb21lIjoxMDY3MjAwLCJwcmVUYXhJbmNvbWUiOjEwNjcyMDAsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NDAwMDAwLCJjb2dzIjo5NzkyMDAwLCJlbXBsb3llZVBheSI6MTMxODg0MSwib2ZmaWNlclBheSI6OTYwMDAsImRlcHJlY2lhdGlvbiI6MzM2MDAwLCJvdGhlclNnYSI6MTcyODAwMCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyNTI4OTksImVtcGxveWVlQm9udXMiOjY1OTQyLCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo4NjQwMCwib2ZmaWNlckJvbnVzIjo5NjAwLCJjb2dzRGVwcmVjaWF0aW9uIjo3NjgwMCwic2dhRGVwcmVjaWF0aW9uIjoyNTkyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjY3MjAwLCJvcmRpbmFyeUluY29tZSI6MTExMzYwMCwicHJlVGF4SW5jb21lIjoxMTEzNjAwLCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwMDAwMDAsImNvZ3MiOjEwMjAwMDAwLCJlbXBsb3llZVBheSI6MTQwMDAwMCwib2ZmaWNlclBheSI6MTAwMDAwLCJkZXByZWNpYXRpb24iOjM1MDAwMCwib3RoZXJTZ2EiOjE4MDAwMDAsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMzMwMDAwLCJlbXBsb3llZUJvbnVzIjo3MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6OTAwMDAsIm9mZmljZXJCb251cyI6MTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjgwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjI3MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NzAwMDAsIm9yZGluYXJ5SW5jb21lIjoxMTYwMDAwLCJwcmVUYXhJbmNvbWUiOjExNjAwMDAsIm5ldEluY29tZSI6MH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwicHJvamVjdEJhc2VZZWFyU2FsZXMiOjYwMDAwMDAsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wNDUsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiaW52ZXN0bWVudCI6NDUwMDAwMCwic3Vic2lkeSI6MTUwMDAwMCwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Rmlyc3RZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdEJhc2VZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNTAwMDAwLDIwMDAwMDAwXSwic3Vic2lkeSI6WzEwMDAwMCw1MDAwMDAwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjY6cHJvamVjdDo3LTEiOjAsIjIwMjY6cHJvamVjdDo3LTQiOjAsIjIwMjY6cHJvamVjdDo3LTYiOjAsIjIwMjY6cHJvamVjdDo3LTgiOjAsIjIwMjY6cHJvamVjdDo3LTkiOjAsIjIwMjY6cHJvamVjdDpQMi00IjowLCIyMDI2OnByb2plY3Q6UDItMTQiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OlAyLTQiOjAsIjIwMjc6cHJvamVjdDpQMi0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MDAwMDAwLCIyMDI4OnByb2plY3Q6Ny00IjoyMTAwMDAwLCIyMDI4OnByb2plY3Q6Ny02Ijo2MjMwMDAsIjIwMjg6cHJvamVjdDo3LTgiOjQ4MDAwMCwiMjAyODpwcm9qZWN0OjctOSI6MzAwMDAsIjIwMjg6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjg6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3MjYwMDAwLCIyMDI5OnByb2plY3Q6Ny00IjoyMzIzMjAwLCIyMDI5OnByb2plY3Q6Ny02Ijo2OTQyNTYsIjIwMjk6cHJvamVjdDo3LTgiOjUzNDE0NCwiMjAyOTpwcm9qZWN0OjctOSI6MzE4MDAsIjIwMjk6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjk6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Nzg0NjAwLCIyMDMwOnByb2plY3Q6Ny00IjoyODExMDcyLCIyMDMwOnByb2plY3Q6Ny02IjoxMDExNDMyLCIyMDMwOnByb2plY3Q6Ny04Ijo1OTQzOTUsIjIwMzA6cHJvamVjdDo3LTkiOjMzNzA4LCIyMDMwOnByb2plY3Q6UDItNCI6MTEzMDAwLCIyMDMwOnByb2plY3Q6UDItMTQiOjMzNzAwMCwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2MjkzNjYsIjIwMzE6cHJvamVjdDo3LTQiOjM0MDEzOTcsIjIwMzE6cHJvamVjdDo3LTYiOjE0MTA1ODEsIjIwMzE6cHJvamVjdDo3LTgiOjY2MTQ0MywiMjAzMTpwcm9qZWN0OjctOSI6MzU3MzAsIjIwMzE6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMzE6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzODAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTM4NDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjczNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMwMTEyNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjgyODAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjkyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTE3ODMxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjo2MjAxNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyNDg0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6NjQ0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTA2NzIwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMDY3MjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTc5MjAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjc2ODAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQ2OTI0MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjg2NDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjk2MDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTI1Mjg5OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjo2NTk0MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyNTkyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6NjcyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTExMzYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMTEzNjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTYwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExNjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RGaXJzdFllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjEiOjEwMDAwMDAwMDAwLCJkcml2ZXI6cHJvamVjdEJhc2VZZWFyU2FsZXMiOjYwMDAwMDAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEJhc2VZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwMDAwMDAsImRyaXZlcjpzdWJzaWR5IjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxMDAwMDAsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwMDAwMDAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -5876,7 +5876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -6010,61 +6010,53 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
+          <t xml:space="preserve">補助事業 原価率（設備導入期間）</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
+          <t xml:space="preserve">ベース事業 原価率（設備導入期間）</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
+          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -6085,11 +6077,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
+          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6110,11 +6102,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.5</v>
+        <v>90</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6135,11 +6127,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.4</v>
+        <v>90</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6160,11 +6152,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6185,11 +6177,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6210,7 +6202,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6235,11 +6227,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6260,11 +6252,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6285,13 +6277,11 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6312,11 +6302,11 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上高（設備導入初年度）</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6337,11 +6327,13 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上高（基準年度）</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <v>6000000</v>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6362,53 +6354,61 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（設備導入初年度）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>7.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>2</v>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上高（基準年度）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>7.000000000000001</v>
+        <v>6000000</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>10</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>4</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6416,41 +6416,41 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>1</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6458,20 +6458,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E24" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6479,20 +6479,20 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6503,13 +6503,13 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -6521,45 +6521,41 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E27" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6567,41 +6563,45 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2</v>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6612,17 +6612,17 @@
         <v>-5</v>
       </c>
       <c r="E31" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6630,20 +6630,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6651,20 +6651,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6672,20 +6672,20 @@
         </is>
       </c>
       <c r="D34" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E34" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>7.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -6693,20 +6693,20 @@
         </is>
       </c>
       <c r="D35" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6717,42 +6717,38 @@
         <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B37" s="2">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D37" s="2">
         <v>4.5</v>
       </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="E37" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6760,41 +6756,45 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D39" s="2">
-        <v>-5</v>
-      </c>
-      <c r="E39" s="2">
-        <v>10</v>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6802,20 +6802,20 @@
         </is>
       </c>
       <c r="D40" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E40" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -6823,20 +6823,20 @@
         </is>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E41" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
@@ -6847,54 +6847,96 @@
         <v>0</v>
       </c>
       <c r="E42" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>4500000</v>
+        <v>0.5</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>6</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B45" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B44" s="2">
+      <c r="B46" s="2">
         <v>1500000</v>
       </c>
-      <c r="C44" s="0" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
         </is>
       </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6906,7 +6948,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C288"/>
+  <dimension ref="A1:C294"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -9066,7 +9108,7 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateToBase:0</t>
         </is>
       </c>
       <c r="B144" s="2">
@@ -9081,7 +9123,7 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateToBase:1</t>
         </is>
       </c>
       <c r="B145" s="2">
@@ -9096,7 +9138,7 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B146" s="2">
@@ -9111,11 +9153,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -9126,26 +9168,26 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -9156,11 +9198,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>-0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -9171,11 +9213,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -9186,7 +9228,7 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B152" s="2">
@@ -9201,7 +9243,7 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B153" s="2">
@@ -9216,11 +9258,11 @@
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -9231,11 +9273,11 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
@@ -9246,26 +9288,26 @@
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
@@ -9276,7 +9318,7 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B158" s="2">
@@ -9291,11 +9333,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -9306,7 +9348,7 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B160" s="2">
@@ -9321,7 +9363,7 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B161" s="2">
@@ -9336,7 +9378,7 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B162" s="2">
@@ -9351,7 +9393,7 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -9366,7 +9408,7 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B164" s="2">
@@ -9381,7 +9423,7 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B165" s="2">
@@ -9396,7 +9438,7 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B166" s="2">
@@ -9411,11 +9453,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -9426,26 +9468,26 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -9456,7 +9498,7 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B170" s="2">
@@ -9471,7 +9513,7 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B171" s="2">
@@ -9486,26 +9528,26 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -9516,7 +9558,7 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B174" s="2">
@@ -9531,11 +9573,11 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -9546,7 +9588,7 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectBaseYearSales:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B176" s="2">
@@ -9561,11 +9603,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectBaseYearSales:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>10000000000</v>
+        <v>0.03</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9576,7 +9618,7 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:0</t>
         </is>
       </c>
       <c r="B178" s="2">
@@ -9591,11 +9633,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:projectBaseYearSales:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>1</v>
+        <v>10000000000</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9606,7 +9648,7 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B180" s="2">
@@ -9621,11 +9663,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9636,7 +9678,7 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B182" s="2">
@@ -9651,11 +9693,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9666,7 +9708,7 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B184" s="2">
@@ -9681,11 +9723,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.99</v>
+        <v>0.02</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9696,7 +9738,7 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateToBase:0</t>
         </is>
       </c>
       <c r="B186" s="2">
@@ -9711,11 +9753,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateToBase:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9726,26 +9768,26 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9756,7 +9798,7 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectFirstYearSales:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B190" s="2">
@@ -9771,11 +9813,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectFirstYearSales:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>10000000000</v>
+        <v>1</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9786,11 +9828,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>-0.03</v>
+        <v>-0.5</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9801,11 +9843,11 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9816,26 +9858,26 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectFirstYearSales:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.2</v>
+        <v>10000000000</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9846,11 +9888,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9861,11 +9903,11 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9876,11 +9918,11 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>-0.5</v>
+        <v>-0.03</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9891,11 +9933,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9906,26 +9948,26 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9936,26 +9978,26 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9966,7 +10008,7 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B204" s="2">
@@ -9981,11 +10023,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9996,22 +10038,22 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B207" s="2">
@@ -10026,7 +10068,7 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B208" s="2">
@@ -10041,7 +10083,7 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B209" s="2">
@@ -10056,26 +10098,26 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -10086,26 +10128,26 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -10116,7 +10158,7 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B214" s="2">
@@ -10131,11 +10173,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10146,26 +10188,26 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.03</v>
+        <v>0.4</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -10176,26 +10218,26 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>5000000</v>
+        <v>0.02</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10206,26 +10248,26 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>4500000</v>
+        <v>0.03</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10236,11 +10278,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>23</v>
+        <v>100000</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10251,11 +10293,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.2</v>
+        <v>5000000</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10266,11 +10308,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10281,11 +10323,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0.005</v>
+        <v>4500000</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -10296,11 +10338,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.68</v>
+        <v>23</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -10311,11 +10353,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10326,26 +10368,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10356,11 +10398,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsRateToBase</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.01</v>
+        <v>0.68</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10371,11 +10413,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>-0.005</v>
+        <v>0.68</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10386,11 +10428,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10401,26 +10443,26 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.04</v>
+        <v>0.015</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10431,11 +10473,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.045</v>
+        <v>0.01</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10446,11 +10488,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.04</v>
+        <v>-0.005</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10461,11 +10503,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.004</v>
+        <v>0.9</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10476,11 +10518,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10491,7 +10533,7 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B239" s="2">
@@ -10506,11 +10548,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10521,11 +10563,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10536,11 +10578,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectBaseYearSales</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>6000000</v>
+        <v>0.004</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10551,11 +10593,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10566,26 +10608,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.07</v>
+        <v>0.005</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10596,11 +10638,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.68</v>
+        <v>0.005</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10611,11 +10653,11 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectBaseYearSales</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0.95</v>
+        <v>6000000</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
@@ -10626,22 +10668,22 @@
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectFirstYearSales</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B249" s="2">
@@ -10656,11 +10698,11 @@
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.04</v>
+        <v>0.07</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10671,11 +10713,11 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectCogsRateToBase</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
@@ -10686,11 +10728,11 @@
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10701,56 +10743,56 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectFirstYearSales</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10761,11 +10803,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10776,11 +10818,11 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10791,26 +10833,26 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>0.21</v>
+        <v>0.9</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
@@ -10821,11 +10863,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10836,11 +10878,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>0.015</v>
+        <v>0.06</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10851,11 +10893,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>1500000</v>
+        <v>0.07</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10866,11 +10908,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>7</v>
+        <v>0.07</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10881,11 +10923,11 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>3.5</v>
+        <v>0.005</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10896,11 +10938,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>35</v>
+        <v>0.21</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10911,11 +10953,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>21</v>
+        <v>0.01</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10926,26 +10968,26 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>10</v>
+        <v>1500000</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10956,7 +10998,7 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B270" s="2">
@@ -10971,26 +11013,26 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -11001,11 +11043,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -11016,26 +11058,26 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -11046,11 +11088,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -11061,26 +11103,26 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -11091,11 +11133,11 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
@@ -11106,26 +11148,26 @@
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11136,11 +11178,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11151,26 +11193,26 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11181,11 +11223,11 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
@@ -11196,7 +11238,7 @@
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B286" s="2">
@@ -11211,11 +11253,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11226,13 +11268,103 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B288" s="2">
+        <v>22</v>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>0</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>95</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B291" s="2">
+        <v>70</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B292" s="2">
+        <v>0</v>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B293" s="2">
+        <v>350</v>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B288" s="2">
+      <c r="B294" s="2">
         <v>213</v>
       </c>
-      <c r="C288" s="0" t="inlineStr">
+      <c r="C294" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11260,7 +11392,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4MDAwMDAsImNvZ3MiOjkzODQwMDAsImVtcGxveWVlUGF5IjoxMjQwMzI2LCJvZmZpY2VyUGF5Ijo5MjAwMCwiZGVwcmVjaWF0aW9uIjozMjIwMDAsIm90aGVyU2dhIjoxNjU2MDAwLCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTE3ODMxMCwiZW1wbG95ZWVCb251cyI6NjIwMTYsIm9mZmljZXJDb21wZW5zYXRpb24iOjgyODAwLCJvZmZpY2VyQm9udXMiOjkyMDAsImNvZ3NEZXByZWNpYXRpb24iOjczNjAwLCJzZ2FEZXByZWNpYXRpb24iOjI0ODQwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NjQ0MDAsIm9yZGluYXJ5SW5jb21lIjoxMDY3MjAwLCJwcmVUYXhJbmNvbWUiOjEwNjcyMDAsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NDAwMDAwLCJjb2dzIjo5NzkyMDAwLCJlbXBsb3llZVBheSI6MTMxODg0MSwib2ZmaWNlclBheSI6OTYwMDAsImRlcHJlY2lhdGlvbiI6MzM2MDAwLCJvdGhlclNnYSI6MTcyODAwMCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyNTI4OTksImVtcGxveWVlQm9udXMiOjY1OTQyLCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo4NjQwMCwib2ZmaWNlckJvbnVzIjo5NjAwLCJjb2dzRGVwcmVjaWF0aW9uIjo3NjgwMCwic2dhRGVwcmVjaWF0aW9uIjoyNTkyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjY3MjAwLCJvcmRpbmFyeUluY29tZSI6MTExMzYwMCwicHJlVGF4SW5jb21lIjoxMTEzNjAwLCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwMDAwMDAsImNvZ3MiOjEwMjAwMDAwLCJlbXBsb3llZVBheSI6MTQwMDAwMCwib2ZmaWNlclBheSI6MTAwMDAwLCJkZXByZWNpYXRpb24iOjM1MDAwMCwib3RoZXJTZ2EiOjE4MDAwMDAsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMzMwMDAwLCJlbXBsb3llZUJvbnVzIjo3MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6OTAwMDAsIm9mZmljZXJCb251cyI6MTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjgwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjI3MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NzAwMDAsIm9yZGluYXJ5SW5jb21lIjoxMTYwMDAwLCJwcmVUYXhJbmNvbWUiOjExNjAwMDAsIm5ldEluY29tZSI6MH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwib3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksIm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsIm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwib3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsInByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwicHJvamVjdEJhc2VZZWFyU2FsZXMiOjYwMDAwMDAsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wNDUsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDE1LCJvdGhlclNnYVJhdGVFbmQiOjAuMDA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiaW52ZXN0bWVudCI6NDUwMDAwMCwic3Vic2lkeSI6MTUwMDAwMCwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Rmlyc3RZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdEJhc2VZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNTAwMDAwLDIwMDAwMDAwXSwic3Vic2lkeSI6WzEwMDAwMCw1MDAwMDAwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjY6cHJvamVjdDo3LTEiOjAsIjIwMjY6cHJvamVjdDo3LTQiOjAsIjIwMjY6cHJvamVjdDo3LTYiOjAsIjIwMjY6cHJvamVjdDo3LTgiOjAsIjIwMjY6cHJvamVjdDo3LTkiOjAsIjIwMjY6cHJvamVjdDpQMi00IjowLCIyMDI2OnByb2plY3Q6UDItMTQiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OlAyLTQiOjAsIjIwMjc6cHJvamVjdDpQMi0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MDAwMDAwLCIyMDI4OnByb2plY3Q6Ny00IjoyMTAwMDAwLCIyMDI4OnByb2plY3Q6Ny02Ijo2MjMwMDAsIjIwMjg6cHJvamVjdDo3LTgiOjQ4MDAwMCwiMjAyODpwcm9qZWN0OjctOSI6MzAwMDAsIjIwMjg6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjg6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3MjYwMDAwLCIyMDI5OnByb2plY3Q6Ny00IjoyMzIzMjAwLCIyMDI5OnByb2plY3Q6Ny02Ijo2OTQyNTYsIjIwMjk6cHJvamVjdDo3LTgiOjUzNDE0NCwiMjAyOTpwcm9qZWN0OjctOSI6MzE4MDAsIjIwMjk6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjk6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Nzg0NjAwLCIyMDMwOnByb2plY3Q6Ny00IjoyODExMDcyLCIyMDMwOnByb2plY3Q6Ny02IjoxMDExNDMyLCIyMDMwOnByb2plY3Q6Ny04Ijo1OTQzOTUsIjIwMzA6cHJvamVjdDo3LTkiOjMzNzA4LCIyMDMwOnByb2plY3Q6UDItNCI6MTEzMDAwLCIyMDMwOnByb2plY3Q6UDItMTQiOjMzNzAwMCwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2MjkzNjYsIjIwMzE6cHJvamVjdDo3LTQiOjM0MDEzOTcsIjIwMzE6cHJvamVjdDo3LTYiOjE0MTA1ODEsIjIwMzE6cHJvamVjdDo3LTgiOjY2MTQ0MywiMjAzMTpwcm9qZWN0OjctOSI6MzU3MzAsIjIwMzE6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMzE6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzODAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTM4NDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjczNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMwMTEyNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjgyODAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjkyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTE3ODMxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjo2MjAxNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyNDg0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6NjQ0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTA2NzIwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMDY3MjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTc5MjAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjc2ODAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQ2OTI0MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjg2NDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjk2MDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTI1Mjg5OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjo2NTk0MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyNTkyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6NjcyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTExMzYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMTEzNjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTYwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExNjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjIsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJOb25PcGVyYXRpbmdSYXRlIjotMC4wMDUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjpvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZToxIjowLjUsImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RGaXJzdFllYXJTYWxlcyI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RGaXJzdFllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjEiOjEwMDAwMDAwMDAwLCJkcml2ZXI6cHJvamVjdEJhc2VZZWFyU2FsZXMiOjYwMDAwMDAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEJhc2VZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4yLCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjEsImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4wMywiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6aW52ZXN0bWVudCI6NDUwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUwMDAwMCwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwMDAwMDAsImRyaXZlcjpzdWJzaWR5IjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxMDAwMDAsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwMDAwMDAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MjEsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6My41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo3MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjMwLCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowfSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCJ9</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4MDAwMDAsImNvZ3MiOjkzODQwMDAsImVtcGxveWVlUGF5IjoxMjQwMzI2LCJvZmZpY2VyUGF5Ijo5MjAwMCwiZGVwcmVjaWF0aW9uIjozMjIwMDAsIm90aGVyU2dhIjoxNjU2MDAwLCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTE3ODMxMCwiZW1wbG95ZWVCb251cyI6NjIwMTYsIm9mZmljZXJDb21wZW5zYXRpb24iOjgyODAwLCJvZmZpY2VyQm9udXMiOjkyMDAsImNvZ3NEZXByZWNpYXRpb24iOjczNjAwLCJzZ2FEZXByZWNpYXRpb24iOjI0ODQwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NjQ0MDAsIm9yZGluYXJ5SW5jb21lIjoxMDY3MjAwLCJwcmVUYXhJbmNvbWUiOjEwNjcyMDAsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NDAwMDAwLCJjb2dzIjo5NzkyMDAwLCJlbXBsb3llZVBheSI6MTMxODg0MSwib2ZmaWNlclBheSI6OTYwMDAsImRlcHJlY2lhdGlvbiI6MzM2MDAwLCJvdGhlclNnYSI6MTcyODAwMCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyNTI4OTksImVtcGxveWVlQm9udXMiOjY1OTQyLCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo4NjQwMCwib2ZmaWNlckJvbnVzIjo5NjAwLCJjb2dzRGVwcmVjaWF0aW9uIjo3NjgwMCwic2dhRGVwcmVjaWF0aW9uIjoyNTkyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjY3MjAwLCJvcmRpbmFyeUluY29tZSI6MTExMzYwMCwicHJlVGF4SW5jb21lIjoxMTEzNjAwLCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwMDAwMDAsImNvZ3MiOjEwMjAwMDAwLCJlbXBsb3llZVBheSI6MTQwMDAwMCwib2ZmaWNlclBheSI6MTAwMDAwLCJkZXByZWNpYXRpb24iOjM1MDAwMCwib3RoZXJTZ2EiOjE4MDAwMDAsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMzMwMDAwLCJlbXBsb3llZUJvbnVzIjo3MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6OTAwMDAsIm9mZmljZXJCb251cyI6MTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjgwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjI3MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NzAwMDAsIm9yZGluYXJ5SW5jb21lIjoxMTYwMDAwLCJwcmVUYXhJbmNvbWUiOjExNjAwMDAsIm5ldEluY29tZSI6MH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6NjAwMDAwMCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NTAwMDAwLCJzdWJzaWR5IjoxNTAwMDAwLCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RDb2dzUmF0ZVRvQmFzZSI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVUb0Jhc2UiOlswLDAuOTldLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Rmlyc3RZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdEJhc2VZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNTAwMDAwLDIwMDAwMDAwXSwic3Vic2lkeSI6WzEwMDAwMCw1MDAwMDAwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjY6cHJvamVjdDo3LTEiOjAsIjIwMjY6cHJvamVjdDo3LTQiOjAsIjIwMjY6cHJvamVjdDo3LTYiOjAsIjIwMjY6cHJvamVjdDo3LTgiOjAsIjIwMjY6cHJvamVjdDo3LTkiOjAsIjIwMjY6cHJvamVjdDpQMi00IjowLCIyMDI2OnByb2plY3Q6UDItMTQiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OlAyLTQiOjAsIjIwMjc6cHJvamVjdDpQMi0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MDAwMDAwLCIyMDI4OnByb2plY3Q6Ny00IjoyMTAwMDAwLCIyMDI4OnByb2plY3Q6Ny02Ijo2MjMwMDAsIjIwMjg6cHJvamVjdDo3LTgiOjQ4MDAwMCwiMjAyODpwcm9qZWN0OjctOSI6MzAwMDAsIjIwMjg6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjg6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3MjYwMDAwLCIyMDI5OnByb2plY3Q6Ny00IjoyMzIzMjAwLCIyMDI5OnByb2plY3Q6Ny02Ijo2OTQyNTYsIjIwMjk6cHJvamVjdDo3LTgiOjUzNDE0NCwiMjAyOTpwcm9qZWN0OjctOSI6MzE4MDAsIjIwMjk6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjk6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Nzg0NjAwLCIyMDMwOnByb2plY3Q6Ny00IjoyODExMDcyLCIyMDMwOnByb2plY3Q6Ny02IjoxMDExNDMyLCIyMDMwOnByb2plY3Q6Ny04Ijo1OTQzOTUsIjIwMzA6cHJvamVjdDo3LTkiOjMzNzA4LCIyMDMwOnByb2plY3Q6UDItNCI6MTEzMDAwLCIyMDMwOnByb2plY3Q6UDItMTQiOjMzNzAwMCwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2MjkzNjYsIjIwMzE6cHJvamVjdDo3LTQiOjM0MDEzOTcsIjIwMzE6cHJvamVjdDo3LTYiOjE0MTA1ODEsIjIwMzE6cHJvamVjdDo3LTgiOjY2MTQ0MywiMjAzMTpwcm9qZWN0OjctOSI6MzU3MzAsIjIwMzE6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMzE6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzODAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTM4NDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjczNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMwMTEyNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjgyODAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjkyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTE3ODMxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjo2MjAxNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyNDg0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6NjQ0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTA2NzIwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMDY3MjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTc5MjAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjc2ODAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQ2OTI0MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjg2NDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjk2MDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTI1Mjg5OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjo2NTk0MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyNTkyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6NjcyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTExMzYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMTEzNjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTYwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExNjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVRvQmFzZSI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlVG9CYXNlOjEiOjAuOTksImRyaXZlcjpvdGhlckNvZ3NSYXRlVG9CYXNlIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVRvQmFzZToxIjowLjk5LCJkcml2ZXI6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Rmlyc3RZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0QmFzZVllYXJTYWxlcyI6NjAwMDAwMCwiZHJpdmVyLXJhbmdlOnByb2plY3RCYXNlWWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczoxIjoxMDAwMDAwMDAwMCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjppbnZlc3RtZW50Ijo0NTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAwMDAwMCwiZHJpdmVyOnN1YnNpZHkiOjE1MDAwMDAsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEwMDAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAwMDAwMCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -1329,22 +1329,22 @@
         <v>10200000</v>
       </c>
       <c r="E5" s="2">
-        <v>10582000</v>
+        <v>10608000</v>
       </c>
       <c r="F5" s="2">
-        <v>10978240</v>
+        <v>10951200</v>
       </c>
       <c r="G5" s="2">
-        <v>15289248</v>
+        <v>15204883</v>
       </c>
       <c r="H5" s="2">
-        <v>17039212</v>
+        <v>17098830</v>
       </c>
       <c r="I5" s="2">
-        <v>18738890</v>
+        <v>18675695</v>
       </c>
       <c r="J5" s="2">
-        <v>20692266</v>
+        <v>20491306</v>
       </c>
     </row>
     <row r="6">
@@ -1397,22 +1397,22 @@
         <v>4800000</v>
       </c>
       <c r="E7" s="4">
-        <v>5018000</v>
+        <v>4992000</v>
       </c>
       <c r="F7" s="4">
-        <v>5245760</v>
+        <v>5272800</v>
       </c>
       <c r="G7" s="4">
-        <v>7583712</v>
+        <v>7668077</v>
       </c>
       <c r="H7" s="4">
-        <v>8106126</v>
+        <v>8046508</v>
       </c>
       <c r="I7" s="4">
-        <v>9004168</v>
+        <v>9067363</v>
       </c>
       <c r="J7" s="4">
-        <v>10033065</v>
+        <v>10234025</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>32.166666666666664</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2">
-        <v>32.33333333333333</v>
+        <v>32.5</v>
       </c>
       <c r="G8" s="2">
-        <v>33.15579618903718</v>
+        <v>33.52463782562467</v>
       </c>
       <c r="H8" s="2">
-        <v>32.23709301501535</v>
+        <v>31.99999936369915</v>
       </c>
       <c r="I8" s="2">
-        <v>32.45557140816993</v>
+        <v>32.683358121516385</v>
       </c>
       <c r="J8" s="2">
-        <v>32.65405017117635</v>
+        <v>33.308103336624754</v>
       </c>
     </row>
     <row r="9">
@@ -1771,22 +1771,22 @@
         <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>1265040</v>
+        <v>1239040</v>
       </c>
       <c r="F18" s="4">
-        <v>1365228</v>
+        <v>1392268</v>
       </c>
       <c r="G18" s="4">
-        <v>2093816</v>
+        <v>2178181</v>
       </c>
       <c r="H18" s="4">
-        <v>2270113</v>
+        <v>2210495</v>
       </c>
       <c r="I18" s="4">
-        <v>2793433</v>
+        <v>2856628</v>
       </c>
       <c r="J18" s="4">
-        <v>3416792</v>
+        <v>3617752</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>8.109230769230768</v>
+        <v>7.942564102564102</v>
       </c>
       <c r="F19" s="2">
-        <v>8.414866863905326</v>
+        <v>8.581533530571992</v>
       </c>
       <c r="G19" s="2">
-        <v>9.154110355633902</v>
+        <v>9.522951992221383</v>
       </c>
       <c r="H19" s="2">
-        <v>9.027967729047825</v>
+        <v>8.790874077731626</v>
       </c>
       <c r="I19" s="2">
-        <v>10.068944094050483</v>
+        <v>10.296730807396935</v>
       </c>
       <c r="J19" s="2">
-        <v>11.12044000437294</v>
+        <v>11.774493169821344</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>1160000</v>
       </c>
       <c r="E20" s="4">
-        <v>1187040</v>
+        <v>1161040</v>
       </c>
       <c r="F20" s="4">
-        <v>1284108</v>
+        <v>1311148</v>
       </c>
       <c r="G20" s="4">
-        <v>2009451</v>
+        <v>2093816</v>
       </c>
       <c r="H20" s="4">
-        <v>2180686</v>
+        <v>2121068</v>
       </c>
       <c r="I20" s="4">
-        <v>2698641</v>
+        <v>2761836</v>
       </c>
       <c r="J20" s="4">
-        <v>3316312</v>
+        <v>3517272</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>1160000</v>
       </c>
       <c r="E21" s="2">
-        <v>1187040</v>
+        <v>1161040</v>
       </c>
       <c r="F21" s="2">
-        <v>1284108</v>
+        <v>1311148</v>
       </c>
       <c r="G21" s="2">
-        <v>2009451</v>
+        <v>2093816</v>
       </c>
       <c r="H21" s="2">
-        <v>2180686</v>
+        <v>2121068</v>
       </c>
       <c r="I21" s="2">
-        <v>2698641</v>
+        <v>2761836</v>
       </c>
       <c r="J21" s="2">
-        <v>3316312</v>
+        <v>3517272</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>830928</v>
+        <v>812728</v>
       </c>
       <c r="F22" s="2">
-        <v>898876</v>
+        <v>917804</v>
       </c>
       <c r="G22" s="2">
-        <v>1406616</v>
+        <v>1465671</v>
       </c>
       <c r="H22" s="2">
-        <v>1526480</v>
+        <v>1484747</v>
       </c>
       <c r="I22" s="2">
-        <v>1889048</v>
+        <v>1933285</v>
       </c>
       <c r="J22" s="2">
-        <v>2321419</v>
+        <v>2462091</v>
       </c>
     </row>
     <row r="23">
@@ -2043,22 +2043,22 @@
         <v>3010000</v>
       </c>
       <c r="E26" s="4">
-        <v>3189600</v>
+        <v>3163600</v>
       </c>
       <c r="F26" s="4">
-        <v>3368064</v>
+        <v>3395104</v>
       </c>
       <c r="G26" s="4">
-        <v>5138830</v>
+        <v>5223195</v>
       </c>
       <c r="H26" s="4">
-        <v>5474580</v>
+        <v>5414962</v>
       </c>
       <c r="I26" s="4">
-        <v>6169769</v>
+        <v>6232964</v>
       </c>
       <c r="J26" s="4">
-        <v>6978482</v>
+        <v>7179442</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.166666666666674</v>
       </c>
       <c r="E27" s="2">
-        <v>5.966777408637869</v>
+        <v>5.1029900332225875</v>
       </c>
       <c r="F27" s="2">
-        <v>5.595184349134685</v>
+        <v>7.317739284359592</v>
       </c>
       <c r="G27" s="2">
-        <v>52.57518859499106</v>
+        <v>53.84491903635353</v>
       </c>
       <c r="H27" s="2">
-        <v>6.533588384904743</v>
+        <v>3.6714501373201758</v>
       </c>
       <c r="I27" s="2">
-        <v>12.698490112483519</v>
+        <v>15.10632946269983</v>
       </c>
       <c r="J27" s="2">
-        <v>13.10767064374696</v>
+        <v>15.185038771281212</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.066666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>20.446153846153848</v>
+        <v>20.27948717948718</v>
       </c>
       <c r="F28" s="2">
-        <v>20.759763313609465</v>
+        <v>20.926429980276133</v>
       </c>
       <c r="G28" s="2">
-        <v>22.466834200733093</v>
+        <v>22.835675837320572</v>
       </c>
       <c r="H28" s="2">
-        <v>21.771749498853428</v>
+        <v>21.534655847537227</v>
       </c>
       <c r="I28" s="2">
-        <v>22.23896514940783</v>
+        <v>22.46675186275428</v>
       </c>
       <c r="J28" s="2">
-        <v>22.71247134815244</v>
+        <v>23.366524513600844</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>12808.510638297872</v>
       </c>
       <c r="E35" s="2">
-        <v>13458.227848101265</v>
+        <v>13348.523206751055</v>
       </c>
       <c r="F35" s="2">
-        <v>14033.6</v>
+        <v>14146.266666666666</v>
       </c>
       <c r="G35" s="2">
-        <v>17598.73287671233</v>
+        <v>17887.654109589042</v>
       </c>
       <c r="H35" s="2">
-        <v>18371.073825503358</v>
+        <v>18171.013422818793</v>
       </c>
       <c r="I35" s="2">
-        <v>20362.27392739274</v>
+        <v>20570.838283828383</v>
       </c>
       <c r="J35" s="2">
-        <v>22584.084142394822</v>
+        <v>23234.44012944984</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>1615040</v>
+        <v>1589040</v>
       </c>
       <c r="F36" s="4">
-        <v>1715228</v>
+        <v>1742268</v>
       </c>
       <c r="G36" s="4">
-        <v>2893816</v>
+        <v>2978181</v>
       </c>
       <c r="H36" s="4">
-        <v>3070113</v>
+        <v>3010495</v>
       </c>
       <c r="I36" s="4">
-        <v>3593433</v>
+        <v>3656628</v>
       </c>
       <c r="J36" s="4">
-        <v>4216792</v>
+        <v>4417752</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>10.352820512820513</v>
+        <v>10.186153846153847</v>
       </c>
       <c r="F37" s="2">
-        <v>10.572164694280078</v>
+        <v>10.738831360946746</v>
       </c>
       <c r="G37" s="2">
-        <v>12.651690030498894</v>
+        <v>13.020531667086377</v>
       </c>
       <c r="H37" s="2">
-        <v>12.209471990394402</v>
+        <v>11.972378339078201</v>
       </c>
       <c r="I37" s="2">
-        <v>12.952548345607756</v>
+        <v>13.180335058954206</v>
       </c>
       <c r="J37" s="2">
-        <v>13.724154834979647</v>
+        <v>14.37820800042805</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>2.3896107770829067</v>
       </c>
       <c r="E38" s="2">
-        <v>6.956291390728486</v>
+        <v>5.234437086092725</v>
       </c>
       <c r="F38" s="2">
-        <v>6.20343768575391</v>
+        <v>9.642803201933248</v>
       </c>
       <c r="G38" s="2">
-        <v>68.71319731254385</v>
+        <v>70.93702002217799</v>
       </c>
       <c r="H38" s="2">
-        <v>6.0921979835621975</v>
+        <v>1.0850247181081407</v>
       </c>
       <c r="I38" s="2">
-        <v>17.04562665934446</v>
+        <v>21.462683047140096</v>
       </c>
       <c r="J38" s="2">
-        <v>17.347171910537917</v>
+        <v>20.814914724713596</v>
       </c>
     </row>
   </sheetData>
@@ -3795,32 +3795,32 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.83 % / 補助 — / ベース 67.83 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 — / ベース 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.67 % / 補助 — / ベース 67.67 %</t>
+          <t xml:space="preserve">全社 67.5 % / 補助 — / ベース 67.5 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.84 % / 補助 65 % / ベース 67.5 %</t>
+          <t xml:space="preserve">全社 66.48 % / 補助 65 % / ベース 67 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.76 % / 補助 68 % / ベース 67.67 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.54 % / 補助 68 % / ベース 67.33 %</t>
+          <t xml:space="preserve">全社 67.32 % / 補助 68 % / ベース 67 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.35 % / 補助 68 % / ベース 67 %</t>
+          <t xml:space="preserve">全社 66.69 % / 補助 68 % / ベース 66 %</t>
         </is>
       </c>
     </row>
@@ -3857,32 +3857,32 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.17 % / 補助 — / ベース 32.17 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 — / ベース 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.33 % / 補助 — / ベース 32.33 %</t>
+          <t xml:space="preserve">全社 32.5 % / 補助 — / ベース 32.5 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.16 % / 補助 35 % / ベース 32.5 %</t>
+          <t xml:space="preserve">全社 33.52 % / 補助 35 % / ベース 33 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.24 % / 補助 32 % / ベース 32.33 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.46 % / 補助 32 % / ベース 32.67 %</t>
+          <t xml:space="preserve">全社 32.68 % / 補助 32 % / ベース 33 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.65 % / 補助 32 % / ベース 33 %</t>
+          <t xml:space="preserve">全社 33.31 % / 補助 32 % / ベース 34 %</t>
         </is>
       </c>
     </row>
@@ -3981,32 +3981,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.11 % / 補助 — / ベース 8.11 %</t>
+          <t xml:space="preserve">全社 7.94 % / 補助 — / ベース 7.94 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.41 % / 補助 — / ベース 8.41 %</t>
+          <t xml:space="preserve">全社 8.58 % / 補助 — / ベース 8.58 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.15 % / 補助 10.38 % / ベース 8.72 %</t>
+          <t xml:space="preserve">全社 9.52 % / 補助 10.38 % / ベース 9.22 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.03 % / 補助 9.56 % / ベース 8.81 %</t>
+          <t xml:space="preserve">全社 8.79 % / 補助 9.56 % / ベース 8.48 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 11.51 % / ベース 9.4 %</t>
+          <t xml:space="preserve">全社 10.3 % / 補助 11.51 % / ベース 9.73 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.12 % / 補助 13.27 % / ベース 9.98 %</t>
+          <t xml:space="preserve">全社 11.77 % / 補助 13.27 % / ベース 10.98 %</t>
         </is>
       </c>
     </row>
@@ -4043,32 +4043,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.35 % / 補助 — / ベース 10.35 %</t>
+          <t xml:space="preserve">全社 10.19 % / 補助 — / ベース 10.19 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.57 % / 補助 — / ベース 10.57 %</t>
+          <t xml:space="preserve">全社 10.74 % / 補助 — / ベース 10.74 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.65 % / 補助 17.88 % / ベース 10.79 %</t>
+          <t xml:space="preserve">全社 13.02 % / 補助 17.88 % / ベース 11.29 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.21 % / 補助 15.76 % / ベース 10.77 %</t>
+          <t xml:space="preserve">全社 11.97 % / 補助 15.76 % / ベース 10.43 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.95 % / 補助 16.64 % / ベース 11.25 %</t>
+          <t xml:space="preserve">全社 13.18 % / 補助 16.64 % / ベース 11.58 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.72 % / 補助 17.5 % / ベース 11.72 %</t>
+          <t xml:space="preserve">全社 14.38 % / 補助 17.5 % / ベース 12.72 %</t>
         </is>
       </c>
     </row>
@@ -4601,32 +4601,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.37 % / 補助 — / ベース 49.37 %</t>
+          <t xml:space="preserve">全社 49.77 % / 補助 — / ベース 49.77 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.07 % / 補助 — / ベース 49.07 %</t>
+          <t xml:space="preserve">全社 48.68 % / 補助 — / ベース 48.68 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.69 % / 補助 32.22 % / ベース 48.79 %</t>
+          <t xml:space="preserve">全社 42.98 % / 補助 32.22 % / ベース 47.66 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.92 % / 補助 33.09 % / ベース 48.84 %</t>
+          <t xml:space="preserve">全社 44.4 % / 補助 33.09 % / ベース 49.63 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.76 % / 補助 30.06 % / ベース 47.75 %</t>
+          <t xml:space="preserve">全社 41.33 % / 補助 30.06 % / ベース 47.02 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.57 % / 補助 27.26 % / ベース 46.7 %</t>
+          <t xml:space="preserve">全社 38.47 % / 補助 27.26 % / ベース 44.67 %</t>
         </is>
       </c>
     </row>
@@ -4787,32 +4787,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,452.76 千円/人 / 補助 — / ベース 5,452.76 千円/人</t>
+          <t xml:space="preserve">全社 5,340.69 千円/人 / 補助 — / ベース 5,340.69 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,809.48 千円/人 / 補助 — / ベース 5,809.48 千円/人</t>
+          <t xml:space="preserve">全社 5,924.54 千円/人 / 補助 — / ベース 5,924.54 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,346.72 千円/人 / 補助 12,979.17 千円/人 / ベース 6,205.97 千円/人</t>
+          <t xml:space="preserve">全社 7,642.74 千円/人 / 補助 12,979.17 千円/人 / ベース 6,561.95 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,801.08 千円/人 / 補助 13,885.12 千円/人 / ベース 6,538.83 千円/人</t>
+          <t xml:space="preserve">全社 7,596.2 千円/人 / 補助 13,885.12 千円/人 / ベース 6,291.45 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9,437.27 千円/人 / 補助 19,450.62 千円/人 / ベース 7,303.28 千円/人</t>
+          <t xml:space="preserve">全社 9,650.77 千円/人 / 補助 19,450.62 千円/人 / ベース 7,562.28 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11,313.88 千円/人 / 補助 26,121.87 千円/人 / ベース 8,089.56 千円/人</t>
+          <t xml:space="preserve">全社 11,979.31 千円/人 / 補助 26,121.87 千円/人 / ベース 8,899.88 千円/人</t>
         </is>
       </c>
     </row>
@@ -4849,32 +4849,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13,458.23 千円/人 / 補助 — / ベース 13,458.23 千円/人</t>
+          <t xml:space="preserve">全社 13,348.52 千円/人 / 補助 — / ベース 13,348.52 千円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14,033.6 千円/人 / 補助 — / ベース 14,033.6 千円/人</t>
+          <t xml:space="preserve">全社 14,146.27 千円/人 / 補助 — / ベース 14,146.27 千円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17,598.73 千円/人 / 補助 31,660 千円/人 / ベース 14,693.51 千円/人</t>
+          <t xml:space="preserve">全社 17,887.65 千円/人 / 補助 31,660 千円/人 / ベース 15,042.13 千円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 18,371.07 千円/人 / 補助 32,888.46 千円/人 / ベース 15,302.36 千円/人</t>
+          <t xml:space="preserve">全社 18,171.01 千円/人 / 補助 32,888.46 千円/人 / ベース 15,060.01 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20,362.27 千円/人 / 補助 38,695.09 千円/人 / ベース 16,386.48 千円/人</t>
+          <t xml:space="preserve">全社 20,570.84 千円/人 / 補助 38,695.09 千円/人 / ベース 16,640.28 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22,584.08 千円/人 / 補助 45,674.18 千円/人 / ベース 17,473.23 千円/人</t>
+          <t xml:space="preserve">全社 23,234.44 千円/人 / 補助 45,674.18 千円/人 / ベース 18,267.54 千円/人</t>
         </is>
       </c>
     </row>
@@ -5283,32 +5283,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.61 倍 / 補助 — / ベース 4.61 倍</t>
+          <t xml:space="preserve">全社 4.54 倍 / 補助 — / ベース 4.54 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.9 倍 / 補助 — / ベース 4.9 倍</t>
+          <t xml:space="preserve">全社 4.98 倍 / 補助 — / ベース 4.98 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.62 倍 / 補助 2.38 倍 / ベース 5.2 倍</t>
+          <t xml:space="preserve">全社 3.72 倍 / 補助 2.38 倍 / ベース 5.44 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.84 倍 / 補助 2.54 倍 / ベース 5.5 倍</t>
+          <t xml:space="preserve">全社 3.76 倍 / 補助 2.54 倍 / ベース 5.33 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.49 倍 / 補助 3.25 倍 / ベース 6.09 倍</t>
+          <t xml:space="preserve">全社 4.57 倍 / 補助 3.25 倍 / ベース 6.27 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.27 倍 / 補助 4.13 倍 / ベース 6.73 倍</t>
+          <t xml:space="preserve">全社 5.52 倍 / 補助 4.13 倍 / ベース 7.31 倍</t>
         </is>
       </c>
     </row>
@@ -5593,32 +5593,32 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -67.83 pt</t>
+          <t xml:space="preserve">差 -68 pt</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -67.67 pt</t>
+          <t xml:space="preserve">差 -67.5 pt</t>
         </is>
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.5 pt</t>
+          <t xml:space="preserve">差 -2 pt</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.33 pt</t>
+          <t xml:space="preserve">差 -0 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.67 pt</t>
+          <t xml:space="preserve">差 1 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1 pt</t>
+          <t xml:space="preserve">差 2 pt</t>
         </is>
       </c>
     </row>
@@ -5655,32 +5655,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.11 pt</t>
+          <t xml:space="preserve">差 -7.94 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.41 pt</t>
+          <t xml:space="preserve">差 -8.58 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.67 pt</t>
+          <t xml:space="preserve">差 1.17 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.75 pt</t>
+          <t xml:space="preserve">差 1.09 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.11 pt</t>
+          <t xml:space="preserve">差 1.78 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.29 pt</t>
+          <t xml:space="preserve">差 2.29 pt</t>
         </is>
       </c>
     </row>
@@ -5851,22 +5851,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 85.51 %</t>
+          <t xml:space="preserve">寄与率 79.27 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 40.42 %</t>
+          <t xml:space="preserve">寄与率 220.51 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 60.61 %</t>
+          <t xml:space="preserve">寄与率 49.09 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 64.03 %</t>
+          <t xml:space="preserve">寄与率 52.44 %</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率</t>
+          <t xml:space="preserve">補助事業 原価率（基準年後初年度）</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -5989,7 +5989,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率</t>
+          <t xml:space="preserve">ベース事業 原価率（基準年後初年度）</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -6010,7 +6010,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率（設備導入期間初年度）</t>
         </is>
       </c>
       <c r="B6" s="2">
@@ -6031,7 +6031,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率（設備導入期間初年度）</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -6404,7 +6404,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率 年当たり改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6530,7 +6530,7 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率 年当たり改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
@@ -6681,7 +6681,7 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率 年当たり改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B35" s="2">
@@ -6702,7 +6702,7 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率 年当たり改善ポイント（基準年後）</t>
         </is>
       </c>
       <c r="B36" s="2">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル_基準年売上開始.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>12.993452414930307</v>
+        <v>11.304334153945739</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>974754</v>
+        <v>861754</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>64.9836</v>
+        <v>57.45026666666667</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         <v>80000</v>
       </c>
       <c r="E6" s="2">
-        <v>80000</v>
+        <v>83200</v>
       </c>
       <c r="F6" s="2">
-        <v>80000</v>
+        <v>85892</v>
       </c>
       <c r="G6" s="2">
-        <v>193000</v>
+        <v>201666</v>
       </c>
       <c r="H6" s="2">
-        <v>193000</v>
+        <v>95388</v>
       </c>
       <c r="I6" s="2">
-        <v>193000</v>
+        <v>99625</v>
       </c>
       <c r="J6" s="2">
-        <v>193000</v>
+        <v>104026</v>
       </c>
     </row>
     <row r="7">
@@ -1465,22 +1465,22 @@
         <v>3640000</v>
       </c>
       <c r="E9" s="2">
-        <v>3752960</v>
+        <v>3762010</v>
       </c>
       <c r="F9" s="2">
-        <v>3880532</v>
+        <v>3899803</v>
       </c>
       <c r="G9" s="2">
-        <v>5489896</v>
+        <v>5519772</v>
       </c>
       <c r="H9" s="2">
-        <v>5836013</v>
+        <v>5544446</v>
       </c>
       <c r="I9" s="2">
-        <v>6210735</v>
+        <v>5935514</v>
       </c>
       <c r="J9" s="2">
-        <v>6616273</v>
+        <v>6358227</v>
       </c>
     </row>
     <row r="10">
@@ -1703,22 +1703,22 @@
         <v>270000</v>
       </c>
       <c r="E16" s="2">
-        <v>270000</v>
+        <v>279050</v>
       </c>
       <c r="F16" s="2">
-        <v>270000</v>
+        <v>289271</v>
       </c>
       <c r="G16" s="2">
-        <v>607000</v>
+        <v>636876</v>
       </c>
       <c r="H16" s="2">
-        <v>607000</v>
+        <v>315433</v>
       </c>
       <c r="I16" s="2">
-        <v>607000</v>
+        <v>331779</v>
       </c>
       <c r="J16" s="2">
-        <v>607000</v>
+        <v>348954</v>
       </c>
     </row>
     <row r="17">
@@ -1771,22 +1771,22 @@
         <v>1160000</v>
       </c>
       <c r="E18" s="4">
-        <v>1239040</v>
+        <v>1229990</v>
       </c>
       <c r="F18" s="4">
-        <v>1392268</v>
+        <v>1372997</v>
       </c>
       <c r="G18" s="4">
-        <v>2178181</v>
+        <v>2148305</v>
       </c>
       <c r="H18" s="4">
-        <v>2210495</v>
+        <v>2502062</v>
       </c>
       <c r="I18" s="4">
-        <v>2856628</v>
+        <v>3131849</v>
       </c>
       <c r="J18" s="4">
-        <v>3617752</v>
+        <v>3875798</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.942564102564102</v>
+        <v>7.884551282051282</v>
       </c>
       <c r="F19" s="2">
-        <v>8.581533530571992</v>
+        <v>8.462752712031559</v>
       </c>
       <c r="G19" s="2">
-        <v>9.522951992221383</v>
+        <v>9.39233487926355</v>
       </c>
       <c r="H19" s="2">
-        <v>8.790874077731626</v>
+        <v>9.950401143941672</v>
       </c>
       <c r="I19" s="2">
-        <v>10.296730807396935</v>
+        <v>11.28876636454424</v>
       </c>
       <c r="J19" s="2">
-        <v>11.774493169821344</v>
+        <v>12.614340916294767</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>1160000</v>
       </c>
       <c r="E20" s="4">
-        <v>1161040</v>
+        <v>1151990</v>
       </c>
       <c r="F20" s="4">
-        <v>1311148</v>
+        <v>1291877</v>
       </c>
       <c r="G20" s="4">
-        <v>2093816</v>
+        <v>2063940</v>
       </c>
       <c r="H20" s="4">
-        <v>2121068</v>
+        <v>2412635</v>
       </c>
       <c r="I20" s="4">
-        <v>2761836</v>
+        <v>3037057</v>
       </c>
       <c r="J20" s="4">
-        <v>3517272</v>
+        <v>3775318</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>1160000</v>
       </c>
       <c r="E21" s="2">
-        <v>1161040</v>
+        <v>1151990</v>
       </c>
       <c r="F21" s="2">
-        <v>1311148</v>
+        <v>1291877</v>
       </c>
       <c r="G21" s="2">
-        <v>2093816</v>
+        <v>2063940</v>
       </c>
       <c r="H21" s="2">
-        <v>2121068</v>
+        <v>2412635</v>
       </c>
       <c r="I21" s="2">
-        <v>2761836</v>
+        <v>3037057</v>
       </c>
       <c r="J21" s="2">
-        <v>3517272</v>
+        <v>3775318</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>812728</v>
+        <v>806393</v>
       </c>
       <c r="F22" s="2">
-        <v>917804</v>
+        <v>904314</v>
       </c>
       <c r="G22" s="2">
-        <v>1465671</v>
+        <v>1444758</v>
       </c>
       <c r="H22" s="2">
-        <v>1484747</v>
+        <v>1688844</v>
       </c>
       <c r="I22" s="2">
-        <v>1933285</v>
+        <v>2125940</v>
       </c>
       <c r="J22" s="2">
-        <v>2462091</v>
+        <v>2642723</v>
       </c>
     </row>
     <row r="23">
@@ -2009,22 +2009,22 @@
         <v>350000</v>
       </c>
       <c r="E25" s="2">
-        <v>350000</v>
+        <v>362250</v>
       </c>
       <c r="F25" s="2">
-        <v>350000</v>
+        <v>375163</v>
       </c>
       <c r="G25" s="2">
-        <v>800000</v>
+        <v>838542</v>
       </c>
       <c r="H25" s="2">
-        <v>800000</v>
+        <v>410821</v>
       </c>
       <c r="I25" s="2">
-        <v>800000</v>
+        <v>431404</v>
       </c>
       <c r="J25" s="2">
-        <v>800000</v>
+        <v>452980</v>
       </c>
     </row>
     <row r="26">
@@ -2043,22 +2043,22 @@
         <v>3010000</v>
       </c>
       <c r="E26" s="4">
-        <v>3163600</v>
+        <v>3166800</v>
       </c>
       <c r="F26" s="4">
-        <v>3395104</v>
+        <v>3400996</v>
       </c>
       <c r="G26" s="4">
-        <v>5223195</v>
+        <v>5231861</v>
       </c>
       <c r="H26" s="4">
-        <v>5414962</v>
+        <v>5317350</v>
       </c>
       <c r="I26" s="4">
-        <v>6232964</v>
+        <v>6139589</v>
       </c>
       <c r="J26" s="4">
-        <v>7179442</v>
+        <v>7090468</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.166666666666674</v>
       </c>
       <c r="E27" s="2">
-        <v>5.1029900332225875</v>
+        <v>5.209302325581389</v>
       </c>
       <c r="F27" s="2">
-        <v>7.317739284359592</v>
+        <v>7.395351774662129</v>
       </c>
       <c r="G27" s="2">
-        <v>53.84491903635353</v>
+        <v>53.833200627110415</v>
       </c>
       <c r="H27" s="2">
-        <v>3.6714501373201758</v>
+        <v>1.6340074784096936</v>
       </c>
       <c r="I27" s="2">
-        <v>15.10632946269983</v>
+        <v>15.463322895803365</v>
       </c>
       <c r="J27" s="2">
-        <v>15.185038771281212</v>
+        <v>15.487665379555526</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.066666666666666</v>
       </c>
       <c r="E28" s="2">
-        <v>20.27948717948718</v>
+        <v>20.3</v>
       </c>
       <c r="F28" s="2">
-        <v>20.926429980276133</v>
+        <v>20.962746548323473</v>
       </c>
       <c r="G28" s="2">
-        <v>22.835675837320572</v>
+        <v>22.87356336914855</v>
       </c>
       <c r="H28" s="2">
-        <v>21.534655847537227</v>
+        <v>21.146464605089022</v>
       </c>
       <c r="I28" s="2">
-        <v>22.46675186275428</v>
+        <v>22.13018117901783</v>
       </c>
       <c r="J28" s="2">
-        <v>23.366524513600844</v>
+        <v>23.076945859427845</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>12808.510638297872</v>
       </c>
       <c r="E35" s="2">
-        <v>13348.523206751055</v>
+        <v>13362.025316455696</v>
       </c>
       <c r="F35" s="2">
-        <v>14146.266666666666</v>
+        <v>14170.816666666668</v>
       </c>
       <c r="G35" s="2">
-        <v>17887.654109589042</v>
+        <v>17917.33219178082</v>
       </c>
       <c r="H35" s="2">
-        <v>18171.013422818793</v>
+        <v>17843.456375838927</v>
       </c>
       <c r="I35" s="2">
-        <v>20570.838283828383</v>
+        <v>20262.6699669967</v>
       </c>
       <c r="J35" s="2">
-        <v>23234.44012944984</v>
+        <v>22946.498381877023</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>1510000</v>
       </c>
       <c r="E36" s="4">
-        <v>1589040</v>
+        <v>1592240</v>
       </c>
       <c r="F36" s="4">
-        <v>1742268</v>
+        <v>1748160</v>
       </c>
       <c r="G36" s="4">
-        <v>2978181</v>
+        <v>2986847</v>
       </c>
       <c r="H36" s="4">
-        <v>3010495</v>
+        <v>2912883</v>
       </c>
       <c r="I36" s="4">
-        <v>3656628</v>
+        <v>3563253</v>
       </c>
       <c r="J36" s="4">
-        <v>4417752</v>
+        <v>4328778</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666666</v>
       </c>
       <c r="E37" s="2">
-        <v>10.186153846153847</v>
+        <v>10.206666666666667</v>
       </c>
       <c r="F37" s="2">
-        <v>10.738831360946746</v>
+        <v>10.775147928994084</v>
       </c>
       <c r="G37" s="2">
-        <v>13.020531667086377</v>
+        <v>13.05841919891435</v>
       </c>
       <c r="H37" s="2">
-        <v>11.972378339078201</v>
+        <v>11.58418709663</v>
       </c>
       <c r="I37" s="2">
-        <v>13.180335058954206</v>
+        <v>12.843764375217756</v>
       </c>
       <c r="J37" s="2">
-        <v>14.37820800042805</v>
+        <v>14.088629346255049</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>2.3896107770829067</v>
       </c>
       <c r="E38" s="2">
-        <v>5.234437086092725</v>
+        <v>5.4463576158940485</v>
       </c>
       <c r="F38" s="2">
-        <v>9.642803201933248</v>
+        <v>9.792493593930573</v>
       </c>
       <c r="G38" s="2">
-        <v>70.93702002217799</v>
+        <v>70.85661495515285</v>
       </c>
       <c r="H38" s="2">
-        <v>1.0850247181081407</v>
+        <v>-2.476323695187599</v>
       </c>
       <c r="I38" s="2">
-        <v>21.462683047140096</v>
+        <v>22.327364332861976</v>
       </c>
       <c r="J38" s="2">
-        <v>20.814914724713596</v>
+        <v>21.483880038829682</v>
       </c>
     </row>
   </sheetData>
@@ -2828,13 +2828,13 @@
         <v>623000</v>
       </c>
       <c r="H8" s="4">
-        <v>694256</v>
+        <v>1031256</v>
       </c>
       <c r="I8" s="4">
-        <v>1011432</v>
+        <v>1348432</v>
       </c>
       <c r="J8" s="4">
-        <v>1410581</v>
+        <v>1747581</v>
       </c>
     </row>
     <row r="9">
@@ -2872,13 +2872,13 @@
         <v>10.383333333333333</v>
       </c>
       <c r="H9" s="2">
-        <v>9.56275482093664</v>
+        <v>14.204628099173553</v>
       </c>
       <c r="I9" s="2">
-        <v>11.51369441978007</v>
+        <v>15.349953327413884</v>
       </c>
       <c r="J9" s="2">
-        <v>13.270603345486457</v>
+        <v>16.44106525262184</v>
       </c>
     </row>
     <row r="10">
@@ -2974,13 +2974,13 @@
         <v>113000</v>
       </c>
       <c r="H12" s="2">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>113000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3008,13 +3008,13 @@
         <v>337000</v>
       </c>
       <c r="H13" s="2">
-        <v>337000</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>337000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>337000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3042,13 +3042,13 @@
         <v>450000</v>
       </c>
       <c r="H14" s="2">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>450000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3076,13 +3076,13 @@
         <v>1583000</v>
       </c>
       <c r="H15" s="4">
-        <v>1710200</v>
+        <v>1597200</v>
       </c>
       <c r="I15" s="4">
-        <v>2089535</v>
+        <v>1976535</v>
       </c>
       <c r="J15" s="4">
-        <v>2557754</v>
+        <v>2444754</v>
       </c>
     </row>
     <row r="16">
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="H16" s="2">
-        <v>8.035375868603921</v>
+        <v>0.8970309538850252</v>
       </c>
       <c r="I16" s="2">
-        <v>22.180739094842707</v>
+        <v>23.750000000000004</v>
       </c>
       <c r="J16" s="2">
-        <v>22.407808435848175</v>
+        <v>23.688879782042815</v>
       </c>
     </row>
     <row r="17">
@@ -3414,13 +3414,13 @@
         <v>31660</v>
       </c>
       <c r="H23" s="2">
-        <v>32888.46153846154</v>
+        <v>30715.384615384617</v>
       </c>
       <c r="I23" s="2">
-        <v>38695.09259259259</v>
+        <v>36602.5</v>
       </c>
       <c r="J23" s="2">
-        <v>45674.17857142857</v>
+        <v>43656.32142857143</v>
       </c>
     </row>
     <row r="24">
@@ -3919,32 +3919,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.06 % / 補助 — / ベース 24.06 %</t>
+          <t xml:space="preserve">全社 24.12 % / 補助 — / ベース 24.12 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.92 % / 補助 — / ベース 23.92 %</t>
+          <t xml:space="preserve">全社 24.04 % / 補助 — / ベース 24.04 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24 % / 補助 24.62 % / ベース 23.78 %</t>
+          <t xml:space="preserve">全社 24.13 % / 補助 24.62 % / ベース 23.96 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.21 % / 補助 22.44 % / ベース 23.52 %</t>
+          <t xml:space="preserve">全社 22.05 % / 補助 17.8 % / ベース 23.78 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.39 % / 補助 20.49 % / ベース 23.27 %</t>
+          <t xml:space="preserve">全社 21.39 % / 補助 16.65 % / ベース 23.59 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.53 % / 補助 18.73 % / ベース 23.02 %</t>
+          <t xml:space="preserve">全社 20.69 % / 補助 15.56 % / ベース 23.41 %</t>
         </is>
       </c>
     </row>
@@ -3981,32 +3981,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.94 % / 補助 — / ベース 7.94 %</t>
+          <t xml:space="preserve">全社 7.88 % / 補助 — / ベース 7.88 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.58 % / 補助 — / ベース 8.58 %</t>
+          <t xml:space="preserve">全社 8.46 % / 補助 — / ベース 8.46 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.52 % / 補助 10.38 % / ベース 9.22 %</t>
+          <t xml:space="preserve">全社 9.39 % / 補助 10.38 % / ベース 9.04 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.79 % / 補助 9.56 % / ベース 8.48 %</t>
+          <t xml:space="preserve">全社 9.95 % / 補助 14.2 % / ベース 8.22 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.3 % / 補助 11.51 % / ベース 9.73 %</t>
+          <t xml:space="preserve">全社 11.29 % / 補助 15.35 % / ベース 9.41 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.77 % / 補助 13.27 % / ベース 10.98 %</t>
+          <t xml:space="preserve">全社 12.61 % / 補助 16.44 % / ベース 10.59 %</t>
         </is>
       </c>
     </row>
@@ -4043,32 +4043,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.19 % / 補助 — / ベース 10.19 %</t>
+          <t xml:space="preserve">全社 10.21 % / 補助 — / ベース 10.21 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.74 % / 補助 — / ベース 10.74 %</t>
+          <t xml:space="preserve">全社 10.78 % / 補助 — / ベース 10.78 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.02 % / 補助 17.88 % / ベース 11.29 %</t>
+          <t xml:space="preserve">全社 13.06 % / 補助 17.88 % / ベース 11.34 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.97 % / 補助 15.76 % / ベース 10.43 %</t>
+          <t xml:space="preserve">全社 11.58 % / 補助 14.2 % / ベース 10.52 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.18 % / 補助 16.64 % / ベース 11.58 %</t>
+          <t xml:space="preserve">全社 12.84 % / 補助 15.35 % / ベース 11.68 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.38 % / 補助 17.5 % / ベース 12.72 %</t>
+          <t xml:space="preserve">全社 14.09 % / 補助 16.44 % / ベース 12.84 %</t>
         </is>
       </c>
     </row>
@@ -4601,32 +4601,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.77 % / 補助 — / ベース 49.77 %</t>
+          <t xml:space="preserve">全社 49.72 % / 補助 — / ベース 49.72 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.68 % / 補助 — / ベース 48.68 %</t>
+          <t xml:space="preserve">全社 48.6 % / 補助 — / ベース 48.6 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.98 % / 補助 32.22 % / ベース 47.66 %</t>
+          <t xml:space="preserve">全社 42.91 % / 補助 32.22 % / ベース 47.55 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 44.4 % / 補助 33.09 % / ベース 49.63 %</t>
+          <t xml:space="preserve">全社 45.22 % / 補助 35.43 % / ベース 49.42 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.33 % / 補助 30.06 % / ベース 47.02 %</t>
+          <t xml:space="preserve">全社 41.96 % / 補助 31.78 % / ベース 46.8 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.47 % / 補助 27.26 % / ベース 44.67 %</t>
+          <t xml:space="preserve">全社 38.95 % / 補助 28.52 % / ベース 44.44 %</t>
         </is>
       </c>
     </row>
@@ -4787,32 +4787,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,340.69 千円/人 / 補助 — / ベース 5,340.69 千円/人</t>
+          <t xml:space="preserve">全社 5,301.68 千円/人 / 補助 — / ベース 5,301.68 千円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5,924.54 千円/人 / 補助 — / ベース 5,924.54 千円/人</t>
+          <t xml:space="preserve">全社 5,842.54 千円/人 / 補助 — / ベース 5,842.54 千円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,642.74 千円/人 / 補助 12,979.17 千円/人 / ベース 6,561.95 千円/人</t>
+          <t xml:space="preserve">全社 7,537.91 千円/人 / 補助 12,979.17 千円/人 / ベース 6,435.89 千円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7,596.2 千円/人 / 補助 13,885.12 千円/人 / ベース 6,291.45 千円/人</t>
+          <t xml:space="preserve">全社 8,598.15 千円/人 / 補助 20,625.12 千円/人 / ベース 6,102.93 千円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9,650.77 千円/人 / 補助 19,450.62 千円/人 / ベース 7,562.28 千円/人</t>
+          <t xml:space="preserve">全社 10,580.57 千円/人 / 補助 25,931.38 千円/人 / ベース 7,309.09 千円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11,979.31 千円/人 / 補助 26,121.87 千円/人 / ベース 8,899.88 千円/人</t>
+          <t xml:space="preserve">全社 12,833.77 千円/人 / 補助 32,362.61 千円/人 / ベース 8,581.52 千円/人</t>
         </is>
       </c>
     </row>
@@ -4849,32 +4849,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13,348.52 千円/人 / 補助 — / ベース 13,348.52 千円/人</t>
+          <t xml:space="preserve">全社 13,362.03 千円/人 / 補助 — / ベース 13,362.03 千円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14,146.27 千円/人 / 補助 — / ベース 14,146.27 千円/人</t>
+          <t xml:space="preserve">全社 14,170.82 千円/人 / 補助 — / ベース 14,170.82 千円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17,887.65 千円/人 / 補助 31,660 千円/人 / ベース 15,042.13 千円/人</t>
+          <t xml:space="preserve">全社 17,917.33 千円/人 / 補助 31,660 千円/人 / ベース 15,077.94 千円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 18,171.01 千円/人 / 補助 32,888.46 千円/人 / ベース 15,060.01 千円/人</t>
+          <t xml:space="preserve">全社 17,843.46 千円/人 / 補助 30,715.38 千円/人 / ベース 15,122.56 千円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20,570.84 千円/人 / 補助 38,695.09 千円/人 / ベース 16,640.28 千円/人</t>
+          <t xml:space="preserve">全社 20,262.67 千円/人 / 補助 36,602.5 千円/人 / ベース 16,719.09 千円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23,234.44 千円/人 / 補助 45,674.18 千円/人 / ベース 18,267.54 千円/人</t>
+          <t xml:space="preserve">全社 22,946.5 千円/人 / 補助 43,656.32 千円/人 / ベース 18,362.51 千円/人</t>
         </is>
       </c>
     </row>
@@ -5097,32 +5097,32 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.24 % / 補助 — / ベース 2.24 %</t>
+          <t xml:space="preserve">全社 2.32 % / 補助 — / ベース 2.32 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.16 % / 補助 — / ベース 2.16 %</t>
+          <t xml:space="preserve">全社 2.31 % / 補助 — / ベース 2.31 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.5 % / 補助 7.5 % / ベース 2.07 %</t>
+          <t xml:space="preserve">全社 3.67 % / 補助 7.5 % / ベース 2.3 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.18 % / 補助 6.2 % / ベース 1.96 %</t>
+          <t xml:space="preserve">全社 1.63 % / 補助 0 % / ベース 2.3 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.88 % / 補助 5.12 % / ベース 1.85 %</t>
+          <t xml:space="preserve">全社 1.55 % / 補助 0 % / ベース 2.28 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.6 % / 補助 4.23 % / ベース 1.74 %</t>
+          <t xml:space="preserve">全社 1.47 % / 補助 0 % / ベース 2.25 %</t>
         </is>
       </c>
     </row>
@@ -5283,32 +5283,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.54 倍 / 補助 — / ベース 4.54 倍</t>
+          <t xml:space="preserve">全社 4.4 倍 / 補助 — / ベース 4.4 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.98 倍 / 補助 — / ベース 4.98 倍</t>
+          <t xml:space="preserve">全社 4.66 倍 / 補助 — / ベース 4.66 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.72 倍 / 補助 2.38 倍 / ベース 5.44 倍</t>
+          <t xml:space="preserve">全社 3.56 倍 / 補助 2.38 倍 / ベース 4.93 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.76 倍 / 補助 2.54 倍 / ベース 5.33 倍</t>
+          <t xml:space="preserve">全社 7.09 倍 / 補助 — / ベース 4.58 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.57 倍 / 補助 3.25 倍 / ベース 6.27 倍</t>
+          <t xml:space="preserve">全社 8.26 倍 / 補助 — / ベース 5.13 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.52 倍 / 補助 4.13 倍 / ベース 7.31 倍</t>
+          <t xml:space="preserve">全社 9.56 倍 / 補助 — / ベース 5.7 倍</t>
         </is>
       </c>
     </row>
@@ -5655,32 +5655,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -7.94 pt</t>
+          <t xml:space="preserve">差 -7.88 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -8.58 pt</t>
+          <t xml:space="preserve">差 -8.46 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.17 pt</t>
+          <t xml:space="preserve">差 1.34 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.09 pt</t>
+          <t xml:space="preserve">差 5.98 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.78 pt</t>
+          <t xml:space="preserve">差 5.94 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.29 pt</t>
+          <t xml:space="preserve">差 5.85 pt</t>
         </is>
       </c>
     </row>
@@ -5851,22 +5851,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 79.27 %</t>
+          <t xml:space="preserve">寄与率 80.36 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 220.51 %</t>
+          <t xml:space="preserve">寄与率 115.41 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 49.09 %</t>
+          <t xml:space="preserve">寄与率 50.36 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 52.44 %</t>
+          <t xml:space="preserve">寄与率 53.65 %</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">制度下限5.0%/年（基準年→事業化報告3年目）</t>
         </is>
       </c>
       <c r="D37" s="2">
@@ -11392,7 +11392,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4MDAwMDAsImNvZ3MiOjkzODQwMDAsImVtcGxveWVlUGF5IjoxMjQwMzI2LCJvZmZpY2VyUGF5Ijo5MjAwMCwiZGVwcmVjaWF0aW9uIjozMjIwMDAsIm90aGVyU2dhIjoxNjU2MDAwLCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTE3ODMxMCwiZW1wbG95ZWVCb251cyI6NjIwMTYsIm9mZmljZXJDb21wZW5zYXRpb24iOjgyODAwLCJvZmZpY2VyQm9udXMiOjkyMDAsImNvZ3NEZXByZWNpYXRpb24iOjczNjAwLCJzZ2FEZXByZWNpYXRpb24iOjI0ODQwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NjQ0MDAsIm9yZGluYXJ5SW5jb21lIjoxMDY3MjAwLCJwcmVUYXhJbmNvbWUiOjEwNjcyMDAsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NDAwMDAwLCJjb2dzIjo5NzkyMDAwLCJlbXBsb3llZVBheSI6MTMxODg0MSwib2ZmaWNlclBheSI6OTYwMDAsImRlcHJlY2lhdGlvbiI6MzM2MDAwLCJvdGhlclNnYSI6MTcyODAwMCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyNTI4OTksImVtcGxveWVlQm9udXMiOjY1OTQyLCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo4NjQwMCwib2ZmaWNlckJvbnVzIjo5NjAwLCJjb2dzRGVwcmVjaWF0aW9uIjo3NjgwMCwic2dhRGVwcmVjaWF0aW9uIjoyNTkyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjY3MjAwLCJvcmRpbmFyeUluY29tZSI6MTExMzYwMCwicHJlVGF4SW5jb21lIjoxMTEzNjAwLCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwMDAwMDAsImNvZ3MiOjEwMjAwMDAwLCJlbXBsb3llZVBheSI6MTQwMDAwMCwib2ZmaWNlclBheSI6MTAwMDAwLCJkZXByZWNpYXRpb24iOjM1MDAwMCwib3RoZXJTZ2EiOjE4MDAwMDAsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMzMwMDAwLCJlbXBsb3llZUJvbnVzIjo3MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6OTAwMDAsIm9mZmljZXJCb251cyI6MTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjgwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjI3MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NzAwMDAsIm9yZGluYXJ5SW5jb21lIjoxMTYwMDAwLCJwcmVUYXhJbmNvbWUiOjExNjAwMDAsIm5ldEluY29tZSI6MH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZSI6NjAwMDAwLCJsaWFiaWxpdGllcyI6NzkwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJsb25nVGVybURlYnQiOjMxMDAwMDAsIm5ldEFzc2V0cyI6NjQwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo4MDAwMDB9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYwMDAwMCwiY3VycmVudEFzc2V0cyI6NzgwMDAwMCwiY2FzaCI6MjcwMDAwMCwiZml4ZWRBc3NldHMiOjc4MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo2NDAwMDAwLCJidWlsZGluZ3MiOjIyMDAwMDAsIm1hY2hpbmVyeSI6MzIwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJzb2Z0d2FyZSI6NzAwMDAwLCJsaWFiaWxpdGllcyI6ODMwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMTAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjo0MDAwMDAwLCJsb25nVGVybURlYnQiOjMyMDAwMDAsIm5ldEFzc2V0cyI6NzMwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjcwMDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4IjoxMDAwMDAwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI4LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJwcm9qZWN0Q29nc1JhdGVUb0Jhc2UiOjAuNjgsIm90aGVyQ29nc1JhdGVUb0Jhc2UiOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4yMSwicHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJwcm9qZWN0QmFzZVllYXJTYWxlcyI6NjAwMDAwMCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wNywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNiwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wMTUsIm90aGVyU2dhUmF0ZUVuZCI6MC4wMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJpbnZlc3RtZW50Ijo0NTAwMDAwLCJzdWJzaWR5IjoxNTAwMDAwLCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOlswLDAuOTldLCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sInByb2plY3RDb2dzUmF0ZVRvQmFzZSI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVUb0Jhc2UiOlswLDAuOTldLCJwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6WzAsMV0sInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6WzAsMV0sInByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6WzAsMC4zXSwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6Wy0wLjUsMC41XSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjpbLTAuNSwwLjVdLCJlZmZlY3RpdmVUYXhSYXRlIjpbMCwwLjZdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Rmlyc3RZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdEJhc2VZZWFyU2FsZXMiOlswLDEwMDAwMDAwMDAwXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4xXSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjEsMC4yXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAsMC4wM10sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMCwwLjAzXSwib3RoZXJTZ2FSYXRlRW5kIjpbMCwwLjAzXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sImludmVzdG1lbnQiOlsxNTAwMDAwLDIwMDAwMDAwXSwic3Vic2lkeSI6WzEwMDAwMCw1MDAwMDAwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjMwLCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjY6cHJvamVjdDo3LTEiOjAsIjIwMjY6cHJvamVjdDo3LTQiOjAsIjIwMjY6cHJvamVjdDo3LTYiOjAsIjIwMjY6cHJvamVjdDo3LTgiOjAsIjIwMjY6cHJvamVjdDo3LTkiOjAsIjIwMjY6cHJvamVjdDpQMi00IjowLCIyMDI2OnByb2plY3Q6UDItMTQiOjAsIjIwMjY6cHJvamVjdDo3LTEzIjowLCIyMDI2OnByb2plY3Q6Ny0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMSI6MCwiMjAyNzpwcm9qZWN0OjctNCI6MCwiMjAyNzpwcm9qZWN0OjctNiI6MCwiMjAyNzpwcm9qZWN0OjctOCI6MCwiMjAyNzpwcm9qZWN0OjctOSI6MCwiMjAyNzpwcm9qZWN0OlAyLTQiOjAsIjIwMjc6cHJvamVjdDpQMi0xNCI6MCwiMjAyNzpwcm9qZWN0OjctMTMiOjAsIjIwMjc6cHJvamVjdDo3LTE0IjowLCIyMDI4OnByb2plY3Q6Ny0xIjo2MDAwMDAwLCIyMDI4OnByb2plY3Q6Ny00IjoyMTAwMDAwLCIyMDI4OnByb2plY3Q6Ny02Ijo2MjMwMDAsIjIwMjg6cHJvamVjdDo3LTgiOjQ4MDAwMCwiMjAyODpwcm9qZWN0OjctOSI6MzAwMDAsIjIwMjg6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjg6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI4OnByb2plY3Q6Ny0xMyI6NDgsIjIwMjg6cHJvamVjdDo3LTE0IjoyLCIyMDI5OnByb2plY3Q6Ny0xIjo3MjYwMDAwLCIyMDI5OnByb2plY3Q6Ny00IjoyMzIzMjAwLCIyMDI5OnByb2plY3Q6Ny02Ijo2OTQyNTYsIjIwMjk6cHJvamVjdDo3LTgiOjUzNDE0NCwiMjAyOTpwcm9qZWN0OjctOSI6MzE4MDAsIjIwMjk6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMjk6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDI5OnByb2plY3Q6Ny0xMyI6NTAsIjIwMjk6cHJvamVjdDo3LTE0IjoyLCIyMDMwOnByb2plY3Q6Ny0xIjo4Nzg0NjAwLCIyMDMwOnByb2plY3Q6Ny00IjoyODExMDcyLCIyMDMwOnByb2plY3Q6Ny02IjoxMDExNDMyLCIyMDMwOnByb2plY3Q6Ny04Ijo1OTQzOTUsIjIwMzA6cHJvamVjdDo3LTkiOjMzNzA4LCIyMDMwOnByb2plY3Q6UDItNCI6MTEzMDAwLCIyMDMwOnByb2plY3Q6UDItMTQiOjMzNzAwMCwiMjAzMDpwcm9qZWN0OjctMTMiOjUyLCIyMDMwOnByb2plY3Q6Ny0xNCI6MiwiMjAzMTpwcm9qZWN0OjctMSI6MTA2MjkzNjYsIjIwMzE6cHJvamVjdDo3LTQiOjM0MDEzOTcsIjIwMzE6cHJvamVjdDo3LTYiOjE0MTA1ODEsIjIwMzE6cHJvamVjdDo3LTgiOjY2MTQ0MywiMjAzMTpwcm9qZWN0OjctOSI6MzU3MzAsIjIwMzE6cHJvamVjdDpQMi00IjoxMTMwMDAsIjIwMzE6cHJvamVjdDpQMi0xNCI6MzM3MDAwLCIyMDMxOnByb2plY3Q6Ny0xMyI6NTQsIjIwMzE6cHJvamVjdDo3LTE0IjoyfSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzODAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTM4NDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjczNjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzMwMTEyNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjgyODAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjkyMDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTE3ODMxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjo2MjAxNiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyNDg0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6NjQ0MDAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTA2NzIwMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMDY3MjAwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyMzpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0NDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTc5MjAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjc2ODAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQ2OTI0MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjg2NDAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjk2MDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTI1Mjg5OSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjo2NTk0MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyNTkyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6NjcyMDAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTExMzYwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMTEzNjAwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjowLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MDAwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyMDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00Ijo4MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2NDAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05Ijo5MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjoxMDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMzMwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjcwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjI3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1Ijo3MDAwMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMTYwMDAwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExNjAwMDAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLCJhY3R1YWw6cHJvamVjdDoyMDI1OlAyLTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjowLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzkwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3ODAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0MDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMDAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OTAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MzAwMDAwLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAwMDAwMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwMDAwMDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAwMDAwMCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybzoxIjowLjk5LCJkcml2ZXI6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybzowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOnByb2plY3RDb2dzUmF0ZVRvQmFzZSI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NSYXRlVG9CYXNlOjEiOjAuOTksImRyaXZlcjpvdGhlckNvZ3NSYXRlVG9CYXNlIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVRvQmFzZToxIjowLjk5LCJkcml2ZXI6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZToxIjoxLCJkcml2ZXI6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwiZHJpdmVyLXJhbmdlOnByb2plY3RSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA0LCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZToxIjowLjMsImRyaXZlcjpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Tm9uT3BlcmF0aW5nUmF0ZToxIjowLjUsImRyaXZlcjpvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyTm9uT3BlcmF0aW5nUmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZTowIjotMC41LCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlckV4dHJhb3JkaW5hcnlSYXRlOjEiOjAuNSwiZHJpdmVyOmVmZmVjdGl2ZVRheFJhdGUiOjAuMywiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MCI6MCwiZHJpdmVyLXJhbmdlOmVmZmVjdGl2ZVRheFJhdGU6MSI6MC42LCJkcml2ZXI6cHJvamVjdEZpcnN0WWVhclNhbGVzIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEZpcnN0WWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Rmlyc3RZZWFyU2FsZXM6MSI6MTAwMDAwMDAwMDAsImRyaXZlcjpwcm9qZWN0QmFzZVllYXJTYWxlcyI6NjAwMDAwMCwiZHJpdmVyLXJhbmdlOnByb2plY3RCYXNlWWVhclNhbGVzOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0QmFzZVllYXJTYWxlczoxIjoxMDAwMDAwMDAwMCwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC40LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4yLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA0NSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjAzLCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMDMsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjppbnZlc3RtZW50Ijo0NTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNTAwMDAwLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAwMDAwMCwiZHJpdmVyOnN1YnNpZHkiOjE1MDAwMDAsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEwMDAwMCwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAwMDAwMCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsIm1vbmV5VW5pdCI6IuWNg+WGhiIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODq++8iOWfuua6luW5tOWjsuS4iumWi+Wni++8iSIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTM4MDAwMDAsImNvZ3MiOjkzODQwMDAsImVtcGxveWVlUGF5IjoxMjQwMzI2LCJvZmZpY2VyUGF5Ijo5MjAwMCwiZGVwcmVjaWF0aW9uIjozMjIwMDAsIm90aGVyU2dhIjoxNjU2MDAwLCJoZWFkY291bnQiOjIxMiwib2ZmaWNlckNvdW50Ijo1LCJlbXBsb3llZVNhbGFyeSI6MTE3ODMxMCwiZW1wbG95ZWVCb251cyI6NjIwMTYsIm9mZmljZXJDb21wZW5zYXRpb24iOjgyODAwLCJvZmZpY2VyQm9udXMiOjkyMDAsImNvZ3NEZXByZWNpYXRpb24iOjczNjAwLCJzZ2FEZXByZWNpYXRpb24iOjI0ODQwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NjQ0MDAsIm9yZGluYXJ5SW5jb21lIjoxMDY3MjAwLCJwcmVUYXhJbmNvbWUiOjEwNjcyMDAsIm5ldEluY29tZSI6MH19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6MCwiY29ncyI6MCwiZW1wbG95ZWVQYXkiOjAsIm9mZmljZXJQYXkiOjAsImRlcHJlY2lhdGlvbiI6MCwib3RoZXJTZ2EiOjAsImhlYWRjb3VudCI6MCwib2ZmaWNlckNvdW50IjowfSwib3RoZXIiOnsic2FsZXMiOjE0NDAwMDAwLCJjb2dzIjo5NzkyMDAwLCJlbXBsb3llZVBheSI6MTMxODg0MSwib2ZmaWNlclBheSI6OTYwMDAsImRlcHJlY2lhdGlvbiI6MzM2MDAwLCJvdGhlclNnYSI6MTcyODAwMCwiaGVhZGNvdW50IjoyMjEsIm9mZmljZXJDb3VudCI6NSwiZW1wbG95ZWVTYWxhcnkiOjEyNTI4OTksImVtcGxveWVlQm9udXMiOjY1OTQyLCJvZmZpY2VyQ29tcGVuc2F0aW9uIjo4NjQwMCwib2ZmaWNlckJvbnVzIjo5NjAwLCJjb2dzRGVwcmVjaWF0aW9uIjo3NjgwMCwic2dhRGVwcmVjaWF0aW9uIjoyNTkyMDAsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjY3MjAwLCJvcmRpbmFyeUluY29tZSI6MTExMzYwMCwicHJlVGF4SW5jb21lIjoxMTEzNjAwLCJuZXRJbmNvbWUiOjB9fSx7InllYXIiOjIwMjUsInJvbGUiOiJsYXRlc3QiLCJwcm9qZWN0Ijp7InNhbGVzIjowLCJjb2dzIjowLCJlbXBsb3llZVBheSI6MCwib2ZmaWNlclBheSI6MCwiZGVwcmVjaWF0aW9uIjowLCJvdGhlclNnYSI6MCwiaGVhZGNvdW50IjowLCJvZmZpY2VyQ291bnQiOjB9LCJvdGhlciI6eyJzYWxlcyI6MTUwMDAwMDAsImNvZ3MiOjEwMjAwMDAwLCJlbXBsb3llZVBheSI6MTQwMDAwMCwib2ZmaWNlclBheSI6MTAwMDAwLCJkZXByZWNpYXRpb24iOjM1MDAwMCwib3RoZXJTZ2EiOjE4MDAwMDAsImhlYWRjb3VudCI6MjMwLCJvZmZpY2VyQ291bnQiOjUsImVtcGxveWVlU2FsYXJ5IjoxMzMwMDAwLCJlbXBsb3llZUJvbnVzIjo3MDAwMCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6OTAwMDAsIm9mZmljZXJCb251cyI6MTAwMDAsImNvZ3NEZXByZWNpYXRpb24iOjgwMDAwLCJzZ2FEZXByZWNpYXRpb24iOjI3MDAwMCwicmVzZWFyY2hEZXZlbG9wbWVudCI6NzAwMDAsIm9yZGluYXJ5SW5jb21lIjoxMTYwMDAwLCJwcmVUYXhJbmNvbWUiOjExNjAwMDAsIm5ldEluY29tZSI6MH19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIwMDAwMCwiY3VycmVudEFzc2V0cyI6NjcwMDAwMCwiY2FzaCI6MjQwMDAwMCwiZml4ZWRBc3NldHMiOjY1MDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1MzAwMDAwLCJidWlsZGluZ3MiOjE5MDAwMDAsIm1hY2hpbmVyeSI6MjQwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6NzAwMDAwLCJzb2Z0d2FyZSI6NTAwMDAwLCJsaWFiaWxpdGllcyI6NzUwMDAwMCwiY3VycmVudExpYWJpbGl0aWVzIjozOTAwMDAwLCJzaG9ydFRlcm1EZWJ0IjoxMjAwMDAwLCJmaXhlZExpYWJpbGl0aWVzIjozNjAwMDAwLCJsb25nVGVybURlYnQiOjI5MDAwMDAsIm5ldEFzc2V0cyI6NTcwMDAwMCwic2hhcmVob2xkZXJFcXVpdHkiOjU0MDAwMDAsImNhcGl0YWwiOjEwMDAwMDAsImNhcGV4Ijo1MDAwMDB9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMwMDAwMCwiY3VycmVudEFzc2V0cyI6NzIwMDAwMCwiY2FzaCI6MjUwMDAwMCwiZml4ZWRBc3NldHMiOjcxMDAwMDAsInRhbmdpYmxlQXNzZXRzIjo1ODAwMDAwLCJidWlsZGluZ3MiOjIwMDAwMDAsIm1hY2hpbmVyeSI6MjgwMDAwMCwibGFuZCI6MTAwMDAwMCwiaW50YW5naWJsZUFzc2V0cyI6ODAwMDAwLCJzb2Z0d2FyZ